--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -90,13 +90,13 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -90,13 +90,13 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -18868,7 +18868,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
@@ -18957,9 +18957,10 @@
           <t>MXF (OP-1a), codec IMX50, 50 Mb/s (CBR), croma 4:2:2, entrelaçado (Interlaced UFF, 16:9FHA), extensão .mxf</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>GoFastWay</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>GoFastWay
+www.gofastway.tv</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -19001,9 +19002,10 @@
           <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>GoFastWay</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>GoFastWay
+www.gofastway.tv</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -19045,9 +19047,10 @@
           <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>GoFastWay</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>GoFastWay
+www.gofastway.tv</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -19089,9 +19092,10 @@
           <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>GoFastWay</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>GoFastWay
+www.gofastway.tv</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -19103,6 +19107,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J5"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Imprensa'!$A$1:$I$125</definedName>
@@ -17193,7 +17193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17596,34 +17596,34 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Monoposte 10x5</t>
+          <t>Mupi Papel</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Área de mancha publicitária: 10000x5000mm.</t>
+          <t>Área total: 118,5x175cm. Área de mancha publicitária: 116x171cm.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas. Ficheiros prontos para impressão em CMYK — não se aceita Pantone.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+          <t>Papel: Couché mate (COM) ou Sunrise, entre 130 e 140 g/m². Densidade até 117µm. Prazo de entrega: até 5 dias úteis antes do início da campanha. Quantidades requeridas: mais 10% além da quantidade contratada. A arte final não deve conter elementos de informação relevante junto às margens de corte.</t>
         </is>
       </c>
       <c r="I11" s="2" t="n"/>
@@ -17631,34 +17631,34 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Monoposte 11x5</t>
+          <t>Carris Metropolitana</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Área de mancha publicitária: 11000x5000mm.</t>
+          <t>3 medidas obrigatórias, para adaptação a todos os tamanhos de autocarro: 1590x535mm, 1440x640mm, 2210x640mm.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
+          <t>Material obrigatório: PPA 3,5mm - 650g (impressão direta), alvéolos na vertical. Placas superiores a 200cm de comprimento fornecidas em 2 folhas com colagem em sistema de encosto (fita cola 3M ref.ª 8959) — também permitido numa só folha. Escala: tamanho real. Resolução: 300 dpi. Cores: CMYK — não se aceita Pantone (ficheiros em RGB são convertidos). Fontes convertidas em curvas (outlines). Formato: PDF editável, gravado em versão anterior à utilizada para o criar. Imagens incorporadas a 300dpi no ficheiro final.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+          <t>Margem de segurança de 40mm a toda a volta (textos, logótipos e imagens críticas). Sangria de 5mm a toda a volta para corte e ajuste. Elementos de fundo (cores, imagens contínuas ou texturas) devem ocupar a área total com sangria. Entrega das artes finais: 6 dias úteis antes do 1º dia de implementação — é obrigatório fornecer as 3 medidas. Implementação: Áreas 1 e 2 entram à quarta-feira; Áreas 3 e 4 entram à quinta-feira.</t>
         </is>
       </c>
       <c r="I12" s="2" t="n"/>
@@ -17666,22 +17666,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BIG Outdoors</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Monoposte 12x5</t>
+          <t>Citie Premium</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Área de mancha publicitária: 12000x5000mm.</t>
+          <t>2,40x1,70m.</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -17693,7 +17693,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK, prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações.</t>
         </is>
       </c>
       <c r="I13" s="2" t="n"/>
@@ -17701,34 +17701,38 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>DreamMedia</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Mupi Papel</t>
+          <t>Power Street</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Área total: 1185x1750mm. Área visível: 1160x1710mm.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
+          <t>1080x1920px (Full HD).</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Papel, gramagem 130g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Vídeo pronto: .MOV ou .MP4 (MP4 preferencial), RGB, 30fps ou 60fps. Materiais abertos para produção também aceites: Adobe Photoshop (1080x1920px, layers abertos, RGB, 72dpi, fontes em curvas) ou Adobe Illustrator/After Effects (1080x1920px, fontes em curvas, imagens rasterizadas no ficheiro).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Se enviar PDF, atenção a cores/perfis embebidos/resolução de imagens; enviar fontes; texto convertido em curvas, aberto e editável. Impressão offset: CMYK, mín. 300 dpi, máx. 400 dpi. Impressão digital: CMYK, mín. 150 dpi, máx. 200 dpi. Ficheiro na medida indicada + 3cm de bleed (3mm se a AF for elaborada à escala de 10%); respeitar área de segurança virtual para evitar corte de elementos na afixação; sempre que possível, enviar com prova de cor. Após receção, a JCDecaux envia um JPG para validação final antes de imprimir; após aprovação, declina responsabilidade por desformatações/falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção de água (cobb60) 15-30g/m², absorção de água (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura por tração (húmido) &gt;0,6kN/m — materiais fora destes requisitos podem não ser afixados. Especificações ambientais: papel com certificação PEFC/FSC (ou equivalente); tintas conformes REACH/GreenGuard, isentas de metais pesados; papel reciclado, sem cloro (ECF/TCF).</t>
+          <t>Duração: 10″. Em anúncios/vídeos com textos sobrepostos, enviar também as imagens/vídeos limpos, para a inclusão dos textos ser aplicada e editada à parte. Margem de segurança: 30px. Prazo de entrega: 72 horas antes do início da campanha. Enviar para digital@dreammedia.pt (via WeTransfer/Dropbox/Google Drive se superior a 15Mb).</t>
         </is>
       </c>
       <c r="I14" s="2" t="n"/>
@@ -17736,34 +17740,34 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Impressão Senior</t>
+          <t>Monoposte 10x5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Área visível: 3020x2230mm. Área total: 3200x2350mm.</t>
+          <t>Área de mancha publicitária: 10000x5000mm.</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Papel, gramagem 150g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Impressão em 1, 2 ou 4 folhas, entregues alceadas por ordem de colagem (a começar na folha 1, com o verso para baixo). Impressão em 2 folhas: folha 1 3200x1200mm (aparada 3130x1150mm) + folha 2 idêntica, margem de sobreposição 25mm/35mm. Impressão em 4 folhas: 1600x1200mm por folha (aparada 1530x1175mm), aparadas à medida sem margem entre si. Prazo: 7 dias úteis após aprovação da Arte Final. Ficheiro: Illustrator/Photoshop (incluir fontes e respetivos links) ou PDF (cores/perfis embebidos/resolução de imagens, texto em curvas); impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); respeitar área de segurança virtual; enviar com prova de cor sempre que possível. Entrega nas instalações da JCDecaux 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada; horário de entrega 07h-12h e 13h30-16h (Portão 2), Beco da Aviação nº1, Granja do Alpriate, Vialonga. Após receção, a JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção água (cobb60) 15-30g/m², (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura (húmido) &gt;0,6kN/m.</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
       <c r="I15" s="2" t="n"/>
@@ -17771,38 +17775,34 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Mupi Digital</t>
+          <t>Monoposte 11x5</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1080x1920px.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
+          <t>Área de mancha publicitária: 11000x5000mm.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
       <c r="I16" s="2" t="n"/>
@@ -17810,38 +17810,34 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>JCDecaux</t>
+          <t>BIG Outdoors</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Mupi Digital (Shopping)</t>
+          <t>Monoposte 12x5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ficheiro entregue em 1920x1080px (paisagem, para ecrãs de 63''), rodado automaticamente pelo sistema para exibição vertical 1080x1920px.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16:9 (ficheiro) / 9:16 (exibição)</t>
-        </is>
-      </c>
+          <t>Área de mancha publicitária: 12000x5000mm.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Ficheiro nativo (compressão nativa), bitrate máx. 20.000.</t>
+          <t>Ficheiro fechado: JPG, TIFF ou PDF, a 10% do tamanho real, a 300 dpi. Formato editável: textos convertidos em curvas (outlines) ou fontes fornecidas.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Duração do spot: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes. Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
+          <t>Bleed: 10cm a toda a volta (não deve conter informação importante). Ficheiros fornecidos em CMYK prontos para impressão — ficheiros em RGB são convertidos para CMYK, podendo as cores sofrer alterações. Importante: a arte final não deve conter letras de tamanho inferior a 30cm (110 pontos); dar maior destaque ao produto, logótipo, telefone e site para melhores resultados de comunicação.</t>
         </is>
       </c>
       <c r="I17" s="2" t="n"/>
@@ -17859,24 +17855,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Painel 8x3 - Papel</t>
+          <t>Mupi Papel</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Área total: 8000x3000mm. Área visível: 7500x2750mm.</t>
+          <t>Área total: 1185x1750mm. Área visível: 1160x1710mm.</t>
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Papel, gramagem entre 120g e 170g, verso do cartaz com fundo azul. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Papel, gramagem 130g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 12, 14 ou 16 folhas, entregues alceadas (a começar na folha 1, verso para baixo), numeradas no canto superior direito. Impressão em 14 folhas: folhas superiores 1-6 (997mm cada) + folha 7 (997mm), folhas inferiores 9-13 (1135mm cada) + folha 14 (1135mm); margem de sobreposição 25mm à direita nas folhas superiores (exceto a última) e 25mm à direita + no topo nas inferiores (exceto a última, só no topo); áreas de sobreposição isentas de impressão. Impressão em 16 folhas: superiores 1-7 (997mm) + folha 8 (997mm), inferiores 9-15 (997mm) + folha 16 (997mm), mesmas regras de margem. Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
+          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Se enviar PDF, atenção a cores/perfis embebidos/resolução de imagens; enviar fontes; texto convertido em curvas, aberto e editável. Impressão offset: CMYK, mín. 300 dpi, máx. 400 dpi. Impressão digital: CMYK, mín. 150 dpi, máx. 200 dpi. Ficheiro na medida indicada + 3cm de bleed (3mm se a AF for elaborada à escala de 10%); respeitar área de segurança virtual para evitar corte de elementos na afixação; sempre que possível, enviar com prova de cor. Após receção, a JCDecaux envia um JPG para validação final antes de imprimir; após aprovação, declina responsabilidade por desformatações/falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção de água (cobb60) 15-30g/m², absorção de água (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura por tração (húmido) &gt;0,6kN/m — materiais fora destes requisitos podem não ser afixados. Especificações ambientais: papel com certificação PEFC/FSC (ou equivalente); tintas conformes REACH/GreenGuard, isentas de metais pesados; papel reciclado, sem cloro (ECF/TCF).</t>
         </is>
       </c>
       <c r="I18" s="2" t="n"/>
@@ -17894,24 +17890,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Painel 8x3 - Vinil</t>
+          <t>Impressão Senior</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Área total: 8000x3000mm. Área visível: 8000x3000mm (sem margem).</t>
+          <t>Área visível: 3020x2230mm. Área total: 3200x2350mm.</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Vinil PVC branco ou transparente, superfície brilhante ou mate, polyacrylate removível e transparente; base em papel revestido a silicone 135g/m². Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
+          <t>Papel, gramagem 150g, verso do cartaz com fundo branco. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Uso recomendado: outdoors de curta e média duração. Método de impressão: tintas de base solvente, UV ou látex. Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 8 folhas de 1000mm cada, enroladas por ordem (folha 1 a 8), numeradas no canto superior direito; margem de sobreposição 25mm à direita em todas as folhas (áreas de sobreposição isentas de impressão). Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 5cm de bleed (5mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
+          <t>Impressão em 1, 2 ou 4 folhas, entregues alceadas por ordem de colagem (a começar na folha 1, com o verso para baixo). Impressão em 2 folhas: folha 1 3200x1200mm (aparada 3130x1150mm) + folha 2 idêntica, margem de sobreposição 25mm/35mm. Impressão em 4 folhas: 1600x1200mm por folha (aparada 1530x1175mm), aparadas à medida sem margem entre si. Prazo: 7 dias úteis após aprovação da Arte Final. Ficheiro: Illustrator/Photoshop (incluir fontes e respetivos links) ou PDF (cores/perfis embebidos/resolução de imagens, texto em curvas); impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); respeitar área de segurança virtual; enviar com prova de cor sempre que possível. Entrega nas instalações da JCDecaux 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada; horário de entrega 07h-12h e 13h30-16h (Portão 2), Beco da Aviação nº1, Granja do Alpriate, Vialonga. Após receção, a JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem. Critérios de qualidade: opacidade ≥88%, brancura 91-93 ISO, absorção água (cobb60) 15-30g/m², (cobb300) &lt;70g/m², distensão máx. ±2%/m, resistência à rutura (húmido) &gt;0,6kN/m.</t>
         </is>
       </c>
       <c r="I19" s="2" t="n"/>
@@ -17929,17 +17925,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 6m²</t>
+          <t>Mupi Digital</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>328x492px.</t>
+          <t>1080x1920px.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
@@ -17950,7 +17946,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
         </is>
       </c>
       <c r="I20" s="2" t="n"/>
@@ -17968,28 +17964,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 8m²</t>
+          <t>Mupi Digital (Shopping)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>370x656px.</t>
+          <t>Ficheiro entregue em 1920x1080px (paisagem, para ecrãs de 63''), rodado automaticamente pelo sistema para exibição vertical 1080x1920px.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9 (ficheiro) / 9:16 (exibição)</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Ficheiro nativo (compressão nativa), bitrate máx. 20.000.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Duração do spot: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes. Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
         </is>
       </c>
       <c r="I21" s="2" t="n"/>
@@ -18007,28 +18003,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 12m²</t>
+          <t>Painel 8x3 - Papel</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1520x800px.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1.91:1</t>
-        </is>
-      </c>
+          <t>Área total: 8000x3000mm. Área visível: 7500x2750mm.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Papel, gramagem entre 120g e 170g, verso do cartaz com fundo azul. Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 12, 14 ou 16 folhas, entregues alceadas (a começar na folha 1, verso para baixo), numeradas no canto superior direito. Impressão em 14 folhas: folhas superiores 1-6 (997mm cada) + folha 7 (997mm), folhas inferiores 9-13 (1135mm cada) + folha 14 (1135mm); margem de sobreposição 25mm à direita nas folhas superiores (exceto a última) e 25mm à direita + no topo nas inferiores (exceto a última, só no topo); áreas de sobreposição isentas de impressão. Impressão em 16 folhas: superiores 1-7 (997mm) + folha 8 (997mm), inferiores 9-15 (997mm) + folha 16 (997mm), mesmas regras de margem. Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 3cm de bleed (3mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
         </is>
       </c>
       <c r="I22" s="2" t="n"/>
@@ -18046,28 +18038,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 15m²</t>
+          <t>Painel 8x3 - Vinil</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>720x1296px.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
+          <t>Área total: 8000x3000mm. Área visível: 8000x3000mm (sem margem).</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Vinil PVC branco ou transparente, superfície brilhante ou mate, polyacrylate removível e transparente; base em papel revestido a silicone 135g/m². Ficheiro: Illustrator, Photoshop, PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Uso recomendado: outdoors de curta e média duração. Método de impressão: tintas de base solvente, UV ou látex. Prazo: 7 dias úteis após aprovação da Arte Final. Impressão em 8 folhas de 1000mm cada, enroladas por ordem (folha 1 a 8), numeradas no canto superior direito; margem de sobreposição 25mm à direita em todas as folhas (áreas de sobreposição isentas de impressão). Se PDF: cores/perfis embebidos/resolução de imagens, texto em curvas; impressão offset CMYK 300-400 dpi, digital CMYK 150-200 dpi; medida indicada + 5cm de bleed (5mm à escala de 10%); área de segurança virtual; prova de cor recomendada. Entrega nas instalações JCDecaux, Portão 1, Beco da Aviação nº1, Granja do Alpriate, Vialonga, 5 dias úteis antes do início da campanha, com impressão da campanha e guia de transporte certificada, 07h-12h/13h30-16h. Após receção, JCDecaux envia JPG para validação; após aprovação, declina responsabilidade por falhas na imagem.</t>
         </is>
       </c>
       <c r="I23" s="2" t="n"/>
@@ -18085,17 +18073,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 18m²</t>
+          <t>Premium LED 6m²</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>640x1152px.</t>
+          <t>328x492px.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
@@ -18106,7 +18094,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -18124,15 +18112,19 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 22m²</t>
+          <t>Premium LED 8m²</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1248x800px.</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n"/>
+          <t>370x656px.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -18141,7 +18133,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I25" s="2" t="n"/>
@@ -18159,15 +18151,19 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 25m²</t>
+          <t>Premium LED 12m²</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>480x810px.</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n"/>
+          <t>1520x800px.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1.91:1</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -18194,15 +18190,19 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Premium LED 37m²</t>
+          <t>Premium LED 15m²</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>480x738px.</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n"/>
+          <t>720x1296px.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
@@ -18219,34 +18219,38 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Táxi Advertising</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Táxi Advertising</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Decoração de Táxi</t>
+          <t>Premium LED 18m²</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Manter o tamanho original do template (ficheiros vetoriais reais fornecidos pelo fornecedor, com o desenho do lado esquerdo e do lado direito do táxi).</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n"/>
+          <t>640x1152px.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Ficheiros de trabalho em Illustrator (vetoriais). Entrega: JPG ou PDF.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>O texto deve manter-se dentro da linha amarela de segurança (para não ser cortado). O fundo atrás do texto deve ultrapassar a linha branca em pelo menos 50mm de bleed. Impressão em CMYK, resolução 150 pixels/polegada. É obrigatório enviar também um PDF com a maqueta da decoração do táxi, para orientação da colagem do vinil.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I28" s="2" t="n"/>
@@ -18254,34 +18258,34 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4Plus</t>
+          <t>Premium LED 22m²</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 394x140mm. Medida real: 4000x1500mm. Área visível: 3860x1360mm.</t>
+          <t>1248x800px.</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Imagens a 100%, 150 DPI. Papel branco 150g; fita-cola (para unir as 2 laudas) 3M ref. 201E, 50mm; embalamento enrolado individualmente. Entrega até à sexta-feira anterior ao dia em que a campanha começa. Quantidades requeridas: +10% além da quantidade contratada. Aconselha-se que a produção seja sempre feita na Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800). Cartazes entregues à unidade e identificados. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I29" s="2" t="n"/>
@@ -18289,34 +18293,34 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Flashes</t>
+          <t>Premium LED 25m²</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 370x270mm + 5mm de bleed (frente e verso).</t>
+          <t>480x810px.</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Deve ser deixado 20mm no topo para o encaixe — esta área deve estar livre de informação relevante e ser um prolongamento do fundo (não deixar a branco, a menos que o fundo da criatividade o seja). Papel auto-extinguível ou PVC auto-extinguível (FLAMSTOP), 180g/m2, espessura máxima 0,8mm. Cartazes entregues já dobrados e com as duas faces coladas integralmente. Quantidades requeridas: +15% que o número de posições. Prazo de entrega: até 5 dias úteis antes do início da campanha.</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I30" s="2" t="n"/>
@@ -18324,34 +18328,34 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>JCDecaux</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Backlight 4x3</t>
+          <t>Premium LED 37m²</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 403x300mm + 1mm de bleed.</t>
+          <t>480x738px.</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I31" s="2" t="n"/>
@@ -18359,34 +18363,34 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>Táxi Advertising</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MOP</t>
+          <t>Táxi Advertising</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Backlight 8x3</t>
+          <t>Decoração de Táxi</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 803x286mm + 1mm de bleed.</t>
+          <t>Manter o tamanho original do template (ficheiros vetoriais reais fornecidos pelo fornecedor, com o desenho do lado esquerdo e do lado direito do táxi).</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
+          <t>Ficheiros de trabalho em Illustrator (vetoriais). Entrega: JPG ou PDF.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>O texto deve manter-se dentro da linha amarela de segurança (para não ser cortado). O fundo atrás do texto deve ultrapassar a linha branca em pelo menos 50mm de bleed. Impressão em CMYK, resolução 150 pixels/polegada. É obrigatório enviar também um PDF com a maqueta da decoração do táxi, para orientação da colagem do vinil.</t>
         </is>
       </c>
       <c r="I32" s="2" t="n"/>
@@ -18404,12 +18408,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Backlight 10x5</t>
+          <t>4Plus</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 966x481mm + 1mm de bleed.</t>
+          <t>Arte final: 394x140mm. Medida real: 4000x1500mm. Área visível: 3860x1360mm.</t>
         </is>
       </c>
       <c r="E33" s="2" t="n"/>
@@ -18421,7 +18425,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Imagens a 100%, 150 DPI. Papel branco 150g; fita-cola (para unir as 2 laudas) 3M ref. 201E, 50mm; embalamento enrolado individualmente. Entrega até à sexta-feira anterior ao dia em que a campanha começa. Quantidades requeridas: +10% além da quantidade contratada. Aconselha-se que a produção seja sempre feita na Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800). Cartazes entregues à unidade e identificados. Envio via WeTransfer/Hightail/Dropbox ou FTP do cliente (com utilizador e password); CD/DVD sempre com prova de cor.</t>
         </is>
       </c>
       <c r="I33" s="2" t="n"/>
@@ -18439,12 +18443,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Backlight 12x5</t>
+          <t>Flashes</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 1211x481mm + 1mm de bleed.</t>
+          <t>Arte final: 370x270mm + 5mm de bleed (frente e verso).</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
@@ -18456,7 +18460,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Deve ser deixado 20mm no topo para o encaixe — esta área deve estar livre de informação relevante e ser um prolongamento do fundo (não deixar a branco, a menos que o fundo da criatividade o seja). Papel auto-extinguível ou PVC auto-extinguível (FLAMSTOP), 180g/m2, espessura máxima 0,8mm. Cartazes entregues já dobrados e com as duas faces coladas integralmente. Quantidades requeridas: +15% que o número de posições. Prazo de entrega: até 5 dias úteis antes do início da campanha.</t>
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
@@ -18474,12 +18478,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Autocarro - Lateral Direita</t>
+          <t>Backlight 4x3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 434x118mm + 3mm de bleed. Medida real: 2170x588mm. Área visível: 2150x568mm.</t>
+          <t>Arte final: 403x300mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
@@ -18491,7 +18495,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
       <c r="I35" s="2" t="n"/>
@@ -18509,12 +18513,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Autocarro - Lateral Esquerda</t>
+          <t>Backlight 8x3</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 548x150mm + 3mm de bleed. Medida real: 2740x750mm. Área visível: 2720x730mm.</t>
+          <t>Arte final: 803x286mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="E36" s="2" t="n"/>
@@ -18526,7 +18530,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
       <c r="I36" s="2" t="n"/>
@@ -18544,12 +18548,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Autocarro - Lateral Esquerda + Esquerda Especial</t>
+          <t>Backlight 10x5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Dimensões Lateral Esquerda — Arte final: 548x150mm + 3mm de bleed, Medida real: 2740x750mm, Área visível: 2720x730mm. Dimensões Esquerda Especial — Arte final: 434x118mm + 3mm de bleed, Medida real: 2170x588mm, Área visível: 2150x568mm.</t>
+          <t>Arte final: 966x481mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="E37" s="2" t="n"/>
@@ -18561,7 +18565,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
       <c r="I37" s="2" t="n"/>
@@ -18579,12 +18583,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Autocarro - Retaguarda</t>
+          <t>Backlight 12x5</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Arte final: 300x96mm + 1mm de bleed. Medida real: 1500x478mm. Área visível: 2150x568mm.</t>
+          <t>Arte final: 1211x481mm + 1mm de bleed.</t>
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
@@ -18596,7 +18600,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Produção em tela backlight no formato pretendido, com duas possibilidades: lona rígida para campanhas anuais (reutilizável) ou tela flexível para campanhas de curta duração (não reutilizável); telas acabadas com uma nervura à volta para fixação e tensionamento nos painéis PRISMAFLEX. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica PRISMAFLEX (Av. Dom Vicente Afonso Valente, 61, 2625-207 Póvoa de Santa Iria; Tel. +351 210 119 500; geral@prismaflex.pt).</t>
         </is>
       </c>
       <c r="I38" s="2" t="n"/>
@@ -18614,28 +18618,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3 Ecrãs</t>
+          <t>Autocarro - Lateral Direita</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1920x1080px.</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>Arte final: 434x118mm + 3mm de bleed. Medida real: 2170x588mm. Área visível: 2150x568mm.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
       <c r="I39" s="2" t="n"/>
@@ -18653,28 +18653,24 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>4x3 Digital</t>
+          <t>Autocarro - Lateral Esquerda</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1536x1152px (na proporção 4x3, até 3840x2880px).</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>4:3</t>
-        </is>
-      </c>
+          <t>Arte final: 548x150mm + 3mm de bleed. Medida real: 2740x750mm. Área visível: 2720x730mm.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos. Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Compressão nativa.</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
       <c r="I40" s="2" t="n"/>
@@ -18692,28 +18688,24 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Tomi PhotoFun</t>
+          <t>Autocarro - Lateral Esquerda + Esquerda Especial</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1080x810px.</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>4:3</t>
-        </is>
-      </c>
+          <t>Dimensões Lateral Esquerda — Arte final: 548x150mm + 3mm de bleed, Medida real: 2740x750mm, Área visível: 2720x730mm. Dimensões Esquerda Especial — Arte final: 434x118mm + 3mm de bleed, Medida real: 2170x588mm, Área visível: 2150x568mm.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Profundidade de cor: 8 bits ou superior. Deve ter sempre um espaço vazio de conteúdo de 125x125px para o logótipo TOMI no canto da moldura. Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
       <c r="I41" s="2" t="n"/>
@@ -18731,28 +18723,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Tomi Sport TV</t>
+          <t>Autocarro - Retaguarda</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1080x1920px.</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
+          <t>Arte final: 300x96mm + 1mm de bleed. Medida real: 1500x478mm. Área visível: 2150x568mm.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>MP4 (sem fundo), codec H264</t>
+          <t>PDF (qualidade de impressão), JPEG (visualização) e ficheiro editável</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps. Tamanho máximo: 100MB.</t>
+          <t>Fontes em curvas; imagens a 300 dpi; ficheiro em versão antiga do programa; sempre CMYK (sem Pantone/RGB); sem informação relevante junto às margens de corte. Material obrigatório: PPA 3,5mm | 650g (impressão direta). 2 folhas (corte vertical central), com colagem em sistema de encosto, usando fita-cola 3M ref. 8959 — também permitido em uma só folha no formato total. Prazo de entrega: até 2 dias úteis antes do início da campanha. Quantidades necessárias: +5% que o número de faces, e +5% por cada semana extra de afixação. Quando a produção dos materiais não for da responsabilidade da MOP, deve ser feita na gráfica Pinkplate (Parque Empresarial Primóvel - Ed. D1, Albarraque, 2635-395 Rio de Mouro; Tel. 21 9251800).</t>
         </is>
       </c>
       <c r="I42" s="2" t="n"/>
@@ -18770,15 +18758,19 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>LED Galp</t>
+          <t>3 Ecrãs</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>840x336px.</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n"/>
+          <t>1920x1080px.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -18787,7 +18779,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB.</t>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
         </is>
       </c>
       <c r="I43" s="2" t="n"/>
@@ -18795,26 +18787,38 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>MOP</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Especificações por confirmar</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
+          <t>4x3 Digital</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>1536x1152px (na proporção 4x3, até 3840x2880px).</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+          <t>Duração: 10 segundos. Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Compressão nativa.</t>
         </is>
       </c>
       <c r="I44" s="2" t="n"/>
@@ -18822,32 +18826,172 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Tomi PhotoFun</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>1080x810px.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Profundidade de cor: 8 bits ou superior. Deve ter sempre um espaço vazio de conteúdo de 125x125px para o logótipo TOMI no canto da moldura. Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Tomi Sport TV</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>MP4 (sem fundo), codec H264</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps. Tamanho máximo: 100MB.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>MOP</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>LED Galp</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>840x336px.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Especificações por confirmar</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>CS Outdoors</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>CS Outdoors</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Especificações por confirmar</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de CS Outdoors ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I45"/>
+  <autoFilter ref="A1:I49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -11,14 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OOH" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rádio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imprensa" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinema" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Imprensa'!$A$1:$I$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Imprensa'!$A$1:$I$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19371,6 +19373,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fornecedor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Veículo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dimensão</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Aspect Ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Ficheiro</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Publicidade Cinema 2D</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Formato de imagem preferencial: FLAT 1.85 — 1998x1080px.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1.85:1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Ficheiros DATA: sequência de ficheiros DPX 10-bit a 24fps, ou sequência de ficheiros TIFF em RGB. Ficheiros vídeo: QuickTime ProRes a 25fps ou 24fps, com áudio 5.1 ou 2.0 sincronizado à imagem.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner). Dúvidas: bruno.figueiredo@vs2.pt.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>VS2.0</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Publicidade Cinema 3D</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Formato de imagem: FLAT 1.85 — 1998x1080px, ou SCOPE 2.39 — 2048x858px (maior exploração do ecrã).</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1.85:1 (FLAT) ou 2.39:1 (SCOPE)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Ficheiros DATA: dois ficheiros separados (Left eye + Right eye) em sequência, no formato TIFF RGB 16-bit data, ou ficheiros DPX 10-bit — ambos a 24fps.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner). Dúvidas: bruno.figueiredo@vs2.pt.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -17195,7 +17195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18992,8 +18992,113 @@
       </c>
       <c r="I49" s="2" t="n"/>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Grande Formato</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Rede Highway</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>10,15x5,15m. Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>3D Lab</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Rede LED</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Escala 1:10.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Cor: modo RGB. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 100 dpi.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I49"/>
+  <autoFilter ref="A1:I52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -17195,7 +17195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19097,8 +19097,261 @@
       </c>
       <c r="I52" s="2" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Unimidia</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Unimidia</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Mupi Digital | Universidades</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Tamanho total: 1080x1920px. Área visível: 1080x1920px.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 10MB (vídeo produzido pelo cliente).</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Produzido pela Unimidia (material por camadas): .psd, .ai ou .indd, fotografias/imagens com resolução superior a 150dpi, texto convertido em curvas — sujeito a apresentação de orçamento. Produzido pelo cliente (vídeo pronto): .avi, .mp4, .mov, .mpeg, .mpg ou .jpeg, resolução 1080x1920px, 25 frames por segundo, em formato vertical.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Duração máxima: 10 segundos. Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Açores - Lateral Direita</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Açores - Lateral Esquerda</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover - Lateral Direita</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover - Lateral Esquerda</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Indoor - Flyer</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Altura (sem margem): 20cm. Largura (sem margem): 10cm.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Indoor - Banner</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Impressão: 34x12,6cm (largura x altura). Área visível: 37,5x15cm (largura x altura).</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I52"/>
+  <autoFilter ref="A1:I59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -17195,7 +17195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19350,8 +19350,125 @@
       </c>
       <c r="I59" s="2" t="n"/>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Shine Care</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Shine Care</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Mupi Digital</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>MP4.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos. Frame rate: 30 frames por segundo. Rede de mupis digitais em hospitais e clínicas.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã Horizontal</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>1920x1080px.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Media Play</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã Vertical</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I59"/>
+  <autoFilter ref="A1:I62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -19100,7 +19100,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Unimidia</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -19143,7 +19143,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -19178,7 +19178,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -19213,7 +19213,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -19248,7 +19248,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -19283,7 +19283,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -19318,7 +19318,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -17195,7 +17195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19467,8 +19467,109 @@
       </c>
       <c r="I62" s="2" t="n"/>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Mupis Digitais</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Mupi de pé (estrutura autónoma): 202cm de altura total, 73cm de largura. Ecrã de 50″, com 107cm de altura visível, posicionado a 83,5cm do chão; margens de 11cm (topo) e 7cm (laterais do ecrã).</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Conteúdo: 1080x1920px, MP4.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Mupis Tradicionais</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>80cm (largura) x 120cm (altura). Área total = área visível.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Tequilha</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Ecrãs de Cinema Universidades</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã de 50″.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Conteúdo: 1920x1080px, MP4.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Estes ecrãs passam trailers de filmes; entre os trailers, passam spots de TV dos parceiros, incluindo a Tequilha.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I62"/>
+  <autoFilter ref="A1:I65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -20013,12 +20013,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -20052,12 +20052,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>VS2.0</t>
+          <t>NOS Publicidade</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -17195,7 +17195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19568,8 +19568,78 @@
       </c>
       <c r="I65" s="2" t="n"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Unimidia/Spreading</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover Madeira - Lateral Direita</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Unimidia/Spreading</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Spreading</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Táxi Doorcover Madeira - Lateral Esquerda</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I65"/>
+  <autoFilter ref="A1:I67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -11495,7 +11495,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I241" s="2" t="n"/>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I242" s="2" t="n"/>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I243" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I244" s="2" t="n"/>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I246" s="2" t="n"/>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I247" s="2" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I253" s="2" t="n"/>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I254" s="2" t="n"/>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I255" s="2" t="n"/>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I256" s="2" t="n"/>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I257" s="2" t="n"/>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I258" s="2" t="n"/>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I259" s="2" t="n"/>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Imprensa'!$A$1:$I$125</definedName>
   </definedNames>
@@ -19915,7 +19915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20007,8 +20007,62 @@
       </c>
       <c r="I2" s="2" t="n"/>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Live Copies</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Briefing da campanha, fornecido pela agência, para a rádio produzir o guião de conversa entre os animadores (live read).</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Rádio</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Referência</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Frase de 5 segundos, com uma frase quase tipo slogan da marca.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -20029,7 +20029,7 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Briefing da campanha, fornecido pela agência, para a rádio produzir o guião de conversa entre os animadores (live read).</t>
+          <t>Formato de "live read": a agência não entrega um ficheiro de áudio pronto a emitir — entrega um briefing da campanha (conceito, mensagens-chave e tom de comunicação), e é a própria rádio quem escreve o guião e produz a conversa entre os animadores, lida em direto ou gravada com a voz da estação. Por não haver ficheiro de áudio a entregar, não tem Tipo de Ficheiro nem Peso — o que se entrega é o briefing escrito.</t>
         </is>
       </c>
       <c r="I3" s="2" t="n"/>
@@ -20056,7 +20056,7 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Frase de 5 segundos, com uma frase quase tipo slogan da marca.</t>
+          <t>Frase curta, com a duração de 5 segundos, com um texto quase ao estilo de um slogan da marca, lida pelos animadores da rádio em antena. Tal como o Live Copies, não é um ficheiro de áudio entregue pela agência — o que se fornece é o texto da frase, para a rádio gravar ou ler; por isso não tem Tipo de Ficheiro nem Peso.</t>
         </is>
       </c>
       <c r="I4" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -20029,7 +20029,7 @@
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Formato de "live read": a agência não entrega um ficheiro de áudio pronto a emitir — entrega um briefing da campanha (conceito, mensagens-chave e tom de comunicação), e é a própria rádio quem escreve o guião e produz a conversa entre os animadores, lida em direto ou gravada com a voz da estação. Por não haver ficheiro de áudio a entregar, não tem Tipo de Ficheiro nem Peso — o que se entrega é o briefing escrito.</t>
+          <t>É necessário fornecer um briefing da campanha, incluindo o conceito, as mensagens-chave e o tom de comunicação. A partir desse briefing, a própria rádio desenvolve o guião e produz a conversa entre os animadores, que pode ser realizada em direto ou previamente gravada, sempre com as vozes da estação.</t>
         </is>
       </c>
       <c r="I3" s="2" t="n"/>
@@ -20056,7 +20056,7 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Frase curta, com a duração de 5 segundos, com um texto quase ao estilo de um slogan da marca, lida pelos animadores da rádio em antena. Tal como o Live Copies, não é um ficheiro de áudio entregue pela agência — o que se fornece é o texto da frase, para a rádio gravar ou ler; por isso não tem Tipo de Ficheiro nem Peso.</t>
+          <t>É necessário fornecer uma frase curta, com cerca de 5 segundos de duração e uma construção próxima de um slogan de marca, para ser lida em antena pelos animadores da rádio.</t>
         </is>
       </c>
       <c r="I4" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -20000,11 +20000,7 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não foi indicada nenhuma plataforma de distribuição nem rádio específica — specs genéricas de entrega, a confirmar sempre junto da rádio ou da central de meios antes de entregar. Áudio AAC, 2 canais (stereo) ou mono consoante o spot, 48 KHz, bit rate mínimo recomendado 320 kbps (CBR), loudness (integrado) -23 LUFS e peak level -3dB TP máx. — o mesmo padrão de loudness broadcast já usado para TV.</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$355</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$381</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K355"/>
+  <dimension ref="A1:K381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16860,8 +16860,1386 @@
       </c>
       <c r="K355" s="2" t="n"/>
     </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Conversacional</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>Mensagens + botões de resposta.</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>Chat / conversa simulada. Imagens necessárias: 0 (usa avatar do logo). Substituível por asset real: Avatar do chat (círculo) → foto/ícone da marca 96x96 PNG. Emoji 👋 → ícone próprio. Specs do asset: Avatar opcional (círculo, 96x96). Bolhas de chat geradas por CSS. Sem imagens de fundo. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Audiências Game</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>3 labels de audiência (ex: Jovens/Famílias/Profissionais) + enunciado.</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>Drag &amp; drop de mensagens para audiências. Imagens necessárias: 0–3 (ícones de audiência opcionais). Substituível por asset real: Emojis das audiências (👥) → ícones da marca 128x128 PNG transparente. Bins → cores da marca. Specs do asset: Ícones 1:1 PNG transparente 128x128 (opcional; caso contrário emoji). Bins e cartões gerados por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Scratch</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>Pergunta topo + mensagem revelada + CTA.</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>Raspadinha (scratch-to-reveal). Imagens necessárias: 1 imagem-prémio/revelação (recomendado). Substituível por asset real: Camada revelada → imagem real do cliente 300x300. Emojis ✨🔎 → ícones próprios. Specs do asset: Imagem de revelação 300x300 (JPG/PNG). Camada de raspar é CSS/canvas. Imagem por baixo é o asset do cliente. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Slider Relevância</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>2 labels extremos + enunciado + conclusão.</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>Slider comparativo (relevante vs genérico). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones/emojis dos extremos → ícones 96x96 PNG (opcional). Totalmente CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Catch Sinais</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>Enunciado + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>Apanhar itens que caem (jogo). Imagens necessárias: 0–4 (ícones dos itens, opcional). Substituível por asset real: Itens que caem (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG transparente (opcional; senão emoji). Física/posições por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Puzzle Logo</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>Puzzle de peças que monta o logótipo. Imagens necessárias: 1 logótipo (obrigatório). Substituível por asset real: Já usa imagem real (logótipo). Fundo das peças → cor/textura da marca (opcional). Specs do asset: Logótipo 240x240 PNG (fundo sólido ou transparente). A imagem é fatiada em peças por CSS. Entregar logo em alta resolução. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Ligações</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>Jogo da memória (pares). Imagens necessárias: 0–6 (faces das cartas, opcional). Substituível por asset real: Faces das cartas (emoji) → imagens/ícones 128x128 (produtos, símbolos da marca). Specs do asset: Ícones/faces 128x128 (opcional; senão emoji). Cartas geradas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Roda Havas</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>6 labels de segmento + enunciado + resultado.</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>Roda da sorte / estratégia. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos segmentos → ícones 64x64 PNG. Cores dos segmentos → paleta da marca. Segmentos e cores por CSS. Emojis por segmento. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Hold Ligação</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem ao completar.</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>Press-and-hold para carregar. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone central (emoji) → ícone/logo 96x96 PNG (opcional). Totalmente CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Swipe Briefing</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>N afirmações (texto) + resultado.</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>Swipe cards (claro/vago). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ilustrações das cartas → imagens 260x300 (opcional; senão CSS). Cartas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Calculadora Contactos</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>Labels dos campos + enunciado + resultado.</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>Calculadora interativa. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones dos campos (emoji) → ícones 48x48 PNG (opcional). Inputs e cálculo por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Tap Sinais</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>Enunciado + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>Tap rápido em alvos. Imagens necessárias: 0–4 (ícones-alvo, opcional). Substituível por asset real: Alvos (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG (opcional). Alvos por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Procura na Estratégia</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>Enunciado + itens a encontrar (labels) + final.</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>Encontra itens (procura visual). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Itens a encontrar (emoji) → ícones/mini-imagens 64x64 PNG. Grelha por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Método Havas</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>Instrução + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>Simon (sequência de memória). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Pads (cor) → cores da marca. Ícones por pad 64x64 PNG (opcional). Pads e sequência por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Palavra</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>Palavra-alvo + pista + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>Anagrama / ordenar letras. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/pista (emoji) → ícone 96x96 PNG (opcional). Letras por CSS. Definir palavra-chave da campanha. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Da Marca à Pessoa</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>Labels do percurso + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>Percurso animado marca→pessoa. Imagens necessárias: 0–1 (logótipo no início, opcional). Substituível por asset real: Início do percurso → logótipo 128x128. Fim → foto/ícone 'pessoa' 128x128 (opcional). Specs do asset: Logótipo 128x128 (opcional). Trajeto por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Slot Havas</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>Enunciado + linha de prémio + resultado.</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>Slot machine (3 rolos). Imagens necessárias: 0–3 (símbolos dos rolos, opcional). Substituível por asset real: Símbolos dos rolos (emoji) → 3+ ícones 96x96 PNG transparente (produtos/marca). Specs do asset: Símbolos 96x96 PNG transparente (opcional; senão emoji). Rolos e símbolos por CSS/emoji. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Verdade/Mito</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>5 afirmações + feedback por afirmação + resultado.</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>Quiz verdadeiro/falso (5 afirmações). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone das cartas (emoji) → ícone 96x96 PNG (opcional). Verde/vermelho mantêm-se (funcional). Semáforo verde/vermelho é funcional (manter). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Diferenças</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>Enunciado + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>Descobre as diferenças. Imagens necessárias: 2 imagens (A e B) — obrigatório se usado. Substituível por asset real: Já usa 2 imagens reais. Cliente envia o par 300x300 (senão versão ilustrada). Specs do asset: 2 imagens 300x300 quase idênticas (JPG/PNG). Se sem imagens do cliente, usa versão ilustrada. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Enche o Mapa</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>Enunciado + label + mensagem final.</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>Preencher barra/mapa por toques. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/label (emoji) → ícone 96x96 PNG (opcional). Barra por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Configurador</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>6 labels de opção + enunciado + resumo.</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>Seletor de opções (configurar seleção). Imagens necessárias: 0–6 (ícones das opções, opcional). Substituível por asset real: Ícones das opções (emoji) → ícones 96x96 PNG transparente. Cores por opção → paleta da marca. Specs do asset: Ícones 96x96 (opcional; senão emoji). Cores por opção configuráveis. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Countdown</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>Título + subtítulo + CTA.</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>Contagem decrescente para data-alvo. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/fundo (emoji/CSS) → imagem de fundo 300x600 ou ícone 96x96 (opcional). Definir data-alvo por campanha (JS). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Estimativa</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>Pergunta + valor de referência + resultado.</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>Adivinha o número (slider). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone do enunciado (emoji) → ícone 96x96 PNG (opcional). Slider por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Ranking</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>4 itens (labels) + enunciado + confirmação.</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>Ordenar prioridades (drag). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos itens (🎯👥…) → ícones 48x48 PNG da marca (opcional). Itens arrastáveis por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Carrossel Produtos</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>Por slide: título + subtítulo + 3 bullets + CTA.</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>Carrossel de produtos/cards. Imagens necessárias: 1 por slide (recomendado 3–5). Substituível por asset real: Já usa imagens reais (1 por slide). Cliente envia 3–5 imagens 300x300. Specs do asset: Imagens de produto 300x300 (JPG/PNG), fundo neutro. Nº de slides configurável. Peso soma todas as imagens. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Displ.AI+ - Parallax</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>Título + subtítulo + CTA.</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>Cena com camadas parallax. Imagens necessárias: 1–4 camadas (opcional). Substituível por asset real: Camadas ilustradas (CSS) → 1–4 PNG transparentes 420x420 da marca (produto/cena). Specs do asset: Camadas PNG transparente 420x420 (opcional; senão ilustração). Auto-scroll ping-pong. Sem leitura de scroll do host. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K355"/>
+  <autoFilter ref="A1:K381"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16878,7 +16878,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Conversacional</t>
+          <t>Prog - Displ.AI+ - Conversacional</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Audiências Game</t>
+          <t>Prog - Displ.AI+ - Audiências Game</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Scratch</t>
+          <t>Prog - Displ.AI+ - Scratch</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Slider Relevância</t>
+          <t>Prog - Displ.AI+ - Slider Relevância</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Catch Sinais</t>
+          <t>Prog - Displ.AI+ - Catch Sinais</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Puzzle Logo</t>
+          <t>Prog - Displ.AI+ - Puzzle Logo</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Ligações</t>
+          <t>Prog - Displ.AI+ - Ligações</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Roda Havas</t>
+          <t>Prog - Displ.AI+ - Roda Havas</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Hold Ligação</t>
+          <t>Prog - Displ.AI+ - Hold Ligação</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Swipe Briefing</t>
+          <t>Prog - Displ.AI+ - Swipe Briefing</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Calculadora Contactos</t>
+          <t>Prog - Displ.AI+ - Calculadora Contactos</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Tap Sinais</t>
+          <t>Prog - Displ.AI+ - Tap Sinais</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Procura na Estratégia</t>
+          <t>Prog - Displ.AI+ - Procura na Estratégia</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Método Havas</t>
+          <t>Prog - Displ.AI+ - Método Havas</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Palavra</t>
+          <t>Prog - Displ.AI+ - Palavra</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Da Marca à Pessoa</t>
+          <t>Prog - Displ.AI+ - Da Marca à Pessoa</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Slot Havas</t>
+          <t>Prog - Displ.AI+ - Slot Havas</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Verdade/Mito</t>
+          <t>Prog - Displ.AI+ - Verdade/Mito</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Diferenças</t>
+          <t>Prog - Displ.AI+ - Diferenças</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Enche o Mapa</t>
+          <t>Prog - Displ.AI+ - Enche o Mapa</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Configurador</t>
+          <t>Prog - Displ.AI+ - Configurador</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Countdown</t>
+          <t>Prog - Displ.AI+ - Countdown</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Estimativa</t>
+          <t>Prog - Displ.AI+ - Estimativa</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Ranking</t>
+          <t>Prog - Displ.AI+ - Ranking</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Carrossel Produtos</t>
+          <t>Prog - Displ.AI+ - Carrossel Produtos</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Displ.AI+ - Parallax</t>
+          <t>Prog - Displ.AI+ - Parallax</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Digital" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OOH" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rádio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinema" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Digital" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OOH" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rádio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cinema" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$381</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$382</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K381"/>
+  <dimension ref="A1:K382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18238,8 +18238,75 @@
       </c>
       <c r="K381" s="2" t="n"/>
     </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Genérico</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Genérico</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>Branded Content</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Branded Content</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>É necessário enviar:
+ - data da publicação?
+- qual o produto ou serviço a comunicar?
+- qual a mensagem a passar?
+- objectivo da comunicação?
+- alvo?
+- mini-briefing: explicação do produto e pontos/temas a destacar
+- PR ou documento com informação do produto
+- imagens em alta qualidade (jpeg)
+- vídeos a associar (mp4).
+Para a publicação e destaque dos artigos:
+- link do site (ou tags)
+- link do perfil de facebook da marca
+- link do perfil de instagram da marca
+- logotipo (jpeg pu png) com fundo transparente</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K381"/>
+  <autoFilter ref="A1:K382"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$382</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$380</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K382"/>
+  <dimension ref="A1:K380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10572,47 +10572,39 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Branded Mission</t>
+          <t>Carousel Ads</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>ÍCONE DA MISSION: 240x240px. VÍDEO DE EXEMPLO (obrigatório, 1 a 10 vídeos): 9:16, ≥720x1280px, duração recomendada 12-15s. MÚSICA OFICIAL (opcional): capa 300x300 (elementos-chave centrados num diâmetro de 260px), duração 15s-1min (recomendado 15s). LOGO DA MARCA (opcional): imagem principal + até 4 secundárias, mín. 1000x1000px. QUICK EFFECT (opcional): 1 a 10 imagens, 100x100 a 1000x1000px. BRAND SAFETY — competitor exclusion (até 5 concorrentes) / negative content: logos da marca/concorrentes.</t>
+          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>9:16 (vídeo de exemplo)</t>
+          <t>1.91:1 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Ícone: ≤500 KB. Vídeo de exemplo: ≤100 MB, bitrate &gt;2.500kbps. Capa da música: ≤1 MB. Logo principal/secundário: ≤10 MB cada. Logos de brand safety (concorrentes/marca): ≤1024 KB cada.</t>
+          <t>100 KB sugerido por imagem; música até 10 MB</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>Ícone: PNG, JPG ou JPEG. Vídeo de exemplo: MP4, MPEG, 3GP, AVI, MOV. Música: MP3. Logos: JPG/JPEG/PNG (recomendado PNG).</t>
-        </is>
-      </c>
-      <c r="I223" s="2" t="inlineStr">
-        <is>
-          <t>Nome do anunciante: até 24c (sem espaços/emojis/caracteres especiais, exceto '&amp;'). Nome da Mission: até 70c (recomendado ≤18c para caber numa linha; sem espaços/emojis/caracteres especiais como &lt; &gt; " &amp;). Descrição da Mission: até 300c (recomendado ≤150c). Legenda do vídeo de exemplo: até 150c (recomendado 4-60c, sem quebras de linha). Nome da música: até 60c (recomendado ≤12c); nome do artista sem limite (recomendado ≤12c). Nome do logo: até 20c. Nome de concorrente/marca (brand safety): até 20c cada.</t>
-        </is>
-      </c>
-      <c r="J223" s="2" t="inlineStr">
-        <is>
-          <t>Requisitos: pelo menos 1 requisito geral obrigatório (música oficial, hashtag oficial, mencionar conta oficial, usar/acionar Branded Effect, ou Duet); até 3 requisitos específicos opcionais (dançar, lip-sync, mudar de roupa, mostrar a cara); requisitos de marca opcionais (revelar logo &gt;1s, usar Quick Effect).</t>
-        </is>
-      </c>
+          <t>JPG/JPEG, PNG + MP3</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="n"/>
+      <c r="J223" s="2" t="n"/>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/about-branded-mission</t>
+          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
         </is>
       </c>
     </row>
@@ -10629,39 +10621,47 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Carousel Ads</t>
+          <t>In-Feed (Standard Feed)</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
+          <t>Vertical (recomendado): 9:16, ≥540x960px. Horizontal: 16:9, ≥960x540px. Square: 1:1, ≥640x640px. Duração: até 10min</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 9:16</t>
+          <t>9:16 (recomendado), 16:9 ou 1:1</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>100 KB sugerido por imagem; música até 10 MB</t>
+          <t>≤500 MB; bitrate ≥516 kbps</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>JPG/JPEG, PNG + MP3</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="n"/>
-      <c r="J224" s="2" t="n"/>
+          <t xml:space="preserve">MP4, MOV, MPEG, 3GP, AVI. </t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>até 100c, máx. 4 linhas visíveis (recomendado ≤50c CN/JP/KR ou ≤100c outras línguas para não ser coberta por 'Ver mais'), sem '{ }', sem emojis.</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>Zonas seguras variam consoante orientação (vertical/horizontal/quadrado), idioma (LTR/RTL) e uso de anchors — ficheiros de referência disponíveis na TikTok Ads Help.</t>
+        </is>
+      </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -10683,42 +10683,30 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>In-Feed (Standard Feed)</t>
+          <t>Pulse</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Vertical (recomendado): 9:16, ≥540x960px. Horizontal: 16:9, ≥960x540px. Square: 1:1, ≥640x640px. Duração: até 10min. Foto de perfil (opcional): 98x98px, quadrada (se vazia, usa foto default). Nome da conta (App Ads): extraído automaticamente da App Store/Google Play; usado como título da landing page in-app. Download Card (só App Ads): gerado automaticamente, aparece logo após o CTA ou cor de fundo.</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>9:16 (recomendado), 16:9 ou 1:1</t>
-        </is>
-      </c>
+          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>≤500 MB; bitrate ≥516 kbps. Foto de perfil: &lt;50 KB.</t>
+          <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP, AVI. Foto de perfil: JPG, JPEG, PNG.</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>Legenda: exibida em branco, fonte uniforme (não personalizável); não suporta links clicáveis, símbolo '@' nem hashtags. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas).</t>
-        </is>
-      </c>
-      <c r="J225" s="2" t="inlineStr">
-        <is>
-          <t>Zonas seguras variam consoante orientação (vertical/horizontal/quadrado), idioma (LTR/RTL) e uso de anchors — ficheiros de referência disponíveis na TikTok Ads Help.</t>
-        </is>
-      </c>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="n"/>
+      <c r="J225" s="2" t="n"/>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
         </is>
       </c>
     </row>
@@ -10740,30 +10728,34 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Pulse</t>
+          <t>Spark Ads</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="n"/>
+          <t>≥540x960px.</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>9:16 (recomendado)</t>
+        </is>
+      </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>até 500 MB</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
+          <t>.mp4, .mov, .mpeg, .3gp.</t>
         </is>
       </c>
       <c r="I226" s="2" t="n"/>
       <c r="J226" s="2" t="n"/>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -10785,34 +10777,34 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Spark Ads</t>
+          <t>Top Feed</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Pull: usa o vídeo orgânico tal como publicado, sem restrição de duração; legenda extraída diretamente do vídeo, até 4 linhas visíveis. Push: sobe um novo vídeo, ≥540x960px.</t>
+          <t>Segue criativo In-Feed</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>9:16 (recomendado para Push); Pull usa o rácio do vídeo orgânico</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Push: até 500 MB</t>
+          <t>Conforme In-Feed</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>Pull: .mp4 ou .mov (do vídeo orgânico). Push: MP4, MOV, MPEG, 3GP.</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="I227" s="2" t="n"/>
       <c r="J227" s="2" t="n"/>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
       </c>
     </row>
@@ -10834,12 +10826,12 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Top Feed</t>
+          <t>TopView</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Segue criativo In-Feed</t>
+          <t>Vertical, ≥540x960px; duração 5-60s (recomendado 9-15s).</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -10849,76 +10841,80 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Conforme In-Feed</t>
+          <t xml:space="preserve"> ≤500 MB, bitrate ≥2.500kbps</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
-        </is>
-      </c>
-      <c r="I228" s="2" t="n"/>
-      <c r="J228" s="2" t="n"/>
+          <t>.mp4, .mov, .mpeg, .3gp.</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>até 100c, máx. 4 linhas visíveis (recomendado ≤50c CN/JP/KR ou ≤100c outras línguas para não ser coberta por 'Ver mais'), sem '{ }', sem emojis.</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 20 anúncios por ad group.</t>
+        </is>
+      </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>TopView</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Spark Ads Pull: sem duração mínima/máxima (usa o vídeo orgânico tal como publicado). Non-Spark Ads e Spark Ads Push: vertical, ≥540x960px; duração 5-60s (recomendado 9-15s).</t>
+          <t>2 a 6 slides (imagens ou vídeos). Image Carousels: 800x800 recomendado; Video Carousels: 800x450 recomendado. Rácio único em todos os slides do carrossel; conteúdo misto tem de manter o mesmo rácio entre asset de imagem e de vídeo.</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1:1, 1.91:1, 4:5, 2:3, 16:9 ou 9:16 (rácio único por carrossel)</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Non-Spark Ads e Spark Ads Push: ≤500 MB, bitrate ≥2.500kbps. Spark Ads Pull: sem limite próprio (usa o vídeo já publicado).</t>
+          <t>Imagem: até 5 MB; Vídeo: até 1 GB (recomendado &lt;30 MB)</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>Spark Ads Pull: .mp4 ou .mov (normalmente). Non-Spark Ads e Spark Ads Push: .mp4, .mov, .mpeg, .3gp.</t>
+          <t>JPG, PNG (image carousel); MP4, MOV (video carousel)</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Foto de perfil: quadrada, 98x98px, &lt;50 KB, .jpg/.jpeg/.png (elemento-chave centrado numa área de 66x66px); em Spark Ads usa a foto de perfil da conta do vídeo. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas), sem emojis nem '{ }'. Legenda do anúncio: Spark Ads Pull até 100c (extraída do vídeo orgânico, pode ser vazia); Non-Spark/Spark Push até 100c, máx. 4 linhas visíveis (recomendado ≤50c CN/JP/KR ou ≤100c outras línguas para não ser coberta por 'Ver mais'), sem '{ }', emojis só a partir da versão 11.</t>
-        </is>
-      </c>
-      <c r="J229" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 20 anúncios por ad group.</t>
-        </is>
-      </c>
+          <t>1 destino (Carousel de destino único) ou até 6 destinos únicos (Carousel multi-destino).</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="n"/>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -10935,37 +10931,37 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Image Ad</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>2 a 6 slides (imagens ou vídeos). Image Carousels: 800x800 recomendado; Video Carousels: 800x450 recomendado. Rácio único em todos os slides do carrossel; conteúdo misto tem de manter o mesmo rácio entre asset de imagem e de vídeo.</t>
+          <t>1200x1200 ou 1200x628 recomendado</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>1:1, 1.91:1, 4:5, 2:3, 16:9 ou 9:16 (rácio único por carrossel)</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Imagem: até 5 MB; Vídeo: até 1 GB (recomendado &lt;30 MB)</t>
+          <t>Máx. 5 MB</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG (image carousel); MP4, MOV (video carousel)</t>
+          <t>PNG ou JPEG recomendado (BMP e TIFF não aceites; GIF carregado é convertido em imagem estática)</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>1 destino (Carousel de destino único) ou até 6 destinos únicos (Carousel multi-destino).</t>
+          <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
       <c r="J230" s="2" t="n"/>
@@ -10988,32 +10984,28 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Image Ad</t>
+          <t>Text Ad</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1200x628 recomendado</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
-        </is>
-      </c>
+          <t>Sem asset gráfico obrigatório</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Máx. 5 MB</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>PNG ou JPEG recomendado (BMP e TIFF não aceites; GIF carregado é convertido em imagem estática)</t>
+          <t>Texto/post + URL opcional</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -11041,28 +11033,32 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Text Ad</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Sem asset gráfico obrigatório</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="n"/>
+          <t>1200x1200 ou 1920x1080 recomendado. Duração recomendada ≤15s (até 2:20 suportado; alguns anunciantes elegíveis para até 10min, recomendado não ultrapassar 9:55). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (até 60 FPS aceite, não fazer upsample). Thumbnail: rácio igual ao do vídeo, máx. 5 MB. Loop automático se duração &lt;60s. Branding (logo) recomendado persistente no canto superior esquerdo; legendas/closed captions fortemente recomendadas.</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>1:1 ou 16:9</t>
+        </is>
+      </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Máx. 1 GB (recomendado manter abaixo de 30 MB para melhor desempenho)</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Texto/post + URL opcional</t>
+          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC; thumbnail PNG ou JPEG</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
@@ -11080,53 +11076,45 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Medium Rectangle</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1920x1080 recomendado. Duração recomendada ≤15s (até 2:20 suportado; alguns anunciantes elegíveis para até 10min, recomendado não ultrapassar 9:55). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (até 60 FPS aceite, não fazer upsample). Thumbnail: rácio igual ao do vídeo, máx. 5 MB. Loop automático se duração &lt;60s. Branding (logo) recomendado persistente no canto superior esquerdo; legendas/closed captions fortemente recomendadas.</t>
-        </is>
-      </c>
-      <c r="F233" s="2" t="inlineStr">
-        <is>
-          <t>1:1 ou 16:9</t>
-        </is>
-      </c>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="n"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 GB (recomendado manter abaixo de 30 MB para melhor desempenho)</t>
+          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC; thumbnail PNG ou JPEG</t>
-        </is>
-      </c>
-      <c r="I233" s="2" t="inlineStr">
-        <is>
-          <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
-        </is>
-      </c>
+          <t>JPG, PNG, GIF</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="n"/>
       <c r="J233" s="2" t="n"/>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -11148,18 +11136,18 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Medium Rectangle</t>
+          <t>Large Rectangle</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>336x280</t>
         </is>
       </c>
       <c r="F234" s="2" t="n"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11188,17 +11176,17 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Large Rectangle</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>336x280</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="F235" s="2" t="n"/>
@@ -11233,20 +11221,24 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Half Page</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>728x90</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="n"/>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
           <t>150 KB</t>
@@ -11278,24 +11270,20 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Half Page</t>
+          <t>Mobile Banner</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
+          <t>320x50</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="n"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
           <t>150 KB</t>
@@ -11327,28 +11315,32 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Mobile Banner</t>
+          <t>Responsive Display Ads (imagem)</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>320x50</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="n"/>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Imagem — Horizontal: 1.91:1; Square: 1:1; Logo quadrado: 1:1; Logo horizontal: 4:1. Vídeo — Horizontal: 16:9; Square: 1:1; Vertical: 2:3.</t>
+        </is>
+      </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="I238" s="2" t="n"/>
@@ -11372,32 +11364,32 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Responsive Display Ads (imagem)</t>
+          <t>HTML5 Display</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
+          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>Imagem — Horizontal: 1.91:1; Square: 1:1; Logo quadrado: 1:1; Logo horizontal: 4:1. Vídeo — Horizontal: 16:9; Square: 1:1; Vertical: 2:3.</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>150 KB (dentro do HTML5)</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>ZIP HTML5</t>
         </is>
       </c>
       <c r="I239" s="2" t="n"/>
@@ -11411,49 +11403,49 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>HTML5 Display</t>
+          <t>Skippable In-Stream</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>150 KB (dentro do HTML5)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>ZIP HTML5</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I240" s="2" t="n"/>
       <c r="J240" s="2" t="n"/>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -11475,12 +11467,12 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Skippable In-Stream</t>
+          <t>Non-skippable In-Stream (standard)</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -11490,7 +11482,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -11502,7 +11494,7 @@
       <c r="J241" s="2" t="n"/>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11516,12 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Non-skippable In-Stream (standard)</t>
+          <t>Bumper</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -11568,22 +11560,22 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Bumper</t>
+          <t>Non-skippable 30s (Connected TV)</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -11617,22 +11609,22 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Non-skippable 30s (Connected TV)</t>
+          <t>In-Feed Video Ad (ex-Discovery)</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>16 a 30 segundos; formato específico para Connected TV</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -11645,11 +11637,15 @@
           <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
-      <c r="I244" s="2" t="n"/>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
+        </is>
+      </c>
       <c r="J244" s="2" t="n"/>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -11666,22 +11662,22 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>In-Feed Video Ad (ex-Discovery)</t>
+          <t>YouTube Shorts Ads</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
+          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -11694,11 +11690,7 @@
           <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
-        <is>
-          <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
-        </is>
-      </c>
+      <c r="I245" s="2" t="n"/>
       <c r="J245" s="2" t="n"/>
       <c r="K245" s="3" t="inlineStr">
         <is>
@@ -11719,22 +11711,22 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Vertical Video</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>YouTube Shorts Ads</t>
+          <t>Masthead</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -11758,49 +11750,49 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Masthead</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Logo: 1200x1200 (mín. 144x144); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional)</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
+          <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
       <c r="I247" s="2" t="n"/>
       <c r="J247" s="2" t="n"/>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -11817,32 +11809,32 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Logo: 1200x1200 (mín. 144x144); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional)</t>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>16:9 ou 9:16 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (não animado)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="I248" s="2" t="n"/>
@@ -11866,35 +11858,39 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
+          <t>2 a 10 cartões, todos com a mesma proporção entre si</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 4:5 ou 1:1</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="I249" s="2" t="n"/>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Título por cartão: até 40 caracteres</t>
+        </is>
+      </c>
       <c r="J249" s="2" t="n"/>
       <c r="K249" s="3" t="inlineStr">
         <is>
@@ -11905,55 +11901,47 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Audio Ad</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Prog - Audio Ad</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>2 a 10 cartões, todos com a mesma proporção entre si</t>
-        </is>
-      </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
-        </is>
-      </c>
+          <t>Duração máxima: 30''.</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="n"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>5 MB por imagem</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP3; alternativa aceite: WAV 16-bit 44.1kHz. Áudio normalizado a -14 dB LUFS integrado; MP3 ≥192kbps; picos abaixo de -1 dB TP para evitar distorção na transcodificação.</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Título por cartão: até 40 caracteres</t>
+          <t>Nome do anunciante: máx. 45c.</t>
         </is>
       </c>
       <c r="J250" s="2" t="n"/>
-      <c r="K250" s="3" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
-        </is>
-      </c>
+      <c r="K250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -11968,37 +11956,41 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Audio Ad</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Prog - Audio Ad</t>
+          <t>Prog - Standard Banners</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Duração máxima: 30''.</t>
+          <t>300x250, 300x600, 728x90, 320x50</t>
         </is>
       </c>
       <c r="F251" s="2" t="n"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>MP3; alternativa aceite: WAV 16-bit 44.1kHz. Áudio normalizado a -14 dB LUFS integrado; MP3 ≥192kbps; picos abaixo de -1 dB TP para evitar distorção na transcodificação.</t>
-        </is>
-      </c>
-      <c r="I251" s="2" t="inlineStr">
-        <is>
-          <t>Nome do anunciante: máx. 45c.</t>
-        </is>
-      </c>
-      <c r="J251" s="2" t="n"/>
-      <c r="K251" s="2" t="n"/>
+          <t>ZIP com HTML5 e pastas de imagens/scripts, ou JPEG/GIF; enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="n"/>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK).</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>https://support.google.com/dcm/answer/3145300?hl=en</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -12008,44 +12000,44 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Prog - Standard Banners</t>
+          <t>Prog - YouTube Masthead</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>300x250, 300x600, 728x90, 320x50</t>
-        </is>
-      </c>
-      <c r="F252" s="2" t="n"/>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>ZIP com HTML5 e pastas de imagens/scripts, ou JPEG/GIF; enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I252" s="2" t="n"/>
-      <c r="J252" s="2" t="inlineStr">
-        <is>
-          <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK).</t>
-        </is>
-      </c>
+      <c r="J252" s="2" t="n"/>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/dcm/answer/3145300?hl=en</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -12062,27 +12054,27 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Prog - YouTube Masthead</t>
+          <t>Prog - YouTube Select</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12116,7 +12108,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Prog - YouTube Select</t>
+          <t>Prog - YouTube VRC Ad Sequence</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -12165,12 +12157,12 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Ad Sequence</t>
+          <t>Prog - YouTube VRC Non-Skippable</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -12192,7 +12184,7 @@
       <c r="J255" s="2" t="n"/>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -12214,12 +12206,12 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Non-Skippable</t>
+          <t>Prog - YouTube VVC</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -12241,7 +12233,7 @@
       <c r="J256" s="2" t="n"/>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -12263,17 +12255,17 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Prog - YouTube VVC</t>
+          <t>Prog - YouTube VRC Efficient Reach</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -12290,7 +12282,7 @@
       <c r="J257" s="2" t="n"/>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -12312,17 +12304,17 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Efficient Reach</t>
+          <t>Prog - YouTube VRC Target Frequency</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -12346,49 +12338,49 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Target Frequency</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1.91:1 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="I259" s="2" t="n"/>
       <c r="J259" s="2" t="n"/>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -12405,32 +12397,32 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>1.91:1 ou 4:5 ou 1:1</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="I260" s="2" t="n"/>
@@ -12444,49 +12436,49 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5120 KB</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="I261" s="2" t="n"/>
       <c r="J261" s="2" t="n"/>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -12503,22 +12495,22 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>1:1 ou 4:1</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -12552,32 +12544,32 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
+          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>1:1 ou 4:1</t>
+          <t>16:9 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="I263" s="2" t="n"/>
@@ -12591,49 +12583,49 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Business Information (Logo)</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+          <t>Logo: 1200x1200 (mín. 128x128)</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 1:1 ou 9:16</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="I264" s="2" t="n"/>
       <c r="J264" s="2" t="n"/>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -12650,22 +12642,22 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Ad Assets</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Business Information (Logo)</t>
+          <t>Ad Assets (Imagens)</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Logo: 1200x1200 (mín. 128x128)</t>
+          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -12699,88 +12691,92 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Ad Assets</t>
+          <t>Responsive Search Ad</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Ad Assets (Imagens)</t>
+          <t>Responsive Search Ads</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
-        </is>
-      </c>
-      <c r="F266" s="2" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
-        </is>
-      </c>
+          <t>N/A (só texto, sem imagem)</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="n"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>não especificado</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="I266" s="2" t="n"/>
+          <t>N/A (texto)</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+        </is>
+      </c>
       <c r="J266" s="2" t="n"/>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
+          <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Responsive Search Ad</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Responsive Search Ads</t>
+          <t>Video Action Campaigns</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>N/A (só texto, sem imagem)</t>
-        </is>
-      </c>
-      <c r="F267" s="2" t="n"/>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
+        </is>
+      </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>N/A (texto)</t>
+          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
         </is>
       </c>
       <c r="J267" s="2" t="n"/>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/7684791</t>
+          <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
       </c>
     </row>
@@ -12797,43 +12793,39 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Thumbnail</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Video Action Campaigns</t>
+          <t>Thumbnail (vídeo)</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
+          <t>1280x720 (mín. 1280x640)</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV (enviar o link do vídeo carregado no canal de YouTube)</t>
-        </is>
-      </c>
-      <c r="I268" s="2" t="inlineStr">
-        <is>
-          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
-        </is>
-      </c>
+          <t>JPG, GIF ou PNG</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="n"/>
       <c r="J268" s="2" t="n"/>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12066387</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -12850,27 +12842,27 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Thumbnail</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Thumbnail (vídeo)</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>1280x720 (mín. 1280x640)</t>
+          <t>300x60 (só em desktop)</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
+          <t>&lt; 150 KB</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -12889,49 +12881,53 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>300x60 (só em desktop)</t>
+          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>&lt; 150 KB</t>
+          <t>30 MB</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="I270" s="2" t="n"/>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
+        </is>
+      </c>
       <c r="J270" s="2" t="n"/>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12944,17 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
+          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -12968,17 +12964,17 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
         </is>
       </c>
       <c r="J271" s="2" t="n"/>
@@ -13001,37 +12997,37 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
+          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
+          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
         </is>
       </c>
       <c r="J272" s="2" t="n"/>
@@ -13054,37 +13050,37 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
+          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
+          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB por cartão</t>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
+          <t>JPG, PNG, MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
         </is>
       </c>
       <c r="J273" s="2" t="n"/>
@@ -13097,47 +13093,47 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
+          <t>30 MB</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV ou GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
+          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
         </is>
       </c>
       <c r="J274" s="2" t="n"/>
@@ -13160,37 +13156,37 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
+          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
+          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
+          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
         </is>
       </c>
       <c r="J275" s="2" t="n"/>
@@ -13213,37 +13209,37 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
+          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
+          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
         </is>
       </c>
       <c r="J276" s="2" t="n"/>
@@ -13266,37 +13262,37 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
+          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB por cartão</t>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
+          <t>JPG, PNG, MP4 ou MOV</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
         </is>
       </c>
       <c r="J277" s="2" t="n"/>
@@ -13309,53 +13305,53 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Idea Ad</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
+          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
+          <t>9:16 (recomendado, sem restrição rígida)</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
+          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4 ou MOV</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
+          <t>Título: até 100c; Texto na página: até 250c.</t>
         </is>
       </c>
       <c r="J278" s="2" t="n"/>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -13377,32 +13373,32 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Idea Ad</t>
+          <t>Showcase Ad</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
+          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>9:16 (recomendado, sem restrição rígida)</t>
+          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
+          <t>Até 32 MB</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>Título: até 100c; Texto na página: até 250c.</t>
+          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
         </is>
       </c>
       <c r="J279" s="2" t="n"/>
@@ -13430,17 +13426,17 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Showcase Ad</t>
+          <t>Quiz Ad</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
+          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
+          <t>Title Pin: 2:3; Results Pin: 2:3</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -13455,7 +13451,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
+          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
         </is>
       </c>
       <c r="J280" s="2" t="n"/>
@@ -13468,53 +13464,49 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Quiz Ad</t>
+          <t>AR Lenses</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
-        </is>
-      </c>
-      <c r="F281" s="2" t="inlineStr">
-        <is>
-          <t>Title Pin: 2:3; Results Pin: 2:3</t>
-        </is>
-      </c>
+          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="n"/>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Até 32 MB</t>
+          <t>Varia por asset AR</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
-        </is>
-      </c>
-      <c r="I281" s="2" t="inlineStr">
-        <is>
-          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
-        </is>
-      </c>
-      <c r="J281" s="2" t="n"/>
+          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="n"/>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
+        </is>
+      </c>
       <c r="K281" s="3" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -13531,36 +13523,40 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Branded Effects</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>AR Lenses</t>
+          <t>Sponsored Snap</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
-        </is>
-      </c>
-      <c r="F282" s="2" t="n"/>
+          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Varia por asset AR</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
-        </is>
-      </c>
-      <c r="I282" s="2" t="n"/>
-      <c r="J282" s="2" t="inlineStr">
-        <is>
-          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
-        </is>
-      </c>
+          <t>MP4, MOV, JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="n"/>
       <c r="K282" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
@@ -13570,53 +13566,45 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Sponsored Snap</t>
+          <t>Vertical Video Ad</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+          <t>Recomendado até 1080x1920, mín. 720x1280. Duração recomendada &lt;15s (até 2:20 suportado). Frame rate máx. 60 fps. Bitrate máx. 25 Mbps (alvo 5-10 Mbps).</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="G283" s="2" t="inlineStr">
-        <is>
-          <t>Varia; validar no Ads Manager</t>
-        </is>
-      </c>
+          <t>9:16 (recomendado); também aceites 4:5, 2:3, 1:1, 1.91:1 ou 16:9</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="n"/>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV, JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="I283" s="2" t="inlineStr">
-        <is>
-          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
-        </is>
-      </c>
+          <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="n"/>
       <c r="J283" s="2" t="n"/>
       <c r="K283" s="3" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://business.x.com/en/products/vertical-video-ads</t>
         </is>
       </c>
     </row>
@@ -13633,35 +13621,47 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Vertical Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Vertical Video Ad</t>
+          <t>Amplify Pre-roll</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Recomendado até 1080x1920, mín. 720x1280. Duração recomendada &lt;15s (até 2:20 suportado). Frame rate máx. 60 fps. Bitrate máx. 25 Mbps (alvo 5-10 Mbps).</t>
+          <t>Recomendado 1200x1200 (mín. 600x600 para 1:1); se não for 1:1, mín. 640x360. Duração recomendada ≤15s (máx. 2:20). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (superior aceite, não fazer upsample).</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>9:16 (recomendado); também aceites 4:5, 2:3, 1:1, 1.91:1 ou 16:9</t>
-        </is>
-      </c>
-      <c r="G284" s="2" t="n"/>
+          <t>1:1 (recomendado — ocupa sempre espaço quadrado em desktop/mobile/timeline/perfil) ou 9:16 (vertical, ocupa o mesmo espaço); o anúncio é automaticamente combinado com conteúdo de rácio semelhante do publisher</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 GB</t>
+        </is>
+      </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
-        </is>
-      </c>
-      <c r="I284" s="2" t="n"/>
-      <c r="J284" s="2" t="n"/>
+          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>URL (opcional): tem de começar por http:// ou https://.</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>Branding e legendas/closed captions fortemente recomendados.</t>
+        </is>
+      </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/products/vertical-video-ads</t>
+          <t>https://business.x.com/en/advertising/campaign-types/amplify-pre-roll</t>
         </is>
       </c>
     </row>
@@ -13678,47 +13678,39 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Amplify Pre-roll</t>
+          <t>X Live</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1200x1200 (mín. 600x600 para 1:1); se não for 1:1, mín. 640x360. Duração recomendada ≤15s (máx. 2:20). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (superior aceite, não fazer upsample).</t>
-        </is>
-      </c>
-      <c r="F285" s="2" t="inlineStr">
-        <is>
-          <t>1:1 (recomendado — ocupa sempre espaço quadrado em desktop/mobile/timeline/perfil) ou 9:16 (vertical, ocupa o mesmo espaço); o anúncio é automaticamente combinado com conteúdo de rácio semelhante do publisher</t>
-        </is>
-      </c>
+          <t>Resolução: 1280x720 recomendado, 1920x1080 máximo. Frame rate: 30 fps recomendado, 60 fps máximo. Keyframe interval: OBS a cada 3s; Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180).</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="n"/>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 GB</t>
+          <t>Bitrate de vídeo: 9 Mbps recomendado, 12 Mbps máximo. Bitrate de áudio: máx. 128 bps.</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+          <t>Protocolo RTMP; codec de vídeo H.264/AVC; codec de áudio AAC-LC. Encoders suportados: OBS, Wirecast, Restream, Golightstream, Socialive, Teradek, Elemental, Vmix, StreamYard, Streamlabs.</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>URL (opcional): tem de começar por http:// ou https://.</t>
-        </is>
-      </c>
-      <c r="J285" s="2" t="inlineStr">
-        <is>
-          <t>Branding e legendas/closed captions fortemente recomendados.</t>
-        </is>
-      </c>
+          <t>Descrição da página do evento: até 280c (pode incluir links externos). Carousel do evento: até 5 vídeos (live, VOD, GIFs ou fotos — investimento adicional). Timeline post: até 5 termos específicos (palavras-chave, nomes).</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="n"/>
       <c r="K285" s="3" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/advertising/campaign-types/amplify-pre-roll</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -13735,35 +13727,27 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>X Live</t>
+          <t>Timeline Takeover</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Resolução: 1280x720 recomendado, 1920x1080 máximo. Frame rate: 30 fps recomendado, 60 fps máximo. Keyframe interval: OBS a cada 3s; Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180).</t>
+          <t>Sem specs próprias — usa as specs do formato subjacente escolhido: Image Ads, Video Ads, Carousel Ads, X Live, Promoted Ads com Conversation Button/Polls, ou Branded Notifications.</t>
         </is>
       </c>
       <c r="F286" s="2" t="n"/>
-      <c r="G286" s="2" t="inlineStr">
-        <is>
-          <t>Bitrate de vídeo: 9 Mbps recomendado, 12 Mbps máximo. Bitrate de áudio: máx. 128 bps.</t>
-        </is>
-      </c>
+      <c r="G286" s="2" t="n"/>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>Protocolo RTMP; codec de vídeo H.264/AVC; codec de áudio AAC-LC. Encoders suportados: OBS, Wirecast, Restream, Golightstream, Socialive, Teradek, Elemental, Vmix, StreamYard, Streamlabs.</t>
-        </is>
-      </c>
-      <c r="I286" s="2" t="inlineStr">
-        <is>
-          <t>Descrição da página do evento: até 280c (pode incluir links externos). Carousel do evento: até 5 vídeos (live, VOD, GIFs ou fotos — investimento adicional). Timeline post: até 5 termos específicos (palavras-chave, nomes).</t>
-        </is>
-      </c>
+          <t>Conforme o formato subjacente escolhido</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="n"/>
       <c r="J286" s="2" t="n"/>
       <c r="K286" s="3" t="inlineStr">
         <is>
@@ -13789,22 +13773,34 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Timeline Takeover</t>
+          <t>Spotlight Takeover</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>Sem specs próprias — usa as specs do formato subjacente escolhido: Image Ads, Video Ads, Carousel Ads, X Live, Promoted Ads com Conversation Button/Polls, ou Branded Notifications.</t>
-        </is>
-      </c>
-      <c r="F287" s="2" t="n"/>
-      <c r="G287" s="2" t="n"/>
+          <t>Recomendado 1280x720. Companion Promoted Ads: 3 a 6 anúncios obrigatórios (imagem, vídeo, GIF, etc.) para apoiar o trend.</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 5 MB; GIF: máx. 15 MB</t>
+        </is>
+      </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>Conforme o formato subjacente escolhido</t>
-        </is>
-      </c>
-      <c r="I287" s="2" t="n"/>
+          <t>Vídeo MP4 ou imagem estática (ou GIF); entrega via darkpost, só media (cartões não aceites)</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>Nome do trend (obrigatório): máx. 20c; Descrição do trend (opcional, muito recomendado): máx. 30c — evitar frases tipo clickbait ('50% off', 'compre um leve dois').</t>
+        </is>
+      </c>
       <c r="J287" s="2" t="n"/>
       <c r="K287" s="3" t="inlineStr">
         <is>
@@ -13825,43 +13821,35 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Spotlight Takeover</t>
+          <t>Branded Notifications</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1280x720. Companion Promoted Ads: 3 a 6 anúncios obrigatórios (imagem, vídeo, GIF, etc.) para apoiar o trend.</t>
-        </is>
-      </c>
-      <c r="F288" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="G288" s="2" t="inlineStr">
-        <is>
-          <t>Imagem: máx. 5 MB; GIF: máx. 15 MB</t>
-        </is>
-      </c>
+          <t>Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads.</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="n"/>
+      <c r="G288" s="2" t="n"/>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>Vídeo MP4 ou imagem estática (ou GIF); entrega via darkpost, só media (cartões não aceites)</t>
-        </is>
-      </c>
-      <c r="I288" s="2" t="inlineStr">
-        <is>
-          <t>Nome do trend (obrigatório): máx. 20c; Descrição do trend (opcional, muito recomendado): máx. 30c — evitar frases tipo clickbait ('50% off', 'compre um leve dois').</t>
-        </is>
-      </c>
-      <c r="J288" s="2" t="n"/>
+          <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="n"/>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
+        </is>
+      </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://business.x.com/en/advertising/branded-notifications</t>
         </is>
       </c>
     </row>
@@ -13878,35 +13866,31 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Catalog Ad</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Branded Notifications</t>
+          <t>Dynamic Product Ads</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads.</t>
+          <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada).</t>
         </is>
       </c>
       <c r="F289" s="2" t="n"/>
       <c r="G289" s="2" t="n"/>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
+          <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
         </is>
       </c>
       <c r="I289" s="2" t="n"/>
-      <c r="J289" s="2" t="inlineStr">
-        <is>
-          <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
-        </is>
-      </c>
+      <c r="J289" s="2" t="n"/>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/advertising/branded-notifications</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -13923,31 +13907,31 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Catalog Ad</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Product Ads</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="inlineStr">
-        <is>
-          <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada).</t>
-        </is>
-      </c>
+          <t>Conversation Button</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n"/>
       <c r="F290" s="2" t="n"/>
       <c r="G290" s="2" t="n"/>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
-        </is>
-      </c>
-      <c r="I290" s="2" t="n"/>
+          <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media)</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>Conversation Card (post original): texto até 280c, hashtag até 21c (incl. o caracter #). Post pré-preenchido (após clique no CTA): texto até 256c, título até 23c. Thank You post: texto até 23c, URL opcional até 23c.</t>
+        </is>
+      </c>
       <c r="J290" s="2" t="n"/>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#conversation</t>
         </is>
       </c>
     </row>
@@ -13969,118 +13953,122 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Conversation Button</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="n"/>
+          <t>Polls</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção). Pode ter ou não media associada (imagem ou vídeo).</t>
+        </is>
+      </c>
       <c r="F291" s="2" t="n"/>
       <c r="G291" s="2" t="n"/>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media)</t>
+          <t>Feature adicionada a um post, com ou sem media</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>Conversation Card (post original): texto até 280c, hashtag até 21c (incl. o caracter #). Post pré-preenchido (após clique no CTA): texto até 256c, título até 23c. Thank You post: texto até 23c, URL opcional até 23c.</t>
+          <t>Texto do post: até 280c; 2 a 4 opções de resposta, até 25c cada (não conta para os 280c do post).</t>
         </is>
       </c>
       <c r="J291" s="2" t="n"/>
       <c r="K291" s="3" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#conversation</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Polls</t>
+          <t>Prog - Companion Banner (Audio)</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção). Pode ter ou não media associada (imagem ou vídeo).</t>
-        </is>
-      </c>
-      <c r="F292" s="2" t="n"/>
-      <c r="G292" s="2" t="n"/>
+          <t>640x640px</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>Feature adicionada a um post, com ou sem media</t>
-        </is>
-      </c>
-      <c r="I292" s="2" t="inlineStr">
-        <is>
-          <t>Texto do post: até 280c; 2 a 4 opções de resposta, até 25c cada (não conta para os 280c do post).</t>
-        </is>
-      </c>
+          <t>JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="n"/>
       <c r="J292" s="2" t="n"/>
-      <c r="K292" s="3" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
-        </is>
-      </c>
+      <c r="K292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>TopReach</t>
+          <t>Prog - Pre-Roll</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>Combina os placements TopView (primeiro conteúdo ao abrir a app) e Top Feed (primeiro anúncio in-feed no For You), por 1 dia (24h). Sem dayparting. Frequência: 1 impressão por utilizador, por placement (alcance único garantido de frequência 1).</t>
-        </is>
-      </c>
-      <c r="F293" s="2" t="n"/>
-      <c r="G293" s="2" t="n"/>
+          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>10 MB</t>
+        </is>
+      </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>Suporta Spark Ads e Non-Spark Ads (recomendado 1-2 criativos por campanha); Duet/Stitch: Spark Ads segue os toggles do vídeo original, Non-Spark Ads não suportado.</t>
+          <t>Vídeo MP4</t>
         </is>
       </c>
       <c r="I293" s="2" t="n"/>
-      <c r="J293" s="2" t="inlineStr">
-        <is>
-          <t>Objetivo: Reach. Targeting disponível: idade (18+) e localização (país). Tracking de terceiros suportado (impressões e cliques). Landing page: webview standard (HTTPS) ou páginas internas TikTok (Branded Hashtag Challenge, Effect, TikTok Shop) — não suporta redirecionamento automático para app store nem link de TopView para LIVE. Música: mesma política dos in-feed ads reservation (Commercial Music Library ou faixas próprias autorizadas). Permite desativar comentários e download do vídeo. Add-ons: só os disponíveis em ambos os placements (TopView + Top Feed). Som: sempre ativo. Watermark: pode pedir vídeo descarregável sem marca de água.</t>
-        </is>
-      </c>
-      <c r="K293" s="3" t="inlineStr">
-        <is>
-          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
-        </is>
-      </c>
+      <c r="J293" s="2" t="n"/>
+      <c r="K293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -14095,32 +14083,32 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Prog - Companion Banner (Audio)</t>
+          <t>Prog - Connected TV</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>640x640px</t>
+          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>JPEG ou PNG</t>
+          <t>Vídeo MP4</t>
         </is>
       </c>
       <c r="I294" s="2" t="n"/>
@@ -14135,42 +14123,46 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll</t>
+          <t>Prog - Companion Banner (YouTube)</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
+          <t>300x60 (só em desktop)</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>&lt; 150 KB</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>Vídeo MP4</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="I295" s="2" t="n"/>
       <c r="J295" s="2" t="n"/>
-      <c r="K295" s="2" t="n"/>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -14180,40 +14172,40 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n"/>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Prog - Connected TV</t>
+          <t>Prog - Uber Journey Ad</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>Vídeo MP4</t>
-        </is>
-      </c>
-      <c r="I296" s="2" t="n"/>
+          <t>Display: imagens. Video: MP4.</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+        </is>
+      </c>
       <c r="J296" s="2" t="n"/>
       <c r="K296" s="2" t="n"/>
     </row>
@@ -14225,44 +14217,40 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Prog - Companion Banner (YouTube)</t>
+          <t>Prog - Rewarded Video</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>300x60 (só em desktop)</t>
-        </is>
-      </c>
-      <c r="F297" s="2" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
+          <t>Aplica-se só a anúncios de vídeo — o utilizador recebe uma recompensa (ex.: moeda in-app, power-up) depois de ver o anúncio.</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="n"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>&lt; 150 KB</t>
+          <t>Até 10 MB</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
         </is>
       </c>
       <c r="I297" s="2" t="n"/>
       <c r="J297" s="2" t="n"/>
       <c r="K297" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/displayvideo/answer/9166157?hl=en</t>
         </is>
       </c>
     </row>
@@ -14274,42 +14262,46 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="C298" s="2" t="n"/>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>In-Feed Video</t>
+        </is>
+      </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Prog - Uber Journey Ad</t>
+          <t>Prog - Outstream</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
+          <t>Dimensões: mín. 256px no lado maior e no lado menor, exceto 300x250 e 320x180 (exceções aceites). Colocação: só no corpo principal da página (não em sidebar, cabeçalho ou rodapé).</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
+          <t>4:3 ou 16:9 (horizontal); 3:4 ou 9:16 (vertical) — fora destes rácios o anúncio não serve</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+          <t>Até 10 MB</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>Display: imagens. Video: MP4.</t>
-        </is>
-      </c>
-      <c r="I298" s="2" t="inlineStr">
-        <is>
-          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
-        </is>
-      </c>
+          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; só tags VAST (VPAID não suportado); áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="n"/>
       <c r="J298" s="2" t="n"/>
-      <c r="K298" s="2" t="n"/>
+      <c r="K298" s="3" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/3129957?hl=en</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -14322,117 +14314,121 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C299" s="2" t="n"/>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Prog - Rewarded Video</t>
+          <t>Prog - Rich Media</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Aplica-se só a anúncios de vídeo — o utilizador recebe uma recompensa (ex.: moeda in-app, power-up) depois de ver o anúncio.</t>
+          <t>Specs a definir</t>
         </is>
       </c>
       <c r="F299" s="2" t="n"/>
-      <c r="G299" s="2" t="inlineStr">
-        <is>
-          <t>Até 10 MB</t>
-        </is>
-      </c>
-      <c r="H299" s="2" t="inlineStr">
-        <is>
-          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
-        </is>
-      </c>
+      <c r="G299" s="2" t="n"/>
+      <c r="H299" s="2" t="n"/>
       <c r="I299" s="2" t="n"/>
       <c r="J299" s="2" t="n"/>
-      <c r="K299" s="3" t="inlineStr">
-        <is>
-          <t>https://support.google.com/displayvideo/answer/9166157?hl=en</t>
-        </is>
-      </c>
+      <c r="K299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Notícias Ilimitadas</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Notícias Ilimitadas</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Prog - Outstream</t>
+          <t>Window Splash Vídeo</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Dimensões: mín. 256px no lado maior e no lado menor, exceto 300x250 e 320x180 (exceções aceites). Colocação: só no corpo principal da página (não em sidebar, cabeçalho ou rodapé).</t>
+          <t>Imagem: 800x600px. Vídeo (opcional): duração máx. 15s; deixar espaço no centro da imagem para o vídeo.</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>4:3 ou 16:9 (horizontal); 3:4 ou 9:16 (vertical) — fora destes rácios o anúncio não serve</t>
+          <t>16:9 (vídeo)</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Até 10 MB</t>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; só tags VAST (VPAID não suportado); áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I300" s="2" t="n"/>
       <c r="J300" s="2" t="n"/>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>https://support.google.com/displayvideo/answer/3129957?hl=en</t>
+          <t>https://noticiasilimitadas.pt/digital/window-splash-video/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Notícias Ilimitadas</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="n"/>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Prog - Rich Media</t>
+          <t>Intro Full Vídeo</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Specs a definir</t>
-        </is>
-      </c>
-      <c r="F301" s="2" t="n"/>
-      <c r="G301" s="2" t="n"/>
-      <c r="H301" s="2" t="n"/>
+          <t>Duração máx. 15s.</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>16:9 e 9:16</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>MP4, som off por defeito.</t>
+        </is>
+      </c>
       <c r="I301" s="2" t="n"/>
       <c r="J301" s="2" t="n"/>
-      <c r="K301" s="2" t="n"/>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/intro-full-video/</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -14452,34 +14448,34 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Window Splash Vídeo</t>
+          <t>Splash/Intro</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 800x600px. Vídeo (opcional): duração máx. 15s; deixar espaço no centro da imagem para o vídeo.</t>
+          <t>Imagem: 1024x600px (ou 800x600px) + 480x640px; para campanhas programáticas: 800x600px + 320x480px; em HTML5, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>16:9 (vídeo)</t>
+          <t>16:9 e 9:16 (vídeo)</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I302" s="2" t="n"/>
       <c r="J302" s="2" t="n"/>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/window-splash-video/</t>
+          <t>https://noticiasilimitadas.pt/digital/splash-intro/</t>
         </is>
       </c>
     </row>
@@ -14496,39 +14492,39 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Intro Full Vídeo</t>
+          <t>Vídeo FullScreen TakeOver</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. 15s.</t>
+          <t>Imagem: Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px. Vídeo: duração máx. 15s (medidas recomendadas 1024x600 e 480x640).</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>16:9 e 9:16</t>
+          <t>16:9 e 9:16 (vídeo)</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>MP4, som off por defeito.</t>
+          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I303" s="2" t="n"/>
       <c r="J303" s="2" t="n"/>
       <c r="K303" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/intro-full-video/</t>
+          <t>https://noticiasilimitadas.pt/digital/video-fullscreen-takeover/</t>
         </is>
       </c>
     </row>
@@ -14545,17 +14541,17 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Splash/Intro</t>
+          <t>FullScreen TakeOver</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 1024x600px (ou 800x600px) + 480x640px; para campanhas programáticas: 800x600px + 320x480px; em HTML5, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
+          <t>Imagem: Splash/Intro 1024x600px + 480x640px + 640x480px; Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px; em HTML5 para a Intro, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -14577,7 +14573,7 @@
       <c r="J304" s="2" t="n"/>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/splash-intro/</t>
+          <t>https://noticiasilimitadas.pt/digital/FullScreen-TakeOver/</t>
         </is>
       </c>
     </row>
@@ -14599,34 +14595,30 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Vídeo FullScreen TakeOver</t>
+          <t>TakeOver</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Imagem: Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px. Vídeo: duração máx. 15s (medidas recomendadas 1024x600 e 480x640).</t>
-        </is>
-      </c>
-      <c r="F305" s="2" t="inlineStr">
-        <is>
-          <t>16:9 e 9:16 (vídeo)</t>
-        </is>
-      </c>
+          <t>1260x200px + 728x150px + 320x100px, e também 300x600px ou 300x250px. Pode incluir vídeo (contactar para mais info).</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="n"/>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Máx. 200 KB por ficheiro.</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
+          <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
       <c r="I305" s="2" t="n"/>
       <c r="J305" s="2" t="n"/>
       <c r="K305" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/video-fullscreen-takeover/</t>
+          <t>https://noticiasilimitadas.pt/digital/takeover/</t>
         </is>
       </c>
     </row>
@@ -14643,39 +14635,35 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Skin</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>FullScreen TakeOver</t>
+          <t>Skin (Imagem)</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>Imagem: Splash/Intro 1024x600px + 480x640px + 640x480px; Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px; em HTML5 para a Intro, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
-        </is>
-      </c>
-      <c r="F306" s="2" t="inlineStr">
-        <is>
-          <t>16:9 e 9:16 (vídeo)</t>
-        </is>
-      </c>
+          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="n"/>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Máx. 200 KB por imagem.</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
+          <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
       <c r="I306" s="2" t="n"/>
       <c r="J306" s="2" t="n"/>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/FullScreen-TakeOver/</t>
+          <t>https://noticiasilimitadas.pt/digital/skin/</t>
         </is>
       </c>
     </row>
@@ -14692,35 +14680,39 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Skin</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>TakeOver</t>
+          <t>Skin Vídeo</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>1260x200px + 728x150px + 320x100px, e também 300x600px ou 300x250px. Pode incluir vídeo (contactar para mais info).</t>
-        </is>
-      </c>
-      <c r="F307" s="2" t="n"/>
+          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px (deixar espaço na imagem de topo para o vídeo). Laterais não devem conter informação relevante. Vídeo: duração máx. 30s.</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB por ficheiro.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5.</t>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I307" s="2" t="n"/>
       <c r="J307" s="2" t="n"/>
       <c r="K307" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/takeover/</t>
+          <t>https://noticiasilimitadas.pt/digital/skin-video/</t>
         </is>
       </c>
     </row>
@@ -14742,12 +14734,12 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Skin (Imagem)</t>
+          <t>Skin Invertida</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+          <t>2 imagens laterais 310x1080px + 1 imagem de fundo 1300x250px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
         </is>
       </c>
       <c r="F308" s="2" t="n"/>
@@ -14765,7 +14757,7 @@
       <c r="J308" s="2" t="n"/>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/skin/</t>
+          <t>https://noticiasilimitadas.pt/digital/skin-invertida/</t>
         </is>
       </c>
     </row>
@@ -14787,17 +14779,17 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Skin Vídeo</t>
+          <t>Skin Mobile</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px (deixar espaço na imagem de topo para o vídeo). Laterais não devem conter informação relevante. Vídeo: duração máx. 30s.</t>
+          <t>2 imagens 320x100px + 1 imagem 300x600px (pode ter vídeo, deixar espaço na imagem 300x600 para o vídeo). Vídeo (opcional): duração máx. recomendada 15s.</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>16:9 (vídeo)</t>
+          <t>16:9 e 9:16 (vídeo)</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
@@ -14807,14 +14799,14 @@
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
       <c r="I309" s="2" t="n"/>
       <c r="J309" s="2" t="n"/>
       <c r="K309" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/skin-video/</t>
+          <t>https://noticiasilimitadas.pt/digital/skin-mobile/</t>
         </is>
       </c>
     </row>
@@ -14831,23 +14823,23 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Parallax</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Skin Invertida</t>
+          <t>Parallax</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>2 imagens laterais 310x1080px + 1 imagem de fundo 1300x250px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+          <t>320x600px</t>
         </is>
       </c>
       <c r="F310" s="2" t="n"/>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB por imagem.</t>
+          <t>Máx. 200 KB.</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14859,7 +14851,7 @@
       <c r="J310" s="2" t="n"/>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/skin-invertida/</t>
+          <t>https://noticiasilimitadas.pt/digital/parallax/</t>
         </is>
       </c>
     </row>
@@ -14876,39 +14868,31 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Skin Mobile</t>
+          <t>Carrossel</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>2 imagens 320x100px + 1 imagem 300x600px (pode ter vídeo, deixar espaço na imagem 300x600 para o vídeo). Vídeo (opcional): duração máx. recomendada 15s.</t>
-        </is>
-      </c>
-      <c r="F311" s="2" t="inlineStr">
-        <is>
-          <t>16:9 e 9:16 (vídeo)</t>
-        </is>
-      </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
-        </is>
-      </c>
-      <c r="H311" s="2" t="inlineStr">
-        <is>
-          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
-        </is>
-      </c>
-      <c r="I311" s="2" t="n"/>
+          <t>Mín. 3 imagens, 320x320px cada; logótipo da marca 160x50px.</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="n"/>
+      <c r="G311" s="2" t="n"/>
+      <c r="H311" s="2" t="n"/>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 40c; Descrição: máx. 35c; Texto do botão CTA (ex.: Saber mais, Comprar agora, Reserve já, Entre em contacto).</t>
+        </is>
+      </c>
       <c r="J311" s="2" t="n"/>
       <c r="K311" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/skin-mobile/</t>
+          <t>https://noticiasilimitadas.pt/digital/carrossel/</t>
         </is>
       </c>
     </row>
@@ -14925,35 +14909,39 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Parallax</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Parallax</t>
+          <t>FlipBook Ad</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>320x600px</t>
-        </is>
-      </c>
-      <c r="F312" s="2" t="n"/>
+          <t>2 imagens: 300x600px (versão colapsada) + 600x600px (versão expandida) — deixar espaço na imagem expandida para o vídeo. Vídeo (opcional): duração máx. 30s.</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB.</t>
+          <t>Imagem: máx. 100 KB por imagem. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF.</t>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I312" s="2" t="n"/>
       <c r="J312" s="2" t="n"/>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/parallax/</t>
+          <t>https://noticiasilimitadas.pt/digital/flipbook/</t>
         </is>
       </c>
     </row>
@@ -14970,31 +14958,35 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Cubo</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Carrossel</t>
+          <t>Mrec Cubo 3D</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>Mín. 3 imagens, 320x320px cada; logótipo da marca 160x50px.</t>
+          <t>4 a 6 imagens, 300x300px cada.</t>
         </is>
       </c>
       <c r="F313" s="2" t="n"/>
-      <c r="G313" s="2" t="n"/>
-      <c r="H313" s="2" t="n"/>
-      <c r="I313" s="2" t="inlineStr">
-        <is>
-          <t>Título: máx. 40c; Descrição: máx. 35c; Texto do botão CTA (ex.: Saber mais, Comprar agora, Reserve já, Entre em contacto).</t>
-        </is>
-      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG.</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="n"/>
       <c r="J313" s="2" t="n"/>
       <c r="K313" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/carrossel/</t>
+          <t>https://noticiasilimitadas.pt/digital/mrec-cubo-3d/</t>
         </is>
       </c>
     </row>
@@ -15011,39 +15003,35 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>Cubo</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>FlipBook Ad</t>
+          <t>Half Page Cubo 3D</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>2 imagens: 300x600px (versão colapsada) + 600x600px (versão expandida) — deixar espaço na imagem expandida para o vídeo. Vídeo (opcional): duração máx. 30s.</t>
-        </is>
-      </c>
-      <c r="F314" s="2" t="inlineStr">
-        <is>
-          <t>16:9 (vídeo)</t>
-        </is>
-      </c>
+          <t>3 a 6 imagens, 300x600px cada.</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="n"/>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 100 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Máx. 100 KB por imagem.</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+          <t>JPG ou PNG.</t>
         </is>
       </c>
       <c r="I314" s="2" t="n"/>
       <c r="J314" s="2" t="n"/>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/flipbook/</t>
+          <t>https://noticiasilimitadas.pt/digital/half-page-cubo-3d/</t>
         </is>
       </c>
     </row>
@@ -15060,35 +15048,39 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Cubo</t>
+          <t>Ticker</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Mrec Cubo 3D</t>
+          <t>Ticker Expandido</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>4 a 6 imagens, 300x300px cada.</t>
-        </is>
-      </c>
-      <c r="F315" s="2" t="n"/>
+          <t>1260x300px + 728x300px + 320x200px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 KB por imagem.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>JPG ou PNG.</t>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
       <c r="I315" s="2" t="n"/>
       <c r="J315" s="2" t="n"/>
       <c r="K315" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/mrec-cubo-3d/</t>
+          <t>https://noticiasilimitadas.pt/digital/ticker/</t>
         </is>
       </c>
     </row>
@@ -15105,35 +15097,39 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Cubo</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Half Page Cubo 3D</t>
+          <t>Spot TV</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>3 a 6 imagens, 300x600px cada.</t>
-        </is>
-      </c>
-      <c r="F316" s="2" t="n"/>
+          <t>Duração máx. recomendada 15s.</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 KB por imagem.</t>
+          <t>Máx. 2 MB.</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>JPG ou PNG.</t>
+          <t>MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I316" s="2" t="n"/>
       <c r="J316" s="2" t="n"/>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/half-page-cubo-3d/</t>
+          <t>https://noticiasilimitadas.pt/digital/spot-tv/</t>
         </is>
       </c>
     </row>
@@ -15150,22 +15146,22 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Ticker</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Ticker Expandido</t>
+          <t>Flip Ad</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>1260x300px + 728x300px + 320x200px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
+          <t>1024x600px (ou 800x600px) + 480x640px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>16:9 (vídeo)</t>
+          <t>16:9 e 9:16 (vídeo)</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
@@ -15182,7 +15178,7 @@
       <c r="J317" s="2" t="n"/>
       <c r="K317" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/ticker/</t>
+          <t>https://noticiasilimitadas.pt/digital/flip-ad/</t>
         </is>
       </c>
     </row>
@@ -15199,39 +15195,35 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Spot TV</t>
+          <t>Overslide</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 15s.</t>
-        </is>
-      </c>
-      <c r="F318" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>2 imagens: 300x600px + 150x300px.</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="n"/>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 200 KB por imagem.</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>MP4, som off por defeito.</t>
+          <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
       <c r="I318" s="2" t="n"/>
       <c r="J318" s="2" t="n"/>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/spot-tv/</t>
+          <t>https://noticiasilimitadas.pt/digital/overslide/</t>
         </is>
       </c>
     </row>
@@ -15253,34 +15245,34 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Flip Ad</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>1024x600px (ou 800x600px) + 480x640px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
+          <t>600x500px. Vídeo (opcional): 600x500px, ou usar o rácio 16:9; duração máx. 15s; deixar espaço na imagem para o vídeo se usados em conjunto.</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>16:9 e 9:16 (vídeo)</t>
+          <t>16:9 (vídeo, alternativa às dimensões fixas)</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
+          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4.</t>
         </is>
       </c>
       <c r="I319" s="2" t="n"/>
       <c r="J319" s="2" t="n"/>
       <c r="K319" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/flip-ad/</t>
+          <t>https://noticiasilimitadas.pt/digital/layer/</t>
         </is>
       </c>
     </row>
@@ -15297,35 +15289,39 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Overslide</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2 imagens: 300x600px + 150x300px.</t>
-        </is>
-      </c>
-      <c r="F320" s="2" t="n"/>
+          <t>Área fechada: 200x200px; área aberta: 850x650px. Não colocar informação no canto superior direito de nenhuma das duas imagens (fica coberto pela aba). Vídeo (opcional): duração máx. 20s; deixar espaço na imagem aberta para o vídeo.</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB por imagem.</t>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF.</t>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I320" s="2" t="n"/>
       <c r="J320" s="2" t="n"/>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/overslide/</t>
+          <t>https://noticiasilimitadas.pt/digital/peel-off/</t>
         </is>
       </c>
     </row>
@@ -15347,34 +15343,30 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Push Down</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>600x500px. Vídeo (opcional): 600x500px, ou usar o rácio 16:9; duração máx. 15s; deixar espaço na imagem para o vídeo se usados em conjunto.</t>
-        </is>
-      </c>
-      <c r="F321" s="2" t="inlineStr">
-        <is>
-          <t>16:9 (vídeo, alternativa às dimensões fixas)</t>
-        </is>
-      </c>
+          <t>(1260x100px + 1260x370px) + (728x100px + 728x300px) + (320x100px + 320x250px).</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="n"/>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+          <t>Máx. 200 KB por ficheiro.</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4.</t>
+          <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
       <c r="I321" s="2" t="n"/>
       <c r="J321" s="2" t="n"/>
       <c r="K321" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/layer/</t>
+          <t>https://noticiasilimitadas.pt/digital/push-down/</t>
         </is>
       </c>
     </row>
@@ -15391,39 +15383,35 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Audio Ad</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Áudio Ad</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>Área fechada: 200x200px; área aberta: 850x650px. Não colocar informação no canto superior direito de nenhuma das duas imagens (fica coberto pela aba). Vídeo (opcional): duração máx. 20s; deixar espaço na imagem aberta para o vídeo.</t>
-        </is>
-      </c>
-      <c r="F322" s="2" t="inlineStr">
-        <is>
-          <t>16:9 (vídeo)</t>
-        </is>
-      </c>
+          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="n"/>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+          <t>Máx. 100 MB.</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+          <t>MP3.</t>
         </is>
       </c>
       <c r="I322" s="2" t="n"/>
       <c r="J322" s="2" t="n"/>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/peel-off/</t>
+          <t>https://noticiasilimitadas.pt/digital/audio-ad/</t>
         </is>
       </c>
     </row>
@@ -15440,35 +15428,39 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Push Down</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>(1260x100px + 1260x370px) + (728x100px + 728x300px) + (320x100px + 320x250px).</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="n"/>
+          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB por ficheiro.</t>
+          <t>Máx. 100 MB.</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF.</t>
+          <t>MP4.</t>
         </is>
       </c>
       <c r="I323" s="2" t="n"/>
       <c r="J323" s="2" t="n"/>
       <c r="K323" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/push-down/</t>
+          <t>https://noticiasilimitadas.pt/digital/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -15485,20 +15477,24 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Audio Ad</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Áudio Ad</t>
+          <t>InContent Sticky</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
-        </is>
-      </c>
-      <c r="F324" s="2" t="n"/>
+          <t>Duração máx. recomendada 20s.</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
           <t>Máx. 100 MB.</t>
@@ -15506,14 +15502,14 @@
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>MP3.</t>
+          <t>MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I324" s="2" t="n"/>
       <c r="J324" s="2" t="n"/>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/audio-ad/</t>
+          <t>https://noticiasilimitadas.pt/digital/incontent-sticky/</t>
         </is>
       </c>
     </row>
@@ -15530,17 +15526,17 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>InContent</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
+          <t>Duração máx. recomendada 20s.</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
@@ -15555,14 +15551,14 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>MP4.</t>
+          <t>MP4, som off por defeito.</t>
         </is>
       </c>
       <c r="I325" s="2" t="n"/>
       <c r="J325" s="2" t="n"/>
       <c r="K325" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/pre-roll/</t>
+          <t>https://noticiasilimitadas.pt/digital/incontent/</t>
         </is>
       </c>
     </row>
@@ -15579,39 +15575,35 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>InContent Sticky</t>
+          <t>Superboard/Billboard</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s.</t>
-        </is>
-      </c>
-      <c r="F326" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>1260x200px + 728x150px + 320x100px, ou 970x250px + 728x90px + 320x50px.</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="n"/>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB.</t>
+          <t>Máx. 200 KB por ficheiro.</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>MP4, som off por defeito.</t>
+          <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
       <c r="I326" s="2" t="n"/>
       <c r="J326" s="2" t="n"/>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/incontent-sticky/</t>
+          <t>https://noticiasilimitadas.pt/digital/superboard/</t>
         </is>
       </c>
     </row>
@@ -15628,39 +15620,35 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>InContent</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s.</t>
-        </is>
-      </c>
-      <c r="F327" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>300x250px</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="n"/>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB.</t>
+          <t>Máx. 150 KB.</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>MP4, som off por defeito.</t>
+          <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
       <c r="I327" s="2" t="n"/>
       <c r="J327" s="2" t="n"/>
       <c r="K327" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/incontent/</t>
+          <t>https://noticiasilimitadas.pt/digital/mrec/</t>
         </is>
       </c>
     </row>
@@ -15677,23 +15665,23 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Superboard/Billboard</t>
+          <t>Half Page</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>1260x200px + 728x150px + 320x100px, ou 970x250px + 728x90px + 320x50px.</t>
+          <t>300x600px</t>
         </is>
       </c>
       <c r="F328" s="2" t="n"/>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB por ficheiro.</t>
+          <t>Máx. 200 KB.</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -15705,7 +15693,7 @@
       <c r="J328" s="2" t="n"/>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/superboard/</t>
+          <t>https://noticiasilimitadas.pt/digital/half-page/</t>
         </is>
       </c>
     </row>
@@ -15722,23 +15710,23 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Megapub</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>300x250px</t>
+          <t>1260x370px + 728x338px + 320x239px. Se tiver vídeo, deixar espaço nas imagens.</t>
         </is>
       </c>
       <c r="F329" s="2" t="n"/>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>Máx. 150 KB.</t>
+          <t>Máx. 200 KB por ficheiro.</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -15750,7 +15738,7 @@
       <c r="J329" s="2" t="n"/>
       <c r="K329" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/mrec/</t>
+          <t>https://noticiasilimitadas.pt/digital/megapub/</t>
         </is>
       </c>
     </row>
@@ -15767,35 +15755,39 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Half Page</t>
+          <t>Mrec Vídeo</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>300x600px</t>
-        </is>
-      </c>
-      <c r="F330" s="2" t="n"/>
+          <t>300x250px, ou o rácio 16:9.</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (alternativa a 300x250px)</t>
+        </is>
+      </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB.</t>
+          <t>Máx. 3 MB.</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5.</t>
+          <t>MP4.</t>
         </is>
       </c>
       <c r="I330" s="2" t="n"/>
       <c r="J330" s="2" t="n"/>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/half-page/</t>
+          <t>https://noticiasilimitadas.pt/digital/mrec-video/</t>
         </is>
       </c>
     </row>
@@ -15812,35 +15804,35 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Megapub</t>
+          <t>Half Page Vídeo (Imagem + Vídeo)</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>1260x370px + 728x338px + 320x239px. Se tiver vídeo, deixar espaço nas imagens.</t>
+          <t>300x600px.</t>
         </is>
       </c>
       <c r="F331" s="2" t="n"/>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 KB por ficheiro.</t>
+          <t>Imagem: máx. 150 KB. Vídeo: máx. 2 MB.</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5.</t>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
       <c r="I331" s="2" t="n"/>
       <c r="J331" s="2" t="n"/>
       <c r="K331" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/megapub/</t>
+          <t>https://noticiasilimitadas.pt/digital/half-page-video/</t>
         </is>
       </c>
     </row>
@@ -15857,27 +15849,27 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Mrec Vídeo</t>
+          <t>Half Page Full Vídeo</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>300x250px, ou o rácio 16:9.</t>
+          <t>300x600px, ou o rácio 9:16.</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>16:9 (alternativa a 300x250px)</t>
+          <t>9:16 (alternativa a 300x600px)</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>Máx. 3 MB.</t>
+          <t>Máx. 2 MB.</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -15889,7 +15881,7 @@
       <c r="J332" s="2" t="n"/>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/mrec-video/</t>
+          <t>https://noticiasilimitadas.pt/digital/half-page-full-video/</t>
         </is>
       </c>
     </row>
@@ -15906,35 +15898,31 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Half Page Vídeo (Imagem + Vídeo)</t>
+          <t>Social Card</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>300x600px.</t>
+          <t>Sem dimensão fixa — usa o post/link social já publicado.</t>
         </is>
       </c>
       <c r="F333" s="2" t="n"/>
-      <c r="G333" s="2" t="inlineStr">
-        <is>
-          <t>Imagem: máx. 150 KB. Vídeo: máx. 2 MB.</t>
-        </is>
-      </c>
+      <c r="G333" s="2" t="n"/>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
+          <t>Link social do Facebook, Instagram, X (Twitter) ou LinkedIn.</t>
         </is>
       </c>
       <c r="I333" s="2" t="n"/>
       <c r="J333" s="2" t="n"/>
       <c r="K333" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/half-page-video/</t>
+          <t>https://noticiasilimitadas.pt/digital/social-card/</t>
         </is>
       </c>
     </row>
@@ -15951,39 +15939,35 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Gallery</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Half Page Full Vídeo</t>
+          <t>Filmstrip</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>300x600px, ou o rácio 9:16.</t>
-        </is>
-      </c>
-      <c r="F334" s="2" t="inlineStr">
-        <is>
-          <t>9:16 (alternativa a 300x600px)</t>
-        </is>
-      </c>
+          <t>2 a 5 imagens, 300x600px cada.</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="n"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 100 KB por imagem.</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>MP4.</t>
+          <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
       <c r="I334" s="2" t="n"/>
       <c r="J334" s="2" t="n"/>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/half-page-full-video/</t>
+          <t>https://noticiasilimitadas.pt/digital/filmstrip/</t>
         </is>
       </c>
     </row>
@@ -16000,214 +15984,210 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Newsletter Banner</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Social Card</t>
+          <t>Newsletter</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>Sem dimensão fixa — usa o post/link social já publicado.</t>
+          <t>2 imagens: 300x250px + 640x124px.</t>
         </is>
       </c>
       <c r="F335" s="2" t="n"/>
-      <c r="G335" s="2" t="n"/>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por imagem.</t>
+        </is>
+      </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>Link social do Facebook, Instagram, X (Twitter) ou LinkedIn.</t>
+          <t>JPG (formato estático).</t>
         </is>
       </c>
       <c r="I335" s="2" t="n"/>
-      <c r="J335" s="2" t="n"/>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>Só suporta tag de clicks (não é possível usar tag de impressões).</t>
+        </is>
+      </c>
       <c r="K335" s="3" t="inlineStr">
         <is>
-          <t>https://noticiasilimitadas.pt/digital/social-card/</t>
+          <t>https://noticiasilimitadas.pt/digital/newsletter/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Notícias Ilimitadas</t>
+          <t>Azerion</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Notícias Ilimitadas</t>
+          <t>WeTransfer</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Gallery</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Filmstrip</t>
+          <t>Static Starter</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2 a 5 imagens, 300x600px cada.</t>
-        </is>
-      </c>
-      <c r="F336" s="2" t="n"/>
-      <c r="G336" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB por imagem.</t>
-        </is>
-      </c>
+          <t>Ficheiro PSD 2560x1600px (perfil de cores RGB). 3 elementos gráficos em layers: imagem de fundo; copy (em imagem ou texto); logo.</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>8:5</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="n"/>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF.</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="I336" s="2" t="n"/>
-      <c r="J336" s="2" t="n"/>
-      <c r="K336" s="3" t="inlineStr">
-        <is>
-          <t>https://noticiasilimitadas.pt/digital/filmstrip/</t>
-        </is>
-      </c>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>Opções de layout: fundo com copy (base); + CTA à esquerda ou à direita (opcional); + logo no topo, à esquerda ou à direita. Suporte com tracking DCM. Ver ficha técnica adicional fornecida pelo meio ("We Transfer", não disponibilizada aqui).</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Notícias Ilimitadas</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Notícias Ilimitadas</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Newsletter Banner</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Newsletter</t>
+          <t>Display Ads</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>2 imagens: 300x250px + 640x124px.</t>
-        </is>
-      </c>
-      <c r="F337" s="2" t="n"/>
-      <c r="G337" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200 KB por imagem.</t>
-        </is>
-      </c>
+          <t>480x320px, 320x480px, 320x50px, 300x250px ou 640x360px. Máx. 1024px no lado maior; recomendado mín. 512px no lado maior, mantendo o aspect ratio.</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>3:2, 2:3, 6.4:1, 6:5 ou 16:9 (consoante o tamanho escolhido)</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="n"/>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>JPG (formato estático).</t>
+          <t>PNG, JPG ou BMP (também aceite em GIF, redimensionado automaticamente pela Anzu).</t>
         </is>
       </c>
       <c r="I337" s="2" t="n"/>
       <c r="J337" s="2" t="inlineStr">
         <is>
-          <t>Só suporta tag de clicks (não é possível usar tag de impressões).</t>
-        </is>
-      </c>
-      <c r="K337" s="3" t="inlineStr">
-        <is>
-          <t>https://noticiasilimitadas.pt/digital/newsletter/</t>
-        </is>
-      </c>
+          <t>Suporte com tracking DCM. Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox. Ver ficheiro técnico adicional fornecido pelo meio (não disponibilizado aqui).</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Azerion</t>
+          <t>OLX</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>WeTransfer</t>
+          <t>OLX</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Static Starter</t>
+          <t>Homepage Leaderboard</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>Ficheiro PSD 2560x1600px (perfil de cores RGB). 3 elementos gráficos em layers: imagem de fundo; copy (em imagem ou texto); logo.</t>
-        </is>
-      </c>
-      <c r="F338" s="2" t="inlineStr">
-        <is>
-          <t>8:5</t>
-        </is>
-      </c>
-      <c r="G338" s="2" t="n"/>
+          <t>320x100px</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="n"/>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>JPEG, JPG, PNG, GIF ou HTML5 (GWD)</t>
         </is>
       </c>
       <c r="I338" s="2" t="n"/>
-      <c r="J338" s="2" t="inlineStr">
-        <is>
-          <t>Opções de layout: fundo com copy (base); + CTA à esquerda ou à direita (opcional); + logo no topo, à esquerda ou à direita. Suporte com tracking DCM. Ver ficha técnica adicional fornecida pelo meio ("We Transfer", não disponibilizada aqui).</t>
-        </is>
-      </c>
+      <c r="J338" s="2" t="n"/>
       <c r="K338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Azerion</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Azerion</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>Skin</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Display Ads</t>
+          <t>Skin</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>480x320px, 320x480px, 320x50px, 300x250px ou 640x360px. Máx. 1024px no lado maior; recomendado mín. 512px no lado maior, mantendo o aspect ratio.</t>
-        </is>
-      </c>
-      <c r="F339" s="2" t="inlineStr">
-        <is>
-          <t>3:2, 2:3, 6.4:1, 6:5 ou 16:9 (consoante o tamanho escolhido)</t>
-        </is>
-      </c>
+          <t>Ficheiros de trabalho necessários: banners laterais em PSD, fontes (fonts), copies e color book/codes.</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="n"/>
       <c r="G339" s="2" t="n"/>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>PNG, JPG ou BMP (também aceite em GIF, redimensionado automaticamente pela Anzu).</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="I339" s="2" t="n"/>
       <c r="J339" s="2" t="inlineStr">
         <is>
-          <t>Suporte com tracking DCM. Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox. Ver ficheiro técnico adicional fornecido pelo meio (não disponibilizado aqui).</t>
+          <t>Os banners laterais podem ser iguais ou diferentes, ao critério do cliente. Suporte com tracking DCM. O meio ajuda a produzir a versão final — se houver elementos extra com que possa trabalhar para enriquecer o formato, enviar os ficheiros editáveis. As dimensões exatas dos banners laterais constam numa folha técnica adicional fornecida pelo meio (não disponibilizada aqui).</t>
         </is>
       </c>
       <c r="K339" s="2" t="n"/>
@@ -16215,132 +16195,116 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>Azerion</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>Azerion</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Homepage Leaderboard</t>
-        </is>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>320x100px</t>
-        </is>
-      </c>
-      <c r="F340" s="2" t="n"/>
+          <t>Native ad</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="n"/>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>1.91:1, 1.78:1, 1.5:1, 1.33:1 ou 1:1 (pelo menos um obrigatório)</t>
+        </is>
+      </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 200 KB</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>JPEG, JPG, PNG, GIF ou HTML5 (GWD)</t>
-        </is>
-      </c>
-      <c r="I340" s="2" t="n"/>
-      <c r="J340" s="2" t="n"/>
+          <t>Tag (Sizmek, DoubleClick, Weborama, etc.), Imagem (JPG, GIF) ou HTML5 (*)</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>Todos obrigatórios: Short Headline (x2) — máx. 30 caracteres; Long Headline — 90 caracteres; Descrição — 90 caracteres; Business/Brand Name — 25 caracteres.</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>Suporte com tracking DCM.</t>
+        </is>
+      </c>
       <c r="K340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Azerion</t>
+          <t>Bauer</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Azerion</t>
+          <t>Bauer</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>Ficheiros de trabalho necessários: banners laterais em PSD, fontes (fonts), copies e color book/codes.</t>
+          <t>728x90px (Desktop, Tablet)</t>
         </is>
       </c>
       <c r="F341" s="2" t="n"/>
       <c r="G341" s="2" t="n"/>
-      <c r="H341" s="2" t="inlineStr">
-        <is>
-          <t>PSD</t>
-        </is>
-      </c>
+      <c r="H341" s="2" t="n"/>
       <c r="I341" s="2" t="n"/>
-      <c r="J341" s="2" t="inlineStr">
-        <is>
-          <t>Os banners laterais podem ser iguais ou diferentes, ao critério do cliente. Suporte com tracking DCM. O meio ajuda a produzir a versão final — se houver elementos extra com que possa trabalhar para enriquecer o formato, enviar os ficheiros editáveis. As dimensões exatas dos banners laterais constam numa folha técnica adicional fornecida pelo meio (não disponibilizada aqui).</t>
-        </is>
-      </c>
+      <c r="J341" s="2" t="n"/>
       <c r="K341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Azerion</t>
+          <t>Bauer</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Azerion</t>
+          <t>Bauer</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Native ad</t>
-        </is>
-      </c>
-      <c r="E342" s="2" t="n"/>
-      <c r="F342" s="2" t="inlineStr">
-        <is>
-          <t>1.91:1, 1.78:1, 1.5:1, 1.33:1 ou 1:1 (pelo menos um obrigatório)</t>
-        </is>
-      </c>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200 KB</t>
-        </is>
-      </c>
-      <c r="H342" s="2" t="inlineStr">
-        <is>
-          <t>Tag (Sizmek, DoubleClick, Weborama, etc.), Imagem (JPG, GIF) ou HTML5 (*)</t>
-        </is>
-      </c>
-      <c r="I342" s="2" t="inlineStr">
-        <is>
-          <t>Todos obrigatórios: Short Headline (x2) — máx. 30 caracteres; Long Headline — 90 caracteres; Descrição — 90 caracteres; Business/Brand Name — 25 caracteres.</t>
-        </is>
-      </c>
-      <c r="J342" s="2" t="inlineStr">
-        <is>
-          <t>Suporte com tracking DCM.</t>
-        </is>
-      </c>
+          <t>Mobile Leaderboard</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>320x50px (Mobile)</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="n"/>
+      <c r="G342" s="2" t="n"/>
+      <c r="H342" s="2" t="n"/>
+      <c r="I342" s="2" t="n"/>
+      <c r="J342" s="2" t="n"/>
       <c r="K342" s="2" t="n"/>
     </row>
     <row r="343">
@@ -16356,25 +16320,37 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>MREC (mpu)</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>728x90px (Desktop, Tablet)</t>
+          <t>300x250px (All)</t>
         </is>
       </c>
       <c r="F343" s="2" t="n"/>
-      <c r="G343" s="2" t="n"/>
-      <c r="H343" s="2" t="n"/>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>GIF, JPEG ou HTML5</t>
+        </is>
+      </c>
       <c r="I343" s="2" t="n"/>
       <c r="J343" s="2" t="n"/>
-      <c r="K343" s="2" t="n"/>
+      <c r="K343" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#mpu-h4</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -16389,25 +16365,37 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Mobile Leaderboard</t>
+          <t>Billboard (desktop)</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>320x50px (Mobile)</t>
+          <t>970x250px (Desktop)</t>
         </is>
       </c>
       <c r="F344" s="2" t="n"/>
-      <c r="G344" s="2" t="n"/>
-      <c r="H344" s="2" t="n"/>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>GIF, JPEG ou HTML5</t>
+        </is>
+      </c>
       <c r="I344" s="2" t="n"/>
       <c r="J344" s="2" t="n"/>
-      <c r="K344" s="2" t="n"/>
+      <c r="K344" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#bb-h4</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -16422,37 +16410,25 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>MREC (mpu)</t>
+          <t>Mobile Billboard</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>300x250px (All)</t>
+          <t>320x100px (Mobile)</t>
         </is>
       </c>
       <c r="F345" s="2" t="n"/>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 150 KB</t>
-        </is>
-      </c>
-      <c r="H345" s="2" t="inlineStr">
-        <is>
-          <t>GIF, JPEG ou HTML5</t>
-        </is>
-      </c>
+      <c r="G345" s="2" t="n"/>
+      <c r="H345" s="2" t="n"/>
       <c r="I345" s="2" t="n"/>
       <c r="J345" s="2" t="n"/>
-      <c r="K345" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#mpu-h4</t>
-        </is>
-      </c>
+      <c r="K345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -16467,17 +16443,17 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Billboard (desktop)</t>
+          <t>Halfpage (double mpu)</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>970x250px (Desktop)</t>
+          <t>300x600px (All)</t>
         </is>
       </c>
       <c r="F346" s="2" t="n"/>
@@ -16495,7 +16471,7 @@
       <c r="J346" s="2" t="n"/>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#bb-h4</t>
+          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#dmpu-h4</t>
         </is>
       </c>
     </row>
@@ -16512,24 +16488,28 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Mobile Billboard</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>320x100px (Mobile)</t>
+          <t>Responsive (All) — adapta-se ao layout do site.</t>
         </is>
       </c>
       <c r="F347" s="2" t="n"/>
       <c r="G347" s="2" t="n"/>
       <c r="H347" s="2" t="n"/>
       <c r="I347" s="2" t="n"/>
-      <c r="J347" s="2" t="n"/>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio (não disponibilizado aqui).</t>
+        </is>
+      </c>
       <c r="K347" s="2" t="n"/>
     </row>
     <row r="348">
@@ -16545,37 +16525,29 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Interscroller</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Halfpage (double mpu)</t>
+          <t>Mobile Interscroller</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>300x600px (All)</t>
+          <t>300x600px (Mobile)</t>
         </is>
       </c>
       <c r="F348" s="2" t="n"/>
-      <c r="G348" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 250 KB</t>
-        </is>
-      </c>
-      <c r="H348" s="2" t="inlineStr">
-        <is>
-          <t>GIF, JPEG ou HTML5</t>
-        </is>
-      </c>
+      <c r="G348" s="2" t="n"/>
+      <c r="H348" s="2" t="n"/>
       <c r="I348" s="2" t="n"/>
-      <c r="J348" s="2" t="n"/>
-      <c r="K348" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#dmpu-h4</t>
-        </is>
-      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>Servido via tag de terceiros (Mobkoi).</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -16590,17 +16562,17 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Socially Inspired Rich Media</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>Responsive (All) — adapta-se ao layout do site.</t>
+          <t>Multi — formato construído internamente pela Illuminate (Mobile).</t>
         </is>
       </c>
       <c r="F349" s="2" t="n"/>
@@ -16609,7 +16581,7 @@
       <c r="I349" s="2" t="n"/>
       <c r="J349" s="2" t="inlineStr">
         <is>
-          <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio (não disponibilizado aqui).</t>
+          <t>Solução de rich media interativa, otimizada mobile-first, com formatos inspirados em redes sociais, para alcançar utilizadores durante a leitura de conteúdo editorial. Specs técnicas completas num documento à parte ("Social Display RMF Specifications"), não disponibilizado aqui.</t>
         </is>
       </c>
       <c r="K349" s="2" t="n"/>
@@ -16627,26 +16599,30 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Interscroller</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Mobile Interscroller</t>
+          <t>Standard Takeover</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>300x600px (Mobile)</t>
+          <t>Multi (All) — combinação de vários espaços publicitários na página.</t>
         </is>
       </c>
       <c r="F350" s="2" t="n"/>
       <c r="G350" s="2" t="n"/>
-      <c r="H350" s="2" t="n"/>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>Skin/hero images em formato estático: JPG ou PNG.</t>
+        </is>
+      </c>
       <c r="I350" s="2" t="n"/>
       <c r="J350" s="2" t="inlineStr">
         <is>
-          <t>Servido via tag de terceiros (Mobkoi).</t>
+          <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
         </is>
       </c>
       <c r="K350" s="2" t="n"/>
@@ -16664,26 +16640,30 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Socially Inspired Rich Media</t>
+          <t>Hero Takeover</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>Multi — formato construído internamente pela Illuminate (Mobile).</t>
+          <t>Responsive (All).</t>
         </is>
       </c>
       <c r="F351" s="2" t="n"/>
       <c r="G351" s="2" t="n"/>
-      <c r="H351" s="2" t="n"/>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>Skin/hero images em formato estático: JPG ou PNG.</t>
+        </is>
+      </c>
       <c r="I351" s="2" t="n"/>
       <c r="J351" s="2" t="inlineStr">
         <is>
-          <t>Solução de rich media interativa, otimizada mobile-first, com formatos inspirados em redes sociais, para alcançar utilizadores durante a leitura de conteúdo editorial. Specs técnicas completas num documento à parte ("Social Display RMF Specifications"), não disponibilizado aqui.</t>
+          <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
         </is>
       </c>
       <c r="K351" s="2" t="n"/>
@@ -16701,30 +16681,34 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Standard Takeover</t>
-        </is>
-      </c>
-      <c r="E352" s="2" t="inlineStr">
-        <is>
-          <t>Multi (All) — combinação de vários espaços publicitários na página.</t>
-        </is>
-      </c>
-      <c r="F352" s="2" t="n"/>
-      <c r="G352" s="2" t="n"/>
+          <t>In-Article Video</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="n"/>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>Mín. 4 KB, máx. 4 MB</t>
+        </is>
+      </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>Skin/hero images em formato estático: JPG ou PNG.</t>
+          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
       <c r="I352" s="2" t="n"/>
       <c r="J352" s="2" t="inlineStr">
         <is>
-          <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
+          <t>Anúncio de vídeo autónomo entre parágrafos de conteúdo editorial (mobile, tablet e desktop). Reproduz automaticamente quando 50% do anúncio está visível; som desligado por defeito; botão "Learn More" no fundo do anúncio (único elemento clicável).</t>
         </is>
       </c>
       <c r="K352" s="2" t="n"/>
@@ -16742,30 +16726,34 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Hero Takeover</t>
-        </is>
-      </c>
-      <c r="E353" s="2" t="inlineStr">
-        <is>
-          <t>Responsive (All).</t>
-        </is>
-      </c>
-      <c r="F353" s="2" t="n"/>
-      <c r="G353" s="2" t="n"/>
+          <t>Radio Player Pre-Roll</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="n"/>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>Mín. 4 KB, máx. 4 MB</t>
+        </is>
+      </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>Skin/hero images em formato estático: JPG ou PNG.</t>
+          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
       <c r="I353" s="2" t="n"/>
       <c r="J353" s="2" t="inlineStr">
         <is>
-          <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
+          <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer.</t>
         </is>
       </c>
       <c r="K353" s="2" t="n"/>
@@ -16773,44 +16761,52 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Bauer</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Bauer</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>In-Article Video</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="n"/>
+          <t>Prog - Displ.AI+ - Conversacional</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>Mín. 4 KB, máx. 4 MB</t>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
-        </is>
-      </c>
-      <c r="I354" s="2" t="n"/>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>Mensagens + botões de resposta.</t>
+        </is>
+      </c>
       <c r="J354" s="2" t="inlineStr">
         <is>
-          <t>Anúncio de vídeo autónomo entre parágrafos de conteúdo editorial (mobile, tablet e desktop). Reproduz automaticamente quando 50% do anúncio está visível; som desligado por defeito; botão "Learn More" no fundo do anúncio (único elemento clicável).</t>
+          <t>Chat / conversa simulada. Imagens necessárias: 0 (usa avatar do logo). Substituível por asset real: Avatar do chat (círculo) → foto/ícone da marca 96x96 PNG. Emoji 👋 → ícone próprio. Specs do asset: Avatar opcional (círculo, 96x96). Bolhas de chat geradas por CSS. Sem imagens de fundo. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K354" s="2" t="n"/>
@@ -16818,44 +16814,52 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Bauer</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Bauer</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Radio Player Pre-Roll</t>
-        </is>
-      </c>
-      <c r="E355" s="2" t="n"/>
+          <t>Prog - Displ.AI+ - Audiências Game</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+        </is>
+      </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>Mín. 4 KB, máx. 4 MB</t>
+          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
-        </is>
-      </c>
-      <c r="I355" s="2" t="n"/>
+          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>3 labels de audiência (ex: Jovens/Famílias/Profissionais) + enunciado.</t>
+        </is>
+      </c>
       <c r="J355" s="2" t="inlineStr">
         <is>
-          <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer.</t>
+          <t>Drag &amp; drop de mensagens para audiências. Imagens necessárias: 0–3 (ícones de audiência opcionais). Substituível por asset real: Emojis das audiências (👥) → ícones da marca 128x128 PNG transparente. Bins → cores da marca. Specs do asset: Ícones 1:1 PNG transparente 128x128 (opcional; caso contrário emoji). Bins e cartões gerados por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K355" s="2" t="n"/>
@@ -16878,7 +16882,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Conversacional</t>
+          <t>Prog - Displ.AI+ - Scratch</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -16903,12 +16907,12 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>Mensagens + botões de resposta.</t>
+          <t>Pergunta topo + mensagem revelada + CTA.</t>
         </is>
       </c>
       <c r="J356" s="2" t="inlineStr">
         <is>
-          <t>Chat / conversa simulada. Imagens necessárias: 0 (usa avatar do logo). Substituível por asset real: Avatar do chat (círculo) → foto/ícone da marca 96x96 PNG. Emoji 👋 → ícone próprio. Specs do asset: Avatar opcional (círculo, 96x96). Bolhas de chat geradas por CSS. Sem imagens de fundo. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Raspadinha (scratch-to-reveal). Imagens necessárias: 1 imagem-prémio/revelação (recomendado). Substituível por asset real: Camada revelada → imagem real do cliente 300x300. Emojis ✨🔎 → ícones próprios. Specs do asset: Imagem de revelação 300x300 (JPG/PNG). Camada de raspar é CSS/canvas. Imagem por baixo é o asset do cliente. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K356" s="2" t="n"/>
@@ -16931,7 +16935,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Audiências Game</t>
+          <t>Prog - Displ.AI+ - Slider Relevância</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -16956,12 +16960,12 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>3 labels de audiência (ex: Jovens/Famílias/Profissionais) + enunciado.</t>
+          <t>2 labels extremos + enunciado + conclusão.</t>
         </is>
       </c>
       <c r="J357" s="2" t="inlineStr">
         <is>
-          <t>Drag &amp; drop de mensagens para audiências. Imagens necessárias: 0–3 (ícones de audiência opcionais). Substituível por asset real: Emojis das audiências (👥) → ícones da marca 128x128 PNG transparente. Bins → cores da marca. Specs do asset: Ícones 1:1 PNG transparente 128x128 (opcional; caso contrário emoji). Bins e cartões gerados por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Slider comparativo (relevante vs genérico). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones/emojis dos extremos → ícones 96x96 PNG (opcional). Totalmente CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K357" s="2" t="n"/>
@@ -16984,7 +16988,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Scratch</t>
+          <t>Prog - Displ.AI+ - Catch Sinais</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -17009,12 +17013,12 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>Pergunta topo + mensagem revelada + CTA.</t>
+          <t>Enunciado + mensagem final.</t>
         </is>
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>Raspadinha (scratch-to-reveal). Imagens necessárias: 1 imagem-prémio/revelação (recomendado). Substituível por asset real: Camada revelada → imagem real do cliente 300x300. Emojis ✨🔎 → ícones próprios. Specs do asset: Imagem de revelação 300x300 (JPG/PNG). Camada de raspar é CSS/canvas. Imagem por baixo é o asset do cliente. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Apanhar itens que caem (jogo). Imagens necessárias: 0–4 (ícones dos itens, opcional). Substituível por asset real: Itens que caem (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG transparente (opcional; senão emoji). Física/posições por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K358" s="2" t="n"/>
@@ -17037,7 +17041,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Slider Relevância</t>
+          <t>Prog - Displ.AI+ - Puzzle Logo</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -17062,12 +17066,12 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>2 labels extremos + enunciado + conclusão.</t>
+          <t>Instrução + mensagem final.</t>
         </is>
       </c>
       <c r="J359" s="2" t="inlineStr">
         <is>
-          <t>Slider comparativo (relevante vs genérico). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones/emojis dos extremos → ícones 96x96 PNG (opcional). Totalmente CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Puzzle de peças que monta o logótipo. Imagens necessárias: 1 logótipo (obrigatório). Substituível por asset real: Já usa imagem real (logótipo). Fundo das peças → cor/textura da marca (opcional). Specs do asset: Logótipo 240x240 PNG (fundo sólido ou transparente). A imagem é fatiada em peças por CSS. Entregar logo em alta resolução. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
         </is>
       </c>
       <c r="K359" s="2" t="n"/>
@@ -17090,7 +17094,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Catch Sinais</t>
+          <t>Prog - Displ.AI+ - Ligações</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -17115,12 +17119,12 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>Enunciado + mensagem final.</t>
+          <t>Instrução + mensagem final.</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
-          <t>Apanhar itens que caem (jogo). Imagens necessárias: 0–4 (ícones dos itens, opcional). Substituível por asset real: Itens que caem (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG transparente (opcional; senão emoji). Física/posições por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Jogo da memória (pares). Imagens necessárias: 0–6 (faces das cartas, opcional). Substituível por asset real: Faces das cartas (emoji) → imagens/ícones 128x128 (produtos, símbolos da marca). Specs do asset: Ícones/faces 128x128 (opcional; senão emoji). Cartas geradas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K360" s="2" t="n"/>
@@ -17143,7 +17147,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Puzzle Logo</t>
+          <t>Prog - Displ.AI+ - Roda Havas</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -17168,12 +17172,12 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>Instrução + mensagem final.</t>
+          <t>6 labels de segmento + enunciado + resultado.</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>Puzzle de peças que monta o logótipo. Imagens necessárias: 1 logótipo (obrigatório). Substituível por asset real: Já usa imagem real (logótipo). Fundo das peças → cor/textura da marca (opcional). Specs do asset: Logótipo 240x240 PNG (fundo sólido ou transparente). A imagem é fatiada em peças por CSS. Entregar logo em alta resolução. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
+          <t>Roda da sorte / estratégia. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos segmentos → ícones 64x64 PNG. Cores dos segmentos → paleta da marca. Segmentos e cores por CSS. Emojis por segmento. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K361" s="2" t="n"/>
@@ -17196,7 +17200,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Ligações</t>
+          <t>Prog - Displ.AI+ - Hold Ligação</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -17221,12 +17225,12 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>Instrução + mensagem final.</t>
+          <t>Instrução + mensagem ao completar.</t>
         </is>
       </c>
       <c r="J362" s="2" t="inlineStr">
         <is>
-          <t>Jogo da memória (pares). Imagens necessárias: 0–6 (faces das cartas, opcional). Substituível por asset real: Faces das cartas (emoji) → imagens/ícones 128x128 (produtos, símbolos da marca). Specs do asset: Ícones/faces 128x128 (opcional; senão emoji). Cartas geradas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Press-and-hold para carregar. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone central (emoji) → ícone/logo 96x96 PNG (opcional). Totalmente CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K362" s="2" t="n"/>
@@ -17249,7 +17253,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Roda Havas</t>
+          <t>Prog - Displ.AI+ - Swipe Briefing</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -17274,12 +17278,12 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>6 labels de segmento + enunciado + resultado.</t>
+          <t>N afirmações (texto) + resultado.</t>
         </is>
       </c>
       <c r="J363" s="2" t="inlineStr">
         <is>
-          <t>Roda da sorte / estratégia. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos segmentos → ícones 64x64 PNG. Cores dos segmentos → paleta da marca. Segmentos e cores por CSS. Emojis por segmento. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Swipe cards (claro/vago). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ilustrações das cartas → imagens 260x300 (opcional; senão CSS). Cartas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K363" s="2" t="n"/>
@@ -17302,7 +17306,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Hold Ligação</t>
+          <t>Prog - Displ.AI+ - Calculadora Contactos</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -17327,12 +17331,12 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>Instrução + mensagem ao completar.</t>
+          <t>Labels dos campos + enunciado + resultado.</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr">
         <is>
-          <t>Press-and-hold para carregar. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone central (emoji) → ícone/logo 96x96 PNG (opcional). Totalmente CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Calculadora interativa. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones dos campos (emoji) → ícones 48x48 PNG (opcional). Inputs e cálculo por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K364" s="2" t="n"/>
@@ -17355,7 +17359,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Swipe Briefing</t>
+          <t>Prog - Displ.AI+ - Tap Sinais</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -17380,12 +17384,12 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>N afirmações (texto) + resultado.</t>
+          <t>Enunciado + mensagem final.</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr">
         <is>
-          <t>Swipe cards (claro/vago). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ilustrações das cartas → imagens 260x300 (opcional; senão CSS). Cartas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Tap rápido em alvos. Imagens necessárias: 0–4 (ícones-alvo, opcional). Substituível por asset real: Alvos (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG (opcional). Alvos por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K365" s="2" t="n"/>
@@ -17408,7 +17412,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Calculadora Contactos</t>
+          <t>Prog - Displ.AI+ - Procura na Estratégia</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -17433,12 +17437,12 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>Labels dos campos + enunciado + resultado.</t>
+          <t>Enunciado + itens a encontrar (labels) + final.</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
-          <t>Calculadora interativa. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones dos campos (emoji) → ícones 48x48 PNG (opcional). Inputs e cálculo por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Encontra itens (procura visual). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Itens a encontrar (emoji) → ícones/mini-imagens 64x64 PNG. Grelha por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K366" s="2" t="n"/>
@@ -17461,7 +17465,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Tap Sinais</t>
+          <t>Prog - Displ.AI+ - Método Havas</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -17486,12 +17490,12 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>Enunciado + mensagem final.</t>
+          <t>Instrução + mensagem final.</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr">
         <is>
-          <t>Tap rápido em alvos. Imagens necessárias: 0–4 (ícones-alvo, opcional). Substituível por asset real: Alvos (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG (opcional). Alvos por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Simon (sequência de memória). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Pads (cor) → cores da marca. Ícones por pad 64x64 PNG (opcional). Pads e sequência por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K367" s="2" t="n"/>
@@ -17514,7 +17518,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Procura na Estratégia</t>
+          <t>Prog - Displ.AI+ - Palavra</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -17539,12 +17543,12 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>Enunciado + itens a encontrar (labels) + final.</t>
+          <t>Palavra-alvo + pista + mensagem final.</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
-          <t>Encontra itens (procura visual). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Itens a encontrar (emoji) → ícones/mini-imagens 64x64 PNG. Grelha por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Anagrama / ordenar letras. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/pista (emoji) → ícone 96x96 PNG (opcional). Letras por CSS. Definir palavra-chave da campanha. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K368" s="2" t="n"/>
@@ -17567,7 +17571,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Método Havas</t>
+          <t>Prog - Displ.AI+ - Da Marca à Pessoa</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -17592,12 +17596,12 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>Instrução + mensagem final.</t>
+          <t>Labels do percurso + mensagem final.</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
         <is>
-          <t>Simon (sequência de memória). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Pads (cor) → cores da marca. Ícones por pad 64x64 PNG (opcional). Pads e sequência por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Percurso animado marca→pessoa. Imagens necessárias: 0–1 (logótipo no início, opcional). Substituível por asset real: Início do percurso → logótipo 128x128. Fim → foto/ícone 'pessoa' 128x128 (opcional). Specs do asset: Logótipo 128x128 (opcional). Trajeto por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K369" s="2" t="n"/>
@@ -17620,7 +17624,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Palavra</t>
+          <t>Prog - Displ.AI+ - Slot Havas</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -17645,12 +17649,12 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>Palavra-alvo + pista + mensagem final.</t>
+          <t>Enunciado + linha de prémio + resultado.</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>Anagrama / ordenar letras. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/pista (emoji) → ícone 96x96 PNG (opcional). Letras por CSS. Definir palavra-chave da campanha. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Slot machine (3 rolos). Imagens necessárias: 0–3 (símbolos dos rolos, opcional). Substituível por asset real: Símbolos dos rolos (emoji) → 3+ ícones 96x96 PNG transparente (produtos/marca). Specs do asset: Símbolos 96x96 PNG transparente (opcional; senão emoji). Rolos e símbolos por CSS/emoji. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K370" s="2" t="n"/>
@@ -17673,7 +17677,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Da Marca à Pessoa</t>
+          <t>Prog - Displ.AI+ - Verdade/Mito</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -17698,12 +17702,12 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>Labels do percurso + mensagem final.</t>
+          <t>5 afirmações + feedback por afirmação + resultado.</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr">
         <is>
-          <t>Percurso animado marca→pessoa. Imagens necessárias: 0–1 (logótipo no início, opcional). Substituível por asset real: Início do percurso → logótipo 128x128. Fim → foto/ícone 'pessoa' 128x128 (opcional). Specs do asset: Logótipo 128x128 (opcional). Trajeto por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Quiz verdadeiro/falso (5 afirmações). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone das cartas (emoji) → ícone 96x96 PNG (opcional). Verde/vermelho mantêm-se (funcional). Semáforo verde/vermelho é funcional (manter). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K371" s="2" t="n"/>
@@ -17726,7 +17730,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Slot Havas</t>
+          <t>Prog - Displ.AI+ - Diferenças</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -17751,12 +17755,12 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>Enunciado + linha de prémio + resultado.</t>
+          <t>Enunciado + mensagem final.</t>
         </is>
       </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>Slot machine (3 rolos). Imagens necessárias: 0–3 (símbolos dos rolos, opcional). Substituível por asset real: Símbolos dos rolos (emoji) → 3+ ícones 96x96 PNG transparente (produtos/marca). Specs do asset: Símbolos 96x96 PNG transparente (opcional; senão emoji). Rolos e símbolos por CSS/emoji. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Descobre as diferenças. Imagens necessárias: 2 imagens (A e B) — obrigatório se usado. Substituível por asset real: Já usa 2 imagens reais. Cliente envia o par 300x300 (senão versão ilustrada). Specs do asset: 2 imagens 300x300 quase idênticas (JPG/PNG). Se sem imagens do cliente, usa versão ilustrada. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
         </is>
       </c>
       <c r="K372" s="2" t="n"/>
@@ -17779,7 +17783,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Verdade/Mito</t>
+          <t>Prog - Displ.AI+ - Enche o Mapa</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -17804,12 +17808,12 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>5 afirmações + feedback por afirmação + resultado.</t>
+          <t>Enunciado + label + mensagem final.</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>Quiz verdadeiro/falso (5 afirmações). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone das cartas (emoji) → ícone 96x96 PNG (opcional). Verde/vermelho mantêm-se (funcional). Semáforo verde/vermelho é funcional (manter). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Preencher barra/mapa por toques. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/label (emoji) → ícone 96x96 PNG (opcional). Barra por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K373" s="2" t="n"/>
@@ -17832,7 +17836,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Diferenças</t>
+          <t>Prog - Displ.AI+ - Configurador</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -17857,12 +17861,12 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>Enunciado + mensagem final.</t>
+          <t>6 labels de opção + enunciado + resumo.</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>Descobre as diferenças. Imagens necessárias: 2 imagens (A e B) — obrigatório se usado. Substituível por asset real: Já usa 2 imagens reais. Cliente envia o par 300x300 (senão versão ilustrada). Specs do asset: 2 imagens 300x300 quase idênticas (JPG/PNG). Se sem imagens do cliente, usa versão ilustrada. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
+          <t>Seletor de opções (configurar seleção). Imagens necessárias: 0–6 (ícones das opções, opcional). Substituível por asset real: Ícones das opções (emoji) → ícones 96x96 PNG transparente. Cores por opção → paleta da marca. Specs do asset: Ícones 96x96 (opcional; senão emoji). Cores por opção configuráveis. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K374" s="2" t="n"/>
@@ -17885,7 +17889,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Enche o Mapa</t>
+          <t>Prog - Displ.AI+ - Countdown</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -17910,12 +17914,12 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>Enunciado + label + mensagem final.</t>
+          <t>Título + subtítulo + CTA.</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
         <is>
-          <t>Preencher barra/mapa por toques. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/label (emoji) → ícone 96x96 PNG (opcional). Barra por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Contagem decrescente para data-alvo. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/fundo (emoji/CSS) → imagem de fundo 300x600 ou ícone 96x96 (opcional). Definir data-alvo por campanha (JS). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K375" s="2" t="n"/>
@@ -17938,7 +17942,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Configurador</t>
+          <t>Prog - Displ.AI+ - Estimativa</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -17963,12 +17967,12 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>6 labels de opção + enunciado + resumo.</t>
+          <t>Pergunta + valor de referência + resultado.</t>
         </is>
       </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
-          <t>Seletor de opções (configurar seleção). Imagens necessárias: 0–6 (ícones das opções, opcional). Substituível por asset real: Ícones das opções (emoji) → ícones 96x96 PNG transparente. Cores por opção → paleta da marca. Specs do asset: Ícones 96x96 (opcional; senão emoji). Cores por opção configuráveis. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Adivinha o número (slider). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone do enunciado (emoji) → ícone 96x96 PNG (opcional). Slider por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K376" s="2" t="n"/>
@@ -17991,7 +17995,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Countdown</t>
+          <t>Prog - Displ.AI+ - Ranking</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -18016,12 +18020,12 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>Título + subtítulo + CTA.</t>
+          <t>4 itens (labels) + enunciado + confirmação.</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>Contagem decrescente para data-alvo. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/fundo (emoji/CSS) → imagem de fundo 300x600 ou ícone 96x96 (opcional). Definir data-alvo por campanha (JS). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Ordenar prioridades (drag). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos itens (🎯👥…) → ícones 48x48 PNG da marca (opcional). Itens arrastáveis por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K377" s="2" t="n"/>
@@ -18044,7 +18048,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Estimativa</t>
+          <t>Prog - Displ.AI+ - Carrossel Produtos</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -18069,12 +18073,12 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>Pergunta + valor de referência + resultado.</t>
+          <t>Por slide: título + subtítulo + 3 bullets + CTA.</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>Adivinha o número (slider). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone do enunciado (emoji) → ícone 96x96 PNG (opcional). Slider por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Carrossel de produtos/cards. Imagens necessárias: 1 por slide (recomendado 3–5). Substituível por asset real: Já usa imagens reais (1 por slide). Cliente envia 3–5 imagens 300x300. Specs do asset: Imagens de produto 300x300 (JPG/PNG), fundo neutro. Nº de slides configurável. Peso soma todas as imagens. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K378" s="2" t="n"/>
@@ -18097,7 +18101,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Ranking</t>
+          <t>Prog - Displ.AI+ - Parallax</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -18122,12 +18126,12 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>4 itens (labels) + enunciado + confirmação.</t>
+          <t>Título + subtítulo + CTA.</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>Ordenar prioridades (drag). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos itens (🎯👥…) → ícones 48x48 PNG da marca (opcional). Itens arrastáveis por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
+          <t>Cena com camadas parallax. Imagens necessárias: 1–4 camadas (opcional). Substituível por asset real: Camadas ilustradas (CSS) → 1–4 PNG transparentes 420x420 da marca (produto/cena). Specs do asset: Camadas PNG transparente 420x420 (opcional; senão ilustração). Auto-scroll ping-pong. Sem leitura de scroll do host. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
         </is>
       </c>
       <c r="K379" s="2" t="n"/>
@@ -18135,156 +18139,50 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>Branded Content</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Carrossel Produtos</t>
+          <t>Branded Content</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>Por slide: título + subtítulo + 3 bullets + CTA.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
-        <is>
-          <t>Carrossel de produtos/cards. Imagens necessárias: 1 por slide (recomendado 3–5). Substituível por asset real: Já usa imagens reais (1 por slide). Cliente envia 3–5 imagens 300x300. Specs do asset: Imagens de produto 300x300 (JPG/PNG), fundo neutro. Nº de slides configurável. Peso soma todas as imagens. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K380" s="2" t="n"/>
-    </row>
-    <row r="381">
-      <c r="A381" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B381" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C381" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
-      <c r="D381" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Parallax</t>
-        </is>
-      </c>
-      <c r="E381" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F381" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G381" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H381" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="inlineStr">
-        <is>
-          <t>Título + subtítulo + CTA.</t>
-        </is>
-      </c>
-      <c r="J381" s="2" t="inlineStr">
-        <is>
-          <t>Cena com camadas parallax. Imagens necessárias: 1–4 camadas (opcional). Substituível por asset real: Camadas ilustradas (CSS) → 1–4 PNG transparentes 420x420 da marca (produto/cena). Specs do asset: Camadas PNG transparente 420x420 (opcional; senão ilustração). Auto-scroll ping-pong. Sem leitura de scroll do host. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K381" s="2" t="n"/>
-    </row>
-    <row r="382">
-      <c r="A382" s="2" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="B382" s="2" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="C382" s="2" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
-      <c r="D382" s="2" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
-      <c r="E382" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F382" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G382" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H382" s="2" t="inlineStr">
-        <is>
-          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
-        </is>
-      </c>
-      <c r="I382" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J382" s="2" t="inlineStr">
         <is>
           <t>É necessário enviar:
  - data da publicação?
@@ -18303,10 +18201,10 @@
 - logotipo (jpeg pu png) com fundo transparente</t>
         </is>
       </c>
-      <c r="K382" s="2" t="n"/>
+      <c r="K380" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K382"/>
+  <autoFilter ref="A1:K380"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -18544,7 +18442,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K248" r:id="rId235"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K249" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K250" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K251" r:id="rId237"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K252" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K253" r:id="rId239"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K254" r:id="rId240"/>
@@ -18585,11 +18483,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K289" r:id="rId275"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K290" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K291" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K292" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K293" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K297" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K299" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K300" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K295" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K297" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K298" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K300" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K301" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K302" r:id="rId283"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K303" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K304" r:id="rId285"/>
@@ -18624,11 +18522,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K333" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K334" r:id="rId315"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K335" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K336" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K337" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K345" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K346" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K348" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K343" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K344" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K346" r:id="rId319"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21609,7 +21505,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner). Dúvidas: bruno.figueiredo@vs2.pt.</t>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
         </is>
       </c>
       <c r="I2" s="2" t="n"/>
@@ -21648,7 +21544,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner). Dúvidas: bruno.figueiredo@vs2.pt.</t>
+          <t>Áudio: 6 canais (5.1) ou 2 canais (estéreo); ficheiros WAV a 24-bit; sampling 48KHz; nível de referência -20dBFS; velocidade 24fps. Masterização em Dolby Digital Cinema (VS2.0, certified partner).</t>
         </is>
       </c>
       <c r="I3" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -21650,11 +21650,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -21685,11 +21681,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
@@ -21720,11 +21712,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
@@ -21755,11 +21743,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
@@ -21790,11 +21774,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
@@ -21825,11 +21805,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
@@ -21860,11 +21836,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -21895,11 +21867,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 colunas x 16 módulos); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
@@ -21930,11 +21898,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 257x320mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -21965,11 +21929,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
     </row>
     <row r="12">
@@ -22000,11 +21960,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -22035,11 +21991,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
     </row>
     <row r="14">
@@ -22070,11 +22022,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
     </row>
     <row r="15">
@@ -22105,11 +22053,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
     </row>
     <row r="16">
@@ -22140,11 +22084,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
     </row>
     <row r="17">
@@ -22175,11 +22115,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
     </row>
     <row r="18">
@@ -22210,11 +22146,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
     </row>
     <row r="19">
@@ -22245,11 +22177,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sexta-feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
     </row>
     <row r="20">
@@ -22280,11 +22208,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
     </row>
     <row r="21">
@@ -22315,11 +22239,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
     </row>
     <row r="22">
@@ -22350,11 +22270,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
     </row>
     <row r="23">
@@ -22385,11 +22301,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
     </row>
     <row r="24">
@@ -22420,11 +22332,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
     </row>
     <row r="25">
@@ -22455,11 +22363,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
     </row>
     <row r="26">
@@ -22490,11 +22394,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -22525,11 +22425,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
     </row>
     <row r="28">
@@ -22560,11 +22456,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (sábado); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
     </row>
     <row r="29">
@@ -22595,11 +22487,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
     </row>
     <row r="30">
@@ -22630,11 +22518,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
     </row>
     <row r="31">
@@ -22665,11 +22549,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
     </row>
     <row r="32">
@@ -22700,11 +22580,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
     </row>
     <row r="33">
@@ -22735,11 +22611,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
     </row>
     <row r="34">
@@ -22770,11 +22642,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
     </row>
     <row r="35">
@@ -22805,11 +22673,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
     </row>
     <row r="36">
@@ -22840,11 +22704,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
     </row>
     <row r="37">
@@ -22875,11 +22735,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (domingo); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo bright 68 de 52g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
     </row>
     <row r="38">
@@ -22910,11 +22766,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
     </row>
     <row r="39">
@@ -22945,11 +22797,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
     </row>
     <row r="40">
@@ -22980,11 +22828,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
     </row>
     <row r="41">
@@ -23015,11 +22859,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
     </row>
     <row r="42">
@@ -23050,11 +22890,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
     </row>
     <row r="43">
@@ -23085,11 +22921,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
     </row>
     <row r="44">
@@ -23120,11 +22952,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
     </row>
     <row r="45">
@@ -23155,11 +22983,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
     </row>
     <row r="46">
@@ -23190,11 +23014,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
     </row>
     <row r="47">
@@ -23225,11 +23045,7 @@
           <t>PDF, AI, EPS ou TIFF a 300 DPI</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária; mancha de impressão 230x300mm; impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
     </row>
     <row r="48">
@@ -23260,11 +23076,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
     </row>
     <row r="49">
@@ -23295,11 +23107,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
     </row>
     <row r="50">
@@ -23330,11 +23138,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
     </row>
     <row r="51">
@@ -23365,11 +23169,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
     </row>
     <row r="52">
@@ -23400,11 +23200,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
     </row>
     <row r="53">
@@ -23435,11 +23231,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
     </row>
     <row r="54">
@@ -23470,11 +23262,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
     </row>
     <row r="55">
@@ -23505,11 +23293,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a 6ª feira); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
     </row>
     <row r="56">
@@ -23540,11 +23324,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
     </row>
     <row r="57">
@@ -23575,11 +23355,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
     </row>
     <row r="58">
@@ -23610,11 +23386,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
     </row>
     <row r="59">
@@ -23645,11 +23417,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
     </row>
     <row r="60">
@@ -23680,11 +23448,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Formato especial na 1ª página ou última página do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n"/>
     </row>
     <row r="61">
@@ -23715,11 +23479,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
     </row>
     <row r="62">
@@ -23750,11 +23510,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
     </row>
     <row r="63">
@@ -23785,11 +23541,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
     </row>
     <row r="64">
@@ -23820,11 +23572,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
     </row>
     <row r="65">
@@ -23855,11 +23603,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
     </row>
     <row r="66">
@@ -23890,11 +23634,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
     </row>
     <row r="67">
@@ -23925,11 +23665,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
     </row>
     <row r="68">
@@ -23960,11 +23696,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade diária (2ª feira a domingo); distribuição nacional; mancha de impressão 257x320mm (80 módulos, 5 col. x 16 mód.); impressão rotativa offset. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="n"/>
     </row>
     <row r="69">
@@ -23995,11 +23727,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
     </row>
     <row r="70">
@@ -24030,11 +23758,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
     </row>
     <row r="71">
@@ -24065,11 +23789,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
     </row>
     <row r="72">
@@ -24100,11 +23820,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
     </row>
     <row r="73">
@@ -24135,11 +23851,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
     </row>
     <row r="74">
@@ -24170,11 +23882,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
     </row>
     <row r="75">
@@ -24205,11 +23913,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (5ª feira); distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
     </row>
     <row r="76">
@@ -24240,11 +23944,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
     </row>
     <row r="77">
@@ -24275,11 +23975,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="n"/>
     </row>
     <row r="78">
@@ -24310,11 +24006,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
     </row>
     <row r="79">
@@ -24345,11 +24037,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
     </row>
     <row r="80">
@@ -24380,11 +24068,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
     </row>
     <row r="81">
@@ -24415,11 +24099,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
     </row>
     <row r="82">
@@ -24450,11 +24130,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade trimestral; distribuição nacional; mancha de impressão 205x275mm; capa couché 115g, miolo papel mate 60g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
     </row>
     <row r="83">
@@ -24485,11 +24161,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
     </row>
     <row r="84">
@@ -24520,11 +24192,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
     </row>
     <row r="85">
@@ -24555,11 +24223,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
     </row>
     <row r="86">
@@ -24590,11 +24254,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
     </row>
     <row r="87">
@@ -24625,11 +24285,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
     </row>
     <row r="88">
@@ -24660,11 +24316,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
     </row>
     <row r="89">
@@ -24695,11 +24347,7 @@
           <t>PDF, EPS ou TIFF (CMYK) com 300 DPI</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade semanal (6ª feira); distribuição nacional; mancha de impressão 200x295mm; capa couché 115g, miolo LWC 57g; impressão offset em rotativa; trama 150 linhas; acabamento dois pontos de arame. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
     </row>
     <row r="90">
@@ -24730,11 +24378,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="n"/>
     </row>
     <row r="91">
@@ -24765,11 +24409,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="n"/>
     </row>
     <row r="92">
@@ -24800,11 +24440,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
     </row>
     <row r="93">
@@ -24835,11 +24471,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="n"/>
     </row>
     <row r="94">
@@ -24870,11 +24502,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
     </row>
     <row r="95">
@@ -24905,11 +24533,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="n"/>
     </row>
     <row r="96">
@@ -24940,11 +24564,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="n"/>
     </row>
     <row r="97">
@@ -24975,11 +24595,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
     </row>
     <row r="98">
@@ -25010,11 +24626,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
     </row>
     <row r="99">
@@ -25045,11 +24657,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="n"/>
     </row>
     <row r="100">
@@ -25080,11 +24688,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Formato especial de capa do 1º Caderno. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="n"/>
     </row>
     <row r="101">
@@ -25115,11 +24719,7 @@
           <t>PDF em alta definição (elementos de desenho em vetorial, imagens à parte + JPEG para visualização)</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Saco em papel liso impresso a CMYK + 2 cores; a tarja com a informação é sempre na cor do Expresso (Pantone 315C).</t>
-        </is>
-      </c>
+      <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="n"/>
     </row>
     <row r="102">
@@ -25150,11 +24750,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="n"/>
     </row>
     <row r="103">
@@ -25185,11 +24781,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="n"/>
     </row>
     <row r="104">
@@ -25220,11 +24812,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="n"/>
     </row>
     <row r="105">
@@ -25255,11 +24843,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
     </row>
     <row r="106">
@@ -25290,11 +24874,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="n"/>
     </row>
     <row r="107">
@@ -25325,11 +24905,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
     </row>
     <row r="108">
@@ -25360,11 +24936,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
     </row>
     <row r="109">
@@ -25395,11 +24967,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
     </row>
     <row r="110">
@@ -25430,11 +24998,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
     </row>
     <row r="111">
@@ -25465,11 +25029,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
     </row>
     <row r="112">
@@ -25500,11 +25060,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia sem estufa (1º Caderno/Economia) — papel jornal 45g/m²; localização obrigatória: +30%; a preto e branco: -25%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
     </row>
     <row r="113">
@@ -25535,11 +25091,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
     </row>
     <row r="114">
@@ -25570,11 +25122,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
     </row>
     <row r="115">
@@ -25605,11 +25153,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
     </row>
     <row r="116">
@@ -25640,11 +25184,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="n"/>
     </row>
     <row r="117">
@@ -25675,11 +25215,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
     </row>
     <row r="118">
@@ -25710,11 +25246,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="n"/>
     </row>
     <row r="119">
@@ -25745,11 +25277,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
     </row>
     <row r="120">
@@ -25780,11 +25308,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
     </row>
     <row r="121">
@@ -25815,11 +25339,7 @@
           <t>PDF, EPS, TIFF ou JPEG em alta resolução (300 a 400 DPI, CMYK)</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Impressão offset quadricromia — papel jornal melhorado 55g, capa couché mate 130g, lombada colada; localização obrigatória: +30%. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="n"/>
     </row>
     <row r="122">
@@ -25850,11 +25370,7 @@
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="n"/>
     </row>
     <row r="123">
@@ -25885,11 +25401,7 @@
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="n"/>
     </row>
     <row r="124">
@@ -25920,11 +25432,7 @@
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
     </row>
     <row r="125">
@@ -25955,11 +25463,7 @@
           <t>PDF, EPS ou TIFF em alta resolução de 400 DPI (mínimo 300 DPI), CMYK, sem atribuição de perfil final</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Periodicidade bimestral (janeiro, março, maio, julho, setembro, novembro); revista bilingue (português + inglês); distribuição em Portugal e mais 22 países; páginas duplas com desvio de 6mm ao centro (3mm para a esquerda e 3mm para a direita) para garantir o acerto central. Textos convertidos em curvas; cor exclusivamente a preto — títulos excetuados — deve ter só 100% na chapa de preto e abrir a branco nas restantes chapas para evitar falhas de acerto (se preto mais fechado, 100% preto + 70% cyan); acompanhado de prova de cor; materiais entregues em suporte digital (CD/DVD) ou por e-mail.</t>
-        </is>
-      </c>
+      <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
     </row>
   </sheetData>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -549,11 +549,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Billboard</t>
@@ -594,11 +590,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Cubo</t>
@@ -639,11 +631,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Floor Ad</t>
@@ -684,11 +672,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -733,11 +717,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Header XL</t>
@@ -774,11 +754,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Hero</t>
@@ -819,11 +795,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>In-Article</t>
@@ -868,11 +840,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Interscroller</t>
@@ -917,11 +885,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Interstitial</t>
@@ -966,11 +930,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -1011,11 +971,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mrec Video</t>
@@ -1056,11 +1012,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Push Down</t>
@@ -1105,11 +1057,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -1154,11 +1102,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Video In Stream</t>
@@ -1203,11 +1147,7 @@
           <t>Impresa</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Video Outstream</t>
@@ -1252,11 +1192,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Billboard</t>
@@ -1297,11 +1233,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Billboard XL</t>
@@ -1346,11 +1278,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Carrossel In Content</t>
@@ -1395,11 +1323,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Carrossel Top</t>
@@ -1444,11 +1368,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Dossier</t>
@@ -1493,11 +1413,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Full Frame</t>
@@ -1542,11 +1458,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -1591,11 +1503,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Insterscroll</t>
@@ -1640,11 +1548,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Intro</t>
@@ -1689,11 +1593,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Intro/Splash</t>
@@ -1734,11 +1634,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t>L Frame</t>
@@ -1783,11 +1679,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -1828,11 +1720,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mega Billboard</t>
@@ -1873,11 +1761,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -1918,11 +1802,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Native</t>
@@ -1967,11 +1847,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -2016,11 +1892,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Outstream</t>
@@ -2057,11 +1929,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Page Flip</t>
@@ -2098,11 +1966,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Pop In</t>
@@ -2143,11 +2007,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Post Social Media</t>
@@ -2188,11 +2048,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Pre Roll</t>
@@ -2237,11 +2093,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Pre Roll Vertical</t>
@@ -2286,11 +2138,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Push Down</t>
@@ -2335,11 +2183,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Reel Social Media</t>
@@ -2384,11 +2228,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Side Frame</t>
@@ -2429,11 +2269,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Social Card</t>
@@ -2466,11 +2302,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Splash</t>
@@ -2511,11 +2343,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Story Social Media</t>
@@ -2560,11 +2388,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Takeover</t>
@@ -2605,11 +2429,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
+      <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -2654,11 +2474,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
+      <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Vertical Video</t>
@@ -2703,11 +2519,7 @@
           <t>Media Capital</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Video Wall</t>
@@ -2744,11 +2556,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
+      <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Corner Ad</t>
@@ -2789,11 +2597,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
+      <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Floor Ad</t>
@@ -2834,11 +2638,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -2883,11 +2683,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>In Content</t>
@@ -2932,11 +2728,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Intro</t>
@@ -2981,11 +2773,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Layer</t>
@@ -3026,11 +2814,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -3071,11 +2855,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Masthead</t>
@@ -3116,11 +2896,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Sticky Banner</t>
-        </is>
-      </c>
+      <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Masthead Sticky Companion</t>
@@ -3161,11 +2937,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Moldura</t>
@@ -3202,11 +2974,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -3247,11 +3015,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -3296,11 +3060,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
+      <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Peel Off</t>
@@ -3341,11 +3101,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Pre Roll</t>
@@ -3390,11 +3146,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Showcase Rich Media</t>
@@ -3423,11 +3175,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
+      <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sideticker</t>
@@ -3456,11 +3204,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Slash</t>
@@ -3489,11 +3233,7 @@
           <t>Media Livre</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Topo Extensivel</t>
@@ -3522,11 +3262,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
+      <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Audio Ad</t>
@@ -3563,11 +3299,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Newsletter Banner</t>
-        </is>
-      </c>
+      <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Banner Newsletter</t>
@@ -3608,11 +3340,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Carrossel</t>
@@ -3657,11 +3385,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Compare</t>
@@ -3706,11 +3430,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
+      <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Flipper</t>
@@ -3755,11 +3475,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -3804,11 +3520,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Header XL</t>
@@ -3849,11 +3561,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Interstitial</t>
@@ -3894,11 +3602,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Intro Dynamic</t>
@@ -3939,11 +3643,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Intro Folheto</t>
@@ -3980,11 +3680,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Manchete</t>
@@ -4025,11 +3721,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -4070,11 +3762,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -4111,11 +3799,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Outstream</t>
@@ -4160,11 +3844,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
+      <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Peel Off</t>
@@ -4209,11 +3889,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Pre-Roll</t>
@@ -4258,11 +3934,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
+      <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Skin</t>
@@ -4303,11 +3975,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Sticky Banner</t>
-        </is>
-      </c>
+      <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sticky Dynamic</t>
@@ -4348,11 +4016,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
+      <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sticky Footer</t>
@@ -4393,11 +4057,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sticky Intro</t>
@@ -4442,11 +4102,7 @@
           <t>Observador</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Twin Ad</t>
-        </is>
-      </c>
+      <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Twin Ad</t>
@@ -4491,11 +4147,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
+      <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Ad Selector</t>
@@ -4540,11 +4192,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Barra Topo</t>
@@ -4585,11 +4233,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Barra Topo Extensivel</t>
@@ -4630,11 +4274,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Billboard</t>
@@ -4675,11 +4315,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
+      <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Cubo</t>
@@ -4720,11 +4356,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Floor Ad</t>
-        </is>
-      </c>
+      <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Floor Ad</t>
@@ -4765,11 +4397,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
+      <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Gallery Flip</t>
@@ -4814,11 +4442,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -4863,11 +4487,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Interstitial</t>
@@ -4912,11 +4532,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -4957,11 +4573,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Newsletter Banner</t>
-        </is>
-      </c>
+      <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Newsletter</t>
@@ -5002,11 +4614,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Open Door</t>
@@ -5047,11 +4655,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Parallax</t>
-        </is>
-      </c>
+      <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Parallax</t>
@@ -5096,11 +4700,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -5145,11 +4745,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Scratch</t>
@@ -5194,11 +4790,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
+      <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Shopping Ads</t>
@@ -5243,11 +4835,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
+      <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Slide Door Video</t>
@@ -5292,11 +4880,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
+      <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Slide R Video</t>
@@ -5333,11 +4917,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Takeover XXL</t>
@@ -5378,11 +4958,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
+      <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Top Header Gallery</t>
@@ -5419,11 +4995,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Twin Ad</t>
-        </is>
-      </c>
+      <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Twin Ad</t>
@@ -5464,11 +5036,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Video Incontent</t>
@@ -5513,11 +5081,7 @@
           <t>Público</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Video Pre-Roll</t>
@@ -5562,11 +5126,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
+      <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="inlineStr">
         <is>
           <t>3D Cube (Teads)</t>
@@ -5607,11 +5167,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
           <t>App Install Native (Outbrain)</t>
@@ -5656,11 +5212,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
+      <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Audio Digital (Spotify)</t>
@@ -5697,11 +5249,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
+      <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Audio Mid-Roll</t>
@@ -5738,11 +5286,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
+      <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Audio Post-Roll</t>
@@ -5779,11 +5323,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
+      <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Audio Pre-Roll</t>
@@ -5820,11 +5360,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Billboard 1 e 2 Posição</t>
@@ -5865,11 +5401,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Billboard Carousel</t>
@@ -5914,11 +5446,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Billboard IAB</t>
@@ -5955,11 +5483,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Billboard Responsive</t>
@@ -6000,11 +5524,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
+      <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Branded Content</t>
@@ -6033,11 +5553,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Capa Falsa</t>
@@ -6082,11 +5598,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Carousel (Teads)</t>
@@ -6127,11 +5639,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Carousel Native (Outbrain)</t>
@@ -6176,11 +5684,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Carousel Performance</t>
@@ -6205,11 +5709,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Clip Native (Outbrain)</t>
@@ -6234,11 +5734,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Sticky Banner</t>
-        </is>
-      </c>
+      <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Companion Banner</t>
@@ -6279,11 +5775,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Countdown</t>
-        </is>
-      </c>
+      <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Countdown</t>
@@ -6328,11 +5820,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
+      <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="inlineStr">
         <is>
           <t>CTV - Homescreen</t>
@@ -6357,11 +5845,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
+      <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="inlineStr">
         <is>
           <t>CTV - Pause Ad</t>
@@ -6386,11 +5870,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
+      <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="inlineStr">
         <is>
           <t>CTV - Pre-Roll</t>
@@ -6415,11 +5895,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
+      <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Display Standard (CPC Surf)</t>
@@ -6464,11 +5940,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Drag and Drop (Teads)</t>
@@ -6509,11 +5981,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Flip Flow (Teads)</t>
@@ -6554,11 +6022,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Flow (Teads)</t>
@@ -6599,11 +6063,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Halfpage</t>
@@ -6648,11 +6108,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Halfpage Flip</t>
@@ -6697,11 +6153,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Header XL</t>
@@ -6726,11 +6178,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Header XL Galeria</t>
@@ -6755,11 +6203,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Header XL Galeria Video</t>
@@ -6784,11 +6228,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Header XL Navigation</t>
@@ -6813,11 +6253,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Header XL Video</t>
@@ -6842,11 +6278,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Header XL Widget</t>
@@ -6871,11 +6303,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Header XL Zoom</t>
@@ -6900,11 +6328,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Homepage Takeover (Spotify)</t>
@@ -6949,11 +6373,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Hover (Teads)</t>
@@ -6998,11 +6418,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed</t>
-        </is>
-      </c>
+      <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="inlineStr">
         <is>
           <t>In-feed Display (Spotify)</t>
@@ -7047,11 +6463,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed</t>
-        </is>
-      </c>
+      <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="inlineStr">
         <is>
           <t>In-feed Video (Spotify)</t>
@@ -7080,11 +6492,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Inline Midscroll</t>
@@ -7125,11 +6533,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
+      <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Interscroller Display (Teads)</t>
@@ -7174,11 +6578,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
+      <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Interscroller Video (Teads)</t>
@@ -7223,11 +6623,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Intra</t>
@@ -7272,11 +6668,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Intra Plus</t>
@@ -7317,11 +6709,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Intra Plus Vídeo</t>
@@ -7362,11 +6750,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Intra Vídeo</t>
@@ -7411,11 +6795,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="inlineStr">
         <is>
           <t>In-stream Video (Spotify)</t>
@@ -7460,11 +6840,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Landing Page</t>
-        </is>
-      </c>
+      <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Landing Page</t>
@@ -7493,11 +6869,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -7538,11 +6910,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Landing Page</t>
-        </is>
-      </c>
+      <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Microsite</t>
@@ -7571,11 +6939,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
+      <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Mobile Banner</t>
@@ -7616,11 +6980,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -7661,11 +7021,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Mrec Carousel</t>
@@ -7706,11 +7062,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Overlay Video</t>
@@ -7755,11 +7107,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
+      <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Reel</t>
@@ -7804,11 +7152,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Scratch (Teads)</t>
@@ -7853,11 +7197,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Scroller (Teads)</t>
@@ -7898,11 +7238,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
+      <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Shoppable Carousel Performance (Teads)</t>
@@ -7943,11 +7279,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
+      <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Shoppable Display (Teads)</t>
@@ -7988,11 +7320,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -8033,11 +7361,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -8074,11 +7398,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
+      <c r="C171" s="2" t="n"/>
       <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Skin</t>
@@ -8111,11 +7431,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C172" s="2" t="n"/>
       <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Slider (Teads)</t>
@@ -8160,11 +7476,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C173" s="2" t="n"/>
       <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Smart6 (Teads)</t>
@@ -8209,11 +7521,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C174" s="2" t="n"/>
       <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Social (Teads)</t>
@@ -8246,11 +7554,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C175" s="2" t="n"/>
       <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Social Performance</t>
@@ -8283,11 +7587,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C176" s="2" t="n"/>
       <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Social Video</t>
@@ -8320,11 +7620,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C177" s="2" t="n"/>
       <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Spin Card (Teads)</t>
@@ -8365,11 +7661,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Standard Green Ad</t>
@@ -8410,11 +7702,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C179" s="2" t="n"/>
       <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Standard Native (Outbrain)</t>
@@ -8459,11 +7747,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
+      <c r="C180" s="2" t="n"/>
       <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Stories Display (Teads)</t>
@@ -8496,11 +7780,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
+      <c r="C181" s="2" t="n"/>
       <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Stories Video (Teads)</t>
@@ -8533,11 +7813,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C182" s="2" t="n"/>
       <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Swipe Carousel (Teads)</t>
@@ -8582,11 +7858,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
+      <c r="C183" s="2" t="n"/>
       <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Topscroll</t>
@@ -8631,11 +7903,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
+      <c r="C184" s="2" t="n"/>
       <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Topscroll Carousel</t>
@@ -8668,11 +7936,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
+      <c r="C185" s="2" t="n"/>
       <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Topscroll Expand</t>
@@ -8713,11 +7977,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
+      <c r="C186" s="2" t="n"/>
       <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Topscroll Expand Video</t>
@@ -8758,11 +8018,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
+      <c r="C187" s="2" t="n"/>
       <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Topscroll Prismo</t>
@@ -8803,11 +8059,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>Topscroll</t>
-        </is>
-      </c>
+      <c r="C188" s="2" t="n"/>
       <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Topscroll Video</t>
@@ -8840,11 +8092,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>Twin Ad</t>
-        </is>
-      </c>
+      <c r="C189" s="2" t="n"/>
       <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Twin Ad</t>
@@ -8885,11 +8133,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C190" s="2" t="n"/>
       <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Video In-Stream Mid-Roll</t>
@@ -8934,11 +8178,7 @@
           <t>Sapo</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C191" s="2" t="n"/>
       <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Video In-Stream Pre-Roll</t>
@@ -8983,11 +8223,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C192" s="2" t="n"/>
       <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Article and Newsletter Ads</t>
@@ -9032,11 +8268,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C193" s="2" t="n"/>
       <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -9085,11 +8317,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
+      <c r="C194" s="2" t="n"/>
       <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Connected TV Ads</t>
@@ -9134,11 +8362,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C195" s="2" t="n"/>
       <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Conversation Ads</t>
@@ -9183,11 +8407,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C196" s="2" t="n"/>
       <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Document Ads</t>
@@ -9232,11 +8452,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C197" s="2" t="n"/>
       <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Event Ads</t>
@@ -9285,11 +8501,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C198" s="2" t="n"/>
       <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Follower Ads</t>
@@ -9338,11 +8550,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C199" s="2" t="n"/>
       <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Job Ads</t>
@@ -9387,11 +8595,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C200" s="2" t="n"/>
       <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Lead Gen Forms</t>
@@ -9436,11 +8640,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C201" s="2" t="n"/>
       <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Message Ads</t>
@@ -9485,11 +8685,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C202" s="2" t="n"/>
       <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -9538,11 +8734,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C203" s="2" t="n"/>
       <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -9591,11 +8783,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C204" s="2" t="n"/>
       <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Spotlight Ads</t>
@@ -9644,11 +8832,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C205" s="2" t="n"/>
       <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Text Ads</t>
@@ -9697,11 +8881,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C206" s="2" t="n"/>
       <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Thought Leader Ads</t>
@@ -9746,11 +8926,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C207" s="2" t="n"/>
       <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Carousel Ad</t>
@@ -9799,11 +8975,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
+      <c r="C208" s="2" t="n"/>
       <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -9852,11 +9024,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C209" s="2" t="n"/>
       <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Image Pin</t>
@@ -9905,11 +9073,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C210" s="2" t="n"/>
       <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Video Ad</t>
@@ -9958,11 +9122,7 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C211" s="2" t="n"/>
       <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Carousel Ad</t>
@@ -10011,11 +9171,7 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C212" s="2" t="n"/>
       <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Free-form Ad</t>
@@ -10064,11 +9220,7 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C213" s="2" t="n"/>
       <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Image Ad</t>
@@ -10117,11 +9269,7 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
+      <c r="C214" s="2" t="n"/>
       <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Product Ad</t>
@@ -10162,11 +9310,7 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C215" s="2" t="n"/>
       <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Video Ad</t>
@@ -10215,11 +9359,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
+      <c r="C216" s="2" t="n"/>
       <c r="D216" s="2" t="inlineStr">
         <is>
           <t>AR Filters</t>
@@ -10260,11 +9400,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
+      <c r="C217" s="2" t="n"/>
       <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -10313,11 +9449,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C218" s="2" t="n"/>
       <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Commercial Ad</t>
@@ -10362,11 +9494,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C219" s="2" t="n"/>
       <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -10415,11 +9543,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C220" s="2" t="n"/>
       <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -10468,11 +9592,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
+      <c r="C221" s="2" t="n"/>
       <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Story</t>
@@ -10521,11 +9641,7 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
+      <c r="C222" s="2" t="n"/>
       <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Branded Effect</t>
@@ -10570,11 +9686,7 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C223" s="2" t="n"/>
       <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Carousel Ads</t>
@@ -10619,11 +9731,7 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C224" s="2" t="n"/>
       <c r="D224" s="2" t="inlineStr">
         <is>
           <t>In-Feed (Standard Feed)</t>
@@ -10676,11 +9784,7 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C225" s="2" t="n"/>
       <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Pulse</t>
@@ -10721,11 +9825,7 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C226" s="2" t="n"/>
       <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Spark Ads</t>
@@ -10770,11 +9870,7 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C227" s="2" t="n"/>
       <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Top Feed</t>
@@ -10819,11 +9915,7 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C228" s="2" t="n"/>
       <c r="D228" s="2" t="inlineStr">
         <is>
           <t>TopView</t>
@@ -10876,11 +9968,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C229" s="2" t="n"/>
       <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Carousel Ad</t>
@@ -10929,11 +10017,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C230" s="2" t="n"/>
       <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Image Ad</t>
@@ -10982,11 +10066,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C231" s="2" t="n"/>
       <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Text Ad</t>
@@ -11031,11 +10111,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C232" s="2" t="n"/>
       <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Video Ad</t>
@@ -11084,11 +10160,7 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C233" s="2" t="n"/>
       <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Medium Rectangle</t>
@@ -11129,11 +10201,7 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C234" s="2" t="n"/>
       <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Large Rectangle</t>
@@ -11174,11 +10242,7 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C235" s="2" t="n"/>
       <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -11219,11 +10283,7 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C236" s="2" t="n"/>
       <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Half Page</t>
@@ -11268,11 +10328,7 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
+      <c r="C237" s="2" t="n"/>
       <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Mobile Banner</t>
@@ -11313,11 +10369,7 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C238" s="2" t="n"/>
       <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Responsive Display Ads (imagem)</t>
@@ -11362,11 +10414,7 @@
           <t>Google Display Network</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C239" s="2" t="n"/>
       <c r="D239" s="2" t="inlineStr">
         <is>
           <t>HTML5 Display</t>
@@ -11411,11 +10459,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C240" s="2" t="n"/>
       <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Skippable In-Stream</t>
@@ -11460,11 +10504,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C241" s="2" t="n"/>
       <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Non-skippable In-Stream (standard)</t>
@@ -11509,11 +10549,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C242" s="2" t="n"/>
       <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Bumper</t>
@@ -11558,11 +10594,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
+      <c r="C243" s="2" t="n"/>
       <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Non-skippable 30s (Connected TV)</t>
@@ -11607,11 +10639,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C244" s="2" t="n"/>
       <c r="D244" s="2" t="inlineStr">
         <is>
           <t>In-Feed Video Ad (ex-Discovery)</t>
@@ -11660,11 +10688,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
+      <c r="C245" s="2" t="n"/>
       <c r="D245" s="2" t="inlineStr">
         <is>
           <t>YouTube Shorts Ads</t>
@@ -11709,11 +10733,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C246" s="2" t="n"/>
       <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Masthead</t>
@@ -11758,11 +10778,7 @@
           <t>Google Demand Gen</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C247" s="2" t="n"/>
       <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Imagem</t>
@@ -11807,11 +10823,7 @@
           <t>Google Demand Gen</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C248" s="2" t="n"/>
       <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Vídeo</t>
@@ -11856,11 +10868,7 @@
           <t>Google Demand Gen</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C249" s="2" t="n"/>
       <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -11909,11 +10917,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
+      <c r="C250" s="2" t="n"/>
       <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Prog - Audio Ad</t>
@@ -11954,11 +10958,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
+      <c r="C251" s="2" t="n"/>
       <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Prog - Standard Banners</t>
@@ -12003,11 +11003,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
+      <c r="C252" s="2" t="n"/>
       <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Prog - YouTube Masthead</t>
@@ -12052,11 +11048,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C253" s="2" t="n"/>
       <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Prog - YouTube Select</t>
@@ -12101,11 +11093,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C254" s="2" t="n"/>
       <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Ad Sequence</t>
@@ -12150,11 +11138,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C255" s="2" t="n"/>
       <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Non-Skippable</t>
@@ -12199,11 +11183,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C256" s="2" t="n"/>
       <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Prog - YouTube VVC</t>
@@ -12248,11 +11228,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C257" s="2" t="n"/>
       <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Efficient Reach</t>
@@ -12297,11 +11273,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C258" s="2" t="n"/>
       <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Target Frequency</t>
@@ -12346,11 +11318,7 @@
           <t>Google App Campaigns</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C259" s="2" t="n"/>
       <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Imagem</t>
@@ -12395,11 +11363,7 @@
           <t>Google App Campaigns</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C260" s="2" t="n"/>
       <c r="D260" s="2" t="inlineStr">
         <is>
           <t>Vídeo</t>
@@ -12444,11 +11408,7 @@
           <t>Google Performance Max</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C261" s="2" t="n"/>
       <c r="D261" s="2" t="inlineStr">
         <is>
           <t>Imagem</t>
@@ -12493,11 +11453,7 @@
           <t>Google Performance Max</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
+      <c r="C262" s="2" t="n"/>
       <c r="D262" s="2" t="inlineStr">
         <is>
           <t>Logo</t>
@@ -12542,11 +11498,7 @@
           <t>Google Performance Max</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C263" s="2" t="n"/>
       <c r="D263" s="2" t="inlineStr">
         <is>
           <t>Vídeo</t>
@@ -12591,11 +11543,7 @@
           <t>Google Search</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
+      <c r="C264" s="2" t="n"/>
       <c r="D264" s="2" t="inlineStr">
         <is>
           <t>Business Information (Logo)</t>
@@ -12640,11 +11588,7 @@
           <t>Google Search</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>Ad Assets</t>
-        </is>
-      </c>
+      <c r="C265" s="2" t="n"/>
       <c r="D265" s="2" t="inlineStr">
         <is>
           <t>Ad Assets (Imagens)</t>
@@ -12689,11 +11633,7 @@
           <t>Google Search</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>Responsive Search Ad</t>
-        </is>
-      </c>
+      <c r="C266" s="2" t="n"/>
       <c r="D266" s="2" t="inlineStr">
         <is>
           <t>Responsive Search Ads</t>
@@ -12738,11 +11678,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C267" s="2" t="n"/>
       <c r="D267" s="2" t="inlineStr">
         <is>
           <t>Video Action Campaigns</t>
@@ -12791,11 +11727,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>Thumbnail</t>
-        </is>
-      </c>
+      <c r="C268" s="2" t="n"/>
       <c r="D268" s="2" t="inlineStr">
         <is>
           <t>Thumbnail (vídeo)</t>
@@ -12840,11 +11772,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
+      <c r="C269" s="2" t="n"/>
       <c r="D269" s="2" t="inlineStr">
         <is>
           <t>Companion Banner</t>
@@ -12889,11 +11817,7 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C270" s="2" t="n"/>
       <c r="D270" s="2" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -12942,11 +11866,7 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C271" s="2" t="n"/>
       <c r="D271" s="2" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -12995,11 +11915,7 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C272" s="2" t="n"/>
       <c r="D272" s="2" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -13048,11 +11964,7 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
+      <c r="C273" s="2" t="n"/>
       <c r="D273" s="2" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -13101,11 +12013,7 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
+      <c r="C274" s="2" t="n"/>
       <c r="D274" s="2" t="inlineStr">
         <is>
           <t>Single Image</t>
@@ -13154,11 +12062,7 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C275" s="2" t="n"/>
       <c r="D275" s="2" t="inlineStr">
         <is>
           <t>Single Video</t>
@@ -13207,11 +12111,7 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C276" s="2" t="n"/>
       <c r="D276" s="2" t="inlineStr">
         <is>
           <t>Carousel</t>
@@ -13260,11 +12160,7 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
+      <c r="C277" s="2" t="n"/>
       <c r="D277" s="2" t="inlineStr">
         <is>
           <t>Collection</t>
@@ -13313,11 +12209,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C278" s="2" t="n"/>
       <c r="D278" s="2" t="inlineStr">
         <is>
           <t>Idea Ad</t>
@@ -13366,11 +12258,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C279" s="2" t="n"/>
       <c r="D279" s="2" t="inlineStr">
         <is>
           <t>Showcase Ad</t>
@@ -13419,11 +12307,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C280" s="2" t="n"/>
       <c r="D280" s="2" t="inlineStr">
         <is>
           <t>Quiz Ad</t>
@@ -13472,11 +12356,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
+      <c r="C281" s="2" t="n"/>
       <c r="D281" s="2" t="inlineStr">
         <is>
           <t>AR Lenses</t>
@@ -13521,11 +12401,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C282" s="2" t="n"/>
       <c r="D282" s="2" t="inlineStr">
         <is>
           <t>Sponsored Snap</t>
@@ -13574,11 +12450,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
+      <c r="C283" s="2" t="n"/>
       <c r="D283" s="2" t="inlineStr">
         <is>
           <t>Vertical Video Ad</t>
@@ -13619,11 +12491,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
+      <c r="C284" s="2" t="n"/>
       <c r="D284" s="2" t="inlineStr">
         <is>
           <t>Amplify Pre-roll</t>
@@ -13676,11 +12544,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C285" s="2" t="n"/>
       <c r="D285" s="2" t="inlineStr">
         <is>
           <t>X Live</t>
@@ -13725,11 +12589,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C286" s="2" t="n"/>
       <c r="D286" s="2" t="inlineStr">
         <is>
           <t>Timeline Takeover</t>
@@ -13766,11 +12626,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C287" s="2" t="n"/>
       <c r="D287" s="2" t="inlineStr">
         <is>
           <t>Spotlight Takeover</t>
@@ -13819,11 +12675,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C288" s="2" t="n"/>
       <c r="D288" s="2" t="inlineStr">
         <is>
           <t>Branded Notifications</t>
@@ -13864,11 +12716,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
+      <c r="C289" s="2" t="n"/>
       <c r="D289" s="2" t="inlineStr">
         <is>
           <t>Dynamic Product Ads</t>
@@ -13905,11 +12753,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C290" s="2" t="n"/>
       <c r="D290" s="2" t="inlineStr">
         <is>
           <t>Conversation Button</t>
@@ -13946,11 +12790,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C291" s="2" t="n"/>
       <c r="D291" s="2" t="inlineStr">
         <is>
           <t>Polls</t>
@@ -13991,11 +12831,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
+      <c r="C292" s="2" t="n"/>
       <c r="D292" s="2" t="inlineStr">
         <is>
           <t>Prog - Companion Banner (Audio)</t>
@@ -14036,11 +12872,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C293" s="2" t="n"/>
       <c r="D293" s="2" t="inlineStr">
         <is>
           <t>Prog - Pre-Roll</t>
@@ -14081,11 +12913,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C294" s="2" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
+      <c r="C294" s="2" t="n"/>
       <c r="D294" s="2" t="inlineStr">
         <is>
           <t>Prog - Connected TV</t>
@@ -14126,11 +12954,7 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="C295" s="2" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
+      <c r="C295" s="2" t="n"/>
       <c r="D295" s="2" t="inlineStr">
         <is>
           <t>Prog - Companion Banner (YouTube)</t>
@@ -14220,11 +13044,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C297" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C297" s="2" t="n"/>
       <c r="D297" s="2" t="inlineStr">
         <is>
           <t>Prog - Rewarded Video</t>
@@ -14265,11 +13085,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C298" s="2" t="n"/>
       <c r="D298" s="2" t="inlineStr">
         <is>
           <t>Prog - Outstream</t>
@@ -14343,11 +13159,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C300" s="2" t="n"/>
       <c r="D300" s="2" t="inlineStr">
         <is>
           <t>Window Splash Vídeo</t>
@@ -14392,11 +13204,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C301" s="2" t="n"/>
       <c r="D301" s="2" t="inlineStr">
         <is>
           <t>Intro Full Vídeo</t>
@@ -14441,11 +13249,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
+      <c r="C302" s="2" t="n"/>
       <c r="D302" s="2" t="inlineStr">
         <is>
           <t>Splash/Intro</t>
@@ -14490,11 +13294,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C303" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C303" s="2" t="n"/>
       <c r="D303" s="2" t="inlineStr">
         <is>
           <t>Vídeo FullScreen TakeOver</t>
@@ -14539,11 +13339,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C304" s="2" t="n"/>
       <c r="D304" s="2" t="inlineStr">
         <is>
           <t>FullScreen TakeOver</t>
@@ -14588,11 +13384,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C305" s="2" t="n"/>
       <c r="D305" s="2" t="inlineStr">
         <is>
           <t>TakeOver</t>
@@ -14633,11 +13425,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
+      <c r="C306" s="2" t="n"/>
       <c r="D306" s="2" t="inlineStr">
         <is>
           <t>Skin (Imagem)</t>
@@ -14678,11 +13466,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
+      <c r="C307" s="2" t="n"/>
       <c r="D307" s="2" t="inlineStr">
         <is>
           <t>Skin Vídeo</t>
@@ -14727,11 +13511,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
+      <c r="C308" s="2" t="n"/>
       <c r="D308" s="2" t="inlineStr">
         <is>
           <t>Skin Invertida</t>
@@ -14772,11 +13552,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
+      <c r="C309" s="2" t="n"/>
       <c r="D309" s="2" t="inlineStr">
         <is>
           <t>Skin Mobile</t>
@@ -14821,11 +13597,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>Parallax</t>
-        </is>
-      </c>
+      <c r="C310" s="2" t="n"/>
       <c r="D310" s="2" t="inlineStr">
         <is>
           <t>Parallax</t>
@@ -14866,11 +13638,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C311" s="2" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
+      <c r="C311" s="2" t="n"/>
       <c r="D311" s="2" t="inlineStr">
         <is>
           <t>Carrossel</t>
@@ -14907,11 +13675,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C312" s="2" t="n"/>
       <c r="D312" s="2" t="inlineStr">
         <is>
           <t>FlipBook Ad</t>
@@ -14956,11 +13720,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C313" s="2" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
+      <c r="C313" s="2" t="n"/>
       <c r="D313" s="2" t="inlineStr">
         <is>
           <t>Mrec Cubo 3D</t>
@@ -15001,11 +13761,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr">
-        <is>
-          <t>Cubo</t>
-        </is>
-      </c>
+      <c r="C314" s="2" t="n"/>
       <c r="D314" s="2" t="inlineStr">
         <is>
           <t>Half Page Cubo 3D</t>
@@ -15046,11 +13802,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C315" s="2" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
+      <c r="C315" s="2" t="n"/>
       <c r="D315" s="2" t="inlineStr">
         <is>
           <t>Ticker Expandido</t>
@@ -15095,11 +13847,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
+      <c r="C316" s="2" t="n"/>
       <c r="D316" s="2" t="inlineStr">
         <is>
           <t>Spot TV</t>
@@ -15144,11 +13892,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C317" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C317" s="2" t="n"/>
       <c r="D317" s="2" t="inlineStr">
         <is>
           <t>Flip Ad</t>
@@ -15193,11 +13937,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C318" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C318" s="2" t="n"/>
       <c r="D318" s="2" t="inlineStr">
         <is>
           <t>Overslide</t>
@@ -15238,11 +13978,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C319" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C319" s="2" t="n"/>
       <c r="D319" s="2" t="inlineStr">
         <is>
           <t>Layer</t>
@@ -15287,11 +14023,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C320" s="2" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
+      <c r="C320" s="2" t="n"/>
       <c r="D320" s="2" t="inlineStr">
         <is>
           <t>Peel Off</t>
@@ -15336,11 +14068,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C321" s="2" t="n"/>
       <c r="D321" s="2" t="inlineStr">
         <is>
           <t>Push Down</t>
@@ -15381,11 +14109,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C322" s="2" t="inlineStr">
-        <is>
-          <t>Audio Ad</t>
-        </is>
-      </c>
+      <c r="C322" s="2" t="n"/>
       <c r="D322" s="2" t="inlineStr">
         <is>
           <t>Áudio Ad</t>
@@ -15426,11 +14150,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C323" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C323" s="2" t="n"/>
       <c r="D323" s="2" t="inlineStr">
         <is>
           <t>Pre-Roll</t>
@@ -15475,11 +14195,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C324" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C324" s="2" t="n"/>
       <c r="D324" s="2" t="inlineStr">
         <is>
           <t>InContent Sticky</t>
@@ -15524,11 +14240,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C325" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C325" s="2" t="n"/>
       <c r="D325" s="2" t="inlineStr">
         <is>
           <t>InContent</t>
@@ -15573,11 +14285,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C326" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C326" s="2" t="n"/>
       <c r="D326" s="2" t="inlineStr">
         <is>
           <t>Superboard/Billboard</t>
@@ -15618,11 +14326,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C327" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C327" s="2" t="n"/>
       <c r="D327" s="2" t="inlineStr">
         <is>
           <t>Mrec</t>
@@ -15663,11 +14367,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C328" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C328" s="2" t="n"/>
       <c r="D328" s="2" t="inlineStr">
         <is>
           <t>Half Page</t>
@@ -15708,11 +14408,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C329" s="2" t="inlineStr">
-        <is>
-          <t>Header XL</t>
-        </is>
-      </c>
+      <c r="C329" s="2" t="n"/>
       <c r="D329" s="2" t="inlineStr">
         <is>
           <t>Megapub</t>
@@ -15753,11 +14449,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C330" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C330" s="2" t="n"/>
       <c r="D330" s="2" t="inlineStr">
         <is>
           <t>Mrec Vídeo</t>
@@ -15802,11 +14494,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C331" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C331" s="2" t="n"/>
       <c r="D331" s="2" t="inlineStr">
         <is>
           <t>Half Page Vídeo (Imagem + Vídeo)</t>
@@ -15847,11 +14535,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C332" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C332" s="2" t="n"/>
       <c r="D332" s="2" t="inlineStr">
         <is>
           <t>Half Page Full Vídeo</t>
@@ -15896,11 +14580,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C333" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C333" s="2" t="n"/>
       <c r="D333" s="2" t="inlineStr">
         <is>
           <t>Social Card</t>
@@ -15937,11 +14617,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C334" s="2" t="inlineStr">
-        <is>
-          <t>Gallery</t>
-        </is>
-      </c>
+      <c r="C334" s="2" t="n"/>
       <c r="D334" s="2" t="inlineStr">
         <is>
           <t>Filmstrip</t>
@@ -15982,11 +14658,7 @@
           <t>Notícias Ilimitadas</t>
         </is>
       </c>
-      <c r="C335" s="2" t="inlineStr">
-        <is>
-          <t>Newsletter Banner</t>
-        </is>
-      </c>
+      <c r="C335" s="2" t="n"/>
       <c r="D335" s="2" t="inlineStr">
         <is>
           <t>Newsletter</t>
@@ -16031,11 +14703,7 @@
           <t>WeTransfer</t>
         </is>
       </c>
-      <c r="C336" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C336" s="2" t="n"/>
       <c r="D336" s="2" t="inlineStr">
         <is>
           <t>Static Starter</t>
@@ -16076,11 +14744,7 @@
           <t>Roblox</t>
         </is>
       </c>
-      <c r="C337" s="2" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
+      <c r="C337" s="2" t="n"/>
       <c r="D337" s="2" t="inlineStr">
         <is>
           <t>Display Ads</t>
@@ -16121,11 +14785,7 @@
           <t>OLX</t>
         </is>
       </c>
-      <c r="C338" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C338" s="2" t="n"/>
       <c r="D338" s="2" t="inlineStr">
         <is>
           <t>Homepage Leaderboard</t>
@@ -16162,11 +14822,7 @@
           <t>Azerion</t>
         </is>
       </c>
-      <c r="C339" s="2" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
+      <c r="C339" s="2" t="n"/>
       <c r="D339" s="2" t="inlineStr">
         <is>
           <t>Skin</t>
@@ -16203,11 +14859,7 @@
           <t>Azerion</t>
         </is>
       </c>
-      <c r="C340" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C340" s="2" t="n"/>
       <c r="D340" s="2" t="inlineStr">
         <is>
           <t>Native ad</t>
@@ -16252,11 +14904,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C341" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C341" s="2" t="n"/>
       <c r="D341" s="2" t="inlineStr">
         <is>
           <t>Leaderboard</t>
@@ -16285,11 +14933,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C342" s="2" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
+      <c r="C342" s="2" t="n"/>
       <c r="D342" s="2" t="inlineStr">
         <is>
           <t>Mobile Leaderboard</t>
@@ -16318,11 +14962,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C343" s="2" t="inlineStr">
-        <is>
-          <t>Mrec</t>
-        </is>
-      </c>
+      <c r="C343" s="2" t="n"/>
       <c r="D343" s="2" t="inlineStr">
         <is>
           <t>MREC (mpu)</t>
@@ -16363,11 +15003,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C344" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C344" s="2" t="n"/>
       <c r="D344" s="2" t="inlineStr">
         <is>
           <t>Billboard (desktop)</t>
@@ -16408,11 +15044,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C345" s="2" t="inlineStr">
-        <is>
-          <t>Billboard</t>
-        </is>
-      </c>
+      <c r="C345" s="2" t="n"/>
       <c r="D345" s="2" t="inlineStr">
         <is>
           <t>Mobile Billboard</t>
@@ -16441,11 +15073,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C346" s="2" t="inlineStr">
-        <is>
-          <t>Halfpage</t>
-        </is>
-      </c>
+      <c r="C346" s="2" t="n"/>
       <c r="D346" s="2" t="inlineStr">
         <is>
           <t>Halfpage (double mpu)</t>
@@ -16486,11 +15114,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C347" s="2" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
+      <c r="C347" s="2" t="n"/>
       <c r="D347" s="2" t="inlineStr">
         <is>
           <t>Native</t>
@@ -16523,11 +15147,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C348" s="2" t="inlineStr">
-        <is>
-          <t>Interscroller</t>
-        </is>
-      </c>
+      <c r="C348" s="2" t="n"/>
       <c r="D348" s="2" t="inlineStr">
         <is>
           <t>Mobile Interscroller</t>
@@ -16560,11 +15180,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C349" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C349" s="2" t="n"/>
       <c r="D349" s="2" t="inlineStr">
         <is>
           <t>Socially Inspired Rich Media</t>
@@ -16597,11 +15213,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C350" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C350" s="2" t="n"/>
       <c r="D350" s="2" t="inlineStr">
         <is>
           <t>Standard Takeover</t>
@@ -16638,11 +15250,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C351" s="2" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
+      <c r="C351" s="2" t="n"/>
       <c r="D351" s="2" t="inlineStr">
         <is>
           <t>Hero Takeover</t>
@@ -16679,11 +15287,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C352" s="2" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
+      <c r="C352" s="2" t="n"/>
       <c r="D352" s="2" t="inlineStr">
         <is>
           <t>In-Article Video</t>
@@ -16724,11 +15328,7 @@
           <t>Bauer</t>
         </is>
       </c>
-      <c r="C353" s="2" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
+      <c r="C353" s="2" t="n"/>
       <c r="D353" s="2" t="inlineStr">
         <is>
           <t>Radio Player Pre-Roll</t>
@@ -16769,11 +15369,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C354" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C354" s="2" t="n"/>
       <c r="D354" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Conversacional</t>
@@ -16822,11 +15418,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C355" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C355" s="2" t="n"/>
       <c r="D355" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Audiências Game</t>
@@ -16875,11 +15467,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C356" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C356" s="2" t="n"/>
       <c r="D356" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Scratch</t>
@@ -16928,11 +15516,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C357" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C357" s="2" t="n"/>
       <c r="D357" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Slider Relevância</t>
@@ -16981,11 +15565,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C358" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C358" s="2" t="n"/>
       <c r="D358" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Catch Sinais</t>
@@ -17034,11 +15614,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C359" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C359" s="2" t="n"/>
       <c r="D359" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Puzzle Logo</t>
@@ -17087,11 +15663,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C360" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C360" s="2" t="n"/>
       <c r="D360" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Ligações</t>
@@ -17140,11 +15712,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C361" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C361" s="2" t="n"/>
       <c r="D361" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Roda Havas</t>
@@ -17193,11 +15761,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C362" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C362" s="2" t="n"/>
       <c r="D362" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Hold Ligação</t>
@@ -17246,11 +15810,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C363" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C363" s="2" t="n"/>
       <c r="D363" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Swipe Briefing</t>
@@ -17299,11 +15859,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C364" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C364" s="2" t="n"/>
       <c r="D364" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Calculadora Contactos</t>
@@ -17352,11 +15908,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C365" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C365" s="2" t="n"/>
       <c r="D365" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Tap Sinais</t>
@@ -17405,11 +15957,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C366" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C366" s="2" t="n"/>
       <c r="D366" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Procura na Estratégia</t>
@@ -17458,11 +16006,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C367" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C367" s="2" t="n"/>
       <c r="D367" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Método Havas</t>
@@ -17511,11 +16055,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C368" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C368" s="2" t="n"/>
       <c r="D368" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Palavra</t>
@@ -17564,11 +16104,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C369" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C369" s="2" t="n"/>
       <c r="D369" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Da Marca à Pessoa</t>
@@ -17617,11 +16153,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C370" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C370" s="2" t="n"/>
       <c r="D370" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Slot Havas</t>
@@ -17670,11 +16202,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C371" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C371" s="2" t="n"/>
       <c r="D371" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Verdade/Mito</t>
@@ -17723,11 +16251,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C372" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C372" s="2" t="n"/>
       <c r="D372" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Diferenças</t>
@@ -17776,11 +16300,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C373" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C373" s="2" t="n"/>
       <c r="D373" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Enche o Mapa</t>
@@ -17829,11 +16349,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C374" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C374" s="2" t="n"/>
       <c r="D374" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Configurador</t>
@@ -17882,11 +16398,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C375" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C375" s="2" t="n"/>
       <c r="D375" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Countdown</t>
@@ -17935,11 +16447,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C376" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C376" s="2" t="n"/>
       <c r="D376" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Estimativa</t>
@@ -17988,11 +16496,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C377" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C377" s="2" t="n"/>
       <c r="D377" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Ranking</t>
@@ -18041,11 +16545,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C378" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C378" s="2" t="n"/>
       <c r="D378" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Carrossel Produtos</t>
@@ -18094,11 +16594,7 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="C379" s="2" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
-        </is>
-      </c>
+      <c r="C379" s="2" t="n"/>
       <c r="D379" s="2" t="inlineStr">
         <is>
           <t>Prog - Displ.AI+ - Parallax</t>
@@ -18147,11 +16643,7 @@
           <t>Genérico</t>
         </is>
       </c>
-      <c r="C380" s="2" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
+      <c r="C380" s="2" t="n"/>
       <c r="D380" s="2" t="inlineStr">
         <is>
           <t>Branded Content</t>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$380</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Imprensa'!$A$1:$I$125</definedName>
@@ -19483,7 +19483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19563,12 +19563,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Spot TV (SD — IMX50)</t>
+          <t>Spot TV (HD — XDCAM HD422)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>720x576px, 25 fps</t>
+          <t>1920x1080px, 25 fps</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -19579,7 +19579,7 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MXF (OP-1a), codec IMX50, 50 Mb/s (CBR), croma 4:2:2, entrelaçado (Interlaced UFF, 16:9FHA), extensão .mxf</t>
+          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -19608,12 +19608,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Spot TV (HD — XDCAM HD422)</t>
+          <t>Ecrã Fracionado / Split Screen</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1920x1080px, 25 fps</t>
+          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -19624,7 +19624,7 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MXF (OP-1a), codec XDCAM HD422, 50 Mb/s mín. (CBR), croma 4:2:2, entrelaçado (Interlaced UFF), extensão .mxf</t>
+          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -19635,7 +19635,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Estrutura obrigatória do ficheiro: o conteúdo publicitário deve começar no primeiro frame de vídeo e terminar no último — pre-roll e post-roll de 0 frames, duração do ficheiro = duração do spot x 25 frames. Áudio: PCM, 2 canais (stereo), 24 bit, 48 KHz, peak level -3dB TP máx., loudness (integrado) -23 LUFS. Nomenclatura sugerida para o ficheiro: &lt;Pub ID&gt;_&lt;Nome do Spot&gt;_&lt;Duração&gt;.mxf (ex.: PUB-2015-000345_Fiat 500X Sport Edition_30.mxf) — não é obrigatória, mas recomendada sempre que possível. Entrega exclusivamente por utilizador registado através do Portal GoFastWay (www.gofastway.tv). Todos os ficheiros passam por controlo automático de qualidade (conformidade técnica com estas specs + análise subjetiva de vídeo e áudio); em caso de inconsistência, a GoFastWay pode pedir a entrega de um novo ficheiro corrigido.</t>
+          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
         </is>
       </c>
       <c r="J3" s="2" t="n"/>
@@ -19653,12 +19653,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ecrã Fracionado / Split Screen</t>
+          <t>Telepromoção</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>480x1080px (25% de um ecrã de 1920x1080px), 25 fps</t>
+          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -19669,7 +19669,7 @@
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>QuickTime (.MOV), ProRes 4444 (com canal Alpha) ou ProRes 422 (sem Alpha), 1080i entrelaçado (Upper/odd Field First), 25 fps</t>
+          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -19680,63 +19680,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Conteúdo publicitário que ocupa no máximo 25% do ecrã, transmitido em simultâneo com programas de entretenimento, desporto e magazine. Duração 10″, com entrada e saída incluídas nesses 10″. Sem áudio. Tem de manter a palavra "PUBLICIDADE" com leitura garantida e dentro da Safe Area durante todo o tempo em que está no ar. Entra pela direita do ecrã na TVI e pela esquerda na CNN Portugal. Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas.</t>
+          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
         </is>
       </c>
       <c r="J4" s="2" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TV</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>TV</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Telepromoção</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1920x1080px (plasma de estúdio; a zona útil do plasma tem 220px de altura a partir da base do ecrã) e oráculo 1920x1080px</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Imagens/grafismos: JPEG, PNG, PSD, AI/EPS (Illustrator versão CC), TIFF ou TGA, todos em resolução HD; ficheiros 3D: C4D (formato ideal), FBX ou OBJ. Vídeo: Formato de vídeo genérico (aplicável salvo indicação em contrário): wrapper MXF OP1a (.MXF), XDCAM HD 4:2:2, 1080i, 25 fps, entrelaçado (Upper/odd Field First), MPEG2 @ 50Mbps, perfil 4:2:2@HL, 1920x1080px, aspect ratio 16:9. Áudio: 8 canais @ 24 bits, PGM nos primeiros dois canais, 48.0 KHz, PCM não comprimido (.wav ou .aiff depois de desembrulhado), nível de referência -20dBFS, loudness -23 LUFS (EBU R.128).</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>GoFastWay
-www.gofastway.tv</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Materiais a fornecer para produção de grafismos, ou grafismos já finalizados — usados no plasma existente no estúdio (para passar vídeos, fotografias ou grafismos) e/ou no oráculo. Devem ser enquadrados dentro das áreas de segurança indicadas para os logos e textos não correrem o risco de serem cortados ou distorcidos (Safe Area geral: 96px horizontais / 54px verticais a partir da margem; Title Safe Area: 192px horizontais / 108px verticais — nenhuma informação relevante deve ficar fora destas áreas. No plasma de estúdio, a zona útil começa a 220px da base do ecrã; no oráculo aplica-se a Title Safe Area). Os guiões para telepromoções de 60″ de duração devem ter entre 730 e 800 caracteres sem espaçamento. Fontes de letra em formato TT, para PC; referências de cor em RGB. Todos os materiais devem ser fornecidos com pelo menos uma semana de antecedência relativamente à data de realização da telepromoção, nos formatos indicados.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$387</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K380"/>
+  <dimension ref="A1:K387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16695,8 +16695,295 @@
       </c>
       <c r="K380" s="2" t="n"/>
     </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="n"/>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>HomePage Banner</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="n"/>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="n"/>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático (Guapo) no fundo do ecrã principal da app, sempre com uma promoção de pelo menos 20% de desconto. Logo: altura até 150px, largura máx. 500px. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="n"/>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Food Wall Banner</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="n"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="n"/>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático no meio da loja Food Wall, focado em marcas de comida, sempre com uma promoção. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="n"/>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>In-store Banner</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>750x266px</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="n"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="n"/>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático em supermercados ou na parede do Glovo Market ("store wall"), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="n"/>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Shoppable Banner</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>750x422px</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="n"/>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="n"/>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>Banner localizado dentro de diferentes categorias das lojas (fora da categoria principal da marca), com os produtos a aparecer por baixo do banner — o utilizador pode adicioná-los diretamente ao cesto ou clicar no banner para ir à loja completa. Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="n"/>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Q-commerce Store Wall Banner</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="n"/>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="n"/>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático nas paredes das lojas de Groceries e Shops (Q-commerce), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="n"/>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>OTP Premium</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>1280x720px</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="n"/>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="n"/>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>Banner "skippable" (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, no fundo do ecrã, com uma secção de texto personalizável. O utilizador pode saltar o anúncio quando quiser. Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 20 carateres; CTA máx. 10 carateres. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="n"/>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>OTP Standard</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>1280x720px</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="n"/>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="n"/>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>Banner (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, e depois de um OTP Premium ter sido saltado ("skipped"). Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 30 carateres; sem tagline. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K387" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K380"/>
+  <autoFilter ref="A1:K387"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$393</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K387"/>
+  <dimension ref="A1:K393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16982,8 +16982,250 @@
       </c>
       <c r="K387" s="2" t="n"/>
     </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="n"/>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Standard (Imagem)</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>320x50, 300x250, 728x90, 300x600, 160x600, 336x280, 970x250, 320x100, 320x480, 970x90, 468x60, 360x640, 120x600, 250x250, 180x150, 320x568</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="n"/>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 500 KB</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG; GIF animado até 30″</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="n"/>
+      <c r="J388" s="2" t="n"/>
+      <c r="K388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="n"/>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Vídeo</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="n"/>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>16:9, 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="n"/>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>Duração máx. 30″. Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
+        </is>
+      </c>
+      <c r="K389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="n"/>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Rich Media / Responsivo</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>1200x628px, 1200x1200px ou 800x1200px</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="n"/>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="n"/>
+      <c r="J390" s="2" t="inlineStr">
+        <is>
+          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video). Pode incluir vídeo em vez de, ou além da, imagem: MP4, 1:1/16:9/9:16, máx. 25 MB, máx. 30″.</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="n"/>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - App Install</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Imagens: 1200x628px, 1200x1200px ou 800x1200px. Logo da app: proporção 1:1.</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>1:1, 16:9 ou 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPG ou MP4</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="n"/>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo opcional, máx. 30″.</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="n"/>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Hero SKU</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Imagem de produto/branding: 1200x628px, 1200x1200px ou 800x1200px. Imagem de fundo: 300x250, 336x280, 300x600, 320x480, 160x600, 728x90, 970x250 ou 320x50px.</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="n"/>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="n"/>
+      <c r="J392" s="2" t="n"/>
+      <c r="K392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="n"/>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - 3.60</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>1200x628px, 1200x1200px ou 800x1200px — mín. 6 imagens do mesmo produto, em ângulos diferentes.</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>1:1, 2:3 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="n"/>
+      <c r="J393" s="2" t="n"/>
+      <c r="K393" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K387"/>
+  <autoFilter ref="A1:K393"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$393</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K393"/>
+  <dimension ref="A1:K402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17224,8 +17224,269 @@
       <c r="J393" s="2" t="n"/>
       <c r="K393" s="2" t="n"/>
     </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Tap Tap</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>Tap Tap</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="n"/>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="n"/>
+      <c r="F394" s="2" t="n"/>
+      <c r="G394" s="2" t="n"/>
+      <c r="H394" s="2" t="n"/>
+      <c r="I394" s="2" t="n"/>
+      <c r="J394" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Shopfully</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Shopfully</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="n"/>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="n"/>
+      <c r="F395" s="2" t="n"/>
+      <c r="G395" s="2" t="n"/>
+      <c r="H395" s="2" t="n"/>
+      <c r="I395" s="2" t="n"/>
+      <c r="J395" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="n"/>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="n"/>
+      <c r="F396" s="2" t="n"/>
+      <c r="G396" s="2" t="n"/>
+      <c r="H396" s="2" t="n"/>
+      <c r="I396" s="2" t="n"/>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="n"/>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="n"/>
+      <c r="F397" s="2" t="n"/>
+      <c r="G397" s="2" t="n"/>
+      <c r="H397" s="2" t="n"/>
+      <c r="I397" s="2" t="n"/>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="n"/>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="n"/>
+      <c r="F398" s="2" t="n"/>
+      <c r="G398" s="2" t="n"/>
+      <c r="H398" s="2" t="n"/>
+      <c r="I398" s="2" t="n"/>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>EXTE</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>EXTE</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="n"/>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="n"/>
+      <c r="F399" s="2" t="n"/>
+      <c r="G399" s="2" t="n"/>
+      <c r="H399" s="2" t="n"/>
+      <c r="I399" s="2" t="n"/>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Oxy</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>Oxy</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="n"/>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n"/>
+      <c r="F400" s="2" t="n"/>
+      <c r="G400" s="2" t="n"/>
+      <c r="H400" s="2" t="n"/>
+      <c r="I400" s="2" t="n"/>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="n"/>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="n"/>
+      <c r="F401" s="2" t="n"/>
+      <c r="G401" s="2" t="n"/>
+      <c r="H401" s="2" t="n"/>
+      <c r="I401" s="2" t="n"/>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="n"/>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="n"/>
+      <c r="F402" s="2" t="n"/>
+      <c r="G402" s="2" t="n"/>
+      <c r="H402" s="2" t="n"/>
+      <c r="I402" s="2" t="n"/>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K393"/>
+  <autoFilter ref="A1:K402"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -17557,7 +17818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20000,8 +20261,62 @@
       </c>
       <c r="I67" s="2" t="n"/>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Formato (specs a confirmar)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:I69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$408</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K402"/>
+  <dimension ref="A1:K408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17464,29 +17464,251 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C402" s="2" t="n"/>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E402" s="2" t="n"/>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
       <c r="F402" s="2" t="n"/>
       <c r="G402" s="2" t="n"/>
-      <c r="H402" s="2" t="n"/>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
       <c r="I402" s="2" t="n"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K402" s="2" t="n"/>
     </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Forretas e Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n"/>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Moldura (barra lateral esquerda)</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="n"/>
+      <c r="G403" s="2" t="n"/>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="n"/>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n"/>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>940x120</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="n"/>
+      <c r="G404" s="2" t="n"/>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="n"/>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>Forretas (Homepage)</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="n"/>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>1920x313</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="n"/>
+      <c r="G405" s="2" t="n"/>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="n"/>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>Descontos</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="n"/>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>468x351</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="n"/>
+      <c r="G406" s="2" t="n"/>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="n"/>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n"/>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>HTML (Email)</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="n"/>
+      <c r="G407" s="2" t="n"/>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>HTML + imagens em JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="n"/>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n"/>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n"/>
+      <c r="F408" s="2" t="n"/>
+      <c r="G408" s="2" t="n"/>
+      <c r="H408" s="2" t="n"/>
+      <c r="I408" s="2" t="n"/>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K402"/>
+  <autoFilter ref="A1:K408"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$408</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$416</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K408"/>
+  <dimension ref="A1:K416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17343,12 +17343,12 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>EXTE</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>EXTE</t>
         </is>
       </c>
       <c r="C398" s="2" t="n"/>
@@ -17372,12 +17372,12 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>Oxy</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>Oxy</t>
         </is>
       </c>
       <c r="C399" s="2" t="n"/>
@@ -17401,12 +17401,12 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C400" s="2" t="n"/>
@@ -17430,28 +17430,36 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C401" s="2" t="n"/>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E401" s="2" t="n"/>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
       <c r="F401" s="2" t="n"/>
       <c r="G401" s="2" t="n"/>
-      <c r="H401" s="2" t="n"/>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
       <c r="I401" s="2" t="n"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K401" s="2" t="n"/>
@@ -17470,7 +17478,7 @@
       <c r="C402" s="2" t="n"/>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral direita)</t>
+          <t>Moldura (barra lateral esquerda)</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -17501,18 +17509,18 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C403" s="2" t="n"/>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral esquerda)</t>
+          <t>Moldura (topo)</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>940x120</t>
         </is>
       </c>
       <c r="F403" s="2" t="n"/>
@@ -17525,7 +17533,7 @@
       <c r="I403" s="2" t="n"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K403" s="2" t="n"/>
@@ -17538,7 +17546,7 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Descontos (Homepage)</t>
+          <t>Forretas (Homepage)</t>
         </is>
       </c>
       <c r="C404" s="2" t="n"/>
@@ -17549,7 +17557,7 @@
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>940x120</t>
+          <t>1920x313</t>
         </is>
       </c>
       <c r="F404" s="2" t="n"/>
@@ -17575,31 +17583,31 @@
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Forretas (Homepage)</t>
+          <t>Descontos</t>
         </is>
       </c>
       <c r="C405" s="2" t="n"/>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>1920x313</t>
+          <t>468x351</t>
         </is>
       </c>
       <c r="F405" s="2" t="n"/>
       <c r="G405" s="2" t="n"/>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>JPEG ou PNG</t>
         </is>
       </c>
       <c r="I405" s="2" t="n"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K405" s="2" t="n"/>
@@ -17612,31 +17620,31 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Descontos</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="C406" s="2" t="n"/>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
+          <t>HTML (Email)</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>468x351</t>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
         </is>
       </c>
       <c r="F406" s="2" t="n"/>
       <c r="G406" s="2" t="n"/>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>JPEG ou PNG</t>
+          <t>HTML + imagens em JPG ou PNG</t>
         </is>
       </c>
       <c r="I406" s="2" t="n"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K406" s="2" t="n"/>
@@ -17655,25 +17663,17 @@
       <c r="C407" s="2" t="n"/>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>HTML (Email)</t>
-        </is>
-      </c>
-      <c r="E407" s="2" t="inlineStr">
-        <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
-        </is>
-      </c>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n"/>
       <c r="F407" s="2" t="n"/>
       <c r="G407" s="2" t="n"/>
-      <c r="H407" s="2" t="inlineStr">
-        <is>
-          <t>HTML + imagens em JPG ou PNG</t>
-        </is>
-      </c>
+      <c r="H407" s="2" t="n"/>
       <c r="I407" s="2" t="n"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K407" s="2" t="n"/>
@@ -17681,34 +17681,350 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C408" s="2" t="n"/>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="E408" s="2" t="n"/>
-      <c r="F408" s="2" t="n"/>
-      <c r="G408" s="2" t="n"/>
-      <c r="H408" s="2" t="n"/>
+          <t>Taboola - Native Ads (Imagem)</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
+        </is>
+      </c>
       <c r="I408" s="2" t="n"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
       <c r="K408" s="2" t="n"/>
     </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="n"/>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Motion Ads (Vídeo)</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>1067x600</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>MP4, MOV ou GIF</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="n"/>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="n"/>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (Imagem)</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="n"/>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="n"/>
+      <c r="J410" s="2" t="n"/>
+      <c r="K410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n"/>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (Vídeo)</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="n"/>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200 MB</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="n"/>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="n"/>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (HTML5)</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="n"/>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="n"/>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="n"/>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display (Tag de 3ºs)</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="n"/>
+      <c r="G413" s="2" t="n"/>
+      <c r="H413" s="2" t="n"/>
+      <c r="I413" s="2" t="n"/>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="n"/>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Carousel</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>1200x627</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="n"/>
+      <c r="G414" s="2" t="n"/>
+      <c r="H414" s="2" t="n"/>
+      <c r="I414" s="2" t="n"/>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="n"/>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>300x250 ou 300x600</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="n"/>
+      <c r="G415" s="2" t="n"/>
+      <c r="H415" s="2" t="n"/>
+      <c r="I415" s="2" t="n"/>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="n"/>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Vertical</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="n"/>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>4:5, 9:16 ou 1:2</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="n"/>
+      <c r="J416" s="2" t="n"/>
+      <c r="K416" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K408"/>
+  <autoFilter ref="A1:K416"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$418</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K416"/>
+  <dimension ref="A1:K418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17401,28 +17401,36 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Suebi</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C400" s="2" t="n"/>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E400" s="2" t="n"/>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
       <c r="F400" s="2" t="n"/>
       <c r="G400" s="2" t="n"/>
-      <c r="H400" s="2" t="n"/>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
       <c r="I400" s="2" t="n"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K400" s="2" t="n"/>
@@ -17441,7 +17449,7 @@
       <c r="C401" s="2" t="n"/>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral direita)</t>
+          <t>Moldura (barra lateral esquerda)</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -17472,18 +17480,18 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C402" s="2" t="n"/>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral esquerda)</t>
+          <t>Moldura (topo)</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>200x700</t>
+          <t>940x120</t>
         </is>
       </c>
       <c r="F402" s="2" t="n"/>
@@ -17496,7 +17504,7 @@
       <c r="I402" s="2" t="n"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K402" s="2" t="n"/>
@@ -17509,7 +17517,7 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Descontos (Homepage)</t>
+          <t>Forretas (Homepage)</t>
         </is>
       </c>
       <c r="C403" s="2" t="n"/>
@@ -17520,7 +17528,7 @@
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>940x120</t>
+          <t>1920x313</t>
         </is>
       </c>
       <c r="F403" s="2" t="n"/>
@@ -17546,31 +17554,31 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Forretas (Homepage)</t>
+          <t>Descontos</t>
         </is>
       </c>
       <c r="C404" s="2" t="n"/>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>1920x313</t>
+          <t>468x351</t>
         </is>
       </c>
       <c r="F404" s="2" t="n"/>
       <c r="G404" s="2" t="n"/>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>JPEG ou PNG</t>
         </is>
       </c>
       <c r="I404" s="2" t="n"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K404" s="2" t="n"/>
@@ -17583,31 +17591,31 @@
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Descontos</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="C405" s="2" t="n"/>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
+          <t>HTML (Email)</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>468x351</t>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
         </is>
       </c>
       <c r="F405" s="2" t="n"/>
       <c r="G405" s="2" t="n"/>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>JPEG ou PNG</t>
+          <t>HTML + imagens em JPG ou PNG</t>
         </is>
       </c>
       <c r="I405" s="2" t="n"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K405" s="2" t="n"/>
@@ -17626,25 +17634,17 @@
       <c r="C406" s="2" t="n"/>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>HTML (Email)</t>
-        </is>
-      </c>
-      <c r="E406" s="2" t="inlineStr">
-        <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
-        </is>
-      </c>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n"/>
       <c r="F406" s="2" t="n"/>
       <c r="G406" s="2" t="n"/>
-      <c r="H406" s="2" t="inlineStr">
-        <is>
-          <t>HTML + imagens em JPG ou PNG</t>
-        </is>
-      </c>
+      <c r="H406" s="2" t="n"/>
       <c r="I406" s="2" t="n"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K406" s="2" t="n"/>
@@ -17652,28 +17652,44 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C407" s="2" t="n"/>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="E407" s="2" t="n"/>
-      <c r="F407" s="2" t="n"/>
-      <c r="G407" s="2" t="n"/>
-      <c r="H407" s="2" t="n"/>
+          <t>Taboola - Native Ads (Imagem)</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
+        </is>
+      </c>
       <c r="I407" s="2" t="n"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
       <c r="K407" s="2" t="n"/>
@@ -17692,33 +17708,33 @@
       <c r="C408" s="2" t="n"/>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Native Ads (Imagem)</t>
+          <t>Taboola - Motion Ads (Vídeo)</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>1200x674 (recomendado); mín. 400x350</t>
+          <t>1067x600</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>Máx. 5 MB</t>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
+          <t>MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="I408" s="2" t="n"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
       <c r="K408" s="2" t="n"/>
@@ -17737,35 +17753,27 @@
       <c r="C409" s="2" t="n"/>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Motion Ads (Vídeo)</t>
+          <t>Taboola - Display Hosted (Imagem)</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>1067x600</t>
-        </is>
-      </c>
-      <c r="F409" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="n"/>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+          <t>Máx. 2 MB</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF</t>
+          <t>JPEG, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I409" s="2" t="n"/>
-      <c r="J409" s="2" t="inlineStr">
-        <is>
-          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
-        </is>
-      </c>
+      <c r="J409" s="2" t="n"/>
       <c r="K409" s="2" t="n"/>
     </row>
     <row r="410">
@@ -17782,7 +17790,7 @@
       <c r="C410" s="2" t="n"/>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Imagem)</t>
+          <t>Taboola - Display Hosted (Vídeo)</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -17793,16 +17801,20 @@
       <c r="F410" s="2" t="n"/>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB</t>
+          <t>Máx. 200 MB</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>JPEG, JPG, PNG ou GIF</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="I410" s="2" t="n"/>
-      <c r="J410" s="2" t="n"/>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+        </is>
+      </c>
       <c r="K410" s="2" t="n"/>
     </row>
     <row r="411">
@@ -17819,7 +17831,7 @@
       <c r="C411" s="2" t="n"/>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Vídeo)</t>
+          <t>Taboola - Display Hosted (HTML5)</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -17830,18 +17842,18 @@
       <c r="F411" s="2" t="n"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 MB</t>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
         </is>
       </c>
       <c r="I411" s="2" t="n"/>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
         </is>
       </c>
       <c r="K411" s="2" t="n"/>
@@ -17860,7 +17872,7 @@
       <c r="C412" s="2" t="n"/>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (HTML5)</t>
+          <t>Taboola - Display (Tag de 3ºs)</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -17869,20 +17881,12 @@
         </is>
       </c>
       <c r="F412" s="2" t="n"/>
-      <c r="G412" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 2 MB (ZIP comprimido)</t>
-        </is>
-      </c>
-      <c r="H412" s="2" t="inlineStr">
-        <is>
-          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
-        </is>
-      </c>
+      <c r="G412" s="2" t="n"/>
+      <c r="H412" s="2" t="n"/>
       <c r="I412" s="2" t="n"/>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
         </is>
       </c>
       <c r="K412" s="2" t="n"/>
@@ -17901,12 +17905,12 @@
       <c r="C413" s="2" t="n"/>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display (Tag de 3ºs)</t>
+          <t>Taboola - Carousel</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+          <t>1200x627</t>
         </is>
       </c>
       <c r="F413" s="2" t="n"/>
@@ -17915,7 +17919,7 @@
       <c r="I413" s="2" t="n"/>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
         </is>
       </c>
       <c r="K413" s="2" t="n"/>
@@ -17934,12 +17938,12 @@
       <c r="C414" s="2" t="n"/>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Carousel</t>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>1200x627</t>
+          <t>300x250 ou 300x600</t>
         </is>
       </c>
       <c r="F414" s="2" t="n"/>
@@ -17948,7 +17952,7 @@
       <c r="I414" s="2" t="n"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
         </is>
       </c>
       <c r="K414" s="2" t="n"/>
@@ -17967,64 +17971,130 @@
       <c r="C415" s="2" t="n"/>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Social Importer (Facebook/Instagram)</t>
-        </is>
-      </c>
-      <c r="E415" s="2" t="inlineStr">
-        <is>
-          <t>300x250 ou 300x600</t>
-        </is>
-      </c>
-      <c r="F415" s="2" t="n"/>
-      <c r="G415" s="2" t="n"/>
-      <c r="H415" s="2" t="n"/>
+          <t>Taboola - Vertical</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="n"/>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>4:5, 9:16 ou 1:2</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
       <c r="I415" s="2" t="n"/>
-      <c r="J415" s="2" t="inlineStr">
-        <is>
-          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
-        </is>
-      </c>
+      <c r="J415" s="2" t="n"/>
       <c r="K415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C416" s="2" t="n"/>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Vertical</t>
+          <t>Suebi - SMS</t>
         </is>
       </c>
       <c r="E416" s="2" t="n"/>
-      <c r="F416" s="2" t="inlineStr">
-        <is>
-          <t>4:5, 9:16 ou 1:2</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="H416" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
+      <c r="F416" s="2" t="n"/>
+      <c r="G416" s="2" t="n"/>
+      <c r="H416" s="2" t="n"/>
       <c r="I416" s="2" t="n"/>
-      <c r="J416" s="2" t="n"/>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
+        </is>
+      </c>
       <c r="K416" s="2" t="n"/>
     </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="n"/>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Suebi - Email / Newsletter</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>600px de largura (imagens)</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="n"/>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>Imagens: recomendado máx. 200 KB</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="n"/>
+      <c r="I417" s="2" t="n"/>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>Suebi</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="n"/>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Suebi - Push Notification</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="n"/>
+      <c r="G418" s="2" t="n"/>
+      <c r="H418" s="2" t="n"/>
+      <c r="I418" s="2" t="n"/>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K416"/>
+  <autoFilter ref="A1:K418"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -18008,7 +18008,7 @@
       <c r="C416" s="2" t="n"/>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Suebi - SMS</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="E416" s="2" t="n"/>
@@ -18037,7 +18037,7 @@
       <c r="C417" s="2" t="n"/>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Suebi - Email / Newsletter</t>
+          <t>Email / Newsletter</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -18074,7 +18074,7 @@
       <c r="C418" s="2" t="n"/>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Suebi - Push Notification</t>
+          <t>Push Notification</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$418</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K418"/>
+  <dimension ref="A1:K412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17227,28 +17227,36 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>Tap Tap</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>Tap Tap</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C394" s="2" t="n"/>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E394" s="2" t="n"/>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
       <c r="F394" s="2" t="n"/>
       <c r="G394" s="2" t="n"/>
-      <c r="H394" s="2" t="n"/>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
       <c r="I394" s="2" t="n"/>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K394" s="2" t="n"/>
@@ -17256,28 +17264,36 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>Shopfully</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Shopfully</t>
+          <t>Forretas e Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C395" s="2" t="n"/>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E395" s="2" t="n"/>
+          <t>Moldura (barra lateral esquerda)</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
       <c r="F395" s="2" t="n"/>
       <c r="G395" s="2" t="n"/>
-      <c r="H395" s="2" t="n"/>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
       <c r="I395" s="2" t="n"/>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K395" s="2" t="n"/>
@@ -17285,28 +17301,36 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>RTB House</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>RTB House</t>
+          <t>Descontos (Homepage)</t>
         </is>
       </c>
       <c r="C396" s="2" t="n"/>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E396" s="2" t="n"/>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>940x120</t>
+        </is>
+      </c>
       <c r="F396" s="2" t="n"/>
       <c r="G396" s="2" t="n"/>
-      <c r="H396" s="2" t="n"/>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
       <c r="I396" s="2" t="n"/>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K396" s="2" t="n"/>
@@ -17314,28 +17338,36 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>AdsMovil</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>AdsMovil</t>
+          <t>Forretas (Homepage)</t>
         </is>
       </c>
       <c r="C397" s="2" t="n"/>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E397" s="2" t="n"/>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>1920x313</t>
+        </is>
+      </c>
       <c r="F397" s="2" t="n"/>
       <c r="G397" s="2" t="n"/>
-      <c r="H397" s="2" t="n"/>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
       <c r="I397" s="2" t="n"/>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K397" s="2" t="n"/>
@@ -17343,28 +17375,36 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>EXTE</t>
+          <t>Descontos</t>
         </is>
       </c>
       <c r="C398" s="2" t="n"/>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E398" s="2" t="n"/>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>468x351</t>
+        </is>
+      </c>
       <c r="F398" s="2" t="n"/>
       <c r="G398" s="2" t="n"/>
-      <c r="H398" s="2" t="n"/>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>JPEG ou PNG</t>
+        </is>
+      </c>
       <c r="I398" s="2" t="n"/>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K398" s="2" t="n"/>
@@ -17372,28 +17412,36 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Oxy</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="C399" s="2" t="n"/>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="n"/>
+          <t>HTML (Email)</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
+        </is>
+      </c>
       <c r="F399" s="2" t="n"/>
       <c r="G399" s="2" t="n"/>
-      <c r="H399" s="2" t="n"/>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>HTML + imagens em JPG ou PNG</t>
+        </is>
+      </c>
       <c r="I399" s="2" t="n"/>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K399" s="2" t="n"/>
@@ -17406,31 +17454,23 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>ClickProfit</t>
         </is>
       </c>
       <c r="C400" s="2" t="n"/>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral direita)</t>
-        </is>
-      </c>
-      <c r="E400" s="2" t="inlineStr">
-        <is>
-          <t>200x700</t>
-        </is>
-      </c>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n"/>
       <c r="F400" s="2" t="n"/>
       <c r="G400" s="2" t="n"/>
-      <c r="H400" s="2" t="inlineStr">
-        <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
-        </is>
-      </c>
+      <c r="H400" s="2" t="n"/>
       <c r="I400" s="2" t="n"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K400" s="2" t="n"/>
@@ -17438,36 +17478,44 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Forretas e Descontos (Homepage)</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C401" s="2" t="n"/>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Moldura (barra lateral esquerda)</t>
+          <t>Taboola - Native Ads (Imagem)</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>200x700</t>
-        </is>
-      </c>
-      <c r="F401" s="2" t="n"/>
-      <c r="G401" s="2" t="n"/>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
       <c r="H401" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
         </is>
       </c>
       <c r="I401" s="2" t="n"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
       <c r="K401" s="2" t="n"/>
@@ -17475,36 +17523,44 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Descontos (Homepage)</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C402" s="2" t="n"/>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Taboola - Motion Ads (Vídeo)</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>940x120</t>
-        </is>
-      </c>
-      <c r="F402" s="2" t="n"/>
-      <c r="G402" s="2" t="n"/>
+          <t>1067x600</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+        </is>
+      </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="I402" s="2" t="n"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
       <c r="K402" s="2" t="n"/>
@@ -17512,73 +17568,77 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Forretas (Homepage)</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C403" s="2" t="n"/>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Moldura (topo)</t>
+          <t>Taboola - Display Hosted (Imagem)</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>1920x313</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
       <c r="F403" s="2" t="n"/>
-      <c r="G403" s="2" t="n"/>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB</t>
+        </is>
+      </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
+          <t>JPEG, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I403" s="2" t="n"/>
-      <c r="J403" s="2" t="inlineStr">
-        <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
+      <c r="J403" s="2" t="n"/>
       <c r="K403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Descontos</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C404" s="2" t="n"/>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
+          <t>Taboola - Display Hosted (Vídeo)</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>468x351</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
       <c r="F404" s="2" t="n"/>
-      <c r="G404" s="2" t="n"/>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200 MB</t>
+        </is>
+      </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>JPEG ou PNG</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="I404" s="2" t="n"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
         </is>
       </c>
       <c r="K404" s="2" t="n"/>
@@ -17586,36 +17646,40 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C405" s="2" t="n"/>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>HTML (Email)</t>
+          <t>Taboola - Display Hosted (HTML5)</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
         </is>
       </c>
       <c r="F405" s="2" t="n"/>
-      <c r="G405" s="2" t="n"/>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
+        </is>
+      </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>HTML + imagens em JPG ou PNG</t>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
         </is>
       </c>
       <c r="I405" s="2" t="n"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
         </is>
       </c>
       <c r="K405" s="2" t="n"/>
@@ -17623,28 +17687,32 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>ClickProfit</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C406" s="2" t="n"/>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="E406" s="2" t="n"/>
+          <t>Taboola - Display (Tag de 3ºs)</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
       <c r="F406" s="2" t="n"/>
       <c r="G406" s="2" t="n"/>
       <c r="H406" s="2" t="n"/>
       <c r="I406" s="2" t="n"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
         </is>
       </c>
       <c r="K406" s="2" t="n"/>
@@ -17663,33 +17731,21 @@
       <c r="C407" s="2" t="n"/>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Native Ads (Imagem)</t>
+          <t>Taboola - Carousel</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>1200x674 (recomendado); mín. 400x350</t>
-        </is>
-      </c>
-      <c r="F407" s="2" t="inlineStr">
-        <is>
-          <t>16:9 (preferencial), 4:3 ou 1:1</t>
-        </is>
-      </c>
-      <c r="G407" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="H407" s="2" t="inlineStr">
-        <is>
-          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
-        </is>
-      </c>
+          <t>1200x627</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="n"/>
+      <c r="G407" s="2" t="n"/>
+      <c r="H407" s="2" t="n"/>
       <c r="I407" s="2" t="n"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
         </is>
       </c>
       <c r="K407" s="2" t="n"/>
@@ -17708,33 +17764,21 @@
       <c r="C408" s="2" t="n"/>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Motion Ads (Vídeo)</t>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>1067x600</t>
-        </is>
-      </c>
-      <c r="F408" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="G408" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
-        </is>
-      </c>
-      <c r="H408" s="2" t="inlineStr">
-        <is>
-          <t>MP4, MOV ou GIF</t>
-        </is>
-      </c>
+          <t>300x250 ou 300x600</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="n"/>
+      <c r="G408" s="2" t="n"/>
+      <c r="H408" s="2" t="n"/>
       <c r="I408" s="2" t="n"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
         </is>
       </c>
       <c r="K408" s="2" t="n"/>
@@ -17753,23 +17797,23 @@
       <c r="C409" s="2" t="n"/>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Imagem)</t>
-        </is>
-      </c>
-      <c r="E409" s="2" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="F409" s="2" t="n"/>
+          <t>Taboola - Vertical</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n"/>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>4:5, 9:16 ou 1:2</t>
+        </is>
+      </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB</t>
+          <t>Máx. 5 MB</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>JPEG, JPG, PNG ou GIF</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
       <c r="I409" s="2" t="n"/>
@@ -17779,40 +17823,28 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C410" s="2" t="n"/>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Vídeo)</t>
-        </is>
-      </c>
-      <c r="E410" s="2" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="n"/>
       <c r="F410" s="2" t="n"/>
-      <c r="G410" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200 MB</t>
-        </is>
-      </c>
-      <c r="H410" s="2" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
+      <c r="G410" s="2" t="n"/>
+      <c r="H410" s="2" t="n"/>
       <c r="I410" s="2" t="n"/>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
         </is>
       </c>
       <c r="K410" s="2" t="n"/>
@@ -17820,40 +17852,36 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C411" s="2" t="n"/>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (HTML5)</t>
+          <t>Email / Newsletter</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+          <t>600px de largura (imagens)</t>
         </is>
       </c>
       <c r="F411" s="2" t="n"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB (ZIP comprimido)</t>
-        </is>
-      </c>
-      <c r="H411" s="2" t="inlineStr">
-        <is>
-          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
-        </is>
-      </c>
+          <t>Imagens: recomendado máx. 200 KB</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="n"/>
       <c r="I411" s="2" t="n"/>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
+          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
         </is>
       </c>
       <c r="K411" s="2" t="n"/>
@@ -17861,23 +17889,23 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Taboola</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C412" s="2" t="n"/>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display (Tag de 3ºs)</t>
+          <t>Push Notification</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
         </is>
       </c>
       <c r="F412" s="2" t="n"/>
@@ -17886,215 +17914,13 @@
       <c r="I412" s="2" t="n"/>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
+          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
         </is>
       </c>
       <c r="K412" s="2" t="n"/>
     </row>
-    <row r="413">
-      <c r="A413" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B413" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C413" s="2" t="n"/>
-      <c r="D413" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Carousel</t>
-        </is>
-      </c>
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>1200x627</t>
-        </is>
-      </c>
-      <c r="F413" s="2" t="n"/>
-      <c r="G413" s="2" t="n"/>
-      <c r="H413" s="2" t="n"/>
-      <c r="I413" s="2" t="n"/>
-      <c r="J413" s="2" t="inlineStr">
-        <is>
-          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
-        </is>
-      </c>
-      <c r="K413" s="2" t="n"/>
-    </row>
-    <row r="414">
-      <c r="A414" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B414" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C414" s="2" t="n"/>
-      <c r="D414" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Social Importer (Facebook/Instagram)</t>
-        </is>
-      </c>
-      <c r="E414" s="2" t="inlineStr">
-        <is>
-          <t>300x250 ou 300x600</t>
-        </is>
-      </c>
-      <c r="F414" s="2" t="n"/>
-      <c r="G414" s="2" t="n"/>
-      <c r="H414" s="2" t="n"/>
-      <c r="I414" s="2" t="n"/>
-      <c r="J414" s="2" t="inlineStr">
-        <is>
-          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
-        </is>
-      </c>
-      <c r="K414" s="2" t="n"/>
-    </row>
-    <row r="415">
-      <c r="A415" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B415" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C415" s="2" t="n"/>
-      <c r="D415" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Vertical</t>
-        </is>
-      </c>
-      <c r="E415" s="2" t="n"/>
-      <c r="F415" s="2" t="inlineStr">
-        <is>
-          <t>4:5, 9:16 ou 1:2</t>
-        </is>
-      </c>
-      <c r="G415" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="H415" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="n"/>
-      <c r="J415" s="2" t="n"/>
-      <c r="K415" s="2" t="n"/>
-    </row>
-    <row r="416">
-      <c r="A416" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="B416" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="C416" s="2" t="n"/>
-      <c r="D416" s="2" t="inlineStr">
-        <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="E416" s="2" t="n"/>
-      <c r="F416" s="2" t="n"/>
-      <c r="G416" s="2" t="n"/>
-      <c r="H416" s="2" t="n"/>
-      <c r="I416" s="2" t="n"/>
-      <c r="J416" s="2" t="inlineStr">
-        <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
-        </is>
-      </c>
-      <c r="K416" s="2" t="n"/>
-    </row>
-    <row r="417">
-      <c r="A417" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="B417" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="C417" s="2" t="n"/>
-      <c r="D417" s="2" t="inlineStr">
-        <is>
-          <t>Email / Newsletter</t>
-        </is>
-      </c>
-      <c r="E417" s="2" t="inlineStr">
-        <is>
-          <t>600px de largura (imagens)</t>
-        </is>
-      </c>
-      <c r="F417" s="2" t="n"/>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>Imagens: recomendado máx. 200 KB</t>
-        </is>
-      </c>
-      <c r="H417" s="2" t="n"/>
-      <c r="I417" s="2" t="n"/>
-      <c r="J417" s="2" t="inlineStr">
-        <is>
-          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
-        </is>
-      </c>
-      <c r="K417" s="2" t="n"/>
-    </row>
-    <row r="418">
-      <c r="A418" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="B418" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="C418" s="2" t="n"/>
-      <c r="D418" s="2" t="inlineStr">
-        <is>
-          <t>Push Notification</t>
-        </is>
-      </c>
-      <c r="E418" s="2" t="inlineStr">
-        <is>
-          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
-        </is>
-      </c>
-      <c r="F418" s="2" t="n"/>
-      <c r="G418" s="2" t="n"/>
-      <c r="H418" s="2" t="n"/>
-      <c r="I418" s="2" t="n"/>
-      <c r="J418" s="2" t="inlineStr">
-        <is>
-          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
-        </is>
-      </c>
-      <c r="K418" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K418"/>
+  <autoFilter ref="A1:K412"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -18426,7 +18252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20869,62 +20695,8 @@
       </c>
       <c r="I67" s="2" t="n"/>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>In-Store Media</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>In-Store Media</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Formato (specs a confirmar)</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Specs técnicas ainda não disponíveis — substituir esta linha quando a Cláudia enviar os materiais deste fornecedor.</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I69"/>
+  <autoFilter ref="A1:I67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$413</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K412"/>
+  <dimension ref="A1:K413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17919,8 +17919,45 @@
       </c>
       <c r="K412" s="2" t="n"/>
     </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>RTB House</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="n"/>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>300x600, 160x600, 336x280, 300x250, 320x50, 320x100, 970x250 ou 728x90</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="n"/>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPG, JPEG, GIF ou HTML</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="n"/>
+      <c r="J413" s="2" t="n"/>
+      <c r="K413" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K412"/>
+  <autoFilter ref="A1:K413"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K393"/>
+  <dimension ref="A1:K367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14829,1320 +14829,46 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Genérico</t>
         </is>
       </c>
       <c r="C334" s="2" t="n"/>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Prog - Displ.AI+ - Conversacional</t>
+          <t>Branded Content</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
+          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>Mensagens + botões de resposta.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">
-        <is>
-          <t>Chat / conversa simulada. Imagens necessárias: 0 (usa avatar do logo). Substituível por asset real: Avatar do chat (círculo) → foto/ícone da marca 96x96 PNG. Emoji 👋 → ícone próprio. Specs do asset: Avatar opcional (círculo, 96x96). Bolhas de chat geradas por CSS. Sem imagens de fundo. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K334" s="2" t="n"/>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B335" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C335" s="2" t="n"/>
-      <c r="D335" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Audiências Game</t>
-        </is>
-      </c>
-      <c r="E335" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F335" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G335" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H335" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I335" s="2" t="inlineStr">
-        <is>
-          <t>3 labels de audiência (ex: Jovens/Famílias/Profissionais) + enunciado.</t>
-        </is>
-      </c>
-      <c r="J335" s="2" t="inlineStr">
-        <is>
-          <t>Drag &amp; drop de mensagens para audiências. Imagens necessárias: 0–3 (ícones de audiência opcionais). Substituível por asset real: Emojis das audiências (👥) → ícones da marca 128x128 PNG transparente. Bins → cores da marca. Specs do asset: Ícones 1:1 PNG transparente 128x128 (opcional; caso contrário emoji). Bins e cartões gerados por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K335" s="2" t="n"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C336" s="2" t="n"/>
-      <c r="D336" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Scratch</t>
-        </is>
-      </c>
-      <c r="E336" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F336" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G336" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H336" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I336" s="2" t="inlineStr">
-        <is>
-          <t>Pergunta topo + mensagem revelada + CTA.</t>
-        </is>
-      </c>
-      <c r="J336" s="2" t="inlineStr">
-        <is>
-          <t>Raspadinha (scratch-to-reveal). Imagens necessárias: 1 imagem-prémio/revelação (recomendado). Substituível por asset real: Camada revelada → imagem real do cliente 300x300. Emojis ✨🔎 → ícones próprios. Specs do asset: Imagem de revelação 300x300 (JPG/PNG). Camada de raspar é CSS/canvas. Imagem por baixo é o asset do cliente. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K336" s="2" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B337" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C337" s="2" t="n"/>
-      <c r="D337" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Slider Relevância</t>
-        </is>
-      </c>
-      <c r="E337" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F337" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G337" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H337" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I337" s="2" t="inlineStr">
-        <is>
-          <t>2 labels extremos + enunciado + conclusão.</t>
-        </is>
-      </c>
-      <c r="J337" s="2" t="inlineStr">
-        <is>
-          <t>Slider comparativo (relevante vs genérico). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones/emojis dos extremos → ícones 96x96 PNG (opcional). Totalmente CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K337" s="2" t="n"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B338" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C338" s="2" t="n"/>
-      <c r="D338" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Catch Sinais</t>
-        </is>
-      </c>
-      <c r="E338" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F338" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G338" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H338" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I338" s="2" t="inlineStr">
-        <is>
-          <t>Enunciado + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J338" s="2" t="inlineStr">
-        <is>
-          <t>Apanhar itens que caem (jogo). Imagens necessárias: 0–4 (ícones dos itens, opcional). Substituível por asset real: Itens que caem (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG transparente (opcional; senão emoji). Física/posições por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K338" s="2" t="n"/>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B339" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C339" s="2" t="n"/>
-      <c r="D339" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Puzzle Logo</t>
-        </is>
-      </c>
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F339" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G339" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H339" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I339" s="2" t="inlineStr">
-        <is>
-          <t>Instrução + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J339" s="2" t="inlineStr">
-        <is>
-          <t>Puzzle de peças que monta o logótipo. Imagens necessárias: 1 logótipo (obrigatório). Substituível por asset real: Já usa imagem real (logótipo). Fundo das peças → cor/textura da marca (opcional). Specs do asset: Logótipo 240x240 PNG (fundo sólido ou transparente). A imagem é fatiada em peças por CSS. Entregar logo em alta resolução. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
-        </is>
-      </c>
-      <c r="K339" s="2" t="n"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B340" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C340" s="2" t="n"/>
-      <c r="D340" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Ligações</t>
-        </is>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F340" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G340" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H340" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I340" s="2" t="inlineStr">
-        <is>
-          <t>Instrução + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J340" s="2" t="inlineStr">
-        <is>
-          <t>Jogo da memória (pares). Imagens necessárias: 0–6 (faces das cartas, opcional). Substituível por asset real: Faces das cartas (emoji) → imagens/ícones 128x128 (produtos, símbolos da marca). Specs do asset: Ícones/faces 128x128 (opcional; senão emoji). Cartas geradas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K340" s="2" t="n"/>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B341" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C341" s="2" t="n"/>
-      <c r="D341" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Roda Havas</t>
-        </is>
-      </c>
-      <c r="E341" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F341" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G341" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H341" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I341" s="2" t="inlineStr">
-        <is>
-          <t>6 labels de segmento + enunciado + resultado.</t>
-        </is>
-      </c>
-      <c r="J341" s="2" t="inlineStr">
-        <is>
-          <t>Roda da sorte / estratégia. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos segmentos → ícones 64x64 PNG. Cores dos segmentos → paleta da marca. Segmentos e cores por CSS. Emojis por segmento. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K341" s="2" t="n"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B342" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C342" s="2" t="n"/>
-      <c r="D342" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Hold Ligação</t>
-        </is>
-      </c>
-      <c r="E342" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F342" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H342" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I342" s="2" t="inlineStr">
-        <is>
-          <t>Instrução + mensagem ao completar.</t>
-        </is>
-      </c>
-      <c r="J342" s="2" t="inlineStr">
-        <is>
-          <t>Press-and-hold para carregar. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone central (emoji) → ícone/logo 96x96 PNG (opcional). Totalmente CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K342" s="2" t="n"/>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B343" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C343" s="2" t="n"/>
-      <c r="D343" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Swipe Briefing</t>
-        </is>
-      </c>
-      <c r="E343" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F343" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G343" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H343" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I343" s="2" t="inlineStr">
-        <is>
-          <t>N afirmações (texto) + resultado.</t>
-        </is>
-      </c>
-      <c r="J343" s="2" t="inlineStr">
-        <is>
-          <t>Swipe cards (claro/vago). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ilustrações das cartas → imagens 260x300 (opcional; senão CSS). Cartas por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K343" s="2" t="n"/>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B344" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C344" s="2" t="n"/>
-      <c r="D344" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Calculadora Contactos</t>
-        </is>
-      </c>
-      <c r="E344" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F344" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G344" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H344" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I344" s="2" t="inlineStr">
-        <is>
-          <t>Labels dos campos + enunciado + resultado.</t>
-        </is>
-      </c>
-      <c r="J344" s="2" t="inlineStr">
-        <is>
-          <t>Calculadora interativa. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícones dos campos (emoji) → ícones 48x48 PNG (opcional). Inputs e cálculo por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K344" s="2" t="n"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B345" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C345" s="2" t="n"/>
-      <c r="D345" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Tap Sinais</t>
-        </is>
-      </c>
-      <c r="E345" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F345" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H345" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I345" s="2" t="inlineStr">
-        <is>
-          <t>Enunciado + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J345" s="2" t="inlineStr">
-        <is>
-          <t>Tap rápido em alvos. Imagens necessárias: 0–4 (ícones-alvo, opcional). Substituível por asset real: Alvos (emoji) → ícones 96x96 PNG transparente da marca. Specs do asset: Ícones 96x96 PNG (opcional). Alvos por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K345" s="2" t="n"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B346" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C346" s="2" t="n"/>
-      <c r="D346" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Procura na Estratégia</t>
-        </is>
-      </c>
-      <c r="E346" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F346" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H346" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I346" s="2" t="inlineStr">
-        <is>
-          <t>Enunciado + itens a encontrar (labels) + final.</t>
-        </is>
-      </c>
-      <c r="J346" s="2" t="inlineStr">
-        <is>
-          <t>Encontra itens (procura visual). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Itens a encontrar (emoji) → ícones/mini-imagens 64x64 PNG. Grelha por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K346" s="2" t="n"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B347" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C347" s="2" t="n"/>
-      <c r="D347" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Método Havas</t>
-        </is>
-      </c>
-      <c r="E347" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F347" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G347" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H347" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I347" s="2" t="inlineStr">
-        <is>
-          <t>Instrução + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J347" s="2" t="inlineStr">
-        <is>
-          <t>Simon (sequência de memória). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Pads (cor) → cores da marca. Ícones por pad 64x64 PNG (opcional). Pads e sequência por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K347" s="2" t="n"/>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B348" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C348" s="2" t="n"/>
-      <c r="D348" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Palavra</t>
-        </is>
-      </c>
-      <c r="E348" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F348" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G348" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H348" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I348" s="2" t="inlineStr">
-        <is>
-          <t>Palavra-alvo + pista + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J348" s="2" t="inlineStr">
-        <is>
-          <t>Anagrama / ordenar letras. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/pista (emoji) → ícone 96x96 PNG (opcional). Letras por CSS. Definir palavra-chave da campanha. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K348" s="2" t="n"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B349" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C349" s="2" t="n"/>
-      <c r="D349" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Da Marca à Pessoa</t>
-        </is>
-      </c>
-      <c r="E349" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F349" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G349" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H349" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I349" s="2" t="inlineStr">
-        <is>
-          <t>Labels do percurso + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J349" s="2" t="inlineStr">
-        <is>
-          <t>Percurso animado marca→pessoa. Imagens necessárias: 0–1 (logótipo no início, opcional). Substituível por asset real: Início do percurso → logótipo 128x128. Fim → foto/ícone 'pessoa' 128x128 (opcional). Specs do asset: Logótipo 128x128 (opcional). Trajeto por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K349" s="2" t="n"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B350" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C350" s="2" t="n"/>
-      <c r="D350" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Slot Havas</t>
-        </is>
-      </c>
-      <c r="E350" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F350" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G350" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H350" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I350" s="2" t="inlineStr">
-        <is>
-          <t>Enunciado + linha de prémio + resultado.</t>
-        </is>
-      </c>
-      <c r="J350" s="2" t="inlineStr">
-        <is>
-          <t>Slot machine (3 rolos). Imagens necessárias: 0–3 (símbolos dos rolos, opcional). Substituível por asset real: Símbolos dos rolos (emoji) → 3+ ícones 96x96 PNG transparente (produtos/marca). Specs do asset: Símbolos 96x96 PNG transparente (opcional; senão emoji). Rolos e símbolos por CSS/emoji. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K350" s="2" t="n"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B351" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C351" s="2" t="n"/>
-      <c r="D351" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Verdade/Mito</t>
-        </is>
-      </c>
-      <c r="E351" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F351" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G351" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H351" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I351" s="2" t="inlineStr">
-        <is>
-          <t>5 afirmações + feedback por afirmação + resultado.</t>
-        </is>
-      </c>
-      <c r="J351" s="2" t="inlineStr">
-        <is>
-          <t>Quiz verdadeiro/falso (5 afirmações). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone das cartas (emoji) → ícone 96x96 PNG (opcional). Verde/vermelho mantêm-se (funcional). Semáforo verde/vermelho é funcional (manter). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K351" s="2" t="n"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B352" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C352" s="2" t="n"/>
-      <c r="D352" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Diferenças</t>
-        </is>
-      </c>
-      <c r="E352" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F352" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G352" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H352" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I352" s="2" t="inlineStr">
-        <is>
-          <t>Enunciado + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J352" s="2" t="inlineStr">
-        <is>
-          <t>Descobre as diferenças. Imagens necessárias: 2 imagens (A e B) — obrigatório se usado. Substituível por asset real: Já usa 2 imagens reais. Cliente envia o par 300x300 (senão versão ilustrada). Specs do asset: 2 imagens 300x300 quase idênticas (JPG/PNG). Se sem imagens do cliente, usa versão ilustrada. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome).</t>
-        </is>
-      </c>
-      <c r="K352" s="2" t="n"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B353" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C353" s="2" t="n"/>
-      <c r="D353" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Enche o Mapa</t>
-        </is>
-      </c>
-      <c r="E353" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F353" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G353" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H353" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I353" s="2" t="inlineStr">
-        <is>
-          <t>Enunciado + label + mensagem final.</t>
-        </is>
-      </c>
-      <c r="J353" s="2" t="inlineStr">
-        <is>
-          <t>Preencher barra/mapa por toques. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/label (emoji) → ícone 96x96 PNG (opcional). Barra por CSS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K353" s="2" t="n"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B354" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C354" s="2" t="n"/>
-      <c r="D354" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Configurador</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F354" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G354" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H354" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I354" s="2" t="inlineStr">
-        <is>
-          <t>6 labels de opção + enunciado + resumo.</t>
-        </is>
-      </c>
-      <c r="J354" s="2" t="inlineStr">
-        <is>
-          <t>Seletor de opções (configurar seleção). Imagens necessárias: 0–6 (ícones das opções, opcional). Substituível por asset real: Ícones das opções (emoji) → ícones 96x96 PNG transparente. Cores por opção → paleta da marca. Specs do asset: Ícones 96x96 (opcional; senão emoji). Cores por opção configuráveis. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K354" s="2" t="n"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B355" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C355" s="2" t="n"/>
-      <c r="D355" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Countdown</t>
-        </is>
-      </c>
-      <c r="E355" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F355" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G355" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H355" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I355" s="2" t="inlineStr">
-        <is>
-          <t>Título + subtítulo + CTA.</t>
-        </is>
-      </c>
-      <c r="J355" s="2" t="inlineStr">
-        <is>
-          <t>Contagem decrescente para data-alvo. Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone/fundo (emoji/CSS) → imagem de fundo 300x600 ou ícone 96x96 (opcional). Definir data-alvo por campanha (JS). Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K355" s="2" t="n"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B356" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C356" s="2" t="n"/>
-      <c r="D356" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Estimativa</t>
-        </is>
-      </c>
-      <c r="E356" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F356" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G356" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H356" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I356" s="2" t="inlineStr">
-        <is>
-          <t>Pergunta + valor de referência + resultado.</t>
-        </is>
-      </c>
-      <c r="J356" s="2" t="inlineStr">
-        <is>
-          <t>Adivinha o número (slider). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Ícone do enunciado (emoji) → ícone 96x96 PNG (opcional). Slider por CSS/JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K356" s="2" t="n"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B357" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C357" s="2" t="n"/>
-      <c r="D357" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Ranking</t>
-        </is>
-      </c>
-      <c r="E357" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F357" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G357" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H357" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I357" s="2" t="inlineStr">
-        <is>
-          <t>4 itens (labels) + enunciado + confirmação.</t>
-        </is>
-      </c>
-      <c r="J357" s="2" t="inlineStr">
-        <is>
-          <t>Ordenar prioridades (drag). Não precisa de nenhuma imagem obrigatória. Substituível por asset real: Emojis dos itens (🎯👥…) → ícones 48x48 PNG da marca (opcional). Itens arrastáveis por JS. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K357" s="2" t="n"/>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B358" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C358" s="2" t="n"/>
-      <c r="D358" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Carrossel Produtos</t>
-        </is>
-      </c>
-      <c r="E358" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F358" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G358" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H358" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I358" s="2" t="inlineStr">
-        <is>
-          <t>Por slide: título + subtítulo + 3 bullets + CTA.</t>
-        </is>
-      </c>
-      <c r="J358" s="2" t="inlineStr">
-        <is>
-          <t>Carrossel de produtos/cards. Imagens necessárias: 1 por slide (recomendado 3–5). Substituível por asset real: Já usa imagens reais (1 por slide). Cliente envia 3–5 imagens 300x300. Specs do asset: Imagens de produto 300x300 (JPG/PNG), fundo neutro. Nº de slides configurável. Peso soma todas as imagens. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K358" s="2" t="n"/>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="B359" s="2" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="C359" s="2" t="n"/>
-      <c r="D359" s="2" t="inlineStr">
-        <is>
-          <t>Prog - Displ.AI+ - Parallax</t>
-        </is>
-      </c>
-      <c r="E359" s="2" t="inlineStr">
-        <is>
-          <t>300x600 px (formato half-page / meia-página, vertical)</t>
-        </is>
-      </c>
-      <c r="F359" s="2" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="G359" s="2" t="inlineStr">
-        <is>
-          <t>150 KB polite load recomendado. Limite máximo por criativo: 5 MB — não exceder; imagens devem ser otimizadas.</t>
-        </is>
-      </c>
-      <c r="H359" s="2" t="inlineStr">
-        <is>
-          <t>HTML5 autocontido (index.html com tudo embutido em base64 — sem chamadas externas). Entregar em ZIP com o index.html na raiz, para deteção automática no DV360. clickTag configurado pela Havas (padrão CM360 + DV360) — o cliente só fornece o URL de destino. Sem autoplay de áudio; animação até 30″ recomendado. Compatível com Chrome, Edge, Safari e Firefox (últimas 2 versões).</t>
-        </is>
-      </c>
-      <c r="I359" s="2" t="inlineStr">
-        <is>
-          <t>Título + subtítulo + CTA.</t>
-        </is>
-      </c>
-      <c r="J359" s="2" t="inlineStr">
-        <is>
-          <t>Cena com camadas parallax. Imagens necessárias: 1–4 camadas (opcional). Substituível por asset real: Camadas ilustradas (CSS) → 1–4 PNG transparentes 420x420 da marca (produto/cena). Specs do asset: Camadas PNG transparente 420x420 (opcional; senão ilustração). Auto-scroll ping-pong. Sem leitura de scroll do host. Materiais sempre necessários, independentemente da mecânica: logótipo em PNG transparente (alta resolução), URL de destino completo (para o clickTag), copies finais revistos em PT-PT, cores da marca em HEX e, se aplicável, a tipografia da marca (.woff2 ou nome). O envio dos restantes assets (ícones/ilustrações) é sempre opcional — sem eles, usa-se o placeholder em emoji/CSS e o formato funciona à mesma.</t>
-        </is>
-      </c>
-      <c r="K359" s="2" t="n"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="2" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="B360" s="2" t="inlineStr">
-        <is>
-          <t>Genérico</t>
-        </is>
-      </c>
-      <c r="C360" s="2" t="n"/>
-      <c r="D360" s="2" t="inlineStr">
-        <is>
-          <t>Branded Content</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F360" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G360" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H360" s="2" t="inlineStr">
-        <is>
-          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
-        </is>
-      </c>
-      <c r="I360" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J360" s="2" t="inlineStr">
         <is>
           <t>É necessário enviar:
  - data da publicação?
@@ -16161,45 +14887,1059 @@
 - logotipo (jpeg pu png) com fundo transparente</t>
         </is>
       </c>
+      <c r="K334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="n"/>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>HomePage Banner</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="n"/>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="n"/>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático (Guapo) no fundo do ecrã principal da app, sempre com uma promoção de pelo menos 20% de desconto. Logo: altura até 150px, largura máx. 500px. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="n"/>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Food Wall Banner</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="n"/>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="n"/>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático no meio da loja Food Wall, focado em marcas de comida, sempre com uma promoção. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="n"/>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>In-store Banner</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>750x266px</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="n"/>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="n"/>
+      <c r="J337" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático em supermercados ou na parede do Glovo Market ("store wall"), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="n"/>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Shoppable Banner</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>750x422px</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="n"/>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="n"/>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>Banner localizado dentro de diferentes categorias das lojas (fora da categoria principal da marca), com os produtos a aparecer por baixo do banner — o utilizador pode adicioná-los diretamente ao cesto ou clicar no banner para ir à loja completa. Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="n"/>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Q-commerce Store Wall Banner</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>512x348px</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="n"/>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="n"/>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>Banner estático nas paredes das lojas de Groceries e Shops (Q-commerce), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="n"/>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>OTP Premium</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>1280x720px</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="n"/>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="n"/>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>Banner "skippable" (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, no fundo do ecrã, com uma secção de texto personalizável. O utilizador pode saltar o anúncio quando quiser. Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 20 carateres; CTA máx. 10 carateres. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Glovo</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="n"/>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>OTP Standard</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>1280x720px</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="n"/>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200KB</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="n"/>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>Banner (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, e depois de um OTP Premium ter sido saltado ("skipped"). Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 30 carateres; sem tagline. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="n"/>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Standard (Imagem)</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>320x50, 300x250, 728x90, 300x600, 160x600, 336x280, 970x250, 320x100, 320x480, 970x90, 468x60, 360x640, 120x600, 250x250, 180x150, 320x568</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="n"/>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 500 KB</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG; GIF animado até 30″</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="n"/>
+      <c r="J342" s="2" t="n"/>
+      <c r="K342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="n"/>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Vídeo</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="n"/>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>16:9, 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="n"/>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>Duração máx. 30″. Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="n"/>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Rich Media / Responsivo</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>1200x628px, 1200x1200px ou 800x1200px</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="n"/>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="n"/>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video). Pode incluir vídeo em vez de, ou além da, imagem: MP4, 1:1/16:9/9:16, máx. 25 MB, máx. 30″.</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="n"/>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - App Install</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Imagens: 1200x628px, 1200x1200px ou 800x1200px. Logo da app: proporção 1:1.</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>1:1, 16:9 ou 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPG ou MP4</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="n"/>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo opcional, máx. 30″.</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="n"/>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - Hero SKU</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Imagem de produto/branding: 1200x628px, 1200x1200px ou 800x1200px. Imagem de fundo: 300x250, 336x280, 300x600, 320x480, 160x600, 728x90, 970x250 ou 320x50px.</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="n"/>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="n"/>
+      <c r="J346" s="2" t="n"/>
+      <c r="K346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="n"/>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Criteo - 3.60</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>1200x628px, 1200x1200px ou 800x1200px — mín. 6 imagens do mesmo produto, em ângulos diferentes.</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>1:1, 2:3 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>PNG ou JPG</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="n"/>
+      <c r="J347" s="2" t="n"/>
+      <c r="K347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Forretas e Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="n"/>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Moldura (barra lateral direita)</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="n"/>
+      <c r="G348" s="2" t="n"/>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="n"/>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Forretas e Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="n"/>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Moldura (barra lateral esquerda)</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>200x700</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="n"/>
+      <c r="G349" s="2" t="n"/>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="n"/>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Descontos (Homepage)</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="n"/>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>940x120</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="n"/>
+      <c r="G350" s="2" t="n"/>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="n"/>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Forretas (Homepage)</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="n"/>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Moldura (topo)</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>1920x313</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="n"/>
+      <c r="G351" s="2" t="n"/>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, GIF ou PNG + fontes usadas</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="n"/>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Descontos</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="n"/>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Imagem Oferta e Native Ad — Cupão</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>468x351</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="n"/>
+      <c r="G352" s="2" t="n"/>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="n"/>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="n"/>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>HTML (Email)</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>600 ou 700px de largura; altura ao critério do cliente</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="n"/>
+      <c r="G353" s="2" t="n"/>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>HTML + imagens em JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="n"/>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>ClickProfit</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="n"/>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="n"/>
+      <c r="F354" s="2" t="n"/>
+      <c r="G354" s="2" t="n"/>
+      <c r="H354" s="2" t="n"/>
+      <c r="I354" s="2" t="n"/>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="n"/>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Native Ads (Imagem)</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>1200x674 (recomendado); mín. 400x350</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>16:9 (preferencial), 4:3 ou 1:1</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="n"/>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="n"/>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Motion Ads (Vídeo)</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>1067x600</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>MP4, MOV ou GIF</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="n"/>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="n"/>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (Imagem)</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="n"/>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>JPEG, JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="n"/>
+      <c r="J357" s="2" t="n"/>
+      <c r="K357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="n"/>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (Vídeo)</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="n"/>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200 MB</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="n"/>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="n"/>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display Hosted (HTML5)</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="n"/>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB (ZIP comprimido)</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="n"/>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Taboola</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="n"/>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Taboola - Display (Tag de 3ºs)</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="n"/>
+      <c r="G360" s="2" t="n"/>
+      <c r="H360" s="2" t="n"/>
+      <c r="I360" s="2" t="n"/>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
+        </is>
+      </c>
       <c r="K360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C361" s="2" t="n"/>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>HomePage Banner</t>
+          <t>Taboola - Carousel</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>1200x627</t>
         </is>
       </c>
       <c r="F361" s="2" t="n"/>
-      <c r="G361" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200KB</t>
-        </is>
-      </c>
-      <c r="H361" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
+      <c r="G361" s="2" t="n"/>
+      <c r="H361" s="2" t="n"/>
       <c r="I361" s="2" t="n"/>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>Banner estático (Guapo) no fundo do ecrã principal da app, sempre com uma promoção de pelo menos 20% de desconto. Logo: altura até 150px, largura máx. 500px. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
         </is>
       </c>
       <c r="K361" s="2" t="n"/>
@@ -16207,40 +15947,32 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C362" s="2" t="n"/>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Food Wall Banner</t>
+          <t>Taboola - Social Importer (Facebook/Instagram)</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>300x250 ou 300x600</t>
         </is>
       </c>
       <c r="F362" s="2" t="n"/>
-      <c r="G362" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200KB</t>
-        </is>
-      </c>
-      <c r="H362" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
+      <c r="G362" s="2" t="n"/>
+      <c r="H362" s="2" t="n"/>
       <c r="I362" s="2" t="n"/>
       <c r="J362" s="2" t="inlineStr">
         <is>
-          <t>Banner estático no meio da loja Food Wall, focado em marcas de comida, sempre com uma promoção. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
         </is>
       </c>
       <c r="K362" s="2" t="n"/>
@@ -16248,29 +15980,29 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Taboola</t>
         </is>
       </c>
       <c r="C363" s="2" t="n"/>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>In-store Banner</t>
-        </is>
-      </c>
-      <c r="E363" s="2" t="inlineStr">
-        <is>
-          <t>750x266px</t>
-        </is>
-      </c>
-      <c r="F363" s="2" t="n"/>
+          <t>Taboola - Vertical</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="n"/>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>4:5, 9:16 ou 1:2</t>
+        </is>
+      </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200KB</t>
+          <t>Máx. 5 MB</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -16279,50 +16011,34 @@
         </is>
       </c>
       <c r="I363" s="2" t="n"/>
-      <c r="J363" s="2" t="inlineStr">
-        <is>
-          <t>Banner estático em supermercados ou na parede do Glovo Market ("store wall"), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
-        </is>
-      </c>
+      <c r="J363" s="2" t="n"/>
       <c r="K363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C364" s="2" t="n"/>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Shoppable Banner</t>
-        </is>
-      </c>
-      <c r="E364" s="2" t="inlineStr">
-        <is>
-          <t>750x422px</t>
-        </is>
-      </c>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="n"/>
       <c r="F364" s="2" t="n"/>
-      <c r="G364" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200KB</t>
-        </is>
-      </c>
-      <c r="H364" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
+      <c r="G364" s="2" t="n"/>
+      <c r="H364" s="2" t="n"/>
       <c r="I364" s="2" t="n"/>
       <c r="J364" s="2" t="inlineStr">
         <is>
-          <t>Banner localizado dentro de diferentes categorias das lojas (fora da categoria principal da marca), com os produtos a aparecer por baixo do banner — o utilizador pode adicioná-los diretamente ao cesto ou clicar no banner para ir à loja completa. Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
         </is>
       </c>
       <c r="K364" s="2" t="n"/>
@@ -16330,40 +16046,36 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C365" s="2" t="n"/>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Q-commerce Store Wall Banner</t>
+          <t>Email / Newsletter</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>600px de largura (imagens)</t>
         </is>
       </c>
       <c r="F365" s="2" t="n"/>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200KB</t>
-        </is>
-      </c>
-      <c r="H365" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
+          <t>Imagens: recomendado máx. 200 KB</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="n"/>
       <c r="I365" s="2" t="n"/>
       <c r="J365" s="2" t="inlineStr">
         <is>
-          <t>Banner estático nas paredes das lojas de Groceries e Shops (Q-commerce), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
         </is>
       </c>
       <c r="K365" s="2" t="n"/>
@@ -16371,40 +16083,32 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>Suebi</t>
         </is>
       </c>
       <c r="C366" s="2" t="n"/>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>OTP Premium</t>
+          <t>Push Notification</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>1280x720px</t>
+          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
         </is>
       </c>
       <c r="F366" s="2" t="n"/>
-      <c r="G366" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200KB</t>
-        </is>
-      </c>
-      <c r="H366" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
+      <c r="G366" s="2" t="n"/>
+      <c r="H366" s="2" t="n"/>
       <c r="I366" s="2" t="n"/>
       <c r="J366" s="2" t="inlineStr">
         <is>
-          <t>Banner "skippable" (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, no fundo do ecrã, com uma secção de texto personalizável. O utilizador pode saltar o anúncio quando quiser. Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 20 carateres; CTA máx. 10 carateres. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
         </is>
       </c>
       <c r="K366" s="2" t="n"/>
@@ -16412,1020 +16116,42 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>RTB House</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Glovo</t>
+          <t>RTB House</t>
         </is>
       </c>
       <c r="C367" s="2" t="n"/>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>OTP Standard</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>1280x720px</t>
+          <t>300x600, 160x600, 336x280, 300x250, 320x50, 320x100, 970x250 ou 728x90</t>
         </is>
       </c>
       <c r="F367" s="2" t="n"/>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200KB</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>PNG, JPG, JPEG, GIF ou HTML</t>
         </is>
       </c>
       <c r="I367" s="2" t="n"/>
-      <c r="J367" s="2" t="inlineStr">
-        <is>
-          <t>Banner (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, e depois de um OTP Premium ter sido saltado ("skipped"). Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 30 carateres; sem tagline. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
-        </is>
-      </c>
+      <c r="J367" s="2" t="n"/>
       <c r="K367" s="2" t="n"/>
     </row>
-    <row r="368">
-      <c r="A368" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="B368" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="C368" s="2" t="n"/>
-      <c r="D368" s="2" t="inlineStr">
-        <is>
-          <t>Criteo - Standard (Imagem)</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>320x50, 300x250, 728x90, 300x600, 160x600, 336x280, 970x250, 320x100, 320x480, 970x90, 468x60, 360x640, 120x600, 250x250, 180x150, 320x568</t>
-        </is>
-      </c>
-      <c r="F368" s="2" t="n"/>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 500 KB</t>
-        </is>
-      </c>
-      <c r="H368" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG; GIF animado até 30″</t>
-        </is>
-      </c>
-      <c r="I368" s="2" t="n"/>
-      <c r="J368" s="2" t="n"/>
-      <c r="K368" s="2" t="n"/>
-    </row>
-    <row r="369">
-      <c r="A369" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="B369" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="C369" s="2" t="n"/>
-      <c r="D369" s="2" t="inlineStr">
-        <is>
-          <t>Criteo - Vídeo</t>
-        </is>
-      </c>
-      <c r="E369" s="2" t="n"/>
-      <c r="F369" s="2" t="inlineStr">
-        <is>
-          <t>16:9, 9:16 ou 1:1</t>
-        </is>
-      </c>
-      <c r="G369" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 25 MB</t>
-        </is>
-      </c>
-      <c r="H369" s="2" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="I369" s="2" t="n"/>
-      <c r="J369" s="2" t="inlineStr">
-        <is>
-          <t>Duração máx. 30″. Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
-        </is>
-      </c>
-      <c r="K369" s="2" t="n"/>
-    </row>
-    <row r="370">
-      <c r="A370" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="B370" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="C370" s="2" t="n"/>
-      <c r="D370" s="2" t="inlineStr">
-        <is>
-          <t>Criteo - Rich Media / Responsivo</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>1200x628px, 1200x1200px ou 800x1200px</t>
-        </is>
-      </c>
-      <c r="F370" s="2" t="n"/>
-      <c r="G370" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 1 MB</t>
-        </is>
-      </c>
-      <c r="H370" s="2" t="inlineStr">
-        <is>
-          <t>PNG ou JPG</t>
-        </is>
-      </c>
-      <c r="I370" s="2" t="n"/>
-      <c r="J370" s="2" t="inlineStr">
-        <is>
-          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video). Pode incluir vídeo em vez de, ou além da, imagem: MP4, 1:1/16:9/9:16, máx. 25 MB, máx. 30″.</t>
-        </is>
-      </c>
-      <c r="K370" s="2" t="n"/>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="B371" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="C371" s="2" t="n"/>
-      <c r="D371" s="2" t="inlineStr">
-        <is>
-          <t>Criteo - App Install</t>
-        </is>
-      </c>
-      <c r="E371" s="2" t="inlineStr">
-        <is>
-          <t>Imagens: 1200x628px, 1200x1200px ou 800x1200px. Logo da app: proporção 1:1.</t>
-        </is>
-      </c>
-      <c r="F371" s="2" t="inlineStr">
-        <is>
-          <t>1:1, 16:9 ou 9:16 (vídeo)</t>
-        </is>
-      </c>
-      <c r="G371" s="2" t="inlineStr">
-        <is>
-          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB</t>
-        </is>
-      </c>
-      <c r="H371" s="2" t="inlineStr">
-        <is>
-          <t>PNG, JPG ou MP4</t>
-        </is>
-      </c>
-      <c r="I371" s="2" t="n"/>
-      <c r="J371" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo opcional, máx. 30″.</t>
-        </is>
-      </c>
-      <c r="K371" s="2" t="n"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="B372" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="C372" s="2" t="n"/>
-      <c r="D372" s="2" t="inlineStr">
-        <is>
-          <t>Criteo - Hero SKU</t>
-        </is>
-      </c>
-      <c r="E372" s="2" t="inlineStr">
-        <is>
-          <t>Imagem de produto/branding: 1200x628px, 1200x1200px ou 800x1200px. Imagem de fundo: 300x250, 336x280, 300x600, 320x480, 160x600, 728x90, 970x250 ou 320x50px.</t>
-        </is>
-      </c>
-      <c r="F372" s="2" t="n"/>
-      <c r="G372" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 1 MB</t>
-        </is>
-      </c>
-      <c r="H372" s="2" t="inlineStr">
-        <is>
-          <t>PNG ou JPG</t>
-        </is>
-      </c>
-      <c r="I372" s="2" t="n"/>
-      <c r="J372" s="2" t="n"/>
-      <c r="K372" s="2" t="n"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="B373" s="2" t="inlineStr">
-        <is>
-          <t>Criteo</t>
-        </is>
-      </c>
-      <c r="C373" s="2" t="n"/>
-      <c r="D373" s="2" t="inlineStr">
-        <is>
-          <t>Criteo - 3.60</t>
-        </is>
-      </c>
-      <c r="E373" s="2" t="inlineStr">
-        <is>
-          <t>1200x628px, 1200x1200px ou 800x1200px — mín. 6 imagens do mesmo produto, em ângulos diferentes.</t>
-        </is>
-      </c>
-      <c r="F373" s="2" t="inlineStr">
-        <is>
-          <t>1:1, 2:3 ou 1.91:1</t>
-        </is>
-      </c>
-      <c r="G373" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 1 MB</t>
-        </is>
-      </c>
-      <c r="H373" s="2" t="inlineStr">
-        <is>
-          <t>PNG ou JPG</t>
-        </is>
-      </c>
-      <c r="I373" s="2" t="n"/>
-      <c r="J373" s="2" t="n"/>
-      <c r="K373" s="2" t="n"/>
-    </row>
-    <row r="374">
-      <c r="A374" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="B374" s="2" t="inlineStr">
-        <is>
-          <t>Forretas e Descontos (Homepage)</t>
-        </is>
-      </c>
-      <c r="C374" s="2" t="n"/>
-      <c r="D374" s="2" t="inlineStr">
-        <is>
-          <t>Moldura (barra lateral direita)</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr">
-        <is>
-          <t>200x700</t>
-        </is>
-      </c>
-      <c r="F374" s="2" t="n"/>
-      <c r="G374" s="2" t="n"/>
-      <c r="H374" s="2" t="inlineStr">
-        <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
-        </is>
-      </c>
-      <c r="I374" s="2" t="n"/>
-      <c r="J374" s="2" t="inlineStr">
-        <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
-      <c r="K374" s="2" t="n"/>
-    </row>
-    <row r="375">
-      <c r="A375" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="B375" s="2" t="inlineStr">
-        <is>
-          <t>Forretas e Descontos (Homepage)</t>
-        </is>
-      </c>
-      <c r="C375" s="2" t="n"/>
-      <c r="D375" s="2" t="inlineStr">
-        <is>
-          <t>Moldura (barra lateral esquerda)</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr">
-        <is>
-          <t>200x700</t>
-        </is>
-      </c>
-      <c r="F375" s="2" t="n"/>
-      <c r="G375" s="2" t="n"/>
-      <c r="H375" s="2" t="inlineStr">
-        <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
-        </is>
-      </c>
-      <c r="I375" s="2" t="n"/>
-      <c r="J375" s="2" t="inlineStr">
-        <is>
-          <t>O Take Over é composto por 3 peças: barra lateral direita, barra lateral esquerda e topo. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
-      <c r="K375" s="2" t="n"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="B376" s="2" t="inlineStr">
-        <is>
-          <t>Descontos (Homepage)</t>
-        </is>
-      </c>
-      <c r="C376" s="2" t="n"/>
-      <c r="D376" s="2" t="inlineStr">
-        <is>
-          <t>Moldura (topo)</t>
-        </is>
-      </c>
-      <c r="E376" s="2" t="inlineStr">
-        <is>
-          <t>940x120</t>
-        </is>
-      </c>
-      <c r="F376" s="2" t="n"/>
-      <c r="G376" s="2" t="n"/>
-      <c r="H376" s="2" t="inlineStr">
-        <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
-        </is>
-      </c>
-      <c r="I376" s="2" t="n"/>
-      <c r="J376" s="2" t="inlineStr">
-        <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
-      <c r="K376" s="2" t="n"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="B377" s="2" t="inlineStr">
-        <is>
-          <t>Forretas (Homepage)</t>
-        </is>
-      </c>
-      <c r="C377" s="2" t="n"/>
-      <c r="D377" s="2" t="inlineStr">
-        <is>
-          <t>Moldura (topo)</t>
-        </is>
-      </c>
-      <c r="E377" s="2" t="inlineStr">
-        <is>
-          <t>1920x313</t>
-        </is>
-      </c>
-      <c r="F377" s="2" t="n"/>
-      <c r="G377" s="2" t="n"/>
-      <c r="H377" s="2" t="inlineStr">
-        <is>
-          <t>JPEG, GIF ou PNG + fontes usadas</t>
-        </is>
-      </c>
-      <c r="I377" s="2" t="n"/>
-      <c r="J377" s="2" t="inlineStr">
-        <is>
-          <t>O topo tem de ter em conta os elementos fixos do site, que não serão sobrepostos. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
-      <c r="K377" s="2" t="n"/>
-    </row>
-    <row r="378">
-      <c r="A378" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="B378" s="2" t="inlineStr">
-        <is>
-          <t>Descontos</t>
-        </is>
-      </c>
-      <c r="C378" s="2" t="n"/>
-      <c r="D378" s="2" t="inlineStr">
-        <is>
-          <t>Imagem Oferta e Native Ad — Cupão</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr">
-        <is>
-          <t>468x351</t>
-        </is>
-      </c>
-      <c r="F378" s="2" t="n"/>
-      <c r="G378" s="2" t="n"/>
-      <c r="H378" s="2" t="inlineStr">
-        <is>
-          <t>JPEG ou PNG</t>
-        </is>
-      </c>
-      <c r="I378" s="2" t="n"/>
-      <c r="J378" s="2" t="inlineStr">
-        <is>
-          <t>Imagem identificativa da oferta. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
-      <c r="K378" s="2" t="n"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="B379" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="C379" s="2" t="n"/>
-      <c r="D379" s="2" t="inlineStr">
-        <is>
-          <t>HTML (Email)</t>
-        </is>
-      </c>
-      <c r="E379" s="2" t="inlineStr">
-        <is>
-          <t>600 ou 700px de largura; altura ao critério do cliente</t>
-        </is>
-      </c>
-      <c r="F379" s="2" t="n"/>
-      <c r="G379" s="2" t="n"/>
-      <c r="H379" s="2" t="inlineStr">
-        <is>
-          <t>HTML + imagens em JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="I379" s="2" t="n"/>
-      <c r="J379" s="2" t="inlineStr">
-        <is>
-          <t>Enviar subject e sender. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
-      <c r="K379" s="2" t="n"/>
-    </row>
-    <row r="380">
-      <c r="A380" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="B380" s="2" t="inlineStr">
-        <is>
-          <t>ClickProfit</t>
-        </is>
-      </c>
-      <c r="C380" s="2" t="n"/>
-      <c r="D380" s="2" t="inlineStr">
-        <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="n"/>
-      <c r="F380" s="2" t="n"/>
-      <c r="G380" s="2" t="n"/>
-      <c r="H380" s="2" t="n"/>
-      <c r="I380" s="2" t="n"/>
-      <c r="J380" s="2" t="inlineStr">
-        <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
-        </is>
-      </c>
-      <c r="K380" s="2" t="n"/>
-    </row>
-    <row r="381">
-      <c r="A381" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B381" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C381" s="2" t="n"/>
-      <c r="D381" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Native Ads (Imagem)</t>
-        </is>
-      </c>
-      <c r="E381" s="2" t="inlineStr">
-        <is>
-          <t>1200x674 (recomendado); mín. 400x350</t>
-        </is>
-      </c>
-      <c r="F381" s="2" t="inlineStr">
-        <is>
-          <t>16:9 (preferencial), 4:3 ou 1:1</t>
-        </is>
-      </c>
-      <c r="G381" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="H381" s="2" t="inlineStr">
-        <is>
-          <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="n"/>
-      <c r="J381" s="2" t="inlineStr">
-        <is>
-          <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
-        </is>
-      </c>
-      <c r="K381" s="2" t="n"/>
-    </row>
-    <row r="382">
-      <c r="A382" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B382" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C382" s="2" t="n"/>
-      <c r="D382" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Motion Ads (Vídeo)</t>
-        </is>
-      </c>
-      <c r="E382" s="2" t="inlineStr">
-        <is>
-          <t>1067x600</t>
-        </is>
-      </c>
-      <c r="F382" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="G382" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
-        </is>
-      </c>
-      <c r="H382" s="2" t="inlineStr">
-        <is>
-          <t>MP4, MOV ou GIF</t>
-        </is>
-      </c>
-      <c r="I382" s="2" t="n"/>
-      <c r="J382" s="2" t="inlineStr">
-        <is>
-          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
-        </is>
-      </c>
-      <c r="K382" s="2" t="n"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B383" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C383" s="2" t="n"/>
-      <c r="D383" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Display Hosted (Imagem)</t>
-        </is>
-      </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="F383" s="2" t="n"/>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 2 MB</t>
-        </is>
-      </c>
-      <c r="H383" s="2" t="inlineStr">
-        <is>
-          <t>JPEG, JPG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="I383" s="2" t="n"/>
-      <c r="J383" s="2" t="n"/>
-      <c r="K383" s="2" t="n"/>
-    </row>
-    <row r="384">
-      <c r="A384" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B384" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C384" s="2" t="n"/>
-      <c r="D384" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Display Hosted (Vídeo)</t>
-        </is>
-      </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="F384" s="2" t="n"/>
-      <c r="G384" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 200 MB</t>
-        </is>
-      </c>
-      <c r="H384" s="2" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="I384" s="2" t="n"/>
-      <c r="J384" s="2" t="inlineStr">
-        <is>
-          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
-        </is>
-      </c>
-      <c r="K384" s="2" t="n"/>
-    </row>
-    <row r="385">
-      <c r="A385" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B385" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C385" s="2" t="n"/>
-      <c r="D385" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Display Hosted (HTML5)</t>
-        </is>
-      </c>
-      <c r="E385" s="2" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="F385" s="2" t="n"/>
-      <c r="G385" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 2 MB (ZIP comprimido)</t>
-        </is>
-      </c>
-      <c r="H385" s="2" t="inlineStr">
-        <is>
-          <t>ZIP (HTML, JS, CSS, JPG, JPEG, GIF, PNG, SVG; máx. 100 ficheiros); index.html na raiz</t>
-        </is>
-      </c>
-      <c r="I385" s="2" t="n"/>
-      <c r="J385" s="2" t="inlineStr">
-        <is>
-          <t>Tem de incluir uma imagem estática de recurso (JPG, PNG ou GIF) para browsers sem JavaScript.</t>
-        </is>
-      </c>
-      <c r="K385" s="2" t="n"/>
-    </row>
-    <row r="386">
-      <c r="A386" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B386" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C386" s="2" t="n"/>
-      <c r="D386" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Display (Tag de 3ºs)</t>
-        </is>
-      </c>
-      <c r="E386" s="2" t="inlineStr">
-        <is>
-          <t>Tamanhos standard IAB: 300x250, 300x600, 320x50, 728x90, 970x250, 160x600 ou 250x250</t>
-        </is>
-      </c>
-      <c r="F386" s="2" t="n"/>
-      <c r="G386" s="2" t="n"/>
-      <c r="H386" s="2" t="n"/>
-      <c r="I386" s="2" t="n"/>
-      <c r="J386" s="2" t="inlineStr">
-        <is>
-          <t>Ad servers aceites: DCM e Adform. Macros de clique obrigatórias quando a tag não é reconhecida automaticamente.</t>
-        </is>
-      </c>
-      <c r="K386" s="2" t="n"/>
-    </row>
-    <row r="387">
-      <c r="A387" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B387" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C387" s="2" t="n"/>
-      <c r="D387" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Carousel</t>
-        </is>
-      </c>
-      <c r="E387" s="2" t="inlineStr">
-        <is>
-          <t>1200x627</t>
-        </is>
-      </c>
-      <c r="F387" s="2" t="n"/>
-      <c r="G387" s="2" t="n"/>
-      <c r="H387" s="2" t="n"/>
-      <c r="I387" s="2" t="n"/>
-      <c r="J387" s="2" t="inlineStr">
-        <is>
-          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
-        </is>
-      </c>
-      <c r="K387" s="2" t="n"/>
-    </row>
-    <row r="388">
-      <c r="A388" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B388" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C388" s="2" t="n"/>
-      <c r="D388" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Social Importer (Facebook/Instagram)</t>
-        </is>
-      </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>300x250 ou 300x600</t>
-        </is>
-      </c>
-      <c r="F388" s="2" t="n"/>
-      <c r="G388" s="2" t="n"/>
-      <c r="H388" s="2" t="n"/>
-      <c r="I388" s="2" t="n"/>
-      <c r="J388" s="2" t="inlineStr">
-        <is>
-          <t>Anúncio importado diretamente do Facebook/Instagram a partir do ID da Meta Ad Library (16 dígitos) — não editável, aparece exatamente como no social.</t>
-        </is>
-      </c>
-      <c r="K388" s="2" t="n"/>
-    </row>
-    <row r="389">
-      <c r="A389" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="B389" s="2" t="inlineStr">
-        <is>
-          <t>Taboola</t>
-        </is>
-      </c>
-      <c r="C389" s="2" t="n"/>
-      <c r="D389" s="2" t="inlineStr">
-        <is>
-          <t>Taboola - Vertical</t>
-        </is>
-      </c>
-      <c r="E389" s="2" t="n"/>
-      <c r="F389" s="2" t="inlineStr">
-        <is>
-          <t>4:5, 9:16 ou 1:2</t>
-        </is>
-      </c>
-      <c r="G389" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 5 MB</t>
-        </is>
-      </c>
-      <c r="H389" s="2" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="I389" s="2" t="n"/>
-      <c r="J389" s="2" t="n"/>
-      <c r="K389" s="2" t="n"/>
-    </row>
-    <row r="390">
-      <c r="A390" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="B390" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="C390" s="2" t="n"/>
-      <c r="D390" s="2" t="inlineStr">
-        <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="E390" s="2" t="n"/>
-      <c r="F390" s="2" t="n"/>
-      <c r="G390" s="2" t="n"/>
-      <c r="H390" s="2" t="n"/>
-      <c r="I390" s="2" t="n"/>
-      <c r="J390" s="2" t="inlineStr">
-        <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
-        </is>
-      </c>
-      <c r="K390" s="2" t="n"/>
-    </row>
-    <row r="391">
-      <c r="A391" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="B391" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="C391" s="2" t="n"/>
-      <c r="D391" s="2" t="inlineStr">
-        <is>
-          <t>Email / Newsletter</t>
-        </is>
-      </c>
-      <c r="E391" s="2" t="inlineStr">
-        <is>
-          <t>600px de largura (imagens)</t>
-        </is>
-      </c>
-      <c r="F391" s="2" t="n"/>
-      <c r="G391" s="2" t="inlineStr">
-        <is>
-          <t>Imagens: recomendado máx. 200 KB</t>
-        </is>
-      </c>
-      <c r="H391" s="2" t="n"/>
-      <c r="I391" s="2" t="n"/>
-      <c r="J391" s="2" t="inlineStr">
-        <is>
-          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
-        </is>
-      </c>
-      <c r="K391" s="2" t="n"/>
-    </row>
-    <row r="392">
-      <c r="A392" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="B392" s="2" t="inlineStr">
-        <is>
-          <t>Suebi</t>
-        </is>
-      </c>
-      <c r="C392" s="2" t="n"/>
-      <c r="D392" s="2" t="inlineStr">
-        <is>
-          <t>Push Notification</t>
-        </is>
-      </c>
-      <c r="E392" s="2" t="inlineStr">
-        <is>
-          <t>Logo 1:1; imagem opcional 512x256 ou 1024x512</t>
-        </is>
-      </c>
-      <c r="F392" s="2" t="n"/>
-      <c r="G392" s="2" t="n"/>
-      <c r="H392" s="2" t="n"/>
-      <c r="I392" s="2" t="n"/>
-      <c r="J392" s="2" t="inlineStr">
-        <is>
-          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
-        </is>
-      </c>
-      <c r="K392" s="2" t="n"/>
-    </row>
-    <row r="393">
-      <c r="A393" s="2" t="inlineStr">
-        <is>
-          <t>RTB House</t>
-        </is>
-      </c>
-      <c r="B393" s="2" t="inlineStr">
-        <is>
-          <t>RTB House</t>
-        </is>
-      </c>
-      <c r="C393" s="2" t="n"/>
-      <c r="D393" s="2" t="inlineStr">
-        <is>
-          <t>Display</t>
-        </is>
-      </c>
-      <c r="E393" s="2" t="inlineStr">
-        <is>
-          <t>300x600, 160x600, 336x280, 300x250, 320x50, 320x100, 970x250 ou 728x90</t>
-        </is>
-      </c>
-      <c r="F393" s="2" t="n"/>
-      <c r="G393" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 1 MB</t>
-        </is>
-      </c>
-      <c r="H393" s="2" t="inlineStr">
-        <is>
-          <t>PNG, JPG, JPEG, GIF ou HTML</t>
-        </is>
-      </c>
-      <c r="I393" s="2" t="n"/>
-      <c r="J393" s="2" t="n"/>
-      <c r="K393" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K393"/>
+  <autoFilter ref="A1:K367"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -16475,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18221,26 +18221,34 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Clearspot</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Especificações por confirmar</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
+          <t>Grande Formato</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Escala 1:10.</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de Clearspot ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
         </is>
       </c>
       <c r="I48" s="2" t="n"/>
@@ -18248,26 +18256,34 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CS Outdoors</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CS Outdoors</t>
+          <t>3D Lab</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Especificações por confirmar</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n"/>
+          <t>Rede Highway</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>10,15x5,15m. Escala 1:10.</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Concessionária adicionada à base para já sem formatos associados — as especificações técnicas de CS Outdoors ainda não foram fornecidas. Atualizar esta linha (e acrescentar as linhas de formato que fizerem falta) assim que a informação chegar.</t>
+          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
         </is>
       </c>
       <c r="I49" s="2" t="n"/>
@@ -18285,7 +18301,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Grande Formato</t>
+          <t>Rede LED</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -18302,7 +18318,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+          <t>Cor: modo RGB. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 100 dpi.</t>
         </is>
       </c>
       <c r="I50" s="2" t="n"/>
@@ -18310,34 +18326,42 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Unimidia</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Rede Highway</t>
+          <t>Mupi Digital | Universidades</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>10,15x5,15m. Escala 1:10.</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
+          <t>Tamanho total: 1080x1920px. Área visível: 1080x1920px.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 10MB (vídeo produzido pelo cliente).</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+          <t>Produzido pela Unimidia (material por camadas): .psd, .ai ou .indd, fotografias/imagens com resolução superior a 150dpi, texto convertido em curvas — sujeito a apresentação de orçamento. Produzido pelo cliente (vídeo pronto): .avi, .mp4, .mov, .mpeg, .mpg ou .jpeg, resolução 1080x1920px, 25 frames por segundo, em formato vertical.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Cor: modo CMYK. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 450 dpi.</t>
+          <t>Duração máxima: 10 segundos. Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
         </is>
       </c>
       <c r="I51" s="2" t="n"/>
@@ -18345,34 +18369,34 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>3D Lab</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Rede LED</t>
+          <t>Táxi Açores - Lateral Direita</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Escala 1:10.</t>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
         </is>
       </c>
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>TIFF ou JPEG — aconselhável também o envio em PDF editável.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Cor: modo RGB. Fontes convertidas em curvas (ficheiros vetoriais) ou fonte enviada junto com o ficheiro. Resolução: 100 dpi.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
         </is>
       </c>
       <c r="I52" s="2" t="n"/>
@@ -18385,37 +18409,29 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Unimidia</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Mupi Digital | Universidades</t>
+          <t>Táxi Açores - Lateral Esquerda</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tamanho total: 1080x1920px. Área visível: 1080x1920px.</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 10MB (vídeo produzido pelo cliente).</t>
-        </is>
-      </c>
+          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Produzido pela Unimidia (material por camadas): .psd, .ai ou .indd, fotografias/imagens com resolução superior a 150dpi, texto convertido em curvas — sujeito a apresentação de orçamento. Produzido pelo cliente (vídeo pronto): .avi, .mp4, .mov, .mpeg, .mpg ou .jpeg, resolução 1080x1920px, 25 frames por segundo, em formato vertical.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Duração máxima: 10 segundos. Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
         </is>
       </c>
       <c r="I53" s="2" t="n"/>
@@ -18433,12 +18449,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Táxi Açores - Lateral Direita</t>
+          <t>Táxi Doorcover - Lateral Direita</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
@@ -18450,7 +18466,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
         </is>
       </c>
       <c r="I54" s="2" t="n"/>
@@ -18468,12 +18484,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Táxi Açores - Lateral Esquerda</t>
+          <t>Táxi Doorcover - Lateral Esquerda</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Cortante: 1650x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
         </is>
       </c>
       <c r="E55" s="2" t="n"/>
@@ -18485,7 +18501,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Considerar uma margem de segurança sobre os limites visíveis, para evitar perda de informação vital.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
         </is>
       </c>
       <c r="I55" s="2" t="n"/>
@@ -18503,24 +18519,24 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Táxi Doorcover - Lateral Direita</t>
+          <t>Táxi Indoor - Flyer</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Altura (sem margem): 20cm. Largura (sem margem): 10cm.</t>
         </is>
       </c>
       <c r="E56" s="2" t="n"/>
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
         </is>
       </c>
       <c r="I56" s="2" t="n"/>
@@ -18538,24 +18554,24 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Táxi Doorcover - Lateral Esquerda</t>
+          <t>Táxi Indoor - Banner</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Cortante: 2200x750mm. Área visível variável consoante o ano/modelo da viatura.</t>
+          <t>Impressão: 34x12,6cm (largura x altura). Área visível: 37,5x15cm (largura x altura).</t>
         </is>
       </c>
       <c r="E57" s="2" t="n"/>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
         </is>
       </c>
       <c r="I57" s="2" t="n"/>
@@ -18563,34 +18579,38 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Unimidia/Spreading</t>
+          <t>Shine Care</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Shine Care</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Táxi Indoor - Flyer</t>
+          <t>Mupi Digital</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Altura (sem margem): 20cm. Largura (sem margem): 10cm.</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n"/>
+          <t>1080x1920px.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+          <t>MP4.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+          <t>Duração: 10 segundos. Frame rate: 30 frames por segundo. Rede de mupis digitais em hospitais e clínicas.</t>
         </is>
       </c>
       <c r="I58" s="2" t="n"/>
@@ -18598,34 +18618,38 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Unimidia/Spreading</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Spreading</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Táxi Indoor - Banner</t>
+          <t>Ecrã Horizontal</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Impressão: 34x12,6cm (largura x altura). Área visível: 37,5x15cm (largura x altura).</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n"/>
+          <t>1920x1080px.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros PDF, EPS ou TIFF.</t>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido.</t>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
         </is>
       </c>
       <c r="I59" s="2" t="n"/>
@@ -18633,17 +18657,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Shine Care</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Shine Care</t>
+          <t>Media Play</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Mupi Digital</t>
+          <t>Ecrã Vertical</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -18659,12 +18683,12 @@
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>MP4.</t>
+          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos. Frame rate: 30 frames por segundo. Rede de mupis digitais em hospitais e clínicas.</t>
+          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
         </is>
       </c>
       <c r="I60" s="2" t="n"/>
@@ -18672,79 +18696,63 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ecrã Horizontal</t>
+          <t>Mupis Digitais</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1920x1080px.</t>
+          <t>Mupi de pé (estrutura autónoma): 202cm de altura total, 73cm de largura. Ecrã de 50″, com 107cm de altura visível, posicionado a 83,5cm do chão; margens de 11cm (topo) e 7cm (laterais do ecrã).</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
-        </is>
-      </c>
+          <t>Conteúdo: 1080x1920px, MP4.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Media Play</t>
+          <t>Tequilha</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ecrã Vertical</t>
+          <t>Mupis Tradicionais</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1080x1920px.</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
+          <t>80cm (largura) x 120cm (altura). Área total = área visível.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
     </row>
     <row r="63">
@@ -18760,166 +18768,104 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Mupis Digitais</t>
+          <t>Ecrãs de Cinema Universidades</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Mupi de pé (estrutura autónoma): 202cm de altura total, 73cm de largura. Ecrã de 50″, com 107cm de altura visível, posicionado a 83,5cm do chão; margens de 11cm (topo) e 7cm (laterais do ecrã).</t>
+          <t>Ecrã de 50″.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Conteúdo: 1080x1920px, MP4.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="n"/>
+          <t>Conteúdo: 1920x1080px, MP4.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Estes ecrãs passam trailers de filmes; entre os trailers, passam spots de TV dos parceiros, incluindo a Tequilha.</t>
+        </is>
+      </c>
       <c r="I63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Mupis Tradicionais</t>
+          <t>Táxi Doorcover Madeira - Lateral Direita</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>80cm (largura) x 120cm (altura). Área total = área visível.</t>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Unimidia/Spreading</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Tequilha</t>
+          <t>Spreading</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Ecrãs de Cinema Universidades</t>
+          <t>Táxi Doorcover Madeira - Lateral Esquerda</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Ecrã de 50″.</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Conteúdo: 1920x1080px, MP4.</t>
+          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Estes ecrãs passam trailers de filmes; entre os trailers, passam spots de TV dos parceiros, incluindo a Tequilha.</t>
+          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
         </is>
       </c>
       <c r="I65" s="2" t="n"/>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Unimidia/Spreading</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Spreading</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Táxi Doorcover Madeira - Lateral Direita</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Unimidia/Spreading</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Spreading</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Táxi Doorcover Madeira - Lateral Esquerda</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Escala 1/10. Área visível variável consoante o ano/modelo da viatura (táxis da Madeira).</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>InDesign CS3, Illustrator CS3, Photoshop CS3 ou PDF. Ficheiros EPS ou TIFF.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Artes finais gravadas em CMYK, com resolução mínima 300 dpi e máxima 450 dpi, pelo menos com 50% do tamanho pretendido. Textos convertidos em curvas, a acompanhar de prova de cor. Prazo de entrega das artes finais: até 6 dias úteis antes da ação/campanha — a Spreading não se responsabiliza por atrasos na produção/campanha se este prazo não for cumprido. Margem de segurança de 5 a 10cm sobre os limites visíveis; considerar a mesma margem junto aos puxadores das portas.</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:I65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -16475,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18864,8 +18864,195 @@
       </c>
       <c r="I65" s="2" t="n"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Hero Header (Newsletter)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>600x400</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Canal: Newsletter. Indicar título e texto no corpo do email — curtos, diretos ao tema, a captar a curiosidade do leitor. CTA: Comprar ou Saiba mais. Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Ledwall Vídeo (Ecospot — Parque de Estacionamento)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>384x512, 672x672 ou 1920x1080</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 150 MB</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264 (livraria x264), bitrate &lt; 3000</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Ledwall Imagem (Ecospot — Parque de Estacionamento)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>384x512, 672x672 ou 1920x1080</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>JPG e/ou PNG, modo de cor RGB, resolução 72dpi</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Image Advertising (Continente Feed)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 1312x320; Tablet: 959x256; Mobile: 735x413</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Image + Video Advertising (Continente Feed)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Imagem — Desktop: 743x320, Tablet: 503x256, Mobile: 503x256. Vídeo — Desktop: 569x320, Tablet: 456x256, Mobile: 735x413.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB (imagem; peso do vídeo não indicado)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG (imagem; formato do vídeo não indicado)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I65"/>
+  <autoFilter ref="A1:I70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -16475,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19051,8 +19051,203 @@
       </c>
       <c r="I70" s="2" t="n"/>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Banner Cupão Plus (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>458x236</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Cupões.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Banner Cupão (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>458x112</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Cupões.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Banner Usar Cartão (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>458x112</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Usar Cartão.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Banner Destaques (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Banner Vantagens/Folhetos (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>654x240</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I70"/>
+  <autoFilter ref="A1:I75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -18893,7 +18893,11 @@
           <t>Canal: Newsletter. Indicar título e texto no corpo do email — curtos, diretos ao tema, a captar a curiosidade do leitor. CTA: Comprar ou Saiba mais. Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Header-397e4d8f0b1880c78e1ce86047334b9d</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -18932,7 +18936,11 @@
           <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Ledwall-Video-123e4d8f0b188253b2e481717ab1e89d</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -18971,7 +18979,11 @@
           <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Ledwall-179e4d8f0b18839bbee701966fbfe361</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -19010,7 +19022,11 @@
           <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Image-Advertising-3f3e4d8f0b1880da8163f327a16c13f2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -19049,7 +19065,11 @@
           <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Image-Video-Advertising-3f7e4d8f0b1880c4b983f2a3a7e2723d</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -19248,6 +19268,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I75"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -16475,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19266,14 +19266,230 @@
       </c>
       <c r="I75" s="2" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Video Ads - Auto Play (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Homepage, Plug&amp;Charge.</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Video-Ads-Auto-Play-106e4d8f0b1882a98475014f0da845d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Banner Plug&amp;Charge (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Plug&amp;Charge.</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Plug-Charge-3cee4d8f0b1880bf9363e9d7a56da35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Sponsored Products Display (App Continente)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>456x1140</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Product Grid.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-90fe4d8f0b18835ca782816027b56ee2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Banner Ecrã Loja (App Continente)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>345x109</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Em loja.</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Ecr-Loja-3ece4d8f0b1880db8984c5d9c585137c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Hero Banner (App Continente)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>1029x516</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Banner-651e4d8f0b18836d92ca8117823842cc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -16475,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19477,8 +19477,137 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Banner Oportunidades (App Continente)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>1029x772</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Oportunidades. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Oportunidades-ecfe4d8f0b1882f6978c81988921c3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Top Banner (Continente Online)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 1320x132; Tablet: 720x124; Mobile: 345x115</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Homepage, Folhetos, Oportunidades.</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Top-Banner-2abe4d8f0b1882fdb5b1817348bac988</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Sponsored Products Display (Continente Online)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 172x431; Mobile: 160x431</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Product Grid.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-307e4d8f0b18832cb4ed81b572620cab</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I80"/>
+  <autoFilter ref="A1:I83"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>
@@ -19490,6 +19619,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -16475,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19606,8 +19606,39 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Sponsored Products (Continente Online)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Não necessita de criatividades — enviar idealmente até 4 SKUs por posicionamento. Keyword Search (Pesquisa): produtos visíveis na zona de pesquisa, associados às keywords da campanha. Destaque Produto Categoria (Product Grid): produtos visíveis na página de categoria. Destaque Produto Homepage (Destaques): produtos visíveis na Homepage, na zona de destaques de produtos.</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-61be4d8f0b18820a9a8d81a25c6be12d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I83"/>
+  <autoFilter ref="A1:I84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>
@@ -19622,6 +19653,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -16475,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19637,8 +19637,207 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Banner Pesquisa (Continente Online)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>320x100 (Desktop, Tablet e Mobile)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Categoria.</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Pesquisa-e4ee4d8f0b188272a6f101cfdd8470d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Banner Lateral (Continente Online)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>200x200 (Desktop, Tablet e Mobile)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Categoria.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Lateral-f3be4d8f0b18822aa57e01481055c040</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Hero Banner (Continente Online)</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 1919x640; Mobile: 767x575</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Banner-da2e4d8f0b1882f68c558138a2a5151d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Feed (Meta)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>1080x1080</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Off Site (Facebook/Instagram).</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Feed-027e4d8f0b18833694fa0199c0e3d6d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Story (Meta)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Off Site (Facebook/Instagram).</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Story-bb5e4d8f0b188230989c0197e2ace3bf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I84"/>
+  <autoFilter ref="A1:I89"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>
@@ -19654,6 +19853,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$367</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$389</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K367"/>
+  <dimension ref="A1:K389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16150,8 +16150,938 @@
       <c r="J367" s="2" t="n"/>
       <c r="K367" s="2" t="n"/>
     </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="n"/>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Hero Header (Newsletter)</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>600x400</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="n"/>
+      <c r="G368" s="2" t="n"/>
+      <c r="H368" s="2" t="n"/>
+      <c r="I368" s="2" t="n"/>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>Canal: Newsletter. Indicar título e texto no corpo do email — curtos, diretos ao tema, a captar a curiosidade do leitor. CTA: Comprar ou Saiba mais. Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
+        </is>
+      </c>
+      <c r="K368" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Header-397e4d8f0b1880c78e1ce86047334b9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="n"/>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Image Advertising (Continente Feed)</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 1312x320; Tablet: 959x256; Mobile: 735x413</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="n"/>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="n"/>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
+        </is>
+      </c>
+      <c r="K369" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Image-Advertising-3f3e4d8f0b1880da8163f327a16c13f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="n"/>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Image + Video Advertising (Continente Feed)</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Imagem — Desktop: 743x320, Tablet: 503x256, Mobile: 503x256. Vídeo — Desktop: 569x320, Tablet: 456x256, Mobile: 735x413.</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="n"/>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB (imagem; peso do vídeo não indicado)</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG (imagem; formato do vídeo não indicado)</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="n"/>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
+        </is>
+      </c>
+      <c r="K370" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Image-Video-Advertising-3f7e4d8f0b1880c4b983f2a3a7e2723d</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="n"/>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Banner Cupão Plus (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>458x236</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="n"/>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="n"/>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Cupões.</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="n"/>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Banner Cupão (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>458x112</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="n"/>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="n"/>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Cupões.</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="n"/>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Banner Usar Cartão (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>458x112</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="n"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="n"/>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Usar Cartão.</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="n"/>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Banner Destaques (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="n"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="n"/>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="n"/>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Banner Vantagens/Folhetos (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>654x240</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="n"/>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="n"/>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="n"/>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Video Ads - Auto Play (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="n"/>
+      <c r="G376" s="2" t="n"/>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="n"/>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Homepage, Plug&amp;Charge.</t>
+        </is>
+      </c>
+      <c r="K376" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Video-Ads-Auto-Play-106e4d8f0b1882a98475014f0da845d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="n"/>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Banner Plug&amp;Charge (App Cartão Continente)</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>660x484</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="n"/>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="n"/>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Plug&amp;Charge.</t>
+        </is>
+      </c>
+      <c r="K377" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Plug-Charge-3cee4d8f0b1880bf9363e9d7a56da35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="n"/>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Sponsored Products Display (App Continente)</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>456x1140</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="n"/>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="n"/>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Product Grid.</t>
+        </is>
+      </c>
+      <c r="K378" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-90fe4d8f0b18835ca782816027b56ee2</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="n"/>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Banner Ecrã Loja (App Continente)</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>345x109</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="n"/>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="n"/>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Em loja.</t>
+        </is>
+      </c>
+      <c r="K379" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Ecr-Loja-3ece4d8f0b1880db8984c5d9c585137c</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="n"/>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Hero Banner (App Continente)</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>1029x516</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="n"/>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="n"/>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="K380" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Banner-651e4d8f0b18836d92ca8117823842cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="n"/>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Banner Oportunidades (App Continente)</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>1029x772</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="n"/>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="n"/>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Página Oportunidades. Objetivo: Awareness.</t>
+        </is>
+      </c>
+      <c r="K381" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Oportunidades-ecfe4d8f0b1882f6978c81988921c3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="n"/>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Top Banner (Continente Online)</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 1320x132; Tablet: 720x124; Mobile: 345x115</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="n"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="n"/>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>Localizações: Homepage, Folhetos, Oportunidades.</t>
+        </is>
+      </c>
+      <c r="K382" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Top-Banner-2abe4d8f0b1882fdb5b1817348bac988</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="n"/>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Sponsored Products Display (Continente Online)</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 172x431; Mobile: 160x431</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="n"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="n"/>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Product Grid.</t>
+        </is>
+      </c>
+      <c r="K383" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-307e4d8f0b18832cb4ed81b572620cab</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="n"/>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Sponsored Products (Continente Online)</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="n"/>
+      <c r="F384" s="2" t="n"/>
+      <c r="G384" s="2" t="n"/>
+      <c r="H384" s="2" t="n"/>
+      <c r="I384" s="2" t="n"/>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>Não necessita de criatividades — enviar idealmente até 4 SKUs por posicionamento. Keyword Search (Pesquisa): produtos visíveis na zona de pesquisa, associados às keywords da campanha. Destaque Produto Categoria (Product Grid): produtos visíveis na página de categoria. Destaque Produto Homepage (Destaques): produtos visíveis na Homepage, na zona de destaques de produtos.</t>
+        </is>
+      </c>
+      <c r="K384" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-61be4d8f0b18820a9a8d81a25c6be12d</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="n"/>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Banner Pesquisa (Continente Online)</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>320x100 (Desktop, Tablet e Mobile)</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="n"/>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="n"/>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Categoria.</t>
+        </is>
+      </c>
+      <c r="K385" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Pesquisa-e4ee4d8f0b188272a6f101cfdd8470d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="n"/>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Banner Lateral (Continente Online)</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>200x200 (Desktop, Tablet e Mobile)</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="n"/>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="n"/>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Categoria.</t>
+        </is>
+      </c>
+      <c r="K386" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Banner-Lateral-f3be4d8f0b18822aa57e01481055c040</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="n"/>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Hero Banner (Continente Online)</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Desktop: 1919x640; Mobile: 767x575</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="n"/>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>JPG/PNG</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="n"/>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>Localização: Homepage.</t>
+        </is>
+      </c>
+      <c r="K387" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Hero-Banner-da2e4d8f0b1882f68c558138a2a5151d</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="n"/>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Feed (Meta)</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>1080x1080</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="n"/>
+      <c r="G388" s="2" t="n"/>
+      <c r="H388" s="2" t="n"/>
+      <c r="I388" s="2" t="n"/>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>Off Site (Facebook/Instagram).</t>
+        </is>
+      </c>
+      <c r="K388" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Feed-027e4d8f0b18833694fa0199c0e3d6d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Endless</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="n"/>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Story (Meta)</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="n"/>
+      <c r="G389" s="2" t="n"/>
+      <c r="H389" s="2" t="n"/>
+      <c r="I389" s="2" t="n"/>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>Off Site (Facebook/Instagram).</t>
+        </is>
+      </c>
+      <c r="K389" s="3" t="inlineStr">
+        <is>
+          <t>https://thankful-dinner-552.notion.site/Story-bb5e4d8f0b188230989c0197e2ace3bf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K367"/>
+  <autoFilter ref="A1:K389"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -16464,6 +17394,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId309"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K324" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K326" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K368" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K370" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K377" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K379" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K382" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K383" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K386" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId328"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16475,7 +17422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18877,25 +19824,33 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Hero Header (Newsletter)</t>
+          <t>Ledwall Vídeo (Ecospot — Parque de Estacionamento)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>600x400</t>
+          <t>384x512, 672x672 ou 1920x1080</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 150 MB</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264 (livraria x264), bitrate &lt; 3000</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Canal: Newsletter. Indicar título e texto no corpo do email — curtos, diretos ao tema, a captar a curiosidade do leitor. CTA: Comprar ou Saiba mais. Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
+          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>https://thankful-dinner-552.notion.site/Hero-Header-397e4d8f0b1880c78e1ce86047334b9d</t>
+          <t>https://thankful-dinner-552.notion.site/Ledwall-Video-123e4d8f0b188253b2e481717ab1e89d</t>
         </is>
       </c>
     </row>
@@ -18912,7 +19867,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Ledwall Vídeo (Ecospot — Parque de Estacionamento)</t>
+          <t>Ledwall Imagem (Ecospot — Parque de Estacionamento)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -18923,12 +19878,12 @@
       <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Máx. 150 MB</t>
+          <t>Máx. 2 MB</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>MP4, codec H264 (livraria x264), bitrate &lt; 3000</t>
+          <t>JPG e/ou PNG, modo de cor RGB, resolução 72dpi</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -18938,926 +19893,15 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>https://thankful-dinner-552.notion.site/Ledwall-Video-123e4d8f0b188253b2e481717ab1e89d</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Ledwall Imagem (Ecospot — Parque de Estacionamento)</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>384x512, 672x672 ou 1920x1080</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 2 MB</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>JPG e/ou PNG, modo de cor RGB, resolução 72dpi</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
           <t>https://thankful-dinner-552.notion.site/Ledwall-179e4d8f0b18839bbee701966fbfe361</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Image Advertising (Continente Feed)</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Desktop: 1312x320; Tablet: 959x256; Mobile: 735x413</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Image-Advertising-3f3e4d8f0b1880da8163f327a16c13f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Image + Video Advertising (Continente Feed)</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Imagem — Desktop: 743x320, Tablet: 503x256, Mobile: 503x256. Vídeo — Desktop: 569x320, Tablet: 456x256, Mobile: 735x413.</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB (imagem; peso do vídeo não indicado)</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG (imagem; formato do vídeo não indicado)</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Localizações: Liga Portugal, Ficha de Receitas, LP Receitas, Coleção de Selos, Festival Comida CNT.</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Image-Video-Advertising-3f7e4d8f0b1880c4b983f2a3a7e2723d</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Banner Cupão Plus (App Cartão Continente)</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>458x236</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Página Cupões.</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Banner Cupão (App Cartão Continente)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>458x112</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Página Cupões.</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Banner Usar Cartão (App Cartão Continente)</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>458x112</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Página Usar Cartão.</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Banner Destaques (App Cartão Continente)</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>660x484</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Homepage.</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Banner Vantagens/Folhetos (App Cartão Continente)</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>654x240</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="n"/>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 250 KB</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Homepage.</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Video Ads - Auto Play (App Cartão Continente)</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>660x484</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Localizações: Homepage, Plug&amp;Charge.</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Video-Ads-Auto-Play-106e4d8f0b1882a98475014f0da845d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Banner Plug&amp;Charge (App Cartão Continente)</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>660x484</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Plug&amp;Charge.</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Banner-Plug-Charge-3cee4d8f0b1880bf9363e9d7a56da35e</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Sponsored Products Display (App Continente)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>456x1140</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Product Grid.</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-90fe4d8f0b18835ca782816027b56ee2</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Banner Ecrã Loja (App Continente)</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>345x109</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Em loja.</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Banner-Ecr-Loja-3ece4d8f0b1880db8984c5d9c585137c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Hero Banner (App Continente)</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>1029x516</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Homepage. Objetivo: Awareness.</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Hero-Banner-651e4d8f0b18836d92ca8117823842cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Banner Oportunidades (App Continente)</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>1029x772</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n"/>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Página Oportunidades. Objetivo: Awareness.</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Banner-Oportunidades-ecfe4d8f0b1882f6978c81988921c3c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Top Banner (Continente Online)</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Desktop: 1320x132; Tablet: 720x124; Mobile: 345x115</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Localizações: Homepage, Folhetos, Oportunidades.</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Top-Banner-2abe4d8f0b1882fdb5b1817348bac988</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Sponsored Products Display (Continente Online)</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Desktop: 172x431; Mobile: 160x431</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="n"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Product Grid.</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-Display-307e4d8f0b18832cb4ed81b572620cab</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Sponsored Products (Continente Online)</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Não necessita de criatividades — enviar idealmente até 4 SKUs por posicionamento. Keyword Search (Pesquisa): produtos visíveis na zona de pesquisa, associados às keywords da campanha. Destaque Produto Categoria (Product Grid): produtos visíveis na página de categoria. Destaque Produto Homepage (Destaques): produtos visíveis na Homepage, na zona de destaques de produtos.</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Sponsored-Products-61be4d8f0b18820a9a8d81a25c6be12d</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Banner Pesquisa (Continente Online)</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>320x100 (Desktop, Tablet e Mobile)</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Categoria.</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Banner-Pesquisa-e4ee4d8f0b188272a6f101cfdd8470d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Banner Lateral (Continente Online)</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>200x200 (Desktop, Tablet e Mobile)</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 100 KB</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Categoria.</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Banner-Lateral-f3be4d8f0b18822aa57e01481055c040</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Hero Banner (Continente Online)</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Desktop: 1919x640; Mobile: 767x575</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 250 KB</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>JPG/PNG</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Localização: Homepage.</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Hero-Banner-da2e4d8f0b1882f68c558138a2a5151d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Feed (Meta)</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>1080x1080</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
-      <c r="G88" s="2" t="n"/>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Off Site (Facebook/Instagram).</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Feed-027e4d8f0b18833694fa0199c0e3d6d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Endless</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Story (Meta)</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>1080x1920</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Off Site (Facebook/Instagram).</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>https://thankful-dinner-552.notion.site/Story-bb5e4d8f0b188230989c0197e2ace3bf</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I89"/>
+  <autoFilter ref="A1:I67"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$389</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K389"/>
+  <dimension ref="A1:K392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17080,8 +17080,127 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="n"/>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>120x60 ou 88x31</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="n"/>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 50 KB</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>GIF</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="n"/>
+      <c r="J390" s="2" t="n"/>
+      <c r="K390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="n"/>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>300x250, 728x90, 468x60, 160x600, 120x600, 980x90 ou 250x250</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="n"/>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 50 KB</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>GIF</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="n"/>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>Conjunto genérico de banners + conjunto específico, consoante a campanha.</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>Awin</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="n"/>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>HTML (Email)</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>500x500</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="n"/>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 50 KB</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="n"/>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>Necessário em caso de ativação por email marketing, modelo CPL.</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K389"/>
+  <autoFilter ref="A1:K392"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -17422,7 +17541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19897,8 +20016,136 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Grandes Formatos / Empenas</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Variável por localização (ex.: 36 m² a 216 m²)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Publicidade em fachadas/empenas de grande dimensão — medida específica por local; consultar a Clearspot para o site em concreto.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>DOOH - Saldanha Square</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>3 ecrãs LED (comunicação simultânea), 3,84x2,88m cada — 864x648px (P4)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>MOV/MP4, codec H264</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Duração do spot: 10 segundos.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>DOOH - Oeiras Valley</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>2160x504px</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>MOV/MP4</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Duração do spot: 10 segundos. Entrada de material: quarta-feira às 06h00. Exibição 7 dias por semana.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Clearspot</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Rede de Praias (50 faces)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Rede de 50 faces instalada nas principais entradas das praias. Especificações técnicas (dimensão/peso/tipo de ficheiro) não indicadas no media kit — confirmar com a Clearspot.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:I71"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$400</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K392"/>
+  <dimension ref="A1:K400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17199,8 +17199,344 @@
       </c>
       <c r="K392" s="2" t="n"/>
     </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="n"/>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Display - Banners</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>300x250, 300x600, 320x50, 320x480, 480x320, 300x50, 728x90, 160x600 ou 320x100</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="n"/>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 400 KB</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>JPG, GIF, PNG, JPEG, JS Tag, Iframe Tag ou MRAID Tag</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="n"/>
+      <c r="J393" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPC. Recomendado um mínimo de 3 tamanhos por campanha (320x50, 320x480 e 300x600).</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="n"/>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>In-Game Display</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>300x250, 320x50 ou 728x90</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="n"/>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 300 KB</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>JPG, GIF, PNG ou JPEG</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="n"/>
+      <c r="J394" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPM. Recomendado usar os 3 tamanhos por campanha.</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="n"/>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado: 320x480. Outros: 300x250 ou 300x600.</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="n"/>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>HTML: máx. 1 MB. Vídeo: máx. 5 MB, até 30″.</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>JS Tag, iFrame Tag, MRAID Tag (in-app) ou HTML (extensão .html; .zip não suportado)</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="n"/>
+      <c r="J395" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPC. Inclui RM Interstitial (320x480) e RM Expandable Banner (320x50 recolhido → 320x480 expandido).</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="n"/>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo (Instream/Outstream)</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>1280x720 ou 1080x1350</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>4:3 ou 16:9</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>MP4, MOV, FLV, VAST 3.0 ou VPAID 2.0; companion asset: GIF, JPG, JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="n"/>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPCV. Duração máx. 30″ (recomendado 15-30″). Vídeos do YouTube não são aceites.</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="n"/>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo Rewarded</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>480x320 ou 1024x768</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>4:3 ou 16:9</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>MP4, MOV, FLV ou VAST 3.0; companion asset: GIF, JPG, JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="n"/>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPM ou CPCV. Duração: 15 ou 30″, não passível de ser saltado. Vídeos do YouTube não são aceites.</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="n"/>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Áudio</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="n"/>
+      <c r="F398" s="2" t="n"/>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 3 MB</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>VAST 2.0, MP3, WAV, WMA ou OGG; companion asset (300x250, máx. 50 KB): JPG, JPEG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="n"/>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPE. Duração: 15″, 30″ ou 60″. Qualidade mínima: 128 kbps / 44100 Hz.</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="n"/>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Push Notifications</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Imagem principal: 452x226 e 600x400 (ambas obrigatórias). Logo: 48x48.</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="n"/>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="n"/>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPC (mín. 150 cliques/dia). Título: máx. 30 carateres. Subtítulo: máx. 35 carateres. Sem emojis no texto. Máx. 10 criatividades por campanha.</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>AdsMovil</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="n"/>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Connected TV</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Resolução HD</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>4:3 ou 16:9</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 5 MB</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>MP4, VAST 2.0 ou VAST 3.0</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="n"/>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>Compra: CPM. Duração: 15 ou 30″, não passível de ser saltado. Vídeos do YouTube não são suportados; dispositivos CTV não suportam VPAID.</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K392"/>
+  <autoFilter ref="A1:K400"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$400</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$403</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K400"/>
+  <dimension ref="A1:K403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17535,8 +17535,131 @@
       </c>
       <c r="K400" s="2" t="n"/>
     </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="n"/>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Standard Banners</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>1388x1734, 720x540, 2640x600, 1760x400 ou 300x250</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="n"/>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="n"/>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>Ver no link as safe zones e danger zones.</t>
+        </is>
+      </c>
+      <c r="K401" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Outlook</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>Outlook</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="n"/>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Native Ads</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Logo da marca: 100x100. Imagem: 1200x627 ou 627x627.</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="n"/>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 120 KB</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="n"/>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>Short Headline (x2): máx. 30 carateres. Long Headline: máx. 90 carateres. Descrição: máx. 90 carateres. Business/Brand Name: máx. 25 carateres.</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Open AI</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Open AI</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n"/>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>1200x1200</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="n"/>
+      <c r="G403" s="2" t="n"/>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="n"/>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 50 carateres (recomendado 16-24). Descrição: máx. 100 carateres (recomendado 32-48).</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K400"/>
+  <autoFilter ref="A1:K403"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -17866,6 +17989,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId327"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId329"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$403</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$413</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K403"/>
+  <dimension ref="A1:K413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17658,8 +17658,418 @@
       </c>
       <c r="K403" s="2" t="n"/>
     </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n"/>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Virtual Category (Icon) - Homepage</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>100x100</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="n"/>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="n"/>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="n"/>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Screening (Takeover) - Homepage</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>1920x1100</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="n"/>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="n"/>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="n"/>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Screening (Takeover) - Listing Page</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>1920x1100</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="n"/>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="n"/>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n"/>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Full Branding - Homepage</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>2x 1920x1100, 4x 270x190</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="n"/>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="n"/>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n"/>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Full Branding - Listing</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>2x 1920x1100, 4x 270x190, 1x 1237x300, 1x 1029x300</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="n"/>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="n"/>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="n"/>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>My Account</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>890x70</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="n"/>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="n"/>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>Posição: My Account Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="n"/>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Megaboard (Topboard)</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>1920x300</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="n"/>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="n"/>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n"/>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Skyscraper</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>160x600</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="n"/>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="n"/>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="n"/>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC)</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="n"/>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="n"/>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="n"/>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>970x250</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="n"/>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="n"/>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K403"/>
+  <autoFilter ref="A1:K413"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$423</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K413"/>
+  <dimension ref="A1:K423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18068,8 +18068,422 @@
       </c>
       <c r="K413" s="2" t="n"/>
     </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="n"/>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Native (In Feed)</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>210x150</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="n"/>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="n"/>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="n"/>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Text Link / Brand Link</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="n"/>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="n"/>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="n"/>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Video Outstream</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>MP4, até 30 segundos</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="n"/>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="n"/>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>TopMobileBoard (Leaderboard)</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>300x100 ou 320x100</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="n"/>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="n"/>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Mobile).</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="n"/>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Virtual Category (Icon) - Homepage (Mobile)</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>80x83</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="n"/>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="n"/>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="n"/>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>TopMobileBoard (Anchor)</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>600x200</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="n"/>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="n"/>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="n"/>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Full Branding Mobile</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>1x 600x200, 3x 300x250</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="n"/>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="n"/>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="n"/>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (Mobile)</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="n"/>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="n"/>
+      <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K421" s="2" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="n"/>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>1000x563</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="n"/>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="n"/>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
+        </is>
+      </c>
+      <c r="K422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="n"/>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>Text Link / Brand Link (Mobile)</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="n"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="n"/>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+        </is>
+      </c>
+      <c r="K423" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K413"/>
+  <autoFilter ref="A1:K423"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$423</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$438</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K423"/>
+  <dimension ref="A1:K438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18482,8 +18482,627 @@
       </c>
       <c r="K423" s="2" t="n"/>
     </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="n"/>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Top Mobile Board (Seller/Observed Page)</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>320x100</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="n"/>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="n"/>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K424" s="2" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="n"/>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (App)</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="n"/>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="n"/>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
+        </is>
+      </c>
+      <c r="K425" s="2" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="n"/>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Observed Ads (App)</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>320x100</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="n"/>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="n"/>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Observed Page (App).</t>
+        </is>
+      </c>
+      <c r="K426" s="2" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n"/>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Top Mobile Board (App - Homepage)</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>320x100</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="n"/>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="n"/>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (App — Android e iOS).</t>
+        </is>
+      </c>
+      <c r="K427" s="2" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="n"/>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Showcase (Masthead)</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>1920x300</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="n"/>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="n"/>
+      <c r="J428" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+      <c r="K428" s="2" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="n"/>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Megaboard (Topboard)</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>1920x300</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="n"/>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="n"/>
+      <c r="J429" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+      <c r="K429" s="2" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="n"/>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: 252x152. Logo: 80x36.</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="n"/>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="n"/>
+      <c r="J430" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
+        </is>
+      </c>
+      <c r="K430" s="2" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="n"/>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Skyscraper | Halfpage</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>160x600 ou 300x600</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="n"/>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="n"/>
+      <c r="J431" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K431" s="2" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="n"/>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>914x212</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="n"/>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="n"/>
+      <c r="J432" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K432" s="2" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="n"/>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC)</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="n"/>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="n"/>
+      <c r="J433" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K433" s="2" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="n"/>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="n"/>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="n"/>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K434" s="2" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="n"/>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Video Outstream</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 10 MB</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>MP4, até 30 segundos</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="n"/>
+      <c r="J435" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K435" s="2" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="n"/>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Showcase (Masthead) (Mobile)</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>1080x450</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="n"/>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="n"/>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Homepage (Mobile).</t>
+        </is>
+      </c>
+      <c r="K436" s="2" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="n"/>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>Full Branding Mobile</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>1x 600x200, 3x 300x250</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="n"/>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="n"/>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K437" s="2" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="n"/>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>TopMobileBoard (Anchor)</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>600x200</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="n"/>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="n"/>
+      <c r="J438" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K438" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K423"/>
+  <autoFilter ref="A1:K438"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$443</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K438"/>
+  <dimension ref="A1:K443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19101,8 +19101,213 @@
       </c>
       <c r="K438" s="2" t="n"/>
     </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>StandVirtual</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="n"/>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (Mobile)</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="n"/>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="n"/>
+      <c r="J439" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K439" s="2" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="n"/>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>Megaboard (Topboard)</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>1920x200</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="n"/>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="n"/>
+      <c r="J440" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+        </is>
+      </c>
+      <c r="K440" s="2" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="n"/>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>Native (In List)</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>820x200</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="n"/>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="n"/>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K441" s="2" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="n"/>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="n"/>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="n"/>
+      <c r="J442" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="n"/>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC)</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="n"/>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="n"/>
+      <c r="J443" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+        </is>
+      </c>
+      <c r="K443" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K438"/>
+  <autoFilter ref="A1:K443"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$443</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$446</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K443"/>
+  <dimension ref="A1:K446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14277,7 +14277,11 @@
       </c>
       <c r="I318" s="2" t="n"/>
       <c r="J318" s="2" t="n"/>
-      <c r="K318" s="2" t="n"/>
+      <c r="K318" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -17697,7 +17701,11 @@
           <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
         </is>
       </c>
-      <c r="K404" s="2" t="n"/>
+      <c r="K404" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -17735,10 +17743,14 @@
       <c r="I405" s="2" t="n"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
-        </is>
-      </c>
-      <c r="K405" s="2" t="n"/>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="K405" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -17776,10 +17788,14 @@
       <c r="I406" s="2" t="n"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones).</t>
-        </is>
-      </c>
-      <c r="K406" s="2" t="n"/>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="K406" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -17817,10 +17833,14 @@
       <c r="I407" s="2" t="n"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
-        </is>
-      </c>
-      <c r="K407" s="2" t="n"/>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="K407" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -17858,10 +17878,14 @@
       <c r="I408" s="2" t="n"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
-        </is>
-      </c>
-      <c r="K408" s="2" t="n"/>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="K408" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -17902,7 +17926,11 @@
           <t>Posição: My Account Page (Desktop).</t>
         </is>
       </c>
-      <c r="K409" s="2" t="n"/>
+      <c r="K409" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -17940,10 +17968,14 @@
       <c r="I410" s="2" t="n"/>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
-        </is>
-      </c>
-      <c r="K410" s="2" t="n"/>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="K410" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -17984,7 +18016,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
-      <c r="K411" s="2" t="n"/>
+      <c r="K411" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -18025,7 +18061,11 @@
           <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
-      <c r="K412" s="2" t="n"/>
+      <c r="K412" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -18066,7 +18106,11 @@
           <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
         </is>
       </c>
-      <c r="K413" s="2" t="n"/>
+      <c r="K413" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -18107,7 +18151,11 @@
           <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
-      <c r="K414" s="2" t="n"/>
+      <c r="K414" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -18148,7 +18196,11 @@
           <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
         </is>
       </c>
-      <c r="K415" s="2" t="n"/>
+      <c r="K415" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -18193,7 +18245,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
-      <c r="K416" s="2" t="n"/>
+      <c r="K416" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -18234,7 +18290,11 @@
           <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
-      <c r="K417" s="2" t="n"/>
+      <c r="K417" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -18275,7 +18335,11 @@
           <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
         </is>
       </c>
-      <c r="K418" s="2" t="n"/>
+      <c r="K418" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -18316,7 +18380,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
-      <c r="K419" s="2" t="n"/>
+      <c r="K419" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -18357,7 +18425,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
-      <c r="K420" s="2" t="n"/>
+      <c r="K420" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -18398,7 +18470,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
-      <c r="K421" s="2" t="n"/>
+      <c r="K421" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -18439,7 +18515,11 @@
           <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
         </is>
       </c>
-      <c r="K422" s="2" t="n"/>
+      <c r="K422" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -18480,7 +18560,11 @@
           <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
         </is>
       </c>
-      <c r="K423" s="2" t="n"/>
+      <c r="K423" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -18521,7 +18605,11 @@
           <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
         </is>
       </c>
-      <c r="K424" s="2" t="n"/>
+      <c r="K424" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -18562,7 +18650,11 @@
           <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
         </is>
       </c>
-      <c r="K425" s="2" t="n"/>
+      <c r="K425" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -18603,7 +18695,11 @@
           <t>Posição: Observed Page (App).</t>
         </is>
       </c>
-      <c r="K426" s="2" t="n"/>
+      <c r="K426" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -18644,7 +18740,11 @@
           <t>Posição: Homepage (App — Android e iOS).</t>
         </is>
       </c>
-      <c r="K427" s="2" t="n"/>
+      <c r="K427" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -18682,10 +18782,14 @@
       <c r="I428" s="2" t="n"/>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
-        </is>
-      </c>
-      <c r="K428" s="2" t="n"/>
+          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="K428" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -18723,10 +18827,14 @@
       <c r="I429" s="2" t="n"/>
       <c r="J429" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
-        </is>
-      </c>
-      <c r="K429" s="2" t="n"/>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+        </is>
+      </c>
+      <c r="K429" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -18767,7 +18875,11 @@
           <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
-      <c r="K430" s="2" t="n"/>
+      <c r="K430" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -18808,7 +18920,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
-      <c r="K431" s="2" t="n"/>
+      <c r="K431" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -18849,7 +18965,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
-      <c r="K432" s="2" t="n"/>
+      <c r="K432" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -18890,7 +19010,11 @@
           <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
-      <c r="K433" s="2" t="n"/>
+      <c r="K433" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -18931,7 +19055,11 @@
           <t>Posição: Ad Page (Desktop).</t>
         </is>
       </c>
-      <c r="K434" s="2" t="n"/>
+      <c r="K434" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -18976,7 +19104,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
-      <c r="K435" s="2" t="n"/>
+      <c r="K435" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -19017,7 +19149,11 @@
           <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
-      <c r="K436" s="2" t="n"/>
+      <c r="K436" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -19058,7 +19194,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
-      <c r="K437" s="2" t="n"/>
+      <c r="K437" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -19099,7 +19239,11 @@
           <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
-      <c r="K438" s="2" t="n"/>
+      <c r="K438" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -19140,7 +19284,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
-      <c r="K439" s="2" t="n"/>
+      <c r="K439" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -19181,7 +19329,11 @@
           <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
         </is>
       </c>
-      <c r="K440" s="2" t="n"/>
+      <c r="K440" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -19222,7 +19374,11 @@
           <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
-      <c r="K441" s="2" t="n"/>
+      <c r="K441" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -19263,7 +19419,11 @@
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
-      <c r="K442" s="2" t="n"/>
+      <c r="K442" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -19304,10 +19464,149 @@
           <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
-      <c r="K443" s="2" t="n"/>
+      <c r="K443" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="n"/>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>Text Link (Brand Link)</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="n"/>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="n"/>
+      <c r="J444" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+        </is>
+      </c>
+      <c r="K444" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="n"/>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>Rectangle (MREC) (Mobile)</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>300x250</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="n"/>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="n"/>
+      <c r="J445" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+        </is>
+      </c>
+      <c r="K445" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>Imovirtual</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="n"/>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>Text Link (Brand Link) (Mobile)</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>Logo: 80x80 (opcional)</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="n"/>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="n"/>
+      <c r="J446" s="2" t="inlineStr">
+        <is>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+        </is>
+      </c>
+      <c r="K446" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K443"/>
+  <autoFilter ref="A1:K446"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -19617,27 +19916,71 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K313" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K314" r:id="rId307"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K315" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K324" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K326" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K368" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K370" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K377" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K379" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K382" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K383" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K386" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K318" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K323" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K324" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K326" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K368" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K369" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K370" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K377" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K378" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K379" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K380" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K382" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K383" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K385" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K386" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K404" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K407" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K408" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K409" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K410" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K411" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K412" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K413" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K414" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K415" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K416" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K417" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K418" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K419" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K420" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K421" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K422" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K423" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K424" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K425" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K426" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K427" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K428" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K429" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K430" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K431" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K432" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K433" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K434" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K435" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K436" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K437" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K438" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K439" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K440" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K441" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K442" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K443" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K444" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K445" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K446" r:id="rId373"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$446</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -19992,7 +19992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -22595,8 +22595,2051 @@
       </c>
       <c r="I71" s="2" t="n"/>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Category Window (Higiene)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Largura total 133 cm (área visível 100 cm); altura 255 cm; faixas laterais 15 cm cada</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) para a categoria Higiene — sem retalhista nem especificações de produção/impressão indicadas no documento.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Archmedia 220cm</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Largura total 220 cm (área visível 170 cm); altura 220 cm; faixa lateral 25 cm</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Archmedia 250cm</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Largura total 250 cm (área visível 200 cm); altura 220 cm; faixa lateral 25 cm</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Archmedia 320cm</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Largura total 320 cm (área visível 270 cm); altura 220 cm; faixa lateral 25 cm</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Category Window (Várias Medidas)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Conforme indicado no documento: largura topo 1336 cm; alturas laterais 2000 cm e 2200 cm</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Nome do ficheiro indica "140x255cm", mas os valores no PDF (em cm) não batem certo — possível troca de unidade (cm/mm) no documento de origem. Reportado literalmente, sem correção. Molde técnico, sem retalhista nem specs de produção.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Shelf Display Media Luna</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Suporte 160x500mm; vinil base 158x100mm; vinil frontal (com luz) 291x49mm</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Escala real 1:1 + 2mm de sangria</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>PDF qualidade de imprensa (PDF 1.4, CMYK, 300 dpi, tipografia incrustada, transparências conservadas)</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0. Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Contratação mínima de 2 meses. Entrega 1,5 meses antes do início da campanha. Documento da In-Store Media España.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Hall-Media</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48 cm)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Criatividade em português. Não colocar informação importante entre 40 e 56 cm da base (alturas de defesas de alarme variam por loja). Entrega: 1 mês antes para validação, 2 semanas antes para Arte Final.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Door-Media — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>134x150 cms, 114x125 cms ou 90x100 cms</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Criatividade em português. Não colocar texto/imagem no centro onde abrem as portas.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Welcome Screen — Auchan</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>1280x256, 384x576, 384x768, 768x256 ou 960x192 px</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM; entrega da AF segundo indicações ISM.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Welcome Screen — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã físico 3,00x2,00m; resolução 1532x1024 px</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — Auchan</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>120x52x4 cms, 105x52x4 cms ou 90x52x4 cms (segmentos 4/52/4/52cm)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Recomenda-se logo da marca nas laterais. Não colocar informação entre 40 e 56 cm da base (defesas variam por loja).</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — Continente</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Media (Cartão) — El Corte Inglês (Supercor)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>140x48x14 cms</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — El Corte Inglês (Supercor)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Face maior: 490x1210mm. Lateral (com logo/nome da marca): 105x1210mm.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0, quadricromia. Pode colocar logo/nome da marca na faixa lateral.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — Auchan</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>104x16 cms, 106x22 cms ou 133x40 cms (CxL)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — Continente</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>49x121,5 cms</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Não colocar informação entre 31,5 e 47,5 cm da base (zona de defesa variável por loja). Documento da In-Store Media España.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — E.Leclerc</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Alarm-Media (Papel) — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Tiras laterais 105x1210mm (x2); faces maiores 485x1210mm (x2)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha. Nota: o nome do ficheiro de origem referia "Supercor Restelo", mas o conteúdo do documento identifica claramente este suporte como El Corte Inglês Gaia.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Media (Papel) — El Corte Inglês Departamental</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Painel frontal: 490x1210mm. Lateral (logo/nome): 105x1210mm.</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Entrega: 10 dias úteis antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Walk — Auchan</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm; cantos arredondados</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão autocolante opaco 3M com lâmina antideslizante MSM; offset 4/0 + verniz UVI brilhante. Não são permitidos passatempos/jogos de sorte.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Walk — Continente</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>600x100, 400x100 ou 250x100 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Mesmo material/impressão da versão Auchan (vinil de chão 3M, offset 4/0). Sem passatempos/jogos de sorte.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Alarm Walk — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>600x100, 400x100, 250x100 ou 180x100 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Mesmo material/impressão das restantes. Tem uma variante de tamanho extra (180x100) face a Auchan/Continente.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Cart Media — Continente</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Tamanho total 32,2x69 cms; área visível 32,2x30,5 cms (frente e verso)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Material: polipropileno branco 0,5mm (PVC) 200 microns; offset UV 4/0 + verniz UV brilho. Cantos arredondados; criatividade em português.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Floor Media — Auchan</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>120x90 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão autocolante opaco 3M, lâmina antideslizante MSM; offset 4/0. Incluir logo ISM; sem passatempos/jogos de sorte.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Floor Media 120x90 — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>120x90 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Mesmas especificações de material/impressão da versão Auchan.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Floor Media 90x60 — Continente</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>90x60 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Mesma produção/material das restantes Floor Media.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Floor Media XXL — Continente</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>200x100 cms; margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão autocolante opaco 3M; offset 4/0. Incluir logo ISM.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Floor Media — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>120x90 cms (Hipermercados) ou 90x60 cms (Supermercados); margem branco 1 cm</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Vinil de chão autocolante opaco 3M, lâmina antideslizante; offset 4/0. Incluir logo ISM; cantos arredondados.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Frame Media Congelados</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>7 tiras de 7x100cm (área total 7cm x várias metragens, depende do perímetro da arca)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (perímetros não uniformes, pode requerer corte). Recomenda-se só logo ou imagem do produto.</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Sticker Freezer</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>16x16 cms</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil removível, digital 4/0. Criatividade contínua nas tiras (arcas não uniformes, pode requerer corte). Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Live Markets — Auchan</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>WMV ou MP4, sem áudio</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Emissão só após validação ISM; entrega até 5 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Live Markets — Continente</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>LCDs Samsung 65"; 1080x1920 px</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Live Markets — E.Leclerc</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>LCDs 55"; 720x1280 px</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB; vídeo &lt; 4000 kbps</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>AVI, MOV ou MP4, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Resolução/ecrã diferentes das restantes Live Markets (720x1280 vs. 1080x1920). Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Live Markets — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Conteúdo deve ser animado (não estático). LCDs Samsung. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Live Matosinhos — Continente</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Painel físico 5,76x4,8m; resolução 1008x576 px</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Écran exterior/totem de grande formato em localização específica (Matosinhos). Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Mupis Digitais — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920, 1080x1634, 1080x1374, 1355x1080, 1355x982 ou 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Mupi (retroiluminado) — Pingo Doce</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Tamanho total 120x176 cm; área visível 107x159 cms</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Resolução 300 DPI, escala real 1:1</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Material: papel especial para luz, 135 gr (mupi retroiluminado físico, distinto do digital). Arte Final em português.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Digital Mupis — Auchan</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>WMV ou MP4</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Filme em português ou legendado/traduzido. Entrega 5 dias antes; emissão só após validação ISM.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Passadeira Vinil</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Total 16mts; módulos centrais 100x200cm (x7); módulos início/fim 100x100cm (x2)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Resolução 300 DPI, escala real 1:1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil de chão removível com lâmina antideslizante; digital 4/0. Imagens início/fim iguais entre si (idem para as centrais); não usar fundo branco nem preto; incluir logo ISM no início e fim.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Stopper Digital</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã LCD 15"; 1080x1920 px</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps, sem áudio</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Stopper-Media Max</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Área total 20,4x40,4 cms; área visível 19,2x39,2 cms; sangria 1,2 cms</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; resolução 1080 DPI à escala real, 300 microns</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Material: PVC eco branco/mate; digital 4/0. Evitar textos/logos/numeração perto do corte.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Stopper-Media Max XXL</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Área total 60,4x20,4 cms; área visível 59,2x19,2 cms; sangria 1,2 cms</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; resolução 1080 DPI à escala real, 300 microns</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Material: PVC eco branco/mate; digital 4/0. Mesmas recomendações de corte que o Stopper-Media Max (tamanho normal).</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Stopper Media LED 200x800</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Tamanho total 221x800mm; área visível 200x800mm; raio de canto R=40mm</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução 1080 DPI à escala real, 300 microns</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Material: PMMA gravado (Easydot); digital 4/4. Saída de cabo na zona superior; pinça única com peças 3D. Evitar elementos perto do corte.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Top Banner (FMCG)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>768x216 px</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, sem áudio</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Entrega 5 dias antes; emissão só após validação ISM. Formato genérico, sem retalhista específico.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Mupi Papel — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Tamanho total 120x176 cms; área visível 107x159 cms</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Material: papel especial para luz, 135 gr; impressão quadricromia, Offset ou Digital. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Elevadores — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Portas exteriores: largura total 99,5cm (2 painéis de 38,5cm + faixas de 5/7,5cm); altura total 209,5cm (área útil 194,5cm). Loja: 13 pisos x 3 elevadores = 39 faces.</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Documento disponível é só de logística de instalação, não uma ficha técnica de produção completa — sem resolução, DPI, formato de ficheiro, peso máximo ou prazo de entrega indicados. Opções de corte do vinil: (1) criatividade única cortada em 2 partes; (2) duas criatividades separadas, uma por porta; (3) criatividade com friso central incluído. Confirmar specs de produção com a In-Store Media antes de fechar o pedido.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Mupis Digitais — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920 px</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>MP4 ou WMV, codec H264, sem áudio</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha. Nota: um dos documentos de origem indicava a nomenclatura de ficheiro "1060X3840", que não bate com a resolução declarada (1080x1920) — reportado tal como consta, sem correção.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Hall Media Digital — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>666x1920 px</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-HALL-666X1920.mp4. Criatividade em português, sem áudio. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Live Markets (Circuito Digital) — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã 42"; 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB (produzido pelo cliente)</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>WMV ou MP4 (cliente); PSD/AI/INDD/PDF, imagens &gt;150dpi, texto em curvas (produção ISM)</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Live Markets (Circuito Digital) — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã 55"; 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB (produzido pelo cliente)</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>WMV ou MP4 (cliente); PSD/AI/INDD/PDF, imagens &gt;150dpi, texto em curvas (produção ISM)</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Stairs Backlights — El Corte Inglês (Espanha)</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>78x108 cms</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:5 + 0,5cm de sangria</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Material: white back paper 150 grs, corte simples; offset 4/0. Criatividade em português. Entrega: 10 dias antes do início da campanha. Atenção: o documento identifica o mercado como "In-Store Media España" — confirmar se este formato se aplica às lojas portuguesas (Gaia/Lisboa) ou se é exclusivo de Espanha antes de o usar num pedido.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Elevadores — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>150x220 cms</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Freehand, Adobe Illustrator ou Corel Draw (paginação); PSD aceite com layers separados e AFs em aberto; CMYK (enviar pantones); resolução mín. 720 DPI à escala 1:10 ou 72 DPI à escala real</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Textos convertidos em vetorial. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Montra Digital — El Corte Inglês Gaia</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>1248x2212 px</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.GAIA-1248X2212.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Lona Gigante Digital — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã físico 18,7x10,6m; resolução 1920x1080 px</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>WMV ou MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Material: ecrã LED de 198m². Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Banners de Exterior — El Corte Inglês</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>100x300 cms</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator (AI); resolução mín. 300 DPI à escala 1:1</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Material: tela blockout com ilhoses; impressão tintas UV ou low solvents. Evitar mensagens nos extremos. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>In-Store Media</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Montra Digital — El Corte Inglês Lisboa</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã físico 400x450cm; resolução 1600x1800 px</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 25 MB</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>MP4, codec H264, 25 fps</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.LISBOA-1600X1800.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I71"/>
+  <autoFilter ref="A1:I128"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$446</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -19992,7 +19992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24638,8 +24638,183 @@
       </c>
       <c r="I128" s="2" t="n"/>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor 21x5</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Área de impressão: 21x5m (escala 1:10, 210x50cm). Área de conteúdo relevante: 20,60x4,70m.</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor 32x5</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Área de impressão: 32,12x5,04m (escala 1:10, 321,2x50,4cm). Área de conteúdo relevante: 31,8x4,8m.</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>8x3 Premium</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Área de impressão: 8,35x3m (escala 1:10, 83,5x30cm). Área de conteúdo relevante: 8,15x2,80m.</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Monoposte 10x5</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Área de impressão: 10x5m (escala 1:10, 100x50cm). Área de conteúdo relevante: 9,80x4,80m.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>CSOutdoors</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor 4x3</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Área de impressão: 4x3m (escala 1:10, 40x30cm). Área de conteúdo relevante: 3,80x2,80m.</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>PDF, JPG, TIF, CDR ou AI</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I128"/>
+  <autoFilter ref="A1:I133"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$446</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$453</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K446"/>
+  <dimension ref="A1:K453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17542,29 +17542,29 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>Outlook</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Ogury</t>
+          <t>Outlook</t>
         </is>
       </c>
       <c r="C401" s="2" t="n"/>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Standard Banners</t>
+          <t>Native Ads</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>1388x1734, 720x540, 2640x600, 1760x400 ou 300x250</t>
+          <t>Logo da marca: 100x100. Imagem: 1200x627 ou 627x627.</t>
         </is>
       </c>
       <c r="F401" s="2" t="n"/>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 KB</t>
+          <t>Máx. 120 KB</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -17575,52 +17575,44 @@
       <c r="I401" s="2" t="n"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>Ver no link as safe zones e danger zones.</t>
-        </is>
-      </c>
-      <c r="K401" s="3" t="inlineStr">
-        <is>
-          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-studio</t>
-        </is>
-      </c>
+          <t>Short Headline (x2): máx. 30 carateres. Long Headline: máx. 90 carateres. Descrição: máx. 90 carateres. Business/Brand Name: máx. 25 carateres.</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>Outlook</t>
+          <t>Open AI</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Outlook</t>
+          <t>Open AI</t>
         </is>
       </c>
       <c r="C402" s="2" t="n"/>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Native Ads</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>Logo da marca: 100x100. Imagem: 1200x627 ou 627x627.</t>
+          <t>1200x1200</t>
         </is>
       </c>
       <c r="F402" s="2" t="n"/>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>Máx. 120 KB</t>
-        </is>
-      </c>
+      <c r="G402" s="2" t="n"/>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="I402" s="2" t="n"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>Short Headline (x2): máx. 30 carateres. Long Headline: máx. 90 carateres. Descrição: máx. 90 carateres. Business/Brand Name: máx. 25 carateres.</t>
+          <t>Título: máx. 50 carateres (recomendado 16-24). Descrição: máx. 100 carateres (recomendado 32-48).</t>
         </is>
       </c>
       <c r="K402" s="2" t="n"/>
@@ -17628,39 +17620,47 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>Open AI</t>
+          <t>OLX</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Open AI</t>
+          <t>OLX</t>
         </is>
       </c>
       <c r="C403" s="2" t="n"/>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Virtual Category (Icon) - Homepage</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>1200x1200</t>
+          <t>100x100</t>
         </is>
       </c>
       <c r="F403" s="2" t="n"/>
-      <c r="G403" s="2" t="n"/>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I403" s="2" t="n"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>Título: máx. 50 carateres (recomendado 16-24). Descrição: máx. 100 carateres (recomendado 32-48).</t>
-        </is>
-      </c>
-      <c r="K403" s="2" t="n"/>
+          <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
+        </is>
+      </c>
+      <c r="K403" s="3" t="inlineStr">
+        <is>
+          <t>https://formatos-publicidade-olx.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -17676,12 +17676,12 @@
       <c r="C404" s="2" t="n"/>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Virtual Category (Icon) - Homepage</t>
+          <t>Screening (Takeover) - Homepage</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>100x100</t>
+          <t>1920x1100</t>
         </is>
       </c>
       <c r="F404" s="2" t="n"/>
@@ -17698,7 +17698,7 @@
       <c r="I404" s="2" t="n"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K404" s="3" t="inlineStr">
@@ -17721,7 +17721,7 @@
       <c r="C405" s="2" t="n"/>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Screening (Takeover) - Homepage</t>
+          <t>Screening (Takeover) - Listing Page</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -17743,7 +17743,7 @@
       <c r="I405" s="2" t="n"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K405" s="3" t="inlineStr">
@@ -17766,12 +17766,12 @@
       <c r="C406" s="2" t="n"/>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Screening (Takeover) - Listing Page</t>
+          <t>Full Branding - Homepage</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>1920x1100</t>
+          <t>2x 1920x1100, 4x 270x190</t>
         </is>
       </c>
       <c r="F406" s="2" t="n"/>
@@ -17788,7 +17788,7 @@
       <c r="I406" s="2" t="n"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K406" s="3" t="inlineStr">
@@ -17811,12 +17811,12 @@
       <c r="C407" s="2" t="n"/>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Full Branding - Homepage</t>
+          <t>Full Branding - Listing</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>2x 1920x1100, 4x 270x190</t>
+          <t>2x 1920x1100, 4x 270x190, 1x 1237x300, 1x 1029x300</t>
         </is>
       </c>
       <c r="F407" s="2" t="n"/>
@@ -17833,7 +17833,7 @@
       <c r="I407" s="2" t="n"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K407" s="3" t="inlineStr">
@@ -17856,12 +17856,12 @@
       <c r="C408" s="2" t="n"/>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Full Branding - Listing</t>
+          <t>My Account</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>2x 1920x1100, 4x 270x190, 1x 1237x300, 1x 1029x300</t>
+          <t>890x70</t>
         </is>
       </c>
       <c r="F408" s="2" t="n"/>
@@ -17872,13 +17872,13 @@
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I408" s="2" t="n"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+          <t>Posição: My Account Page (Desktop).</t>
         </is>
       </c>
       <c r="K408" s="3" t="inlineStr">
@@ -17901,12 +17901,12 @@
       <c r="C409" s="2" t="n"/>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>My Account</t>
+          <t>Megaboard (Topboard)</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>890x70</t>
+          <t>1920x300</t>
         </is>
       </c>
       <c r="F409" s="2" t="n"/>
@@ -17923,7 +17923,7 @@
       <c r="I409" s="2" t="n"/>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>Posição: My Account Page (Desktop).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K409" s="3" t="inlineStr">
@@ -17946,12 +17946,12 @@
       <c r="C410" s="2" t="n"/>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Megaboard (Topboard)</t>
+          <t>Skyscraper</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>1920x300</t>
+          <t>160x600</t>
         </is>
       </c>
       <c r="F410" s="2" t="n"/>
@@ -17968,7 +17968,7 @@
       <c r="I410" s="2" t="n"/>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="K410" s="3" t="inlineStr">
@@ -17991,12 +17991,12 @@
       <c r="C411" s="2" t="n"/>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Skyscraper</t>
+          <t>Rectangle (MREC)</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>160x600</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="F411" s="2" t="n"/>
@@ -18013,7 +18013,7 @@
       <c r="I411" s="2" t="n"/>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop).</t>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
       <c r="K411" s="3" t="inlineStr">
@@ -18036,12 +18036,12 @@
       <c r="C412" s="2" t="n"/>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Rectangle (MREC)</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>970x250</t>
         </is>
       </c>
       <c r="F412" s="2" t="n"/>
@@ -18058,7 +18058,7 @@
       <c r="I412" s="2" t="n"/>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+          <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
         </is>
       </c>
       <c r="K412" s="3" t="inlineStr">
@@ -18081,12 +18081,12 @@
       <c r="C413" s="2" t="n"/>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Native (In Feed)</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>970x250</t>
+          <t>210x150</t>
         </is>
       </c>
       <c r="F413" s="2" t="n"/>
@@ -18097,13 +18097,13 @@
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I413" s="2" t="n"/>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>Posição: várias páginas — Listing Page, Ad Page, Seller Page, Observed Ads (Desktop).</t>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
       <c r="K413" s="3" t="inlineStr">
@@ -18126,29 +18126,29 @@
       <c r="C414" s="2" t="n"/>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Native (In Feed)</t>
+          <t>Text Link / Brand Link</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>210x150</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="F414" s="2" t="n"/>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="I414" s="2" t="n"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
         </is>
       </c>
       <c r="K414" s="3" t="inlineStr">
@@ -18171,29 +18171,33 @@
       <c r="C415" s="2" t="n"/>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Text Link / Brand Link</t>
+          <t>Video Outstream</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
-        </is>
-      </c>
-      <c r="F415" s="2" t="n"/>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
+          <t>Máx. 10 MB</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>MP4, até 30 segundos</t>
         </is>
       </c>
       <c r="I415" s="2" t="n"/>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="K415" s="3" t="inlineStr">
@@ -18216,33 +18220,29 @@
       <c r="C416" s="2" t="n"/>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Video Outstream</t>
+          <t>TopMobileBoard (Leaderboard)</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F416" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>300x100 ou 320x100</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="n"/>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>MP4, até 30 segundos</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I416" s="2" t="n"/>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+          <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
       <c r="K416" s="3" t="inlineStr">
@@ -18265,12 +18265,12 @@
       <c r="C417" s="2" t="n"/>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>TopMobileBoard (Leaderboard)</t>
+          <t>Virtual Category (Icon) - Homepage (Mobile)</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>300x100 ou 320x100</t>
+          <t>80x83</t>
         </is>
       </c>
       <c r="F417" s="2" t="n"/>
@@ -18281,13 +18281,13 @@
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I417" s="2" t="n"/>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Mobile).</t>
+          <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
         </is>
       </c>
       <c r="K417" s="3" t="inlineStr">
@@ -18310,12 +18310,12 @@
       <c r="C418" s="2" t="n"/>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Virtual Category (Icon) - Homepage (Mobile)</t>
+          <t>TopMobileBoard (Anchor)</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>80x83</t>
+          <t>600x200</t>
         </is>
       </c>
       <c r="F418" s="2" t="n"/>
@@ -18326,13 +18326,13 @@
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I418" s="2" t="n"/>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
+          <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
       <c r="K418" s="3" t="inlineStr">
@@ -18355,12 +18355,12 @@
       <c r="C419" s="2" t="n"/>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>TopMobileBoard (Anchor)</t>
+          <t>Full Branding Mobile</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>600x200</t>
+          <t>1x 600x200, 3x 300x250</t>
         </is>
       </c>
       <c r="F419" s="2" t="n"/>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I419" s="2" t="n"/>
@@ -18400,12 +18400,12 @@
       <c r="C420" s="2" t="n"/>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Full Branding Mobile</t>
+          <t>Rectangle (MREC) (Mobile)</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>1x 600x200, 3x 300x250</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="F420" s="2" t="n"/>
@@ -18416,13 +18416,13 @@
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I420" s="2" t="n"/>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Mobile).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="K420" s="3" t="inlineStr">
@@ -18445,12 +18445,12 @@
       <c r="C421" s="2" t="n"/>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (Mobile)</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>1000x563</t>
         </is>
       </c>
       <c r="F421" s="2" t="n"/>
@@ -18461,13 +18461,13 @@
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I421" s="2" t="n"/>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+          <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
         </is>
       </c>
       <c r="K421" s="3" t="inlineStr">
@@ -18490,29 +18490,29 @@
       <c r="C422" s="2" t="n"/>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Text Link / Brand Link (Mobile)</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>1000x563</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="F422" s="2" t="n"/>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="I422" s="2" t="n"/>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
         </is>
       </c>
       <c r="K422" s="3" t="inlineStr">
@@ -18535,29 +18535,29 @@
       <c r="C423" s="2" t="n"/>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Text Link / Brand Link (Mobile)</t>
+          <t>Top Mobile Board (Seller/Observed Page)</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
+          <t>320x100</t>
         </is>
       </c>
       <c r="F423" s="2" t="n"/>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I423" s="2" t="n"/>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+          <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
         </is>
       </c>
       <c r="K423" s="3" t="inlineStr">
@@ -18580,12 +18580,12 @@
       <c r="C424" s="2" t="n"/>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Top Mobile Board (Seller/Observed Page)</t>
+          <t>Rectangle (MREC) (App)</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>320x100</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="F424" s="2" t="n"/>
@@ -18602,7 +18602,7 @@
       <c r="I424" s="2" t="n"/>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>Posição: Seller Listing Page &amp; Observed Page (Mobile).</t>
+          <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
         </is>
       </c>
       <c r="K424" s="3" t="inlineStr">
@@ -18625,12 +18625,12 @@
       <c r="C425" s="2" t="n"/>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (App)</t>
+          <t>Observed Ads (App)</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>320x100</t>
         </is>
       </c>
       <c r="F425" s="2" t="n"/>
@@ -18647,7 +18647,7 @@
       <c r="I425" s="2" t="n"/>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (App — Android e iOS).</t>
+          <t>Posição: Observed Page (App).</t>
         </is>
       </c>
       <c r="K425" s="3" t="inlineStr">
@@ -18670,7 +18670,7 @@
       <c r="C426" s="2" t="n"/>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Observed Ads (App)</t>
+          <t>Top Mobile Board (App - Homepage)</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -18692,7 +18692,7 @@
       <c r="I426" s="2" t="n"/>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>Posição: Observed Page (App).</t>
+          <t>Posição: Homepage (App — Android e iOS).</t>
         </is>
       </c>
       <c r="K426" s="3" t="inlineStr">
@@ -18704,23 +18704,23 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>StandVirtual</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>StandVirtual</t>
         </is>
       </c>
       <c r="C427" s="2" t="n"/>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Top Mobile Board (App - Homepage)</t>
+          <t>Showcase (Masthead)</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>320x100</t>
+          <t>1920x300</t>
         </is>
       </c>
       <c r="F427" s="2" t="n"/>
@@ -18737,7 +18737,7 @@
       <c r="I427" s="2" t="n"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (App — Android e iOS).</t>
+          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K427" s="3" t="inlineStr">
@@ -18760,7 +18760,7 @@
       <c r="C428" s="2" t="n"/>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Showcase (Masthead)</t>
+          <t>Megaboard (Topboard)</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -18782,7 +18782,7 @@
       <c r="I428" s="2" t="n"/>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K428" s="3" t="inlineStr">
@@ -18805,12 +18805,12 @@
       <c r="C429" s="2" t="n"/>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>Megaboard (Topboard)</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>1920x300</t>
+          <t>Imagem: 252x152. Logo: 80x36.</t>
         </is>
       </c>
       <c r="F429" s="2" t="n"/>
@@ -18821,13 +18821,13 @@
       </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I429" s="2" t="n"/>
       <c r="J429" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
         </is>
       </c>
       <c r="K429" s="3" t="inlineStr">
@@ -18850,12 +18850,12 @@
       <c r="C430" s="2" t="n"/>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Skyscraper | Halfpage</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 252x152. Logo: 80x36.</t>
+          <t>160x600 ou 300x600</t>
         </is>
       </c>
       <c r="F430" s="2" t="n"/>
@@ -18866,13 +18866,13 @@
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I430" s="2" t="n"/>
       <c r="J430" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="K430" s="3" t="inlineStr">
@@ -18895,12 +18895,12 @@
       <c r="C431" s="2" t="n"/>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>Skyscraper | Halfpage</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>160x600 ou 300x600</t>
+          <t>914x212</t>
         </is>
       </c>
       <c r="F431" s="2" t="n"/>
@@ -18940,12 +18940,12 @@
       <c r="C432" s="2" t="n"/>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Rectangle (MREC)</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>914x212</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="F432" s="2" t="n"/>
@@ -18962,7 +18962,7 @@
       <c r="I432" s="2" t="n"/>
       <c r="J432" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop).</t>
+          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
         </is>
       </c>
       <c r="K432" s="3" t="inlineStr">
@@ -18985,12 +18985,12 @@
       <c r="C433" s="2" t="n"/>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>Rectangle (MREC)</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="F433" s="2" t="n"/>
@@ -19007,7 +19007,7 @@
       <c r="I433" s="2" t="n"/>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page &amp; Gallery Page (Desktop).</t>
+          <t>Posição: Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="K433" s="3" t="inlineStr">
@@ -19030,29 +19030,33 @@
       <c r="C434" s="2" t="n"/>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Video Outstream</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="F434" s="2" t="n"/>
+          <t>1920x1080</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 10 MB</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>MP4, até 30 segundos</t>
         </is>
       </c>
       <c r="I434" s="2" t="n"/>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="K434" s="3" t="inlineStr">
@@ -19075,33 +19079,29 @@
       <c r="C435" s="2" t="n"/>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>Video Outstream</t>
+          <t>Showcase (Masthead) (Mobile)</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>1920x1080</t>
-        </is>
-      </c>
-      <c r="F435" s="2" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>1080x450</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="n"/>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
-          <t>MP4, até 30 segundos</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I435" s="2" t="n"/>
       <c r="J435" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+          <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
       <c r="K435" s="3" t="inlineStr">
@@ -19124,12 +19124,12 @@
       <c r="C436" s="2" t="n"/>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Showcase (Masthead) (Mobile)</t>
+          <t>Full Branding Mobile</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>1080x450</t>
+          <t>1x 600x200, 3x 300x250</t>
         </is>
       </c>
       <c r="F436" s="2" t="n"/>
@@ -19140,13 +19140,13 @@
       </c>
       <c r="H436" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="I436" s="2" t="n"/>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Mobile).</t>
+          <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
       <c r="K436" s="3" t="inlineStr">
@@ -19169,12 +19169,12 @@
       <c r="C437" s="2" t="n"/>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>Full Branding Mobile</t>
+          <t>TopMobileBoard (Anchor)</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>1x 600x200, 3x 300x250</t>
+          <t>600x200</t>
         </is>
       </c>
       <c r="F437" s="2" t="n"/>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I437" s="2" t="n"/>
@@ -19214,12 +19214,12 @@
       <c r="C438" s="2" t="n"/>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>TopMobileBoard (Anchor)</t>
+          <t>Rectangle (MREC) (Mobile)</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>600x200</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="F438" s="2" t="n"/>
@@ -19236,7 +19236,7 @@
       <c r="I438" s="2" t="n"/>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Mobile).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="K438" s="3" t="inlineStr">
@@ -19248,23 +19248,23 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>StandVirtual</t>
+          <t>Imovirtual</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>StandVirtual</t>
+          <t>Imovirtual</t>
         </is>
       </c>
       <c r="C439" s="2" t="n"/>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (Mobile)</t>
+          <t>Megaboard (Topboard)</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>1920x200</t>
         </is>
       </c>
       <c r="F439" s="2" t="n"/>
@@ -19281,7 +19281,7 @@
       <c r="I439" s="2" t="n"/>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+          <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
         </is>
       </c>
       <c r="K439" s="3" t="inlineStr">
@@ -19304,12 +19304,12 @@
       <c r="C440" s="2" t="n"/>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Megaboard (Topboard)</t>
+          <t>Native (In List)</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>1920x200</t>
+          <t>820x200</t>
         </is>
       </c>
       <c r="F440" s="2" t="n"/>
@@ -19326,7 +19326,7 @@
       <c r="I440" s="2" t="n"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Ter atenção às áreas visíveis (Safe Zones).</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="K440" s="3" t="inlineStr">
@@ -19349,12 +19349,12 @@
       <c r="C441" s="2" t="n"/>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>Native (In List)</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>820x200</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="F441" s="2" t="n"/>
@@ -19371,7 +19371,7 @@
       <c r="I441" s="2" t="n"/>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop).</t>
+          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="K441" s="3" t="inlineStr">
@@ -19394,12 +19394,12 @@
       <c r="C442" s="2" t="n"/>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Rectangle (MREC)</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="F442" s="2" t="n"/>
@@ -19439,29 +19439,29 @@
       <c r="C443" s="2" t="n"/>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Rectangle (MREC)</t>
+          <t>Text Link (Brand Link)</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="F443" s="2" t="n"/>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="I443" s="2" t="n"/>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Desktop).</t>
+          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
         </is>
       </c>
       <c r="K443" s="3" t="inlineStr">
@@ -19484,29 +19484,29 @@
       <c r="C444" s="2" t="n"/>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Text Link (Brand Link)</t>
+          <t>Rectangle (MREC) (Mobile)</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="F444" s="2" t="n"/>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
+          <t>Máx. 1 MB</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>JPG, PNG, GIF ou HTML5</t>
         </is>
       </c>
       <c r="I444" s="2" t="n"/>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="K444" s="3" t="inlineStr">
@@ -19529,29 +19529,29 @@
       <c r="C445" s="2" t="n"/>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Rectangle (MREC) (Mobile)</t>
+          <t>Text Link (Brand Link) (Mobile)</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>Logo: 80x80 (opcional)</t>
         </is>
       </c>
       <c r="F445" s="2" t="n"/>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF ou HTML5</t>
+          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
       <c r="I445" s="2" t="n"/>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page &amp; Ad Page (Mobile).</t>
+          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
         </is>
       </c>
       <c r="K445" s="3" t="inlineStr">
@@ -19563,50 +19563,373 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>Imovirtual</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Imovirtual</t>
+          <t>Ogury</t>
         </is>
       </c>
       <c r="C446" s="2" t="n"/>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Text Link (Brand Link) (Mobile)</t>
+          <t>Display Creatives - Image - Full Screen</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>Logo: 80x80 (opcional)</t>
+          <t>1388x1734 (recomendado, mobile portrait). Safe zone: 780x1734. Danger zone: 304x1734 (cada lado).</t>
         </is>
       </c>
       <c r="F446" s="2" t="n"/>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB (apenas se incluir logo)</t>
+          <t>Ideal: 100 KB. Máx.: 2 MB.</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
       <c r="I446" s="2" t="n"/>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos. CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra"). Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
         </is>
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>https://formatos-publicidade-olx.netlify.app/</t>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#full-screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="n"/>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Thumbnail</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>720x540 (ratio 1,3, mobile portrait). Safe zone: 648x540. Danger zone: 36x540 (cada lado).</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="n"/>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Ideal: 50 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="n"/>
+      <c r="J447" s="2" t="inlineStr">
+        <is>
+          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="K447" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#thumbnail</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="n"/>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Header</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>2640x600 (mobile portrait). Safe zone: 1060x600. Danger zone: 789x600 (cada lado).</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="n"/>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Ideal: 50 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="n"/>
+      <c r="J448" s="2" t="inlineStr">
+        <is>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="K448" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#header</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="n"/>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Footer</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>1760x400 (mobile portrait). Safe zone: 1280x400. Danger zone: 240x400 (cada lado).</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="n"/>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>Ideal: 50 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="n"/>
+      <c r="J449" s="2" t="inlineStr">
+        <is>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="K449" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="n"/>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - Reveal</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>1388x1734 (mobile portrait). Safe zone: 780x1734. Danger zone: 304x1734 (cada lado).</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="n"/>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Ideal: 100 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="n"/>
+      <c r="J450" s="2" t="inlineStr">
+        <is>
+          <t>Unidade criativa dinâmica in-article, pensada para visibilidade máxima durante o scroll em conteúdo mobile web. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="K450" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#reveal</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="n"/>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Image - In-Article MPU</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>300x250 (ratio 1:2)</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="n"/>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Ideal: 100 KB. Máx.: 2 MB.</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="n"/>
+      <c r="J451" s="2" t="inlineStr">
+        <is>
+          <t>Unidade in-article, pensada para consideração e tráfego qualificado. Incluído só nalguns pacotes — confirmar na recomendação de media. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+        </is>
+      </c>
+      <c r="K451" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#in-article-mpu</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="n"/>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>Video Creatives - Horizontal Video</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>16:9. Recomendado: 1024x576px.</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>MP4, VAST tag ou VPAID (legacy)</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="n"/>
+      <c r="J452" s="2" t="inlineStr">
+        <is>
+          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: nome da marca/produto e texto de CTA (máx. 30 carateres; "Visit website" por defeito). Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: Top &amp; Bottom Skins (imagens estáticas JPG/PNG, 768x450px cada, sobrepostas ao vídeo, sem tracking próprio); Bottom Skin isolado (JPG/PNG, 768x930px, sem tracking próprio); End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB). Templates Photoshop disponíveis para as skins/end card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+        </is>
+      </c>
+      <c r="K452" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/video-studio/horizontal-video-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="n"/>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>Video Creatives - Vertical Video</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>9:16. Recomendado: 576x1024px.</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>MP4, VAST tag ou VPAID (legacy)</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="n"/>
+      <c r="J453" s="2" t="inlineStr">
+        <is>
+          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: heading ("Choose your ad" por defeito), nomes de produto/feature, cor de fundo (branco por defeito) — formato interativo tipo "video chooser". Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB, com opção de end card multi-CTA, sem tracking próprio); Video Chooser Image (specs não detalhadas nos materiais enviados — confirmar com a equipa Ogury). Template Photoshop disponível para o End Card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+        </is>
+      </c>
+      <c r="K453" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/video-studio/vertical-video-specs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K446"/>
+  <autoFilter ref="A1:K453"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -19937,7 +20260,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K387" r:id="rId327"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K401" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K403" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K404" r:id="rId331"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K405" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K406" r:id="rId333"/>
@@ -19981,6 +20304,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K444" r:id="rId371"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K445" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K446" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K447" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K448" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K449" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K450" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K451" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K452" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K453" r:id="rId380"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$453</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$467</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K453"/>
+  <dimension ref="A1:K467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19928,8 +19928,650 @@
         </is>
       </c>
     </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="n"/>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Brand Spotlight</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="n"/>
+      <c r="G454" s="2" t="n"/>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr">
+        <is>
+          <t>Carrossel rich media interativo para mostrar vários produtos, features ou mensagens de marca numa experiência deslizável (swipe). Disponível para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos/variações); storytelling sequencial (mensagem revelada passo a passo); 3D Brand Spotlight (transição em cubo 3D); multi-CTA (vários CTAs rastreados individualmente, na mesma slide ou em slides diferentes, cada um com destino próprio); vídeo (no root da criatividade, visível durante o swipe, ou integrado numa slide específica). Boas práticas: limitar a ~5-6 slides; manter o CTA visível; mensagem concisa por slide; consistência visual entre slides. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K454" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/brand-spotlight-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="n"/>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Product Galore</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="n"/>
+      <c r="G455" s="2" t="n"/>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr">
+        <is>
+          <t>Carrossel rich media interativo com navegação em camadas: o utilizador interage com elementos no ecrã de entrada para aceder a vistas de detalhe dedicadas. Para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos, cada um com vista de detalhe); variações e opções (cores, estilos, configurações); product deep dive (um produto, várias camadas de informação); com vídeo (no ecrã de entrada ou dentro de uma vista de detalhe); com carrossel (carrossel dentro da vista de detalhe, para ângulos/features/variações adicionais). Boas práticas: limitar o nº de elementos interativos no ecrã de entrada; elementos clicáveis claramente identificáveis; botão de voltar sempre visível quando necessário; mensagem concisa por ecrã. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K455" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/product-galore-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="n"/>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Pick &amp; Choose</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="n"/>
+      <c r="G456" s="2" t="n"/>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J456" s="2" t="inlineStr">
+        <is>
+          <t>Formato interativo que permite ao utilizador explorar produtos, variantes, features ou configurações diferentes dentro de uma única criatividade: ao tocar numa opção seletora, o visual principal e o conteúdo associado atualizam-se instantaneamente. Para campanhas CPE e CPM. Casos de uso: seleção de produto (navegar vários produtos, cada seleção atualiza o visual/conteúdo); personalização de variante (cores, estilos, sabores, acabamentos — ideal para automóvel, moda, beleza, alimentação, mobiliário, eletrónica de consumo). Boas práticas: limitar o nº de opções selecionáveis; destacar claramente a opção selecionada; cada seleção deve gerar uma mudança visual percetível; CTA sempre visível; consistência visual entre variantes; seletores suficientemente grandes para toque em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails de produto, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K456" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/pick-and-choose-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="n"/>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Drag &amp; Drop</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="n"/>
+      <c r="G457" s="2" t="n"/>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J457" s="2" t="inlineStr">
+        <is>
+          <t>Formato interativo em que o utilizador arrasta um ou mais elementos para áreas-alvo predefinidas para completar uma ação; ao concluir, revela conteúdo/novo ecrã. Para campanhas CPE e CPM. Casos de uso: product reveal (arrastar elemento(s) para revelar produto/oferta/mensagem); demonstração de uso do produto; receitas/ingredientes (arrastar ingredientes para uma tigela/prato/copo); desafio gamificado (ex.: marcar golo, colocar um item, fazer correspondências) antes de desbloquear o passo seguinte. Boas práticas: interação intuitiva, elementos arrastáveis e zonas de largada claramente identificáveis; pistas visuais/animações/copy instrucional; elementos fáceis de manipular em mobile; limitar o nº de ações necessárias; recompensar interações bem-sucedidas; progressão clara (nº de ações em falta). Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K457" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/drag-and-drop-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="n"/>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Hotspots</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="n"/>
+      <c r="G458" s="2" t="n"/>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr">
+        <is>
+          <t>Formato interativo com hotspots clicáveis sobre elementos-chave de um visual; ao tocar, revela conteúdo adicional (informação de produto, features, preço, imagem, vídeo ou CTA). Para campanhas CPE e CPM. Casos de uso: informação de produto (hotspots numa imagem, cada um revela info/preço/CTA); product deep dive (hotspots ligados a componentes/funcionalidades específicas). Boas práticas: limitar o nº de hotspots por ecrã; posicionar em áreas relevantes do visual; garantir visibilidade clara (contraste/espaçamento); conteúdo de cada hotspot conciso; evitar sobreposição de áreas; consistência visual entre o conteúdo dos hotspots; áreas de toque suficientemente grandes em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K458" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/hotspots-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="n"/>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Comparison Slider</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="n"/>
+      <c r="G459" s="2" t="n"/>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr">
+        <is>
+          <t>Formato interativo que permite comparar dois visuais arrastando um slider pelo ecrã — revela progressivamente uma imagem enquanto esconde a outra, criando uma experiência "antes e depois". Para campanhas CPE e CPM. Casos de uso: antes e depois (transformação visual: skincare, tratamentos de beleza, fitness, remodelações); personalização de produto (cores, estilos, sabores, acabamentos, variações); impacto de produto/serviço (ex.: produtos de limpeza, tintas, jardinagem, restauro); comparação de features (ex.: standard vs. premium, modelo antigo vs. novo); melhoria de performance (ex.: desporto, nutrição, saúde e bem-estar). Boas práticas: visuais altamente contrastados; imagens perfeitamente alinhadas; pista de interação clara (setas, labels, animação subtil); foco numa única mensagem-chave; branding e CTA sempre visíveis; otimizar para leitura em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K459" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/comparison-slider-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="n"/>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Puzzle</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="n"/>
+      <c r="G460" s="2" t="n"/>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="n"/>
+      <c r="J460" s="2" t="inlineStr">
+        <is>
+          <t>Formato interativo em que o utilizador reconstrói uma imagem para desbloquear conteúdo adicional; ao completar o puzzle, mostra um ecrã de revelação final. Para campanhas CPE e CPM. Casos de uso: revelação de produto (produto, embalagem ou visual hero); desbloqueio de oferta (promoção, desconto, conteúdo exclusivo); engagement gamificado; storytelling de marca; teaser de evento/lançamento. Boas práticas: usar uma imagem visualmente apelativa e facilmente reconhecível; desafio simples e intuitivo (resolúvel em poucos segundos); revelação final com valor; branding consistente em todos os ecrãs; CTA apelativo; otimizar para interação em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K460" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/puzzle-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="n"/>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Tap to Reveal</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="n"/>
+      <c r="G461" s="2" t="n"/>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr">
+        <is>
+          <t>Formato interativo com uma interação simples de toque que desbloqueia conteúdo adicional: começa com um visual teaser e revela uma segunda camada de conteúdo (imagem, vídeo, slideshow, animação ou mensagem promocional). Para campanhas CPE e CPM. Casos de uso: slideshow reveal; video reveal; offer reveal (promoção/oferta exclusiva/mensagem-chave); transformação criativa (mudança de universo visual, ex. campanhas sazonais/lançamentos); antes e depois (estado transformado — beleza, fitness, automóvel, melhoria de casa). Boas práticas: tornar a interação óbvia; forte contraste entre teaser e conteúdo revelado; primeiro ecrã simples e focado; usar a revelação para a mensagem-chave; transições suaves; otimizar para mobile; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K461" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/tap-to-reveal-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="n"/>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Tap to Map</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Fullscreen e In-Article apenas. Formatos IAB standard: 970x250, 300x600, 300x250, 336x280, 320x480.</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="n"/>
+      <c r="G462" s="2" t="n"/>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr">
+        <is>
+          <t>Combina uma criatividade de marca com um localizador de lojas integrado: o utilizador interage com um visual promocional e depois toca num CTA para aceder a um mapa interativo dentro do próprio anúncio, mostrando lojas, pontos de venda, postos de carregamento, concessionários ou outras localizações físicas próximas. Casos de uso: localizador de loja; localizações de evento; rede de agências/balcões/serviço; rede de postos de carregamento EV. Boas práticas: CTA forte orientado a localização (ex.: "Find a Store"); introdução concisa antes de passar ao mapa; informação de localização completa. Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K462" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/tap-to-map-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="n"/>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Site Scroller</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="n"/>
+      <c r="G463" s="2" t="n"/>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr">
+        <is>
+          <t>Experiência imersiva multi-página que permite navegação vertical por conteúdo de marca através de swipe (cima/baixo), replicando a navegação num site/landing page, com produtos, features, storytelling ou conteúdo promocional distribuídos por várias páginas dentro do mesmo anúncio. Casos de uso: product showcase (features/benefícios/configurações em páginas dedicadas); storytelling (jornada narrativa sequencial); promoção de evento/campanha (vários aspetos de um lançamento/evento em páginas diferentes); com carrossel (carrossel integrado para visibilidade adicional de produto). Boas práticas: limitar a 4-5 páginas no máximo; hierarquia visual clara (uma mensagem-chave por página); incentivar o scroll (setas/indicadores direcionais); consistência visual; fluxo narrativo lógico; terminar com um CTA forte. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K463" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/site-scroller-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="n"/>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - 360°</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>Creative (PNG): 1080x1920. Brand Logo (PNG). Vista 360°: 8+ imagens (PNG).</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="n"/>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>PNG (creative, logo e imagens da vista 360°)</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>CTA: "Buy Now" ou "Learn More" por defeito; customizado máx. 3 palavras.</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr">
+        <is>
+          <t>Mostra o produto a partir de todos os ângulos. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+        </is>
+      </c>
+      <c r="K464" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/360-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="n"/>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Quiz</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>Variável — disponível nos formatos próprios Ogury (ver página de tamanhos suportados) e nos formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250.</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="n"/>
+      <c r="G465" s="2" t="n"/>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>Pergunta/afirmação inicial; opções de resposta (recomendado 1-2 palavras cada); ecrã(s) de resultado (um ecrã partilhado ou dois ecrãs dedicados, um por resposta); texto de CTA para o(s) ecrã(s) final/finais.</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>Carrossel rich media interativo com navegação em camadas (entrada + vista de detalhe), orientado a pergunta/resposta. Para campanhas CPE e CPM. Casos de uso: sondagem de preferência (escolha entre duas opções/preferências/opiniões/produtos, cada resposta rastreada individualmente, podendo revelar conteúdo dedicado); awareness &amp; educação (pergunta verdadeiro/falso, revela a resposta certa + conteúdo educativo — ideal para awareness, saúde, informação pública, sustentabilidade, educação financeira/de marca); recomendação de produto (guia o utilizador para o produto/solução mais relevante consoante a resposta). Boas práticas: perguntas curtas e fáceis de perceber; opções de resposta claras e distintas; labels de resposta curtos; ambas as opções igualmente visíveis; resultado relevante para a escolha do utilizador; foco numa única pergunta; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K465" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/quiz-design-specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="n"/>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Social Display</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>Logo: 256x256px. Imagem: 950x1000px.</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="n"/>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Logo: máx. 100 KB. Imagem: máx. 400 KB.</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>Logo: PNG. Imagem: JPEG (pode incluir texto).</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>Nome da marca, texto superior (máx. 85 carateres recomendado), texto inferior (máx. 50 carateres), domínio da marca, CTA ("Discover" por defeito).</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>Reaproveita os assets da marca para emular a experiência social (Facebook, Instagram, TikTok, Twitter, LinkedIn, Pinterest ou Snapchat — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury.</t>
+        </is>
+      </c>
+      <c r="K466" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/social-display-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="n"/>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Rich Media &amp; Engagement Studio - Social Carousel</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>Logo: 256x256px. Carrossel de imagens (máx. 5): 750x1000px cada.</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Logo: máx. 100 KB. Cada imagem do carrossel: máx. 100 KB.</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>Logo: PNG. Imagens do carrossel: JPEG (podem incluir texto).</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>Nome da marca, texto superior (máx. 85 carateres recomendado), texto inferior (máx. 50 carateres), domínio da marca.</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr">
+        <is>
+          <t>Reaproveita os assets da marca para emular a experiência de carrossel social (Facebook ou Instagram — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+        </is>
+      </c>
+      <c r="K467" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/social-carousel-specs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K453"/>
+  <autoFilter ref="A1:K467"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -20311,6 +20953,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K451" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K452" r:id="rId379"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K453" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K454" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K455" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K456" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K457" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K458" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K459" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K460" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K461" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K462" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K463" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K464" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K465" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K466" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K467" r:id="rId394"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$467</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$473</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K467"/>
+  <dimension ref="A1:K473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20570,8 +20570,278 @@
         </is>
       </c>
     </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="n"/>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Slideshow</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Fullscreen, Header, Footer, Thumbnail, In-article Reveal. Formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250, 120x600, 728x90, 320x100, 300x100, 320x50, 300x50.</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="n"/>
+      <c r="G468" s="2" t="n"/>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr">
+        <is>
+          <t>Anima o storytelling: liga narrativa com transições suaves e mensagens sequenciais, ideal para destacar várias features de produto ou mensagens-chave numa única criatividade. Casos de uso: visual animado único (estático melhorado com movimento subtil); storytelling sequencial (multi-ecrã); multi-CTA (vários CTAs rastreados individualmente, na mesma tela ou em telas diferentes, cada um com destino próprio); Slideshow com vídeo (vídeo visível durante toda a experiência); Slideshow para vídeo (sequência de slideshow seguida de um ecrã de vídeo dedicado); Slideshow com animação Lottie (elementos animados leves — neve, partículas, efeitos de fundo — sem aumentar o peso do ficheiro); Slideshow com disclaimer legal scrollável (texto legal extenso numa área com scroll automático/manual). Boas práticas: limitar a ~5-6 capítulos; manter o CTA visível; mensagem concisa por ecrã; consistência visual entre capítulos. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K468" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/slideshow-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="n"/>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Pop</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="n"/>
+      <c r="G469" s="2" t="n"/>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr">
+        <is>
+          <t>Efeito de expansão rápido e chamativo, que dá impacto visual instantâneo e atrai naturalmente a atenção para elementos-chave, mantendo a experiência fluida e não intrusiva. Casos de uso: destaque de produto (efeito pop subtil); ênfase de CTA; revelação de oferta (promoções/descontos/mensagens-chave); reforço do visual principal. Boas práticas: aplicar o efeito pop a produtos, logos ou CTAs para maximizar o impacto; layout limpo (sem sobrecarregar); uma mensagem de cada vez; contraste visual forte; alinhado com a marca; a animação deve reforçar a mensagem, não distrair. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K469" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/pop-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="n"/>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Glide</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="n"/>
+      <c r="G470" s="2" t="n"/>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr">
+        <is>
+          <t>Efeito de revelação horizontal: um segundo visual desliza suavemente sobre o primeiro, criando uma transição clara e envolvente — ideal para mostrar contrastes, detalhes de produto ou mensagens-chave de forma dinâmica mas controlada. Casos de uso: revelação de cor (preto e branco para cor); revelação de detalhe de produto (vista global para vista de pormenor); comparação visual. Boas práticas: usar dois visuais complementares; layout limpo; foco numa única ideia; contraste forte; visuais alinhados entre si (estilo/composição); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/glide-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="n"/>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Shift</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="n"/>
+      <c r="G471" s="2" t="n"/>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J471" s="2" t="inlineStr">
+        <is>
+          <t>Transição vertical suave entre dois visuais, trazendo o conteúdo para o ecrã de forma natural e guiando a atenção do utilizador — ideal para mostrar duas mensagens/visuais complementares, com uma experiência limpa e premium. Casos de uso: antes/depois; foco de produto (dois ângulos/features complementares); transição de mensagem; marca e produto; tease &amp; reveal; destaque duplo (dois elementos com igual visibilidade). Boas práticas: dois visuais complementares; mensagem simples (uma ideia); continuidade visual (cor/estilo/composição); guiar o olhar do utilizador de um visual para o outro; ambos os visuais com valor standalone forte; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K471" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/shift-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="n"/>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Rise</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="n"/>
+      <c r="G472" s="2" t="n"/>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr">
+        <is>
+          <t>Combina uma transição vertical com um efeito de revelação limpo, introduzindo visuais ou mensagens com clareza e impacto, numa experiência fluida e fácil de seguir. Casos de uso: introdução visual; destaque de produto (revelação suave); revelação de mensagem (estruturada, fácil de ler); marca e mensagem; foco em elemento-chave. Boas práticas: visuais simples e claros; foco numa única mensagem; visuais consistentes entre si; guiar a atenção naturalmente; a revelação deve acrescentar valor real; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K472" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/rise-design-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Ogury</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="n"/>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>Display Creatives - Unfold</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="n"/>
+      <c r="G473" s="2" t="n"/>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>PSD (camadas), AI, INDD, Figma ou XD</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr">
+        <is>
+          <t>Efeito de revelação a partir do centro: os visuais dividem-se e desdobram-se para introduzir novo conteúdo, criando uma transição dinâmica que mantém o utilizador envolvido — ideal para revelar progressivamente vários visuais de forma fluida e estruturada. Casos de uso: storytelling sequencial; showcase de produto (produtos/variações diferentes); destaque de coleção (ex. moda, beleza, automóvel); breakdown de features; revelação de campanha (mensagens-chave progressivas); progressão visual (evolução de um visual para outro). Boas práticas: limitar a 5 ecrãs no máximo; estilo consistente entre todos os visuais; foco numa ideia principal; visuais fortes (impacto imediato em cada ecrã); layout limpo (sem clutter); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+        </is>
+      </c>
+      <c r="K473" s="3" t="inlineStr">
+        <is>
+          <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/unfold-design-specifications</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K467"/>
+  <autoFilter ref="A1:K473"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -20967,6 +21237,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K465" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K466" r:id="rId393"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K467" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K468" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K469" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K470" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K471" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K472" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K473" r:id="rId400"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -26171,7 +26171,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Spot TV (HD — XDCAM HD422)</t>
+          <t>Spot</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$473</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$482</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K473"/>
+  <dimension ref="A1:K482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20840,8 +20840,385 @@
         </is>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="n"/>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Super Like</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>Ícone: 196x196px (mín. 160x160px) — área de output 200x200px, o visual não pode ultrapassar esta área. Cartão pop-up (opcional): 620x788px, com a área do botão CTA a 620x168px na base.</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="n"/>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>Ícone: máx. 50 KB. Cartão pop-up: máx. 3 MB.</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>Ícone: PNG. Cartão pop-up: JPG, JPEG ou PNG.</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="n"/>
+      <c r="J474" s="2" t="inlineStr">
+        <is>
+          <t>Add-on interativo: ícones em forma de coração (ou personalizados) flutuam pelo ecrã quando a audiência dá like ou toca duas vezes no anúncio. Pode incluir-se opcionalmente um cartão pop-up personalizado, que aparece depois da animação — ao clicar, leva à landing page do anúncio. Imagem do ícone: fornecer uma única imagem estática (é redimensionada automaticamente); design rico e preenchido com cor de fundo, evitando formas ocas, sombra, dispersão de elementos, formas finas ou efeito 3D; se retangular, cantos arredondados a 24px; deixar 2px de margem à volta da área válida; evitar que o elemento principal fique demasiado pequeno em relação à área efetiva (vermelha). Cartão pop-up: evitar design totalmente branco ou transparente.</t>
+        </is>
+      </c>
+      <c r="K474" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-super-like</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="n"/>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Pop-out Showcase</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>Elemento pop-out: 448x448px.</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="n"/>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>Elemento pop-out: 100 KB a 500 KB.</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>Elemento pop-out: PNG. Vídeo do anúncio: ver specs gerais do In-Feed.</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>CTA do elemento pop-out: até 27 carateres EN ou até 13 CN/JP/KR. Carateres half-width ocupam 1 espaço, full-width ocupam 2. Não suporta emojis nem carateres especiais ({ }, @, #). Não suporta links na legenda do anúncio. Evitar código de barras, código de ações, ID de Facebook/Instagram/WhatsApp/Messenger ou outra informação de redes sociais.</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr">
+        <is>
+          <t>O vídeo do anúncio toca normalmente e o botão CTA aparece; depois, um elemento pop-out salta para o centro do ecrã, minimiza-se e desloca-se para o canto esquerdo. O vídeo do anúncio tem de ter mín. 8 segundos (recomendado 15s+). O elemento pop-out tem de ser o mesmo produto/SKU/cor do anúncio, e só pode aparecer enquanto o produto está visível no ecrã; só pode ser definido a partir dos 3 segundos de anúncio e até, no mínimo, 5 segundos antes do fim. Sem limitação de ângulo de entrada (o elemento gira até 0° no sentido que corresponde ao ângulo de entrada). Posição do elemento: entre X 125-515, Y 200-710 (ver ferramenta de pré-visualização da TikTok). O elemento ajusta automaticamente o tamanho para não sobrepor a legenda do anúncio.</t>
+        </is>
+      </c>
+      <c r="K475" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-pop-out-showcase</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="n"/>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Display Card</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>Upload recomendado: 1920x1080px (qualquer tamanho é aceite — a plataforma permite recortar/redimensionar). Tamanho final de apresentação: 750x421px.</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="n"/>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>Sem limite de tamanho de ficheiro.</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>JPG, JPEG ou PNG.</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="n"/>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>Card interativo que aparece dentro do anúncio in-feed, para destacar mensagens importantes, ofertas exclusivas ou direcionar para o site/app. O popup do card aparece automaticamente ao fim de alguns segundos — o momento é calculado pela plataforma consoante o objetivo, indústria e comportamento da audiência, não é configurável. Forma do card: sempre retangular. Evitar design transparente no meio do card (a margem pode ser transparente). Incluir um botão CTA claramente visível. A cor deve destacar-se do vídeo. Evitar material com pixels baixos, mosaico ou serrilhado nos contornos. As safe zones variam consoante o formato do anúncio (vertical/quadrado/horizontal) e o comprimento da legenda (legendas mais longas reduzem a safe zone) — descarregar os ficheiros de safe zone correspondentes e usar a ferramenta de pré-visualização para confirmar. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda).</t>
+        </is>
+      </c>
+      <c r="K476" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-display-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="n"/>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Gesture</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>Cartão: 620x788px, com a área do botão CTA a 620x168px na base.</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="n"/>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>Cartão: máx. 3 MB. Música de fundo: máx. 100 KB.</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>Cartão: JPG, JPEG, PNG ou GIF. Música de fundo: MP3.</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>Texto de orientação do gesto: até 27 carateres EN ou até 13 CN/JP/KR. Carateres half-width ocupam 1 espaço, full-width ocupam 2. Não suporta emojis nem carateres especiais ({ }, @, #). Não suporta links na legenda do anúncio. Evitar código de barras, código de ações, ID de Facebook/Instagram/WhatsApp/Messenger ou outra informação de redes sociais.</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr">
+        <is>
+          <t>Convida a audiência a tocar ou deslizar no anúncio para desbloquear recompensas ou mais informação. Música de fundo do pop-up obrigatória: 6 segundos, idealmente consistente com a música do próprio vídeo do anúncio. Momento do pop-up: em Reach &amp; Frequency, a partir dos 3 segundos de anúncio e até 5 segundos antes do fim; em Auction Reach, a partir dos 6 segundos e até 5 segundos antes do fim. Posição, comprimento e ângulo do gesto configuram-se na ferramenta de pré-visualização (o ângulo tem de respeitar a zona marcada a vermelho). Vídeo do anúncio: mín. 8 segundos (recomendado 15s+). Gestos suportados: clique, deslize reto ou deslize curvo. O URL do cartão usa sempre o mesmo URL do botão CTA do anúncio (não se insere em separado).</t>
+        </is>
+      </c>
+      <c r="K477" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-gesture</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="n"/>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Gift Code Sticker</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="n"/>
+      <c r="F478" s="2" t="n"/>
+      <c r="G478" s="2" t="n"/>
+      <c r="H478" s="2" t="n"/>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>Nome do código: até 10 carateres CN/JP/KR ou até 20 noutras línguas. Código: até 10 carateres CN/JP/KR ou até 21 noutras línguas.</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>Adiciona um código promocional exclusivo ao vídeo do anúncio. Elementos do sticker: título, código, botão de copiar e botão CTA. Cor do sticker: cinzento ou azul (sem personalização de cor). Os anúncios com Gift Code Sticker têm de incluir URL (pode ser o mesmo da página de destino do anúncio). Garantir que o sticker fica dentro da safe zone.</t>
+        </is>
+      </c>
+      <c r="K478" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-gift-code-sticker</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="n"/>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Countdown Sticker</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="n"/>
+      <c r="F479" s="2" t="n"/>
+      <c r="G479" s="2" t="n"/>
+      <c r="H479" s="2" t="n"/>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>Título: até 54 carateres EN ou até 27 carateres CN/JP/KR. Não suporta hashtag (#).</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr">
+        <is>
+          <t>Adiciona um temporizador de contagem decrescente ao vídeo do anúncio. Tamanho, ângulo e posição ajustam-se no TikTok Ads Manager. Cor do sticker: laranja, preto, azul ou rosa (sem personalização de cor). O título mostra-se na língua em que foi escrito (não é traduzido automaticamente) — sugerir frases como "termina em"/"começa em". O CTA é o mesmo escolhido no Ads Manager, traduzido automaticamente para a língua do utilizador (suporta Dynamic CTA). Os anúncios com Countdown Sticker têm de incluir URL (pode ser o mesmo da página de destino). O tempo é traduzido e calculado automaticamente consoante o fuso horário do utilizador. Garantir que o sticker fica dentro da safe zone (azul).</t>
+        </is>
+      </c>
+      <c r="K479" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-countdown-sticker</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="n"/>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Voting Sticker</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="n"/>
+      <c r="F480" s="2" t="n"/>
+      <c r="G480" s="2" t="n"/>
+      <c r="H480" s="2" t="n"/>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>Título: até 65 carateres EN ou até 32 CN/JP/KR. Opção A e Opção B: até 16 carateres EN ou até 8 CN/JP/KR cada.</t>
+        </is>
+      </c>
+      <c r="J480" s="2" t="inlineStr">
+        <is>
+          <t>Adiciona um tópico de votação com duas opções ao vídeo do anúncio, para aumentar o engagement e recolher informação relevante. Elementos: título, texto da opção A e texto da opção B. Cor do texto: título sempre a branco (sem personalização); opções A/B disponíveis em vermelho, azul claro ou azul escuro. Garantir que o sticker fica dentro da safe zone.</t>
+        </is>
+      </c>
+      <c r="K480" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-voting-sticker</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="n"/>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Download Card</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="n"/>
+      <c r="F481" s="2" t="n"/>
+      <c r="G481" s="2" t="n"/>
+      <c r="H481" s="2" t="n"/>
+      <c r="I481" s="2" t="n"/>
+      <c r="J481" s="2" t="inlineStr">
+        <is>
+          <t>Mostra elementos da app promovida (avaliação, nº de reviews, indústria) dentro do anúncio in-feed — é um elemento clicável que leva à loja de download da app. Cada elemento-chave (texto, logos) tem de ficar dentro da safe zone, sob pena de ser cortado/tapado. O tamanho da safe zone depende do formato do anúncio (vertical/quadrado/horizontal) e do comprimento da legenda — legendas mais longas reduzem a safe zone; descarregar os ficheiros de safe zone correspondentes ao formato usado. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda). Confirmar sempre na ferramenta de pré-visualização.</t>
+        </is>
+      </c>
+      <c r="K481" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-interactive-add-on-download-card-ad-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="n"/>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Add-on - Story Selection</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo principal: mín. 5s (6s em anúncios 6s Focused View), máx. 60s (recomendado &lt;10s). Sub-vídeo A e sub-vídeo B: máx. 30s cada. Imagem de capa dos sub-vídeos (opcional): 144x192px.</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="n"/>
+      <c r="G482" s="2" t="n"/>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>Vídeos: MP4, MOV, MPEG ou 3GP. Imagens de capa: PNG ou JPG.</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>Tópico de seleção: até 40 carateres EN ou até 20 CN/KR/JP.</t>
+        </is>
+      </c>
+      <c r="J482" s="2" t="inlineStr">
+        <is>
+          <t>Função de seleção de história para anúncios in-feed: a audiência escolhe o próximo vídeo que quer ver. Criativos: vídeo principal (obrigatório), tópico de seleção em texto (obrigatório), sub-vídeo A (obrigatório) + imagem de capa (opcional — se não for fornecida, a plataforma usa a imagem do primeiro segundo do sub-vídeo, mas fornecer uma melhora a experiência), sub-vídeo B (obrigatório) + imagem de capa (opcional, mesma regra). Deixar o texto afastado das margens e evitar cobrir elementos-chave com o botão Play.</t>
+        </is>
+      </c>
+      <c r="K482" s="3" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/about-tiktok-interactive-add-on-story-selection?lang=en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K473"/>
+  <autoFilter ref="A1:K482"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -21243,6 +21620,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K471" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K472" r:id="rId399"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K473" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K474" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K475" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K476" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K477" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K478" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K479" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K480" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K481" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K482" r:id="rId409"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21254,7 +21640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26075,8 +26461,137 @@
       </c>
       <c r="I133" s="2" t="n"/>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã Digital - Canal Executivo (Horizontal)</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>1280x720px (horizontal)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Máx.: 3 MB.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>MP4, WMV ou AVI</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Duração recomendada: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã Digital - Canal Executivo (Vertical)</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>720x1280px (vertical)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Máx.: 3 MB.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>MP4, WMV ou AVI</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Duração recomendada: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>LiftMedia</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã Digital - Canal Residencial</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>960x540px</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Máx.: 400 KB.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>MP4 ou JPG</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios residenciais (Canal Residencial), rede com 868 ecrãs em 578 edifícios em Portugal. Duração: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I133"/>
+  <autoFilter ref="A1:I136"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$488</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$489</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K488"/>
+  <dimension ref="A1:K489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21495,8 +21495,45 @@
       </c>
       <c r="K488" s="2" t="n"/>
     </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="n"/>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>Display Digital</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>Sem especificações obrigatórias — qualquer dimensão é aceite.</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="n"/>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>Sem limite de peso.</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="n"/>
+      <c r="I489" s="2" t="n"/>
+      <c r="J489" s="2" t="inlineStr">
+        <is>
+          <t>Confirmado diretamente pela Kwanko: "Do nosso lado não temos limite de peso nem tamanho nos nossos formatos digitais. Não há especificações requeridas."</t>
+        </is>
+      </c>
+      <c r="K489" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K488"/>
+  <autoFilter ref="A1:K489"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$489</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cinema'!$A$1:$I$3</definedName>
@@ -21959,7 +21959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26909,8 +26909,206 @@
       </c>
       <c r="I136" s="2" t="n"/>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Mupi Digital</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>1080x1920 píxeis (ecrã de 75″).</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>MP4, orientação vertical.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Duração do anúncio: 10 segundos, em loop a cada 1 minuto. Prazo de envio dos ficheiros: 7 dias antes do início da campanha. Formato Retail Media.</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Mupi</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Painel publicitário: 1,40x2,56m (2m²). Dimensão do corte: 1185x1750mm. Área visível: 1147x1697mm. Altura do pé: 550mm.</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Mupi de 2 faces com vidro temperado "securit" de 8mm; estrutura em aço galvanizado com tratamento anticorrosivo; quadro em alumínio com tratamento polyester; iluminado. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor 4x3</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Painel publicitário: 4x3m (12m²), composto por 4 módulos de alumínio de 3x1m cada.</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="2" t="n"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Módulos fixos a 2 vigas de ferro I 120-IPN, distanciadas 2,60m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor 8x3</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Painel publicitário: 8x3m (24m²), composto por 8 módulos de alumínio de 3x1m cada.</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Módulos fixos a 4 vigas de ferro I 120-IPN, distanciadas 2,40m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>GirodMedias</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Monoposte 10x5</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Área publicitária: 10x5m. Produção de 2 telas impressas digitalmente ao formato 10,40x5,40m.</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="2" t="n"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Iluminação por 8 projetores LED de 100W (4 por face). Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Mupi Papel</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>234x348mm + 1mm de bleed.</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>PDF.</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>CMYK, 300 dpi. Margem de segurança: 10mm. Miras de corte. Textos e logótipos convertidos em curvas.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I136"/>
+  <autoFilter ref="A1:I142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$489</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$498</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K489"/>
+  <dimension ref="A1:K498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21509,31 +21509,388 @@
       <c r="C489" s="2" t="n"/>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Display Digital</t>
+          <t>Medium Rectangle</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>Sem especificações obrigatórias — qualquer dimensão é aceite.</t>
+          <t>300x250px.</t>
         </is>
       </c>
       <c r="F489" s="2" t="n"/>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>Sem limite de peso.</t>
-        </is>
-      </c>
-      <c r="H489" s="2" t="n"/>
+          <t>Máx. 150 KB.</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
       <c r="I489" s="2" t="n"/>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>Confirmado diretamente pela Kwanko: "Do nosso lado não temos limite de peso nem tamanho nos nossos formatos digitais. Não há especificações requeridas."</t>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
         </is>
       </c>
       <c r="K489" s="2" t="n"/>
     </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="n"/>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>728x90px.</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="n"/>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB.</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="n"/>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+      <c r="K490" s="2" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="n"/>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>Wide Skyscraper</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>160x600px.</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="n"/>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB.</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="n"/>
+      <c r="J491" s="2" t="inlineStr">
+        <is>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+      <c r="K491" s="2" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="n"/>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Banner</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>320x50px.</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="n"/>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB.</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="n"/>
+      <c r="J492" s="2" t="inlineStr">
+        <is>
+          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+      <c r="K492" s="2" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="n"/>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>Half Page</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>300x600px.</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="n"/>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB.</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="n"/>
+      <c r="J493" s="2" t="inlineStr">
+        <is>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+      <c r="K493" s="2" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="n"/>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>970x250px.</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="n"/>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB.</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF, HTML5.</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="n"/>
+      <c r="J494" s="2" t="inlineStr">
+        <is>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+        </is>
+      </c>
+      <c r="K494" s="2" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="n"/>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>Kit de Email Marketing</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>Largura máxima: 600px.</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="n"/>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>Código fonte: máx. 100 KB (para evitar corte por limite de peso em clientes como o Gmail).</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>HTML estático.</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="n"/>
+      <c r="J495" s="2" t="inlineStr">
+        <is>
+          <t>Apenas código HTML estático — não incluir Javascript, iframes, Flash ou formulários embebidos. O CSS deve estar sempre declarado inline (dentro das tags) e nunca na secção head. Imagens alojadas num servidor público e fiável, com URLs absolutos e completos (ex.: https://www.dominio.pt/assets/header.jpg).</t>
+        </is>
+      </c>
+      <c r="K495" s="2" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="n"/>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>Native Ads</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>Imagem principal: 1200x628px ou 600x600px.</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="n"/>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>Imagem principal: até 250 KB.</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>JPG, PNG (imagem principal).</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>Título do anúncio: 50 a 60 caracteres, de forma impactante. Copy/Descrição: 90 a 100 caracteres, com o contexto da campanha e o benefício direto para o utilizador. Call to Action: texto claro e direto (ex.: "Saber Mais", "Comprar Agora", "Registe-se Aqui").</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="inlineStr">
+        <is>
+          <t>A imagem principal deve estar visualmente limpa, sem texto sobreposto nem logótipos intrusivos.</t>
+        </is>
+      </c>
+      <c r="K496" s="2" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="n"/>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>Catálogo/Feed de Produtos</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="n"/>
+      <c r="F497" s="2" t="n"/>
+      <c r="G497" s="2" t="n"/>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>XML (preferencial) ou CSV, via URL dinâmico.</t>
+        </is>
+      </c>
+      <c r="I497" s="2" t="n"/>
+      <c r="J497" s="2" t="inlineStr">
+        <is>
+          <t>Sincronização/atualização no mínimo diária. Campos obrigatórios: ID único, Título do Produto, Preço de Venda, Preço Anterior (se aplicável), URL da página de produto, URL da imagem em boa resolução, e Categoria.</t>
+        </is>
+      </c>
+      <c r="K497" s="2" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>Kwanko</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="n"/>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>Vouchers e Códigos Promocionais</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="n"/>
+      <c r="F498" s="2" t="n"/>
+      <c r="G498" s="2" t="n"/>
+      <c r="H498" s="2" t="n"/>
+      <c r="I498" s="2" t="n"/>
+      <c r="J498" s="2" t="inlineStr">
+        <is>
+          <t>Ao partilhar materiais para campanhas baseadas em Códigos de Desconto (Cupões), é obrigatório indicar à Kwanko: o código exato (em formato de texto copiável); a mecânica exata do desconto (ex.: -10€ diretos, 20% desconto no carrinho, Oferta de Portes); a data de início e de expiração rigorosas da campanha; e as regras de exclusão (produtos ou marcas não abrangidos pela promoção).</t>
+        </is>
+      </c>
+      <c r="K498" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K489"/>
+  <autoFilter ref="A1:K498"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -21876,7 +21876,7 @@
       <c r="I498" s="2" t="n"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K498" s="3" t="inlineStr">
@@ -21921,7 +21921,7 @@
       <c r="I499" s="2" t="n"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K499" s="3" t="inlineStr">
@@ -21966,7 +21966,7 @@
       <c r="I500" s="2" t="n"/>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K500" s="3" t="inlineStr">
@@ -22011,7 +22011,7 @@
       <c r="I501" s="2" t="n"/>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K501" s="3" t="inlineStr">
@@ -22093,7 +22093,7 @@
       <c r="I503" s="2" t="n"/>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K503" s="3" t="inlineStr">
@@ -22138,7 +22138,7 @@
       <c r="I504" s="2" t="n"/>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K504" s="3" t="inlineStr">
@@ -22183,7 +22183,7 @@
       <c r="I505" s="2" t="n"/>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K505" s="3" t="inlineStr">
@@ -22228,7 +22228,7 @@
       <c r="I506" s="2" t="n"/>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K506" s="3" t="inlineStr">
@@ -22273,7 +22273,7 @@
       <c r="I507" s="2" t="n"/>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K507" s="3" t="inlineStr">
@@ -22318,7 +22318,7 @@
       <c r="I508" s="2" t="n"/>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K508" s="3" t="inlineStr">
@@ -22363,7 +22363,7 @@
       <c r="I509" s="2" t="n"/>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K509" s="3" t="inlineStr">
@@ -22408,7 +22408,7 @@
       <c r="I510" s="2" t="n"/>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K510" s="3" t="inlineStr">
@@ -22453,7 +22453,7 @@
       <c r="I511" s="2" t="n"/>
       <c r="J511" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K511" s="3" t="inlineStr">
@@ -22498,7 +22498,7 @@
       <c r="I512" s="2" t="n"/>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto.</t>
         </is>
       </c>
       <c r="K512" s="3" t="inlineStr">
@@ -22543,7 +22543,7 @@
       <c r="I513" s="2" t="n"/>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K513" s="3" t="inlineStr">
@@ -22588,7 +22588,7 @@
       <c r="I514" s="2" t="n"/>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K514" s="3" t="inlineStr">
@@ -22633,7 +22633,7 @@
       <c r="I515" s="2" t="n"/>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K515" s="3" t="inlineStr">
@@ -22678,7 +22678,7 @@
       <c r="I516" s="2" t="n"/>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K516" s="3" t="inlineStr">
@@ -22723,7 +22723,7 @@
       <c r="I517" s="2" t="n"/>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K517" s="3" t="inlineStr">
@@ -22768,7 +22768,7 @@
       <c r="I518" s="2" t="n"/>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K518" s="3" t="inlineStr">
@@ -22813,7 +22813,7 @@
       <c r="I519" s="2" t="n"/>
       <c r="J519" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K519" s="3" t="inlineStr">
@@ -22858,7 +22858,7 @@
       <c r="I520" s="2" t="n"/>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K520" s="3" t="inlineStr">
@@ -22903,7 +22903,7 @@
       <c r="I521" s="2" t="n"/>
       <c r="J521" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K521" s="3" t="inlineStr">
@@ -22948,7 +22948,7 @@
       <c r="I522" s="2" t="n"/>
       <c r="J522" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K522" s="3" t="inlineStr">
@@ -22993,7 +22993,7 @@
       <c r="I523" s="2" t="n"/>
       <c r="J523" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores.</t>
         </is>
       </c>
       <c r="K523" s="3" t="inlineStr">
@@ -23038,7 +23038,7 @@
       <c r="I524" s="2" t="n"/>
       <c r="J524" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°.</t>
         </is>
       </c>
       <c r="K524" s="3" t="inlineStr">
@@ -23083,7 +23083,7 @@
       <c r="I525" s="2" t="n"/>
       <c r="J525" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K525" s="3" t="inlineStr">
@@ -23128,7 +23128,7 @@
       <c r="I526" s="2" t="n"/>
       <c r="J526" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K526" s="3" t="inlineStr">
@@ -23173,7 +23173,7 @@
       <c r="I527" s="2" t="n"/>
       <c r="J527" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo.</t>
         </is>
       </c>
       <c r="K527" s="3" t="inlineStr">
@@ -23218,7 +23218,7 @@
       <c r="I528" s="2" t="n"/>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K528" s="3" t="inlineStr">
@@ -23263,7 +23263,7 @@
       <c r="I529" s="2" t="n"/>
       <c r="J529" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
         </is>
       </c>
       <c r="K529" s="3" t="inlineStr">
@@ -23308,7 +23308,7 @@
       <c r="I530" s="2" t="n"/>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
         </is>
       </c>
       <c r="K530" s="3" t="inlineStr">
@@ -23353,7 +23353,7 @@
       <c r="I531" s="2" t="n"/>
       <c r="J531" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K531" s="3" t="inlineStr">
@@ -23398,7 +23398,7 @@
       <c r="I532" s="2" t="n"/>
       <c r="J532" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K532" s="3" t="inlineStr">
@@ -23443,7 +23443,7 @@
       <c r="I533" s="2" t="n"/>
       <c r="J533" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
         </is>
       </c>
       <c r="K533" s="3" t="inlineStr">
@@ -23488,7 +23488,7 @@
       <c r="I534" s="2" t="n"/>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas). Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas).</t>
         </is>
       </c>
       <c r="K534" s="3" t="inlineStr">
@@ -23533,7 +23533,7 @@
       <c r="I535" s="2" t="n"/>
       <c r="J535" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo.</t>
         </is>
       </c>
       <c r="K535" s="3" t="inlineStr">
@@ -23578,7 +23578,7 @@
       <c r="I536" s="2" t="n"/>
       <c r="J536" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify.</t>
         </is>
       </c>
       <c r="K536" s="3" t="inlineStr">
@@ -23623,7 +23623,7 @@
       <c r="I537" s="2" t="n"/>
       <c r="J537" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K537" s="3" t="inlineStr">
@@ -23668,7 +23668,7 @@
       <c r="I538" s="2" t="n"/>
       <c r="J538" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K538" s="3" t="inlineStr">
@@ -23713,7 +23713,7 @@
       <c r="I539" s="2" t="n"/>
       <c r="J539" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K539" s="3" t="inlineStr">
@@ -23758,7 +23758,7 @@
       <c r="I540" s="2" t="n"/>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
         </is>
       </c>
       <c r="K540" s="3" t="inlineStr">
@@ -23803,7 +23803,7 @@
       <c r="I541" s="2" t="n"/>
       <c r="J541" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3.</t>
         </is>
       </c>
       <c r="K541" s="3" t="inlineStr">
@@ -23848,7 +23848,7 @@
       <c r="I542" s="2" t="n"/>
       <c r="J542" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K542" s="3" t="inlineStr">
@@ -23893,7 +23893,7 @@
       <c r="I543" s="2" t="n"/>
       <c r="J543" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K543" s="3" t="inlineStr">
@@ -23938,7 +23938,7 @@
       <c r="I544" s="2" t="n"/>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K544" s="3" t="inlineStr">
@@ -23983,7 +23983,7 @@
       <c r="I545" s="2" t="n"/>
       <c r="J545" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização.</t>
         </is>
       </c>
       <c r="K545" s="3" t="inlineStr">
@@ -24028,7 +24028,7 @@
       <c r="I546" s="2" t="n"/>
       <c r="J546" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K546" s="3" t="inlineStr">
@@ -24073,7 +24073,7 @@
       <c r="I547" s="2" t="n"/>
       <c r="J547" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K547" s="3" t="inlineStr">
@@ -24118,7 +24118,7 @@
       <c r="I548" s="2" t="n"/>
       <c r="J548" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K548" s="3" t="inlineStr">
@@ -24163,7 +24163,7 @@
       <c r="I549" s="2" t="n"/>
       <c r="J549" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
         </is>
       </c>
       <c r="K549" s="3" t="inlineStr">
@@ -24208,7 +24208,7 @@
       <c r="I550" s="2" t="n"/>
       <c r="J550" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
         </is>
       </c>
       <c r="K550" s="3" t="inlineStr">
@@ -24253,7 +24253,7 @@
       <c r="I551" s="2" t="n"/>
       <c r="J551" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
         </is>
       </c>
       <c r="K551" s="3" t="inlineStr">
@@ -24298,7 +24298,7 @@
       <c r="I552" s="2" t="n"/>
       <c r="J552" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K552" s="3" t="inlineStr">
@@ -24343,7 +24343,7 @@
       <c r="I553" s="2" t="n"/>
       <c r="J553" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
         </is>
       </c>
       <c r="K553" s="3" t="inlineStr">
@@ -24388,7 +24388,7 @@
       <c r="I554" s="2" t="n"/>
       <c r="J554" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K554" s="3" t="inlineStr">
@@ -24433,7 +24433,7 @@
       <c r="I555" s="2" t="n"/>
       <c r="J555" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados.</t>
         </is>
       </c>
       <c r="K555" s="3" t="inlineStr">
@@ -24478,7 +24478,7 @@
       <c r="I556" s="2" t="n"/>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
         </is>
       </c>
       <c r="K556" s="3" t="inlineStr">
@@ -24523,7 +24523,7 @@
       <c r="I557" s="2" t="n"/>
       <c r="J557" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
         </is>
       </c>
       <c r="K557" s="3" t="inlineStr">
@@ -24568,7 +24568,7 @@
       <c r="I558" s="2" t="n"/>
       <c r="J558" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização.</t>
         </is>
       </c>
       <c r="K558" s="3" t="inlineStr">
@@ -24613,7 +24613,7 @@
       <c r="I559" s="2" t="n"/>
       <c r="J559" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K559" s="3" t="inlineStr">
@@ -24654,7 +24654,7 @@
       <c r="I560" s="2" t="n"/>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL).</t>
+          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL).</t>
         </is>
       </c>
       <c r="K560" s="3" t="inlineStr">
@@ -24699,7 +24699,7 @@
       <c r="I561" s="2" t="n"/>
       <c r="J561" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K561" s="3" t="inlineStr">
@@ -24744,7 +24744,7 @@
       <c r="I562" s="2" t="n"/>
       <c r="J562" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K562" s="3" t="inlineStr">
@@ -24789,7 +24789,7 @@
       <c r="I563" s="2" t="n"/>
       <c r="J563" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K563" s="3" t="inlineStr">
@@ -24834,7 +24834,7 @@
       <c r="I564" s="2" t="n"/>
       <c r="J564" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K564" s="3" t="inlineStr">
@@ -24879,7 +24879,7 @@
       <c r="I565" s="2" t="n"/>
       <c r="J565" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K565" s="3" t="inlineStr">
@@ -24924,7 +24924,7 @@
       <c r="I566" s="2" t="n"/>
       <c r="J566" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K566" s="3" t="inlineStr">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="J567" s="2" t="inlineStr">
         <is>
-          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy. Definição (Azerion): formato publicitário digital que se integra naturalmente no conteúdo/design da plataforma onde aparece, imitando o seu estilo visual para não interromper a experiência do utilizador.</t>
+          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy.</t>
         </is>
       </c>
       <c r="K567" s="3" t="inlineStr">
@@ -25014,7 +25014,7 @@
       <c r="I568" s="2" t="n"/>
       <c r="J568" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K568" s="3" t="inlineStr">
@@ -25059,7 +25059,7 @@
       <c r="I569" s="2" t="n"/>
       <c r="J569" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K569" s="3" t="inlineStr">
@@ -25104,7 +25104,7 @@
       <c r="I570" s="2" t="n"/>
       <c r="J570" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K570" s="3" t="inlineStr">
@@ -25149,7 +25149,7 @@
       <c r="I571" s="2" t="n"/>
       <c r="J571" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K571" s="3" t="inlineStr">
@@ -25194,7 +25194,7 @@
       <c r="I572" s="2" t="n"/>
       <c r="J572" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K572" s="3" t="inlineStr">
@@ -25239,7 +25239,7 @@
       <c r="I573" s="2" t="n"/>
       <c r="J573" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K573" s="3" t="inlineStr">
@@ -25284,7 +25284,7 @@
       <c r="I574" s="2" t="n"/>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K574" s="3" t="inlineStr">
@@ -25329,7 +25329,7 @@
       <c r="I575" s="2" t="n"/>
       <c r="J575" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K575" s="3" t="inlineStr">
@@ -25374,7 +25374,7 @@
       <c r="I576" s="2" t="n"/>
       <c r="J576" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K576" s="3" t="inlineStr">
@@ -25419,7 +25419,7 @@
       <c r="I577" s="2" t="n"/>
       <c r="J577" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K577" s="3" t="inlineStr">
@@ -25464,7 +25464,7 @@
       <c r="I578" s="2" t="n"/>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K578" s="3" t="inlineStr">
@@ -25509,7 +25509,7 @@
       <c r="I579" s="2" t="n"/>
       <c r="J579" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K579" s="3" t="inlineStr">
@@ -25554,7 +25554,7 @@
       <c r="I580" s="2" t="n"/>
       <c r="J580" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K580" s="3" t="inlineStr">
@@ -25599,7 +25599,7 @@
       <c r="I581" s="2" t="n"/>
       <c r="J581" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K581" s="3" t="inlineStr">
@@ -25644,7 +25644,7 @@
       <c r="I582" s="2" t="n"/>
       <c r="J582" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K582" s="3" t="inlineStr">
@@ -25689,7 +25689,7 @@
       <c r="I583" s="2" t="n"/>
       <c r="J583" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K583" s="3" t="inlineStr">
@@ -25734,7 +25734,7 @@
       <c r="I584" s="2" t="n"/>
       <c r="J584" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K584" s="3" t="inlineStr">
@@ -25779,7 +25779,7 @@
       <c r="I585" s="2" t="n"/>
       <c r="J585" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K585" s="3" t="inlineStr">
@@ -25824,7 +25824,7 @@
       <c r="I586" s="2" t="n"/>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="K586" s="3" t="inlineStr">
@@ -25869,7 +25869,7 @@
       <c r="I587" s="2" t="n"/>
       <c r="J587" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Definição (Azerion): criatividade publicitária digital estática e otimizada, usada sobretudo para captar atenção, gerar interação e aumentar vendas. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion.</t>
         </is>
       </c>
       <c r="K587" s="3" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -21870,13 +21870,13 @@
       </c>
       <c r="H498" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I498" s="2" t="n"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K498" s="3" t="inlineStr">
@@ -21915,13 +21915,13 @@
       </c>
       <c r="H499" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I499" s="2" t="n"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K499" s="3" t="inlineStr">
@@ -21960,13 +21960,13 @@
       </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I500" s="2" t="n"/>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K500" s="3" t="inlineStr">
@@ -22005,13 +22005,13 @@
       </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I501" s="2" t="n"/>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K501" s="3" t="inlineStr">
@@ -22087,13 +22087,13 @@
       </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I503" s="2" t="n"/>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K503" s="3" t="inlineStr">
@@ -22132,13 +22132,13 @@
       </c>
       <c r="H504" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I504" s="2" t="n"/>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K504" s="3" t="inlineStr">
@@ -22177,13 +22177,13 @@
       </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I505" s="2" t="n"/>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K505" s="3" t="inlineStr">
@@ -22222,13 +22222,13 @@
       </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I506" s="2" t="n"/>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K506" s="3" t="inlineStr">
@@ -22267,13 +22267,13 @@
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I507" s="2" t="n"/>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K507" s="3" t="inlineStr">
@@ -22312,13 +22312,13 @@
       </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I508" s="2" t="n"/>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K508" s="3" t="inlineStr">
@@ -22357,13 +22357,13 @@
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I509" s="2" t="n"/>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K509" s="3" t="inlineStr">
@@ -22402,13 +22402,13 @@
       </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>JPEG, GIF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I510" s="2" t="n"/>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
         </is>
       </c>
       <c r="K510" s="3" t="inlineStr">
@@ -22447,13 +22447,13 @@
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I511" s="2" t="n"/>
       <c r="J511" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K511" s="3" t="inlineStr">
@@ -22492,13 +22492,13 @@
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I512" s="2" t="n"/>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K512" s="3" t="inlineStr">
@@ -22537,13 +22537,13 @@
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I513" s="2" t="n"/>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K513" s="3" t="inlineStr">
@@ -22582,13 +22582,13 @@
       </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I514" s="2" t="n"/>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K514" s="3" t="inlineStr">
@@ -22627,13 +22627,13 @@
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I515" s="2" t="n"/>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K515" s="3" t="inlineStr">
@@ -22672,13 +22672,13 @@
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I516" s="2" t="n"/>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K516" s="3" t="inlineStr">
@@ -22717,13 +22717,13 @@
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I517" s="2" t="n"/>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K517" s="3" t="inlineStr">
@@ -22762,13 +22762,13 @@
       </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I518" s="2" t="n"/>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K518" s="3" t="inlineStr">
@@ -22807,13 +22807,13 @@
       </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I519" s="2" t="n"/>
       <c r="J519" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K519" s="3" t="inlineStr">
@@ -22852,13 +22852,13 @@
       </c>
       <c r="H520" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I520" s="2" t="n"/>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K520" s="3" t="inlineStr">
@@ -22897,13 +22897,13 @@
       </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I521" s="2" t="n"/>
       <c r="J521" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K521" s="3" t="inlineStr">
@@ -22942,13 +22942,13 @@
       </c>
       <c r="H522" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I522" s="2" t="n"/>
       <c r="J522" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K522" s="3" t="inlineStr">
@@ -22987,13 +22987,13 @@
       </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I523" s="2" t="n"/>
       <c r="J523" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K523" s="3" t="inlineStr">
@@ -23032,13 +23032,13 @@
       </c>
       <c r="H524" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I524" s="2" t="n"/>
       <c r="J524" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K524" s="3" t="inlineStr">
@@ -23077,13 +23077,13 @@
       </c>
       <c r="H525" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I525" s="2" t="n"/>
       <c r="J525" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K525" s="3" t="inlineStr">
@@ -23122,13 +23122,13 @@
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I526" s="2" t="n"/>
       <c r="J526" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K526" s="3" t="inlineStr">
@@ -23167,13 +23167,13 @@
       </c>
       <c r="H527" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I527" s="2" t="n"/>
       <c r="J527" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K527" s="3" t="inlineStr">
@@ -23212,13 +23212,13 @@
       </c>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I528" s="2" t="n"/>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K528" s="3" t="inlineStr">
@@ -23257,13 +23257,13 @@
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I529" s="2" t="n"/>
       <c r="J529" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K529" s="3" t="inlineStr">
@@ -23302,13 +23302,13 @@
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I530" s="2" t="n"/>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K530" s="3" t="inlineStr">
@@ -23347,13 +23347,13 @@
       </c>
       <c r="H531" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I531" s="2" t="n"/>
       <c r="J531" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K531" s="3" t="inlineStr">
@@ -23392,13 +23392,13 @@
       </c>
       <c r="H532" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I532" s="2" t="n"/>
       <c r="J532" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K532" s="3" t="inlineStr">
@@ -23437,13 +23437,13 @@
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I533" s="2" t="n"/>
       <c r="J533" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K533" s="3" t="inlineStr">
@@ -23482,13 +23482,13 @@
       </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I534" s="2" t="n"/>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas).</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K534" s="3" t="inlineStr">
@@ -23527,13 +23527,13 @@
       </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I535" s="2" t="n"/>
       <c r="J535" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K535" s="3" t="inlineStr">
@@ -23572,13 +23572,13 @@
       </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I536" s="2" t="n"/>
       <c r="J536" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K536" s="3" t="inlineStr">
@@ -23617,13 +23617,13 @@
       </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I537" s="2" t="n"/>
       <c r="J537" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K537" s="3" t="inlineStr">
@@ -23662,13 +23662,13 @@
       </c>
       <c r="H538" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I538" s="2" t="n"/>
       <c r="J538" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K538" s="3" t="inlineStr">
@@ -23707,13 +23707,13 @@
       </c>
       <c r="H539" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I539" s="2" t="n"/>
       <c r="J539" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K539" s="3" t="inlineStr">
@@ -23752,13 +23752,13 @@
       </c>
       <c r="H540" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I540" s="2" t="n"/>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K540" s="3" t="inlineStr">
@@ -23797,13 +23797,13 @@
       </c>
       <c r="H541" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I541" s="2" t="n"/>
       <c r="J541" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K541" s="3" t="inlineStr">
@@ -23842,13 +23842,13 @@
       </c>
       <c r="H542" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I542" s="2" t="n"/>
       <c r="J542" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K542" s="3" t="inlineStr">
@@ -23887,13 +23887,13 @@
       </c>
       <c r="H543" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I543" s="2" t="n"/>
       <c r="J543" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K543" s="3" t="inlineStr">
@@ -23932,13 +23932,13 @@
       </c>
       <c r="H544" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I544" s="2" t="n"/>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K544" s="3" t="inlineStr">
@@ -23977,13 +23977,13 @@
       </c>
       <c r="H545" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I545" s="2" t="n"/>
       <c r="J545" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K545" s="3" t="inlineStr">
@@ -24022,13 +24022,13 @@
       </c>
       <c r="H546" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I546" s="2" t="n"/>
       <c r="J546" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K546" s="3" t="inlineStr">
@@ -24067,13 +24067,13 @@
       </c>
       <c r="H547" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I547" s="2" t="n"/>
       <c r="J547" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K547" s="3" t="inlineStr">
@@ -24112,13 +24112,13 @@
       </c>
       <c r="H548" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I548" s="2" t="n"/>
       <c r="J548" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K548" s="3" t="inlineStr">
@@ -24157,13 +24157,13 @@
       </c>
       <c r="H549" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I549" s="2" t="n"/>
       <c r="J549" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K549" s="3" t="inlineStr">
@@ -24202,13 +24202,13 @@
       </c>
       <c r="H550" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I550" s="2" t="n"/>
       <c r="J550" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K550" s="3" t="inlineStr">
@@ -24247,13 +24247,13 @@
       </c>
       <c r="H551" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I551" s="2" t="n"/>
       <c r="J551" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K551" s="3" t="inlineStr">
@@ -24292,13 +24292,13 @@
       </c>
       <c r="H552" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I552" s="2" t="n"/>
       <c r="J552" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K552" s="3" t="inlineStr">
@@ -24337,13 +24337,13 @@
       </c>
       <c r="H553" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I553" s="2" t="n"/>
       <c r="J553" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K553" s="3" t="inlineStr">
@@ -24382,13 +24382,13 @@
       </c>
       <c r="H554" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I554" s="2" t="n"/>
       <c r="J554" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K554" s="3" t="inlineStr">
@@ -24427,13 +24427,13 @@
       </c>
       <c r="H555" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I555" s="2" t="n"/>
       <c r="J555" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K555" s="3" t="inlineStr">
@@ -24472,13 +24472,13 @@
       </c>
       <c r="H556" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I556" s="2" t="n"/>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K556" s="3" t="inlineStr">
@@ -24517,13 +24517,13 @@
       </c>
       <c r="H557" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I557" s="2" t="n"/>
       <c r="J557" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K557" s="3" t="inlineStr">
@@ -24562,13 +24562,13 @@
       </c>
       <c r="H558" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I558" s="2" t="n"/>
       <c r="J558" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K558" s="3" t="inlineStr">
@@ -24607,13 +24607,13 @@
       </c>
       <c r="H559" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I559" s="2" t="n"/>
       <c r="J559" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K559" s="3" t="inlineStr">
@@ -24648,13 +24648,13 @@
       <c r="G560" s="2" t="n"/>
       <c r="H560" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I560" s="2" t="n"/>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL).</t>
+          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL). Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K560" s="3" t="inlineStr">
@@ -24693,13 +24693,13 @@
       </c>
       <c r="H561" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I561" s="2" t="n"/>
       <c r="J561" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K561" s="3" t="inlineStr">
@@ -24738,13 +24738,13 @@
       </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I562" s="2" t="n"/>
       <c r="J562" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K562" s="3" t="inlineStr">
@@ -24783,13 +24783,13 @@
       </c>
       <c r="H563" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I563" s="2" t="n"/>
       <c r="J563" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K563" s="3" t="inlineStr">
@@ -24828,13 +24828,13 @@
       </c>
       <c r="H564" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I564" s="2" t="n"/>
       <c r="J564" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K564" s="3" t="inlineStr">
@@ -24873,13 +24873,13 @@
       </c>
       <c r="H565" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I565" s="2" t="n"/>
       <c r="J565" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K565" s="3" t="inlineStr">
@@ -24918,13 +24918,13 @@
       </c>
       <c r="H566" s="2" t="inlineStr">
         <is>
-          <t>HTML5.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I566" s="2" t="n"/>
       <c r="J566" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
         </is>
       </c>
       <c r="K566" s="3" t="inlineStr">
@@ -24959,7 +24959,7 @@
       <c r="G567" s="2" t="n"/>
       <c r="H567" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG (estático).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I567" s="2" t="inlineStr">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="J567" s="2" t="inlineStr">
         <is>
-          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy.</t>
+          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy. Formato final do anúncio: JPEG, PNG (estático).</t>
         </is>
       </c>
       <c r="K567" s="3" t="inlineStr">
@@ -25008,13 +25008,13 @@
       </c>
       <c r="H568" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I568" s="2" t="n"/>
       <c r="J568" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K568" s="3" t="inlineStr">
@@ -25053,13 +25053,13 @@
       </c>
       <c r="H569" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I569" s="2" t="n"/>
       <c r="J569" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K569" s="3" t="inlineStr">
@@ -25098,13 +25098,13 @@
       </c>
       <c r="H570" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I570" s="2" t="n"/>
       <c r="J570" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K570" s="3" t="inlineStr">
@@ -25143,13 +25143,13 @@
       </c>
       <c r="H571" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I571" s="2" t="n"/>
       <c r="J571" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="K571" s="3" t="inlineStr">
@@ -25188,13 +25188,13 @@
       </c>
       <c r="H572" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I572" s="2" t="n"/>
       <c r="J572" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="K572" s="3" t="inlineStr">
@@ -25233,13 +25233,13 @@
       </c>
       <c r="H573" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I573" s="2" t="n"/>
       <c r="J573" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K573" s="3" t="inlineStr">
@@ -25278,13 +25278,13 @@
       </c>
       <c r="H574" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I574" s="2" t="n"/>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K574" s="3" t="inlineStr">
@@ -25323,13 +25323,13 @@
       </c>
       <c r="H575" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I575" s="2" t="n"/>
       <c r="J575" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="K575" s="3" t="inlineStr">
@@ -25368,13 +25368,13 @@
       </c>
       <c r="H576" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I576" s="2" t="n"/>
       <c r="J576" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K576" s="3" t="inlineStr">
@@ -25413,13 +25413,13 @@
       </c>
       <c r="H577" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I577" s="2" t="n"/>
       <c r="J577" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
         </is>
       </c>
       <c r="K577" s="3" t="inlineStr">
@@ -25458,13 +25458,13 @@
       </c>
       <c r="H578" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I578" s="2" t="n"/>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K578" s="3" t="inlineStr">
@@ -25503,13 +25503,13 @@
       </c>
       <c r="H579" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I579" s="2" t="n"/>
       <c r="J579" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K579" s="3" t="inlineStr">
@@ -25548,13 +25548,13 @@
       </c>
       <c r="H580" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I580" s="2" t="n"/>
       <c r="J580" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K580" s="3" t="inlineStr">
@@ -25593,13 +25593,13 @@
       </c>
       <c r="H581" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I581" s="2" t="n"/>
       <c r="J581" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K581" s="3" t="inlineStr">
@@ -25638,13 +25638,13 @@
       </c>
       <c r="H582" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I582" s="2" t="n"/>
       <c r="J582" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K582" s="3" t="inlineStr">
@@ -25683,13 +25683,13 @@
       </c>
       <c r="H583" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I583" s="2" t="n"/>
       <c r="J583" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K583" s="3" t="inlineStr">
@@ -25728,13 +25728,13 @@
       </c>
       <c r="H584" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I584" s="2" t="n"/>
       <c r="J584" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K584" s="3" t="inlineStr">
@@ -25773,13 +25773,13 @@
       </c>
       <c r="H585" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I585" s="2" t="n"/>
       <c r="J585" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K585" s="3" t="inlineStr">
@@ -25818,13 +25818,13 @@
       </c>
       <c r="H586" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I586" s="2" t="n"/>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K586" s="3" t="inlineStr">
@@ -25863,13 +25863,13 @@
       </c>
       <c r="H587" s="2" t="inlineStr">
         <is>
-          <t>JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I587" s="2" t="n"/>
       <c r="J587" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
         </is>
       </c>
       <c r="K587" s="3" t="inlineStr">
@@ -25978,13 +25978,13 @@
       <c r="G590" s="2" t="n"/>
       <c r="H590" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I590" s="2" t="n"/>
       <c r="J590" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com elementos gráficos estáticos e/ou copy, desenhado para captar a atenção do utilizador, reforçar a mensagem de marca e motivar ações que impulsionem a conversão. Disponível em diferentes opções consoante objetivos e orçamento. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com elementos gráficos estáticos e/ou copy, desenhado para captar a atenção do utilizador, reforçar a mensagem de marca e motivar ações que impulsionem a conversão. Disponível em diferentes opções consoante objetivos e orçamento. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K590" s="3" t="inlineStr">
@@ -26019,13 +26019,13 @@
       <c r="G591" s="2" t="n"/>
       <c r="H591" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I591" s="2" t="n"/>
       <c r="J591" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
         </is>
       </c>
       <c r="K591" s="3" t="inlineStr">
@@ -26060,13 +26060,13 @@
       <c r="G592" s="2" t="n"/>
       <c r="H592" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I592" s="2" t="n"/>
       <c r="J592" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K592" s="3" t="inlineStr">
@@ -26101,13 +26101,13 @@
       <c r="G593" s="2" t="n"/>
       <c r="H593" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I593" s="2" t="n"/>
       <c r="J593" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com vídeo de uma só cena (1 a 4 segundos) com movimento em loop contínuo. Permite incluir um botão de play que ativa o vídeo completo em ecrã inteiro, captando a atenção do utilizador e potenciando o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com vídeo de uma só cena (1 a 4 segundos) com movimento em loop contínuo. Permite incluir um botão de play que ativa o vídeo completo em ecrã inteiro, captando a atenção do utilizador e potenciando o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K593" s="3" t="inlineStr">
@@ -26142,13 +26142,13 @@
       <c r="G594" s="2" t="n"/>
       <c r="H594" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I594" s="2" t="n"/>
       <c r="J594" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer interativo que, através de um slider, revela uma imagem. O logótipo e o CTA mantêm-se fixos por cima das imagens, assegurando a visibilidade da marca e potenciando a interação do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer interativo que, através de um slider, revela uma imagem. O logótipo e o CTA mantêm-se fixos por cima das imagens, assegurando a visibilidade da marca e potenciando a interação do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K594" s="3" t="inlineStr">
@@ -26183,13 +26183,13 @@
       <c r="G595" s="2" t="n"/>
       <c r="H595" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I595" s="2" t="n"/>
       <c r="J595" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer em que o cursor se transforma num elemento gráfico ou num call to action sobre um fundo estático. Pode ainda incluir um botão de play que, ao clicar, reproduz um vídeo em modo CTP, captando a atenção do utilizador e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer em que o cursor se transforma num elemento gráfico ou num call to action sobre um fundo estático. Pode ainda incluir um botão de play que, ao clicar, reproduz um vídeo em modo CTP, captando a atenção do utilizador e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K595" s="3" t="inlineStr">
@@ -26224,13 +26224,13 @@
       <c r="G596" s="2" t="n"/>
       <c r="H596" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I596" s="2" t="n"/>
       <c r="J596" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer animado, com imagens em forma de acordeão. O utilizador pode interagir com elas para as visualizar todas, aumentando a participação e o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer animado, com imagens em forma de acordeão. O utilizador pode interagir com elas para as visualizar todas, aumentando a participação e o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K596" s="3" t="inlineStr">
@@ -26265,13 +26265,13 @@
       <c r="G597" s="2" t="n"/>
       <c r="H597" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I597" s="2" t="n"/>
       <c r="J597" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer interativo, com um jogo de raspadinha com duas imagens a ecrã inteiro. Permite ao utilizador descobrir conteúdo ou prémios, captando atenção e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer interativo, com um jogo de raspadinha com duas imagens a ecrã inteiro. Permite ao utilizador descobrir conteúdo ou prémios, captando atenção e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K597" s="3" t="inlineStr">
@@ -26306,13 +26306,13 @@
       <c r="G598" s="2" t="n"/>
       <c r="H598" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I598" s="2" t="n"/>
       <c r="J598" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com vídeo ou animação exclusiva que reflete a identidade da marca. Gera alto impacto visual e reforça o reconhecimento de marca, aumentando o engagement do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com vídeo ou animação exclusiva que reflete a identidade da marca. Gera alto impacto visual e reforça o reconhecimento de marca, aumentando o engagement do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K598" s="3" t="inlineStr">
@@ -26347,13 +26347,13 @@
       <c r="G599" s="2" t="n"/>
       <c r="H599" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I599" s="2" t="n"/>
       <c r="J599" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer em que o rato se transforma numa luz que ilumina a imagem de fundo. Fomenta a interação ativa do utilizador e destaca produtos ou mensagens-chave de forma apelativa. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer em que o rato se transforma numa luz que ilumina a imagem de fundo. Fomenta a interação ativa do utilizador e destaca produtos ou mensagens-chave de forma apelativa. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K599" s="3" t="inlineStr">
@@ -26388,13 +26388,13 @@
       <c r="G600" s="2" t="n"/>
       <c r="H600" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I600" s="2" t="n"/>
       <c r="J600" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer que permite explorar várias imagens deslizando-as horizontalmente. Aumenta a participação do utilizador e oferece múltiplas oportunidades de conversão dentro do mesmo anúncio. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer que permite explorar várias imagens deslizando-as horizontalmente. Aumenta a participação do utilizador e oferece múltiplas oportunidades de conversão dentro do mesmo anúncio. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K600" s="3" t="inlineStr">
@@ -26429,13 +26429,13 @@
       <c r="G601" s="2" t="n"/>
       <c r="H601" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I601" s="2" t="n"/>
       <c r="J601" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com temporizador que mostra o tempo restante para um evento ou oferta. Gera urgência e motiva o utilizador a interagir ou realizar uma ação imediata. Material necessário: ficheiro PSD em camadas, logótipo, tipografia, copy e data. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com temporizador que mostra o tempo restante para um evento ou oferta. Gera urgência e motiva o utilizador a interagir ou realizar uma ação imediata. Material necessário: ficheiro PSD em camadas, logótipo, tipografia, copy e data. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K601" s="3" t="inlineStr">
@@ -26470,13 +26470,13 @@
       <c r="G602" s="2" t="n"/>
       <c r="H602" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF.</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I602" s="2" t="n"/>
       <c r="J602" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com imagem interativa que inclui pontos clicáveis (hotspots) para revelar informação, produtos ou links. Melhora a exploração do conteúdo e aumenta a interação direta com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Wallpaper de WeTransfer com imagem interativa que inclui pontos clicáveis (hotspots) para revelar informação, produtos ou links. Melhora a exploração do conteúdo e aumenta a interação direta com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
         </is>
       </c>
       <c r="K602" s="3" t="inlineStr">
@@ -26511,13 +26511,13 @@
       <c r="G603" s="2" t="n"/>
       <c r="H603" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I603" s="2" t="n"/>
       <c r="J603" s="2" t="inlineStr">
         <is>
-          <t>24h de WeTransfer em exclusividade para a marca — campanha de um dia de duração, com inventário destinado a publicidade exclusiva para o anunciante, por país. Composto por 3 wallpapers; a campanha tem de conter uma destas opções: 2 criatividades Static + 1 criatividade Click to Play, ou 3 criatividades Static. As imagens iniciais de cada formato têm de ser bem diferentes entre si — se forem parecidas, a WeTransfer pode pedir uma criatividade adicional para otimizar melhor a campanha. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>24h de WeTransfer em exclusividade para a marca — campanha de um dia de duração, com inventário destinado a publicidade exclusiva para o anunciante, por país. Composto por 3 wallpapers; a campanha tem de conter uma destas opções: 2 criatividades Static + 1 criatividade Click to Play, ou 3 criatividades Static. As imagens iniciais de cada formato têm de ser bem diferentes entre si — se forem parecidas, a WeTransfer pode pedir uma criatividade adicional para otimizar melhor a campanha. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
         </is>
       </c>
       <c r="K603" s="3" t="inlineStr">
@@ -26552,13 +26552,13 @@
       <c r="G604" s="2" t="n"/>
       <c r="H604" s="2" t="inlineStr">
         <is>
-          <t>JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>PSD em camadas.</t>
         </is>
       </c>
       <c r="I604" s="2" t="n"/>
       <c r="J604" s="2" t="inlineStr">
         <is>
-          <t>Formato publicitário wallpaper da WeTransfer com ação personalizada e exclusiva, onde a marca pode dar largas à imaginação — disponibilidade a confirmar com a equipa comercial. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Formato publicitário wallpaper da WeTransfer com ação personalizada e exclusiva, onde a marca pode dar largas à imaginação — disponibilidade a confirmar com a equipa comercial. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
         </is>
       </c>
       <c r="K604" s="3" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -19301,7 +19301,7 @@
       <c r="I439" s="2" t="n"/>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos. CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra"). Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos. CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
         </is>
       </c>
       <c r="K439" s="3" t="inlineStr">
@@ -19346,7 +19346,7 @@
       <c r="I440" s="2" t="n"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="K440" s="3" t="inlineStr">
@@ -19391,7 +19391,7 @@
       <c r="I441" s="2" t="n"/>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="K441" s="3" t="inlineStr">
@@ -19436,7 +19436,7 @@
       <c r="I442" s="2" t="n"/>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="K442" s="3" t="inlineStr">
@@ -19481,7 +19481,7 @@
       <c r="I443" s="2" t="n"/>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>Unidade criativa dinâmica in-article, pensada para visibilidade máxima durante o scroll em conteúdo mobile web. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Unidade criativa dinâmica in-article, pensada para visibilidade máxima durante o scroll em conteúdo mobile web. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="K443" s="3" t="inlineStr">
@@ -19526,7 +19526,7 @@
       <c r="I444" s="2" t="n"/>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>Unidade in-article, pensada para consideração e tráfego qualificado. Incluído só nalguns pacotes — confirmar na recomendação de media. CTA: máx. 2-3 palavras com verbo de ação. Template Photoshop disponível (Mobile + IAB, com safe areas). Para redimensionamento pela equipa de design da Ogury, enviar: ficheiro PSD por camadas em alta resolução, logos em vetorial (PSD/AI/EPS/SVG), copy da campanha, fontes e brand guidelines. Prazos: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criatividade. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto de pixel/click/viewability por conjunto de criatividades multi-formato).</t>
+          <t>Unidade in-article, pensada para consideração e tráfego qualificado. Incluído só nalguns pacotes — confirmar na recomendação de media. CTA: máx. 2-3 palavras com verbo de ação.</t>
         </is>
       </c>
       <c r="K444" s="3" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID). Duração máxima: 30 seg (recomendado 15 seg).</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -19575,7 +19575,7 @@
       <c r="I445" s="2" t="n"/>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: nome da marca/produto e texto de CTA (máx. 30 carateres; "Visit website" por defeito). Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: Top &amp; Bottom Skins (imagens estáticas JPG/PNG, 768x450px cada, sobrepostas ao vídeo, sem tracking próprio); Bottom Skin isolado (JPG/PNG, 768x930px, sem tracking próprio); End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB). Templates Photoshop disponíveis para as skins/end card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+          <t>Safe area: margem de 10% em cima/baixo (para overlays de UI). Som opcional — tem de ser compreensível sem áudio (autoplay mudo). Branding/mensagem clara nos primeiros 5 segundos. Tracking de terceiros (ex.: IAS, DoubleVerify) só embrulhado em VAST tags. CTA personalizável: máx. 30 carateres ("Visit website" por defeito). Opcional: skins e end card disponíveis — confirmar specs com a equipa Ogury.</t>
         </is>
       </c>
       <c r="K445" s="3" t="inlineStr">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID).</t>
+          <t>Máx.: 40 MB (MP4) ou 3 MB (VAST/VPAID). Duração máxima: 30 seg (recomendado 15 seg).</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -19624,7 +19624,7 @@
       <c r="I446" s="2" t="n"/>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>Formato: MP4, VAST tag ou VPAID (legacy apenas; VAST preferencial). Recomendado: compliance VAST 4.1 + OM SDK. Safe area: margem de segurança de 10% em cima/baixo (para overlays de UI). Som: deve ser compreensível sem áudio (autoplay mudo). Branding: logo/mensagem clara nos primeiros 5 segundos. Duração máxima: até 30s (recomendado 15s para melhor experiência mobile). Pixels de medição e trackers de terceiros (ex.: IAS, DoubleVerify) devem vir embrulhados em VAST tags. Personalização: heading ("Choose your ad" por defeito), nomes de produto/feature, cor de fundo (branco por defeito) — formato interativo tipo "video chooser". Funcionalidades opcionais, de valor acrescentado — confirmar disponibilidade com a equipa Ogury: End Card (imagem estática a seguir ao vídeo, JPG/PNG, 16:9 ou 9:16, recomendado 1024x576 ou 576x1024px, máx. 250 KB, com opção de end card multi-CTA, sem tracking próprio); Video Chooser Image (specs não detalhadas nos materiais enviados — confirmar com a equipa Ogury). Template Photoshop disponível para o End Card (com safe areas). Prazos de design: criação inicial mín. 2 dias úteis; revisões mín. 1-2 dias úteis; máx. 2 revisões por criativo.</t>
+          <t>Safe area: margem de 10% em cima/baixo (para overlays de UI). Som opcional — tem de ser compreensível sem áudio (autoplay mudo). Branding/mensagem clara nos primeiros 5 segundos. Tracking de terceiros (ex.: IAS, DoubleVerify) só embrulhado em VAST tags. Formato "video chooser": heading, nomes de produto/feature e cor de fundo personalizáveis. Opcional: end card disponível — confirmar specs com a equipa Ogury.</t>
         </is>
       </c>
       <c r="K446" s="3" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="J447" s="2" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo para mostrar vários produtos, features ou mensagens de marca numa experiência deslizável (swipe). Disponível para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos/variações); storytelling sequencial (mensagem revelada passo a passo); 3D Brand Spotlight (transição em cubo 3D); multi-CTA (vários CTAs rastreados individualmente, na mesma slide ou em slides diferentes, cada um com destino próprio); vídeo (no root da criatividade, visível durante o swipe, ou integrado numa slide específica). Boas práticas: limitar a ~5-6 slides; manter o CTA visível; mensagem concisa por slide; consistência visual entre slides. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Carrossel rich media interativo para mostrar vários produtos, features ou mensagens de marca numa experiência deslizável (swipe). Disponível para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K447" s="3" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo com navegação em camadas: o utilizador interage com elementos no ecrã de entrada para aceder a vistas de detalhe dedicadas. Para campanhas CPE e CPM. Casos de uso: product showcase (vários produtos, cada um com vista de detalhe); variações e opções (cores, estilos, configurações); product deep dive (um produto, várias camadas de informação); com vídeo (no ecrã de entrada ou dentro de uma vista de detalhe); com carrossel (carrossel dentro da vista de detalhe, para ângulos/features/variações adicionais). Boas práticas: limitar o nº de elementos interativos no ecrã de entrada; elementos clicáveis claramente identificáveis; botão de voltar sempre visível quando necessário; mensagem concisa por ecrã. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Carrossel rich media interativo com navegação em camadas: o utilizador interage com elementos no ecrã de entrada para aceder a vistas de detalhe dedicadas. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K448" s="3" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="J449" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo que permite ao utilizador explorar produtos, variantes, features ou configurações diferentes dentro de uma única criatividade: ao tocar numa opção seletora, o visual principal e o conteúdo associado atualizam-se instantaneamente. Para campanhas CPE e CPM. Casos de uso: seleção de produto (navegar vários produtos, cada seleção atualiza o visual/conteúdo); personalização de variante (cores, estilos, sabores, acabamentos — ideal para automóvel, moda, beleza, alimentação, mobiliário, eletrónica de consumo). Boas práticas: limitar o nº de opções selecionáveis; destacar claramente a opção selecionada; cada seleção deve gerar uma mudança visual percetível; CTA sempre visível; consistência visual entre variantes; seletores suficientemente grandes para toque em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails de produto, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo que permite ao utilizador explorar produtos, variantes, features ou configurações diferentes dentro de uma única criatividade: ao tocar numa opção seletora, o visual principal e o conteúdo associado atualizam-se instantaneamente. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K449" s="3" t="inlineStr">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo em que o utilizador arrasta um ou mais elementos para áreas-alvo predefinidas para completar uma ação; ao concluir, revela conteúdo/novo ecrã. Para campanhas CPE e CPM. Casos de uso: product reveal (arrastar elemento(s) para revelar produto/oferta/mensagem); demonstração de uso do produto; receitas/ingredientes (arrastar ingredientes para uma tigela/prato/copo); desafio gamificado (ex.: marcar golo, colocar um item, fazer correspondências) antes de desbloquear o passo seguinte. Boas práticas: interação intuitiva, elementos arrastáveis e zonas de largada claramente identificáveis; pistas visuais/animações/copy instrucional; elementos fáceis de manipular em mobile; limitar o nº de ações necessárias; recompensar interações bem-sucedidas; progressão clara (nº de ações em falta). Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo em que o utilizador arrasta um ou mais elementos para áreas-alvo predefinidas para completar uma ação; ao concluir, revela conteúdo/novo ecrã. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K450" s="3" t="inlineStr">
@@ -19849,7 +19849,7 @@
       </c>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo com hotspots clicáveis sobre elementos-chave de um visual; ao tocar, revela conteúdo adicional (informação de produto, features, preço, imagem, vídeo ou CTA). Para campanhas CPE e CPM. Casos de uso: informação de produto (hotspots numa imagem, cada um revela info/preço/CTA); product deep dive (hotspots ligados a componentes/funcionalidades específicas). Boas práticas: limitar o nº de hotspots por ecrã; posicionar em áreas relevantes do visual; garantir visibilidade clara (contraste/espaçamento); conteúdo de cada hotspot conciso; evitar sobreposição de áreas; consistência visual entre o conteúdo dos hotspots; áreas de toque suficientemente grandes em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo com hotspots clicáveis sobre elementos-chave de um visual; ao tocar, revela conteúdo adicional (informação de produto, features, preço, imagem, vídeo ou CTA). Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K451" s="3" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo que permite comparar dois visuais arrastando um slider pelo ecrã — revela progressivamente uma imagem enquanto esconde a outra, criando uma experiência "antes e depois". Para campanhas CPE e CPM. Casos de uso: antes e depois (transformação visual: skincare, tratamentos de beleza, fitness, remodelações); personalização de produto (cores, estilos, sabores, acabamentos, variações); impacto de produto/serviço (ex.: produtos de limpeza, tintas, jardinagem, restauro); comparação de features (ex.: standard vs. premium, modelo antigo vs. novo); melhoria de performance (ex.: desporto, nutrição, saúde e bem-estar). Boas práticas: visuais altamente contrastados; imagens perfeitamente alinhadas; pista de interação clara (setas, labels, animação subtil); foco numa única mensagem-chave; branding e CTA sempre visíveis; otimizar para leitura em mobile. Assets visuais adicionais: uma imagem por opção selecionável; thumbnails, ícones, amostras de cor ou seletores. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo que permite comparar dois visuais arrastando um slider pelo ecrã — revela progressivamente uma imagem enquanto esconde a outra, criando uma experiência "antes e depois". Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K452" s="3" t="inlineStr">
@@ -19935,7 +19935,7 @@
       <c r="I453" s="2" t="n"/>
       <c r="J453" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo em que o utilizador reconstrói uma imagem para desbloquear conteúdo adicional; ao completar o puzzle, mostra um ecrã de revelação final. Para campanhas CPE e CPM. Casos de uso: revelação de produto (produto, embalagem ou visual hero); desbloqueio de oferta (promoção, desconto, conteúdo exclusivo); engagement gamificado; storytelling de marca; teaser de evento/lançamento. Boas práticas: usar uma imagem visualmente apelativa e facilmente reconhecível; desafio simples e intuitivo (resolúvel em poucos segundos); revelação final com valor; branding consistente em todos os ecrãs; CTA apelativo; otimizar para interação em mobile. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo em que o utilizador reconstrói uma imagem para desbloquear conteúdo adicional; ao completar o puzzle, mostra um ecrã de revelação final. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K453" s="3" t="inlineStr">
@@ -19980,7 +19980,7 @@
       </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo com uma interação simples de toque que desbloqueia conteúdo adicional: começa com um visual teaser e revela uma segunda camada de conteúdo (imagem, vídeo, slideshow, animação ou mensagem promocional). Para campanhas CPE e CPM. Casos de uso: slideshow reveal; video reveal; offer reveal (promoção/oferta exclusiva/mensagem-chave); transformação criativa (mudança de universo visual, ex. campanhas sazonais/lançamentos); antes e depois (estado transformado — beleza, fitness, automóvel, melhoria de casa). Boas práticas: tornar a interação óbvia; forte contraste entre teaser e conteúdo revelado; primeiro ecrã simples e focado; usar a revelação para a mensagem-chave; transições suaves; otimizar para mobile; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Formato interativo com uma interação simples de toque que desbloqueia conteúdo adicional: começa com um visual teaser e revela uma segunda camada de conteúdo (imagem, vídeo, slideshow, animação ou mensagem promocional). Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K454" s="3" t="inlineStr">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>Combina uma criatividade de marca com um localizador de lojas integrado: o utilizador interage com um visual promocional e depois toca num CTA para aceder a um mapa interativo dentro do próprio anúncio, mostrando lojas, pontos de venda, postos de carregamento, concessionários ou outras localizações físicas próximas. Casos de uso: localizador de loja; localizações de evento; rede de agências/balcões/serviço; rede de postos de carregamento EV. Boas práticas: CTA forte orientado a localização (ex.: "Find a Store"); introdução concisa antes de passar ao mapa; informação de localização completa. Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Combina uma criatividade de marca com um localizador de lojas integrado: o utilizador interage com um visual promocional e depois toca num CTA para aceder a um mapa interativo dentro do próprio anúncio, mostrando lojas, pontos de venda, postos de carregamento, concessionários ou outras localizações físicas próximas. Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento.</t>
         </is>
       </c>
       <c r="K455" s="3" t="inlineStr">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="J456" s="2" t="inlineStr">
         <is>
-          <t>Experiência imersiva multi-página que permite navegação vertical por conteúdo de marca através de swipe (cima/baixo), replicando a navegação num site/landing page, com produtos, features, storytelling ou conteúdo promocional distribuídos por várias páginas dentro do mesmo anúncio. Casos de uso: product showcase (features/benefícios/configurações em páginas dedicadas); storytelling (jornada narrativa sequencial); promoção de evento/campanha (vários aspetos de um lançamento/evento em páginas diferentes); com carrossel (carrossel integrado para visibilidade adicional de produto). Boas práticas: limitar a 4-5 páginas no máximo; hierarquia visual clara (uma mensagem-chave por página); incentivar o scroll (setas/indicadores direcionais); consistência visual; fluxo narrativo lógico; terminar com um CTA forte. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Experiência imersiva multi-página que permite navegação vertical por conteúdo de marca através de swipe (cima/baixo), replicando a navegação num site/landing page, com produtos, features, storytelling ou conteúdo promocional distribuídos por várias páginas dentro do mesmo anúncio.</t>
         </is>
       </c>
       <c r="K456" s="3" t="inlineStr">
@@ -20119,7 +20119,7 @@
       </c>
       <c r="J457" s="2" t="inlineStr">
         <is>
-          <t>Mostra o produto a partir de todos os ângulos. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+          <t>Mostra o produto a partir de todos os ângulos. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="K457" s="3" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo com navegação em camadas (entrada + vista de detalhe), orientado a pergunta/resposta. Para campanhas CPE e CPM. Casos de uso: sondagem de preferência (escolha entre duas opções/preferências/opiniões/produtos, cada resposta rastreada individualmente, podendo revelar conteúdo dedicado); awareness &amp; educação (pergunta verdadeiro/falso, revela a resposta certa + conteúdo educativo — ideal para awareness, saúde, informação pública, sustentabilidade, educação financeira/de marca); recomendação de produto (guia o utilizador para o produto/solução mais relevante consoante a resposta). Boas práticas: perguntas curtas e fáceis de perceber; opções de resposta claras e distintas; labels de resposta curtos; ambas as opções igualmente visíveis; resultado relevante para a escolha do utilizador; foco numa única pergunta; consistência visual entre ecrãs. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Carrossel rich media interativo com navegação em camadas (entrada + vista de detalhe), orientado a pergunta/resposta. Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K458" s="3" t="inlineStr">
@@ -20213,7 +20213,7 @@
       </c>
       <c r="J459" s="2" t="inlineStr">
         <is>
-          <t>Reaproveita os assets da marca para emular a experiência social (Facebook, Instagram, TikTok, Twitter, LinkedIn, Pinterest ou Snapchat — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury.</t>
+          <t>Reaproveita os assets da marca para emular a experiência social (Facebook, Instagram, TikTok, Twitter, LinkedIn, Pinterest ou Snapchat — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="K459" s="3" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>Reaproveita os assets da marca para emular a experiência de carrossel social (Facebook ou Instagram — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service). Template Photoshop disponível, com safe areas e danger zones oficiais. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2-3 dias úteis consoante a complexidade; máx. 2 revisões por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking. Formatos próprios Ogury e IAB disponíveis para este template: confirmar com a equipa Ogury. Faturação baseada em medição 1P.</t>
+          <t>Reaproveita os assets da marca para emular a experiência de carrossel social (Facebook ou Instagram — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="K460" s="3" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>Anima o storytelling: liga narrativa com transições suaves e mensagens sequenciais, ideal para destacar várias features de produto ou mensagens-chave numa única criatividade. Casos de uso: visual animado único (estático melhorado com movimento subtil); storytelling sequencial (multi-ecrã); multi-CTA (vários CTAs rastreados individualmente, na mesma tela ou em telas diferentes, cada um com destino próprio); Slideshow com vídeo (vídeo visível durante toda a experiência); Slideshow para vídeo (sequência de slideshow seguida de um ecrã de vídeo dedicado); Slideshow com animação Lottie (elementos animados leves — neve, partículas, efeitos de fundo — sem aumentar o peso do ficheiro); Slideshow com disclaimer legal scrollável (texto legal extenso numa área com scroll automático/manual). Boas práticas: limitar a ~5-6 capítulos; manter o CTA visível; mensagem concisa por ecrã; consistência visual entre capítulos. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Anima o storytelling: liga narrativa com transições suaves e mensagens sequenciais, ideal para destacar várias features de produto ou mensagens-chave numa única criatividade.</t>
         </is>
       </c>
       <c r="K461" s="3" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>Efeito de expansão rápido e chamativo, que dá impacto visual instantâneo e atrai naturalmente a atenção para elementos-chave, mantendo a experiência fluida e não intrusiva. Casos de uso: destaque de produto (efeito pop subtil); ênfase de CTA; revelação de oferta (promoções/descontos/mensagens-chave); reforço do visual principal. Boas práticas: aplicar o efeito pop a produtos, logos ou CTAs para maximizar o impacto; layout limpo (sem sobrecarregar); uma mensagem de cada vez; contraste visual forte; alinhado com a marca; a animação deve reforçar a mensagem, não distrair. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Efeito de expansão rápido e chamativo, que dá impacto visual instantâneo e atrai naturalmente a atenção para elementos-chave, mantendo a experiência fluida e não intrusiva.</t>
         </is>
       </c>
       <c r="K462" s="3" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="J463" s="2" t="inlineStr">
         <is>
-          <t>Efeito de revelação horizontal: um segundo visual desliza suavemente sobre o primeiro, criando uma transição clara e envolvente — ideal para mostrar contrastes, detalhes de produto ou mensagens-chave de forma dinâmica mas controlada. Casos de uso: revelação de cor (preto e branco para cor); revelação de detalhe de produto (vista global para vista de pormenor); comparação visual. Boas práticas: usar dois visuais complementares; layout limpo; foco numa única ideia; contraste forte; visuais alinhados entre si (estilo/composição); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Efeito de revelação horizontal: um segundo visual desliza suavemente sobre o primeiro, criando uma transição clara e envolvente — ideal para mostrar contrastes, detalhes de produto ou mensagens-chave de forma dinâmica mas controlada.</t>
         </is>
       </c>
       <c r="K463" s="3" t="inlineStr">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>Transição vertical suave entre dois visuais, trazendo o conteúdo para o ecrã de forma natural e guiando a atenção do utilizador — ideal para mostrar duas mensagens/visuais complementares, com uma experiência limpa e premium. Casos de uso: antes/depois; foco de produto (dois ângulos/features complementares); transição de mensagem; marca e produto; tease &amp; reveal; destaque duplo (dois elementos com igual visibilidade). Boas práticas: dois visuais complementares; mensagem simples (uma ideia); continuidade visual (cor/estilo/composição); guiar o olhar do utilizador de um visual para o outro; ambos os visuais com valor standalone forte; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Transição vertical suave entre dois visuais, trazendo o conteúdo para o ecrã de forma natural e guiando a atenção do utilizador — ideal para mostrar duas mensagens/visuais complementares, com uma experiência limpa e premium.</t>
         </is>
       </c>
       <c r="K464" s="3" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>Combina uma transição vertical com um efeito de revelação limpo, introduzindo visuais ou mensagens com clareza e impacto, numa experiência fluida e fácil de seguir. Casos de uso: introdução visual; destaque de produto (revelação suave); revelação de mensagem (estruturada, fácil de ler); marca e mensagem; foco em elemento-chave. Boas práticas: visuais simples e claros; foco numa única mensagem; visuais consistentes entre si; guiar a atenção naturalmente; a revelação deve acrescentar valor real; alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Combina uma transição vertical com um efeito de revelação limpo, introduzindo visuais ou mensagens com clareza e impacto, numa experiência fluida e fácil de seguir.</t>
         </is>
       </c>
       <c r="K465" s="3" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>Efeito de revelação a partir do centro: os visuais dividem-se e desdobram-se para introduzir novo conteúdo, criando uma transição dinâmica que mantém o utilizador envolvido — ideal para revelar progressivamente vários visuais de forma fluida e estruturada. Casos de uso: storytelling sequencial; showcase de produto (produtos/variações diferentes); destaque de coleção (ex. moda, beleza, automóvel); breakdown de features; revelação de campanha (mensagens-chave progressivas); progressão visual (evolução de um visual para outro). Boas práticas: limitar a 5 ecrãs no máximo; estilo consistente entre todos os visuais; foco numa ideia principal; visuais fortes (impacto imediato em cada ecrã); layout limpo (sem clutter); alinhado com a marca. Ficheiros fonte aceites: PSD (em camadas), AI, INDD, Figma (ficheiro partilhado ou exportação) ou XD — editável, com todas as camadas, assets e elementos linkados. Assets visuais: PSD em camadas, imagens de qualidade (JPG/TIFF/PNG), resolução recomendada 300dpi, sem tamanho/aspect ratio fixo (garantir resolução suficiente para adaptação entre formatos sem pixelização); evitar texto "queimado" na imagem sempre que possível. Logo em alta resolução (preferencial SVG/AI/EPS; aceite PSD ou PNG com fundo transparente), com versão para fundos claros e escuros se aplicável. Fontes: OTF ou TTF, com todos os pesos/estilos usados, totalmente editáveis. Brand guidelines: regras de uso do logo e clear space, paleta de cores (HEX/RGB), hierarquia tipográfica, do's &amp; don'ts de layout/imagem, restrições legais/branding obrigatórias. Template Photoshop disponível, com safe areas e danger zones oficiais dos formatos próprios Ogury — elementos críticos em danger zone podem ser cortados/escondidos por interfaces de dispositivo, overlays ou UI do placement. Prazos: criação inicial mín. 3 dias úteis; revisões mín. 2 dias úteis por ronda; máx. 2 rondas de revisão por criativo. Suporta 1x1 impression pixel, click trackers e viewability tracking (recomendado um conjunto por criativo multi-formato).</t>
+          <t>Efeito de revelação a partir do centro: os visuais dividem-se e desdobram-se para introduzir novo conteúdo, criando uma transição dinâmica que mantém o utilizador envolvido — ideal para revelar progressivamente vários visuais de forma fluida e estruturada.</t>
         </is>
       </c>
       <c r="K466" s="3" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -8279,7 +8279,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Hero: pode diferir dos secundários; Secundários: mín. 3 recomendado, máx. 24, todos com o mesmo rácio entre si; Hero em vídeo: duração mín. 4s, máx. 15min.</t>
+          <t>Hero: pode diferir dos secundários; Secundários: mín. 3 recomendado, máx. 24, todos com o mesmo rácio entre si.</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 10 MB; Vídeo: até 2 GB</t>
+          <t>Imagem: 10 MB; Vídeo: até 2 GB. Hero em vídeo: duração mín. 4s, máx. 15min.</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500. Pins com rácio superior ao recomendado podem ficar cortados no feed.</t>
+          <t>Recomendado 1000x1500.</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -8351,7 +8351,11 @@
           <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
         </is>
       </c>
-      <c r="J185" s="2" t="n"/>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>Pins com rácio superior ao recomendado podem ficar cortados no feed.</t>
+        </is>
+      </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
@@ -8377,7 +8381,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Duração: mín. 4s, máx. 15min (recomendado 6-15s para ads).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -8387,7 +8391,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Até 2 GB</t>
+          <t>Até 2 GB. Duração: mín. 4s, máx. 15min (recomendado 6-15s para ads).</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9272,12 +9276,12 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>2 a 6 slides (imagens ou vídeos). Image Carousels: 800x800 recomendado; Video Carousels: 800x450 recomendado. Rácio único em todos os slides do carrossel; conteúdo misto tem de manter o mesmo rácio entre asset de imagem e de vídeo.</t>
+          <t>Image Carousels: 800x800 recomendado; Video Carousels: 800x450 recomendado.</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>1:1, 1.91:1, 4:5, 2:3, 16:9 ou 9:16 (rácio único por carrossel)</t>
+          <t>1:1, 1.91:1, 4:5, 2:3, 16:9 ou 9:16.</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -9295,7 +9299,11 @@
           <t>1 destino (Carousel de destino único) ou até 6 destinos únicos (Carousel multi-destino).</t>
         </is>
       </c>
-      <c r="J205" s="2" t="n"/>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>2 a 6 slides (imagens ou vídeos). Rácio único em todos os slides do carrossel; conteúdo misto tem de manter o mesmo rácio entre asset de imagem e de vídeo.</t>
+        </is>
+      </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
@@ -9415,7 +9423,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1920x1080 recomendado. Duração recomendada ≤15s (até 2:20 suportado; alguns anunciantes elegíveis para até 10min, recomendado não ultrapassar 9:55). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (até 60 FPS aceite, não fazer upsample). Thumbnail: rácio igual ao do vídeo, máx. 5 MB. Loop automático se duração &lt;60s. Branding (logo) recomendado persistente no canto superior esquerdo; legendas/closed captions fortemente recomendadas.</t>
+          <t>1200x1200 ou 1920x1080 recomendado.</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -9425,12 +9433,12 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 GB (recomendado manter abaixo de 30 MB para melhor desempenho)</t>
+          <t>Máx. 1 GB (recomendado manter abaixo de 30 MB para melhor desempenho). Duração recomendada ≤15s (até 2:20 suportado; alguns anunciantes elegíveis para até 10min, recomendado não ultrapassar 9:55). Thumbnail: rácio igual ao do vídeo, máx. 5 MB.</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC; thumbnail PNG ou JPEG</t>
+          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC; frame rate 29,97 ou 30 FPS (até 60 FPS aceite, não fazer upsample); thumbnail PNG ou JPEG.</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
@@ -9438,7 +9446,11 @@
           <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
-      <c r="J208" s="2" t="n"/>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>Loop automático se duração &lt;60s. Branding (logo) recomendado persistente no canto superior esquerdo; legendas/closed captions fortemente recomendadas.</t>
+        </is>
+      </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
@@ -9763,7 +9775,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080.</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -9773,7 +9785,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads). Saltável a partir dos 5s; sem duração máxima fixa.</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -9808,7 +9820,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>Recomendado 1920x1080.</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -9818,7 +9830,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração: 7 a 15 segundos; não saltável.</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -9853,7 +9865,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>Recomendado 1920x1080, mín. 640x360.</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
@@ -9863,7 +9875,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração: até 6 segundos; não saltável.</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -9898,7 +9910,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>16 a 30 segundos; formato específico para Connected TV</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
@@ -9908,7 +9920,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração: 16 a 30 segundos.</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -9917,7 +9929,11 @@
         </is>
       </c>
       <c r="I219" s="2" t="n"/>
-      <c r="J219" s="2" t="n"/>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>Formato específico para Connected TV.</t>
+        </is>
+      </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
@@ -9943,7 +9959,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080.</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -9953,7 +9969,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração recomendada: 15 segundos.</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -9992,7 +10008,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
+          <t>Vertical: 1080x1920.</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
@@ -10002,7 +10018,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração: 6 a 60 segundos.</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -10037,7 +10053,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Recomendado 1920x1080 ou superior.</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -10047,7 +10063,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Autoplay sem som até 30s, depois mostra miniatura clicável.</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -10221,18 +10237,18 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Duração máxima: 30''.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>1 MB, duração máxima 30''.</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>MP3; alternativa aceite: WAV 16-bit 44.1kHz. Áudio normalizado a -14 dB LUFS integrado; MP3 ≥192kbps; picos abaixo de -1 dB TP para evitar distorção na transcodificação.</t>
+          <t>MP3; alternativa aceite: WAV 16-bit 44.1kHz.</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
@@ -10240,7 +10256,11 @@
           <t>Nome do anunciante: máx. 45c.</t>
         </is>
       </c>
-      <c r="J226" s="2" t="n"/>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>Áudio normalizado a -14 dB LUFS integrado; MP3 ≥192kbps; picos abaixo de -1 dB TP para evitar distorção na transcodificação.</t>
+        </is>
+      </c>
       <c r="K226" s="2" t="n"/>
     </row>
     <row r="227">
@@ -10273,13 +10293,13 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>ZIP com HTML5 e pastas de imagens/scripts, ou JPEG/GIF; enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>ZIP com HTML5 e pastas de imagens/scripts, ou JPEG/GIF.</t>
         </is>
       </c>
       <c r="I227" s="2" t="n"/>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK).</t>
+          <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK). Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
@@ -10307,7 +10327,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Recomendado 1920x1080 ou superior.</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -10317,7 +10337,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Autoplay sem som até 30s, depois mostra miniatura clicável.</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -10352,7 +10372,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080.</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
@@ -10362,7 +10382,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads). Saltável a partir dos 5s; sem duração máxima fixa.</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -10397,7 +10417,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080.</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
@@ -10407,7 +10427,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads). Saltável a partir dos 5s; sem duração máxima fixa.</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -10442,7 +10462,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; NON-SKIPPABLE STANDARD — recomendado 1920x1080; NON-SKIPPABLE 30S — mesma especificação técnica do standard.</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -10452,7 +10472,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads). Duração — Bumper: até 6 segundos; Non-Skippable Standard: 7 a 15 segundos; Non-Skippable 30s: 30 segundos. Nenhuma das variantes é saltável.</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -10487,7 +10507,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080.</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -10497,7 +10517,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads). Saltável a partir dos 5s; sem duração máxima fixa.</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -10532,7 +10552,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080.</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -10542,7 +10562,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads). Duração — Horizontal: 15s (in-stream skippable/in-feed) ou 6s (bumper); Vertical (Shorts): 6 a 60 segundos; Square: 6 a 60 segundos.</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -10577,7 +10597,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+          <t>Horizontal: 1920x1080 (usa também non-skippable in-stream, in-feed e Shorts, specs conforme cada formato individual).</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -10587,7 +10607,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads). Duração — Horizontal: 15s (in-stream skippable/in-feed) ou 6s (bumper).</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -10982,7 +11002,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080.</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -10992,7 +11012,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração mínima: 10 segundos.</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -11513,7 +11533,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
+          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -11523,7 +11543,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
+          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB. Duração de vídeo: máx. 5min.</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -11572,12 +11592,12 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Até 32 MB</t>
+          <t>Até 32 MB. Vídeo: duração 3 a 60s.</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V.</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
@@ -11621,12 +11641,12 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Até 32 MB</t>
+          <t>Até 32 MB. Vídeo: duração 3 a 60s.</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V.</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
@@ -11754,7 +11774,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>Recomendado até 1080x1920, mín. 720x1280. Duração recomendada &lt;15s (até 2:20 suportado). Frame rate máx. 60 fps. Bitrate máx. 25 Mbps (alvo 5-10 Mbps).</t>
+          <t>Recomendado até 1080x1920, mín. 720x1280.</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
@@ -11762,10 +11782,14 @@
           <t>9:16 (recomendado); também aceites 4:5, 2:3, 1:1, 1.91:1 ou 16:9</t>
         </is>
       </c>
-      <c r="G259" s="2" t="n"/>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Duração recomendada &lt;15s (até 2:20 suportado).</t>
+        </is>
+      </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+          <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC; frame rate máx. 60 fps; bitrate máx. 25 Mbps (alvo 5-10 Mbps).</t>
         </is>
       </c>
       <c r="I259" s="2" t="n"/>
@@ -11795,22 +11819,22 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1200x1200 (mín. 600x600 para 1:1); se não for 1:1, mín. 640x360. Duração recomendada ≤15s (máx. 2:20). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (superior aceite, não fazer upsample).</t>
+          <t>Recomendado 1200x1200 (mín. 600x600 para 1:1); se não for 1:1, mín. 640x360.</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>1:1 (recomendado — ocupa sempre espaço quadrado em desktop/mobile/timeline/perfil) ou 9:16 (vertical, ocupa o mesmo espaço); o anúncio é automaticamente combinado com conteúdo de rácio semelhante do publisher</t>
+          <t>1:1 (recomendado) ou 9:16 (vertical).</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 GB</t>
+          <t>Máx. 1 GB. Duração recomendada ≤15s (máx. 2:20).</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC; bitrate 1080p 6.000-10.000k (recomendado 6.000k), 720p 5.000-8.000k (recomendado 5.000k); frame rate 29,97 ou 30 FPS (superior aceite, não fazer upsample).</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
@@ -11820,7 +11844,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>Branding e legendas/closed captions fortemente recomendados.</t>
+          <t>Branding e legendas/closed captions fortemente recomendados. 1:1 ocupa sempre espaço quadrado em desktop/mobile/timeline/perfil; 9:16 ocupa o mesmo espaço. O anúncio é automaticamente combinado com conteúdo de rácio semelhante do publisher.</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
@@ -11848,7 +11872,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Resolução: 1280x720 recomendado, 1920x1080 máximo. Frame rate: 30 fps recomendado, 60 fps máximo. Keyframe interval: OBS a cada 3s; Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180).</t>
+          <t>Resolução: 1280x720 recomendado, 1920x1080 máximo.</t>
         </is>
       </c>
       <c r="F261" s="2" t="n"/>
@@ -11859,7 +11883,7 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>Protocolo RTMP; codec de vídeo H.264/AVC; codec de áudio AAC-LC. Encoders suportados: OBS, Wirecast, Restream, Golightstream, Socialive, Teradek, Elemental, Vmix, StreamYard, Streamlabs.</t>
+          <t>Protocolo RTMP; codec de vídeo H.264/AVC; codec de áudio AAC-LC; frame rate 30 fps recomendado, 60 fps máximo; keyframe interval OBS a cada 3s, Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180). Encoders suportados: OBS, Wirecast, Restream, Golightstream, Socialive, Teradek, Elemental, Vmix, StreamYard, Streamlabs.</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
@@ -11930,7 +11954,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Recomendado 1280x720. Companion Promoted Ads: 3 a 6 anúncios obrigatórios (imagem, vídeo, GIF, etc.) para apoiar o trend.</t>
+          <t>Recomendado 1280x720.</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -11953,7 +11977,11 @@
           <t>Nome do trend (obrigatório): máx. 20c; Descrição do trend (opcional, muito recomendado): máx. 30c — evitar frases tipo clickbait ('50% off', 'compre um leve dois').</t>
         </is>
       </c>
-      <c r="J263" s="2" t="n"/>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>Companion Promoted Ads: 3 a 6 anúncios obrigatórios (imagem, vídeo, GIF, etc.) para apoiar o trend.</t>
+        </is>
+      </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
@@ -11979,20 +12007,20 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F264" s="2" t="n"/>
       <c r="G264" s="2" t="n"/>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I264" s="2" t="n"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
+          <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow. Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads. Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next).</t>
         </is>
       </c>
       <c r="K264" s="3" t="inlineStr">
@@ -12020,18 +12048,22 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F265" s="2" t="n"/>
       <c r="G265" s="2" t="n"/>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I265" s="2" t="n"/>
-      <c r="J265" s="2" t="n"/>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada). Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters).</t>
+        </is>
+      </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
@@ -12060,7 +12092,7 @@
       <c r="G266" s="2" t="n"/>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
@@ -12068,7 +12100,11 @@
           <t>Conversation Card (post original): texto até 280c, hashtag até 21c (incl. o caracter #). Post pré-preenchido (após clique no CTA): texto até 256c, título até 23c. Thank You post: texto até 23c, URL opcional até 23c.</t>
         </is>
       </c>
-      <c r="J266" s="2" t="n"/>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media).</t>
+        </is>
+      </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#conversation</t>
@@ -12094,11 +12130,15 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção). Pode ter ou não media associada (imagem ou vídeo).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F267" s="2" t="n"/>
-      <c r="G267" s="2" t="n"/>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção).</t>
+        </is>
+      </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
           <t>Feature adicionada a um post, com ou sem media</t>
@@ -12109,7 +12149,11 @@
           <t>Texto do post: até 280c; 2 a 4 opções de resposta, até 25c cada (não conta para os 280c do post).</t>
         </is>
       </c>
-      <c r="J267" s="2" t="n"/>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>Pode ter ou não media associada (imagem ou vídeo).</t>
+        </is>
+      </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
@@ -12176,7 +12220,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
@@ -12186,7 +12230,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>10 MB. Secundagem recomendada: 15''. Secundagem máxima: 30''.</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -12195,7 +12239,11 @@
         </is>
       </c>
       <c r="I269" s="2" t="n"/>
-      <c r="J269" s="2" t="n"/>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>Vídeos com mais de 30'' têm skip ad.</t>
+        </is>
+      </c>
       <c r="K269" s="2" t="n"/>
     </row>
     <row r="270">
@@ -12217,7 +12265,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -12227,7 +12275,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>10 MB. Secundagem recomendada: 15''. Secundagem máxima: 30''.</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -12236,7 +12284,11 @@
         </is>
       </c>
       <c r="I270" s="2" t="n"/>
-      <c r="J270" s="2" t="n"/>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>Vídeos com mais de 30'' têm skip ad.</t>
+        </is>
+      </c>
       <c r="K270" s="2" t="n"/>
     </row>
     <row r="271">
@@ -12303,7 +12355,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO: altura mín 486px, largura mín 864px.</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -12313,12 +12365,12 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+          <t>Display: máx 1 MB (todas as fases). Vídeo: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem). Duração do vídeo — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>Display: imagens. Video: MP4.</t>
+          <t>Display: imagens. Vídeo: MP4.</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -12348,7 +12400,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>Aplica-se só a anúncios de vídeo — o utilizador recebe uma recompensa (ex.: moeda in-app, power-up) depois de ver o anúncio.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F273" s="2" t="n"/>
@@ -12359,11 +12411,15 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
+          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV.</t>
         </is>
       </c>
       <c r="I273" s="2" t="n"/>
-      <c r="J273" s="2" t="n"/>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>Áudio: loudness recomendado -24 LKFS ±2 LKFS.</t>
+        </is>
+      </c>
       <c r="K273" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/displayvideo/answer/9166157?hl=en</t>
@@ -12389,12 +12445,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Dimensões: mín. 256px no lado maior e no lado menor, exceto 300x250 e 320x180 (exceções aceites). Colocação: só no corpo principal da página (não em sidebar, cabeçalho ou rodapé).</t>
+          <t>Mín. 256px no lado maior e no lado menor, exceto 300x250 e 320x180 (exceções aceites).</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>4:3 ou 16:9 (horizontal); 3:4 ou 9:16 (vertical) — fora destes rácios o anúncio não serve</t>
+          <t>4:3 ou 16:9 (horizontal); 3:4 ou 9:16 (vertical).</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -12404,11 +12460,15 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; só tags VAST (VPAID não suportado); áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
+          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; só tags VAST (VPAID não suportado).</t>
         </is>
       </c>
       <c r="I274" s="2" t="n"/>
-      <c r="J274" s="2" t="n"/>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>Colocação: só no corpo principal da página (não em sidebar, cabeçalho ou rodapé). Fora dos rácios indicados, o anúncio não serve. Áudio: loudness recomendado -24 LKFS ±2 LKFS.</t>
+        </is>
+      </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/displayvideo/answer/3129957?hl=en</t>
@@ -12463,7 +12523,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 800x600px. Vídeo (opcional): duração máx. 15s; deixar espaço no centro da imagem para o vídeo.</t>
+          <t>Imagem: 800x600px.</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -12473,7 +12533,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -12482,7 +12542,11 @@
         </is>
       </c>
       <c r="I276" s="2" t="n"/>
-      <c r="J276" s="2" t="n"/>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>Deixar espaço no centro da imagem para o vídeo (opcional).</t>
+        </is>
+      </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/window-splash-video/</t>
@@ -12508,7 +12572,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. 15s.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
@@ -12518,7 +12582,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -12553,7 +12617,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 1024x600px (ou 800x600px) + 480x640px; para campanhas programáticas: 800x600px + 320x480px; em HTML5, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
+          <t>Imagem: 1024x600px (ou 800x600px) + 480x640px; para campanhas programáticas: 800x600px + 320x480px; em HTML5, dimensões mobile 320x480px e 480x320px.</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -12563,7 +12627,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -12572,7 +12636,11 @@
         </is>
       </c>
       <c r="I278" s="2" t="n"/>
-      <c r="J278" s="2" t="n"/>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo (opcional): deixar espaço na imagem para o vídeo.</t>
+        </is>
+      </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/splash-intro/</t>
@@ -12598,7 +12666,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>Imagem: Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px. Vídeo: duração máx. 15s (medidas recomendadas 1024x600 e 480x640).</t>
+          <t>Imagem: Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px. Vídeo: medidas recomendadas 1024x600 e 480x640.</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
@@ -12608,7 +12676,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -12643,7 +12711,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Imagem: Splash/Intro 1024x600px + 480x640px + 640x480px; Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px; em HTML5 para a Intro, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
+          <t>Imagem: Splash/Intro 1024x600px + 480x640px + 640x480px; Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px; em HTML5 para a Intro, dimensões mobile 320x480px e 480x320px.</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -12653,7 +12721,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -12662,7 +12730,11 @@
         </is>
       </c>
       <c r="I280" s="2" t="n"/>
-      <c r="J280" s="2" t="n"/>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo (opcional): deixar espaço na imagem para o vídeo.</t>
+        </is>
+      </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/FullScreen-TakeOver/</t>
@@ -12688,7 +12760,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>1260x200px + 728x150px + 320x100px, e também 300x600px ou 300x250px. Pode incluir vídeo (contactar para mais info).</t>
+          <t>1260x200px + 728x150px + 320x100px, e também 300x600px ou 300x250px.</t>
         </is>
       </c>
       <c r="F281" s="2" t="n"/>
@@ -12703,7 +12775,11 @@
         </is>
       </c>
       <c r="I281" s="2" t="n"/>
-      <c r="J281" s="2" t="n"/>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>Pode incluir vídeo — contactar a Notícias Ilimitadas para mais informação.</t>
+        </is>
+      </c>
       <c r="K281" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/takeover/</t>
@@ -12729,7 +12805,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px.</t>
         </is>
       </c>
       <c r="F282" s="2" t="n"/>
@@ -12744,7 +12820,11 @@
         </is>
       </c>
       <c r="I282" s="2" t="n"/>
-      <c r="J282" s="2" t="n"/>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+        </is>
+      </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin/</t>
@@ -12770,7 +12850,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px (deixar espaço na imagem de topo para o vídeo). Laterais não devem conter informação relevante. Vídeo: duração máx. 30s.</t>
+          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px.</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
@@ -12780,7 +12860,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB, duração máx. 30s.</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -12789,7 +12869,11 @@
         </is>
       </c>
       <c r="I283" s="2" t="n"/>
-      <c r="J283" s="2" t="n"/>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>Deixar espaço na imagem de topo para o vídeo. Laterais não devem conter informação relevante.</t>
+        </is>
+      </c>
       <c r="K283" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-video/</t>
@@ -12815,7 +12899,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>2 imagens laterais 310x1080px + 1 imagem de fundo 1300x250px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+          <t>2 imagens laterais 310x1080px + 1 imagem de fundo 1300x250px.</t>
         </is>
       </c>
       <c r="F284" s="2" t="n"/>
@@ -12830,7 +12914,11 @@
         </is>
       </c>
       <c r="I284" s="2" t="n"/>
-      <c r="J284" s="2" t="n"/>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+        </is>
+      </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-invertida/</t>
@@ -12856,7 +12944,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2 imagens 320x100px + 1 imagem 300x600px (pode ter vídeo, deixar espaço na imagem 300x600 para o vídeo). Vídeo (opcional): duração máx. recomendada 15s.</t>
+          <t>2 imagens 320x100px + 1 imagem 300x600px.</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -12866,7 +12954,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB, duração máx. recomendada 15s.</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -12875,7 +12963,11 @@
         </is>
       </c>
       <c r="I285" s="2" t="n"/>
-      <c r="J285" s="2" t="n"/>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>Pode ter vídeo — deixar espaço na imagem 300x600 para o vídeo.</t>
+        </is>
+      </c>
       <c r="K285" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-mobile/</t>
@@ -12979,7 +13071,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2 imagens: 300x600px (versão colapsada) + 600x600px (versão expandida) — deixar espaço na imagem expandida para o vídeo. Vídeo (opcional): duração máx. 30s.</t>
+          <t>2 imagens: 300x600px (versão colapsada) + 600x600px (versão expandida).</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
@@ -12989,7 +13081,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 100 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 100 KB por imagem. Vídeo: máx. 2 MB, duração máx. 30s.</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -12998,7 +13090,11 @@
         </is>
       </c>
       <c r="I288" s="2" t="n"/>
-      <c r="J288" s="2" t="n"/>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>Deixar espaço na imagem expandida para o vídeo (opcional).</t>
+        </is>
+      </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/flipbook/</t>
@@ -13106,7 +13202,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>1260x300px + 728x300px + 320x200px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
+          <t>1260x300px + 728x300px + 320x200px.</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
@@ -13116,7 +13212,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -13125,7 +13221,11 @@
         </is>
       </c>
       <c r="I291" s="2" t="n"/>
-      <c r="J291" s="2" t="n"/>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>Deixar espaço para vídeo, se aplicável (opcional).</t>
+        </is>
+      </c>
       <c r="K291" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/ticker/</t>
@@ -13151,7 +13251,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 15s.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
@@ -13161,7 +13261,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 2 MB, duração máx. recomendada 15s.</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -13196,7 +13296,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>1024x600px (ou 800x600px) + 480x640px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
+          <t>1024x600px (ou 800x600px) + 480x640px.</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
@@ -13206,7 +13306,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -13215,7 +13315,11 @@
         </is>
       </c>
       <c r="I293" s="2" t="n"/>
-      <c r="J293" s="2" t="n"/>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>Deixar espaço para vídeo, se aplicável (opcional).</t>
+        </is>
+      </c>
       <c r="K293" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/flip-ad/</t>
@@ -13282,17 +13386,17 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>600x500px. Vídeo (opcional): 600x500px, ou usar o rácio 16:9; duração máx. 15s; deixar espaço na imagem para o vídeo se usados em conjunto.</t>
+          <t>600x500px. Vídeo (opcional): 600x500px (ou rácio 16:9).</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>16:9 (vídeo, alternativa às dimensões fixas)</t>
+          <t>16:9 (vídeo)</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB, duração máx. 15s.</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -13301,7 +13405,11 @@
         </is>
       </c>
       <c r="I295" s="2" t="n"/>
-      <c r="J295" s="2" t="n"/>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>Deixar espaço na imagem para o vídeo, se usados em conjunto.</t>
+        </is>
+      </c>
       <c r="K295" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/layer/</t>
@@ -13327,7 +13435,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>Área fechada: 200x200px; área aberta: 850x650px. Não colocar informação no canto superior direito de nenhuma das duas imagens (fica coberto pela aba). Vídeo (opcional): duração máx. 20s; deixar espaço na imagem aberta para o vídeo.</t>
+          <t>Área fechada: 200x200px; área aberta: 850x650px.</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -13337,7 +13445,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB, duração máx. 20s.</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -13346,7 +13454,11 @@
         </is>
       </c>
       <c r="I296" s="2" t="n"/>
-      <c r="J296" s="2" t="n"/>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>Não colocar informação no canto superior direito de nenhuma das duas imagens (fica coberto pela aba). Vídeo (opcional): deixar espaço na imagem aberta para o vídeo.</t>
+        </is>
+      </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/peel-off/</t>
@@ -13413,13 +13525,13 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F298" s="2" t="n"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB.</t>
+          <t>Máx. 100 MB, duração máx. recomendada 20s.</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -13428,7 +13540,11 @@
         </is>
       </c>
       <c r="I298" s="2" t="n"/>
-      <c r="J298" s="2" t="n"/>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>CPV contabilizado aos 20s em campanhas por visualizações.</t>
+        </is>
+      </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/audio-ad/</t>
@@ -13454,7 +13570,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
@@ -13464,7 +13580,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB.</t>
+          <t>Máx. 100 MB, duração máx. recomendada 20s.</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -13473,7 +13589,11 @@
         </is>
       </c>
       <c r="I299" s="2" t="n"/>
-      <c r="J299" s="2" t="n"/>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>CPV contabilizado aos 20s em campanhas por visualizações.</t>
+        </is>
+      </c>
       <c r="K299" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/pre-roll/</t>
@@ -13499,7 +13619,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -13509,7 +13629,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB.</t>
+          <t>Máx. 100 MB, duração máx. recomendada 20s.</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -13544,7 +13664,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Duração máx. recomendada 20s.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
@@ -13554,7 +13674,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB.</t>
+          <t>Máx. 100 MB, duração máx. recomendada 20s.</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -26815,13 +26935,13 @@
       <c r="G611" s="2" t="n"/>
       <c r="H611" s="2" t="inlineStr">
         <is>
-          <t>VAST 2.0 (tem de ser enviado pelo cliente). VPAID e MOAT Tracking não são aceites. Vídeo raw não é aceite no Marketplace. Não é possível usar VAST através da Celtra.</t>
+          <t>VAST 2.0.</t>
         </is>
       </c>
       <c r="I611" s="2" t="n"/>
       <c r="J611" s="2" t="inlineStr">
         <is>
-          <t>Medição: CTR e VTR. Ficha técnica: https://drive.google.com/file/d/1zJfF-_mATmPi8gTtEzQBYZxHhdnrKRUm/view</t>
+          <t>Medição: CTR e VTR. Ficha técnica: https://drive.google.com/file/d/1zJfF-_mATmPi8gTtEzQBYZxHhdnrKRUm/view VAST tem de ser enviado pelo cliente. VPAID e MOAT Tracking não são aceites. Vídeo raw não é aceite no Marketplace. Não é possível usar VAST através da Celtra.</t>
         </is>
       </c>
       <c r="K611" s="3" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -6075,7 +6075,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Full Page Ad: HTML5 responsive enviado em zip, juntamente com editáveis (caso sejam necessário ajustes de última hora). Para desenvolvimento, usar o template disponível abaixo. Tipo ficheiro: HTML5 responsive com recursos em WEBP, Leaderboard: 728x90px, Mobile banner: 320x90px</t>
+          <t>Leaderboard: 728x90px; Mobile banner: 320x90px.</t>
         </is>
       </c>
       <c r="F132" s="2" t="n"/>
@@ -6086,11 +6086,15 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>WEBP ou GIF</t>
+          <t>HTML5 responsive (zip, com recursos em WEBP) ou GIF.</t>
         </is>
       </c>
       <c r="I132" s="2" t="n"/>
-      <c r="J132" s="2" t="n"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Enviar também os ficheiros editáveis, caso sejam necessários ajustes de última hora. Usar o template disponível (ver link) para o desenvolvimento.</t>
+        </is>
+      </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus</t>
@@ -6116,7 +6120,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Full Page Ad: HTML5 responsive enviado em zip, juntamente com editáveis (caso sejam necessário ajustes de última hora). Para desenvolvimento, usar o template disponível abaixo. Tipo ficheiro: HTML5 responsive com recursos em WEBP, Leaderboard: 728x90px, Mobile banner: 320x90px</t>
+          <t>Leaderboard: 728x90px; Mobile banner: 320x90px.</t>
         </is>
       </c>
       <c r="F133" s="2" t="n"/>
@@ -6131,7 +6135,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n"/>
-      <c r="J133" s="2" t="n"/>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Enviar também os ficheiros editáveis, caso sejam necessários ajustes de última hora. Usar o template disponível (ver link) para o desenvolvimento.</t>
+        </is>
+      </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus_video</t>
@@ -7396,7 +7404,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Super Leaderboard: 1376x90px: dependendo das dimensões de ecrã, a criatividade vai sendo cortada do lado direito para o esquerdo. A informação principal deverá estar sempre do lado esquerdo.</t>
+          <t>Super Leaderboard: 1376x90px.</t>
         </is>
       </c>
       <c r="F165" s="2" t="n"/>
@@ -7411,7 +7419,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n"/>
-      <c r="J165" s="2" t="n"/>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Dependendo das dimensões de ecrã, a criatividade vai sendo cortada do lado direito para o esquerdo — a informação principal deve estar sempre do lado esquerdo.</t>
+        </is>
+      </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-twin_ad</t>
@@ -7621,7 +7633,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>1920x1080 recomendado (ou 1280x720); duração 6 a 60s (recomendado 6, 15, 30, 45 ou 60s).</t>
+          <t>1920x1080 recomendado (ou 1280x720).</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -7631,7 +7643,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>500 MB</t>
+          <t>500 MB. Duração: 6 a 60s (recomendado 6, 15, 30, 45 ou 60s).</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -7666,7 +7678,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Banner opcional: máx. 300x250 (só desktop); imagem do remetente = foto de perfil LinkedIn do remetente definido.</t>
+          <t>Banner opcional: máx. 300x250 (só desktop).</t>
         </is>
       </c>
       <c r="F171" s="2" t="n"/>
@@ -7685,7 +7697,11 @@
           <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
-      <c r="J171" s="2" t="n"/>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Imagem do remetente = foto de perfil LinkedIn do remetente definido.</t>
+        </is>
+      </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-messaging/conversation-ads/specs</t>
@@ -7944,7 +7960,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Banner opcional: máx. 300x250 (só desktop); imagem do remetente = foto de perfil LinkedIn do remetente definido.</t>
+          <t>Banner opcional: máx. 300x250 (só desktop).</t>
         </is>
       </c>
       <c r="F177" s="2" t="n"/>
@@ -7963,7 +7979,11 @@
           <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
-      <c r="J177" s="2" t="n"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>Imagem do remetente = foto de perfil LinkedIn do remetente definido.</t>
+        </is>
+      </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-messaging/message-ads/specs</t>
@@ -8038,7 +8058,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Landscape: 1920x1080 recomendado (mín. 640x360, máx. 1920x1080); Square: mín. 360x360, máx. 1920x1920; Vertical: mín. 360x450, máx. 1080x1350; Vertical: 720x1280 recomendado (mín. 360x640, máx. 1080x1920). Duração: 3s a 30min (in-stream em streaming até 90s).</t>
+          <t>Landscape: 1920x1080 recomendado (mín. 640x360, máx. 1920x1080); Square: mín. 360x360, máx. 1920x1920; Vertical: mín. 360x450, máx. 1080x1350; Vertical: 720x1280 recomendado (mín. 360x640, máx. 1080x1920).</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -8048,7 +8068,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>75 KB a 500 MB</t>
+          <t>75 KB a 500 MB. Duração: 3s a 30min (in-stream em streaming até 90s).</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -8430,7 +8450,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>2 a 6 imagens (mesmo rácio recomendado em todas). Cross-device recomendado: 1200x1500, 1440x1080 ou 1920x1080. Mobile: 1200x1200, 1080x1440, 900x1200, 1440x1080, 1920x1080. Desktop: 1200x1500, 1440x1080, 1920x1080. Qualquer rácio é aceite mas pode causar letterboxing. GIF: duração recomendada 3-10s. Thumbnail (compact view, gerado automaticamente a partir da 1ª imagem ou substituível): recomendado 400x300; aceite 300x300.</t>
+          <t>2 a 6 imagens (mesmo rácio recomendado em todas). Cross-device recomendado: 1200x1500, 1440x1080 ou 1920x1080. Mobile: 1200x1200, 1080x1440, 900x1200, 1440x1080, 1920x1080. Desktop: 1200x1500, 1440x1080, 1920x1080. Qualquer rácio é aceite mas pode causar letterboxing. Thumbnail (compact view, gerado automaticamente a partir da 1ª imagem ou substituível): recomendado 400x300; aceite 300x300.</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -8440,7 +8460,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>GIF: 3 MB; Outros tipos: 20 MB; Thumbnail: 3 MB</t>
+          <t>GIF: 3 MB; Outros tipos: 20 MB; Thumbnail: 3 MB. GIF: duração recomendada 3-10s.</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -8479,7 +8499,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Imagem (opcional): até 20 ficheiros, largura mín. recomendada 1000px; resoluções recomendadas 1200x1200, 1440x1080 ou 1920x1080. Vídeo (opcional): até 5 ficheiros; duração recomendada 5-30s; resoluções recomendadas 1200x1200, 1200x1500, 1440x1080 ou 1920x1080. Thumbnail (opcional, NÃO gerado automaticamente — sem thumbnail não aparece media no feed): recomendado 400x300 ou 300x300.</t>
+          <t>Imagem (opcional): até 20 ficheiros, largura mín. recomendada 1000px; resoluções recomendadas 1200x1200, 1440x1080 ou 1920x1080. Vídeo (opcional): até 5 ficheiros; resoluções recomendadas 1200x1200, 1200x1500, 1440x1080 ou 1920x1080. Thumbnail (opcional, NÃO gerado automaticamente — sem thumbnail não aparece media no feed): recomendado 400x300 ou 300x300.</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -8489,7 +8509,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Imagem: 10 MB; Vídeo: até 1 GB (recomendado 50-100 MB); Thumbnail: 3 MB</t>
+          <t>Imagem: 10 MB; Vídeo: até 1 GB (recomendado 50-100 MB); Thumbnail: 3 MB. Vídeo: duração recomendada 5-30s.</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -8618,7 +8638,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Vídeo — Cross-device recomendado: 1440x1080 ou 1920x1080. Mobile: 1200x1200, 900x1200, 1200x1500, 1440x1080, 1920x1080. Desktop: 1440x1080, 1920x1080. Qualquer rácio é aceite mas pode causar letterboxing. Duração: 2s a 15min (recomendado 5-30s). Thumbnail: resolução a acompanhar o rácio do vídeo (gerado automaticamente ou substituível).</t>
+          <t>Vídeo — Cross-device recomendado: 1440x1080 ou 1920x1080. Mobile: 1200x1200, 900x1200, 1200x1500, 1440x1080, 1920x1080. Desktop: 1440x1080, 1920x1080. Qualquer rácio é aceite mas pode causar letterboxing. Thumbnail: resolução a acompanhar o rácio do vídeo (gerado automaticamente ou substituível).</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -8628,7 +8648,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: até 1 GB; Thumbnail: 3 MB</t>
+          <t>Vídeo: até 1 GB; Thumbnail: 3 MB. Duração: 2s a 15min (recomendado 5-30s).</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -8667,13 +8687,13 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Estático: 945x2048; Animado: 720x1560, duração 1 a 3 seg.</t>
+          <t>Estático: 945x2048; Animado: 720x1560.</t>
         </is>
       </c>
       <c r="F192" s="2" t="n"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Varia por asset. Duração (animado): 1 a 3 seg.</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -8708,7 +8728,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
+          <t>720x1280.</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -8718,7 +8738,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Varia por asset. Duração de vídeo: 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -8757,7 +8777,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>720x1280. Standard: 3 a 6 seg, não saltável; Extended Play: 7 a 180 seg, só os primeiros 6 seg não saltáveis.</t>
+          <t>720x1280.</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -8767,7 +8787,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Varia; validar no Ads Manager. Duração — Standard: 3 a 6 seg, não saltável; Extended Play: 7 a 180 seg, só os primeiros 6 seg não saltáveis.</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -8851,7 +8871,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>720x1280; duração 3 a 180 seg.</t>
+          <t>720x1280.</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -8861,7 +8881,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Varia; validar no Ads Manager. Duração: 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -8900,7 +8920,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
+          <t>720x1280.</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -8910,7 +8930,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Varia por asset. Duração de vídeo: 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -9039,7 +9059,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Vertical (recomendado): 9:16, ≥540x960px. Horizontal: 16:9, ≥960x540px. Square: 1:1, ≥640x640px. Duração: até 10min</t>
+          <t>Vertical (recomendado): 9:16, ≥540x960px. Horizontal: 16:9, ≥960x540px. Square: 1:1, ≥640x640px.</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -9049,7 +9069,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>≤500 MB; bitrate ≥516 kbps</t>
+          <t>≤500 MB; bitrate ≥516 kbps. Duração: até 10min.</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9223,7 +9243,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Vertical, ≥540x960px; duração 5-60s (recomendado 9-15s).</t>
+          <t>Vertical, ≥540x960px.</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -9233,7 +9253,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ≤500 MB, bitrate ≥2.500kbps</t>
+          <t>≤500 MB, bitrate ≥2.500kbps. Duração: 5-60s (recomendado 9-15s).</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10822,7 +10842,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+          <t>Horizontal, Square, Vertical — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido).</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -10832,7 +10852,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração mínima: 10 segundos.</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -11190,7 +11210,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
+          <t>Feed: 1440x1800 (mín. 120x120px); Stories: 1440x2560 (mín. 250px largura); Reels: 1440x2560 recomendado.</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
@@ -11200,7 +11220,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>4 GB. Duração — Feed: 1s a 241min; Stories: 1s a 3min; Reels: sem duração máxima.</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -11386,7 +11406,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
+          <t>Feed: 1080x1920 (mín. 250px largura); Stories: 1440x2560 (mín. 250px largura); Reels: 1440x2560, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
@@ -11396,7 +11416,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>4 GB. Duração — Feed: 1s a 60min; Stories: 1s a 60min; Reels: 0 a 15min.</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -11725,7 +11745,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+          <t>720x1280.</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -11735,7 +11755,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Varia; validar no Ads Manager. Duração máx. 180 seg. (recomendado &lt;10 seg).</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -11748,7 +11768,11 @@
           <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
         </is>
       </c>
-      <c r="J258" s="2" t="n"/>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+        </is>
+      </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
@@ -17258,16 +17282,20 @@
           <t>Áudio</t>
         </is>
       </c>
-      <c r="E391" s="2" t="n"/>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Imagem de companhia (opcional): 300x250.</t>
+        </is>
+      </c>
       <c r="F391" s="2" t="n"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>Máx. 3 MB</t>
+          <t>Máx. 3 MB. Imagem de companhia: máx. 50 KB.</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>VAST 2.0, MP3, WAV, WMA ou OGG; companion asset (300x250, máx. 50 KB): JPG, JPEG, PNG ou GIF</t>
+          <t>VAST 2.0, MP3, WAV, WMA ou OGG; companion asset: JPG, JPEG, PNG ou GIF.</t>
         </is>
       </c>
       <c r="I391" s="2" t="n"/>
@@ -20740,7 +20768,7 @@
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>Elemento pop-out: PNG. Vídeo do anúncio: ver specs gerais do In-Feed.</t>
+          <t>Elemento pop-out: PNG.</t>
         </is>
       </c>
       <c r="I468" s="2" t="inlineStr">
@@ -20750,7 +20778,7 @@
       </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>O vídeo do anúncio toca normalmente e o botão CTA aparece; depois, um elemento pop-out salta para o centro do ecrã, minimiza-se e desloca-se para o canto esquerdo. O vídeo do anúncio tem de ter mín. 8 segundos (recomendado 15s+). O elemento pop-out tem de ser o mesmo produto/SKU/cor do anúncio, e só pode aparecer enquanto o produto está visível no ecrã; só pode ser definido a partir dos 3 segundos de anúncio e até, no mínimo, 5 segundos antes do fim. Sem limitação de ângulo de entrada (o elemento gira até 0° no sentido que corresponde ao ângulo de entrada). Posição do elemento: entre X 125-515, Y 200-710 (ver ferramenta de pré-visualização da TikTok). O elemento ajusta automaticamente o tamanho para não sobrepor a legenda do anúncio.</t>
+          <t>Vídeo do anúncio: segue as specs gerais do In-Feed. O vídeo do anúncio toca normalmente e o botão CTA aparece; depois, um elemento pop-out salta para o centro do ecrã, minimiza-se e desloca-se para o canto esquerdo. O vídeo do anúncio tem de ter mín. 8 segundos (recomendado 15s+). O elemento pop-out tem de ser o mesmo produto/SKU/cor do anúncio, e só pode aparecer enquanto o produto está visível no ecrã; só pode ser definido a partir dos 3 segundos de anúncio e até, no mínimo, 5 segundos antes do fim. Sem limitação de ângulo de entrada (o elemento gira até 0° no sentido que corresponde ao ângulo de entrada). Posição do elemento: entre X 125-515, Y 200-710 (ver ferramenta de pré-visualização da TikTok). O elemento ajusta automaticamente o tamanho para não sobrepor a legenda do anúncio.</t>
         </is>
       </c>
       <c r="K468" s="3" t="inlineStr">
@@ -21016,11 +21044,15 @@
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>Vídeo principal: mín. 5s (6s em anúncios 6s Focused View), máx. 60s (recomendado &lt;10s). Sub-vídeo A e sub-vídeo B: máx. 30s cada. Imagem de capa dos sub-vídeos (opcional): 144x192px.</t>
+          <t>Imagem de capa dos sub-vídeos (opcional): 144x192px.</t>
         </is>
       </c>
       <c r="F475" s="2" t="n"/>
-      <c r="G475" s="2" t="n"/>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo principal: mín. 5s (6s em anúncios 6s Focused View), máx. 60s (recomendado &lt;10s). Sub-vídeo A e sub-vídeo B: máx. 30s cada.</t>
+        </is>
+      </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
           <t>Vídeos: MP4, MOV, MPEG ou 3GP. Imagens de capa: PNG ou JPG.</t>
@@ -21169,7 +21201,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Máx. 500 MB.</t>
+          <t>Máx. 500 MB. Duração: máx. 30 segundos.</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -21179,7 +21211,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>Duração: máx. 30 segundos. Tagline: máx. 40 carateres.</t>
+          <t>Tagline: máx. 40 carateres.</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
@@ -21218,7 +21250,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>Máx. 500 MB.</t>
+          <t>Máx. 500 MB. Duração: máx. 30 segundos.</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -21228,7 +21260,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>Duração: máx. 30 segundos. Tagline: máx. 40 carateres. CTA (lista fixa): Apply now, Book now, Buy now, Buy tickets, Click now, Download, Find stores, Get coupon, Get info, Learn more, Listen now, More info, Pre-save, Save now, Share, Shop now, Sign up, Visit profile, Visit site, Watch now.</t>
+          <t>Tagline: máx. 40 carateres. CTA (lista fixa): Apply now, Book now, Buy now, Buy tickets, Click now, Download, Find stores, Get coupon, Get info, Learn more, Listen now, More info, Pre-save, Save now, Share, Shop now, Sign up, Visit profile, Visit site, Watch now.</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical.</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>5 MB. Vídeo: qualquer duração (recomendado 30s).</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
+          <t>Horizontal, Vertical, Square.</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração: 10 a 60 segundos (opcional).</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+          <t>Horizontal, Vertical, Square — até 20 vídeos, opcionais mas recomendados.</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube. Duração: 10 a 60 segundos.</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>Mín. 4 KB, máx. 4 MB</t>
+          <t>Mín. 4 KB, máx. 4 MB. Duração máx. 30s.</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
+          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
       <c r="I325" s="2" t="n"/>
@@ -14663,18 +14663,18 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Mín. 4 KB, máx. 4 MB</t>
+          <t>Mín. 4 KB, máx. 4 MB. Duração máx. 30s.</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
+          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
       <c r="I326" s="2" t="n"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer.</t>
+          <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer. Sem autoplay de áudio (som off por defeito).</t>
         </is>
       </c>
       <c r="K326" s="2" t="n"/>
@@ -14698,32 +14698,32 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
+          <t>MREC: 300x250; Halfpage: 300x600.</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>9:16 e 1:1 (imagens estáticas).</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F327" s="2" t="inlineStr">
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>JPEG (imagens estáticas); MP4 (vídeo, se associado).</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G327" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H327" s="2" t="inlineStr">
-        <is>
-          <t>Envio de Briefing a detalhar principais mensagens de comunicação + URLs destino dos artigos (caso se aplique) + editáveis da campanha para utilização pelo meio + Imagens estáticas formato 9:16 e 1:1 + MREC (300x250) + Halfpage (300x600) + Outros elementos/imagens considerados importantes</t>
-        </is>
-      </c>
-      <c r="I327" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J327" s="2" t="inlineStr">
         <is>
-          <t>É necessário enviar:
+          <t>Briefing a detalhar principais mensagens de comunicação. URLs destino dos artigos (caso se aplique). Editáveis da campanha para utilização pelo meio. É necessário enviar:
  - data da publicação?
 - qual o produto ou serviço a comunicar?
 - qual a mensagem a passar?
@@ -16110,12 +16110,12 @@
       <c r="F363" s="2" t="n"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 KB (imagem; peso do vídeo não indicado)</t>
+          <t>Imagem: máx. 100 KB. Vídeo: -.</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>JPG/PNG (imagem; formato do vídeo não indicado)</t>
+          <t>Imagem: JPG/PNG. Vídeo: -.</t>
         </is>
       </c>
       <c r="I363" s="2" t="n"/>
@@ -18039,12 +18039,12 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 10 MB. Duração: até 30 segundos.</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>MP4, até 30 segundos</t>
+          <t>MP4.</t>
         </is>
       </c>
       <c r="I408" s="2" t="n"/>
@@ -18898,12 +18898,12 @@
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 10 MB. Duração: até 30 segundos.</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
-          <t>MP4, até 30 segundos</t>
+          <t>MP4.</t>
         </is>
       </c>
       <c r="I427" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -11745,7 +11745,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>720x1280.</t>
+          <t>720x1280. Fundo de chat personalizado (opcional): 1080x1920.</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -11765,14 +11765,10 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
-        </is>
-      </c>
-      <c r="J258" s="2" t="inlineStr">
-        <is>
-          <t>Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
-        </is>
-      </c>
+          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c). Elementos opcionais de Message Design (até 3): mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="n"/>
       <c r="K258" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
@@ -14168,7 +14164,7 @@
       <c r="I312" s="2" t="n"/>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>Suporte com tracking DCM. Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox. Ver ficheiro técnico adicional fornecido pelo meio (não disponibilizado aqui).</t>
+          <t>Suporte com tracking DCM. Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox.</t>
         </is>
       </c>
       <c r="K312" s="2" t="n"/>
@@ -14452,7 +14448,7 @@
       <c r="I320" s="2" t="n"/>
       <c r="J320" s="2" t="inlineStr">
         <is>
-          <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio (não disponibilizado aqui).</t>
+          <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio.</t>
         </is>
       </c>
       <c r="K320" s="2" t="n"/>
@@ -14518,7 +14514,7 @@
       <c r="I322" s="2" t="n"/>
       <c r="J322" s="2" t="inlineStr">
         <is>
-          <t>Solução de rich media interativa, otimizada mobile-first, com formatos inspirados em redes sociais, para alcançar utilizadores durante a leitura de conteúdo editorial. Specs técnicas completas num documento à parte ("Social Display RMF Specifications"), não disponibilizado aqui.</t>
+          <t>Specs técnicas completas num documento à parte ("Social Display RMF Specifications") — confirmar com o meio antes de produzir.</t>
         </is>
       </c>
       <c r="K322" s="2" t="n"/>
@@ -14761,7 +14757,7 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>512x348px. Logo: altura até 150px, largura máx. 500px.</t>
         </is>
       </c>
       <c r="F328" s="2" t="n"/>
@@ -14775,10 +14771,14 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="I328" s="2" t="n"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>Título: obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha). Tagline: opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha). Texto "Ad": obrigatório, máx. 13 carateres.</t>
+        </is>
+      </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
-          <t>Banner estático (Guapo) no fundo do ecrã principal da app, sempre com uma promoção de pelo menos 20% de desconto. Logo: altura até 150px, largura máx. 500px. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Sempre com uma promoção de pelo menos 20% de desconto. Não colocar informação nem elementos importantes nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
       <c r="K328" s="2" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>512x348px. Logo: altura até 150px, largura máx. 500px.</t>
         </is>
       </c>
       <c r="F329" s="2" t="n"/>
@@ -14816,10 +14816,14 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="I329" s="2" t="n"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>Título: obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha). Tagline: opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha). Texto "Ad": obrigatório, máx. 13 carateres.</t>
+        </is>
+      </c>
       <c r="J329" s="2" t="inlineStr">
         <is>
-          <t>Banner estático no meio da loja Food Wall, focado em marcas de comida, sempre com uma promoção. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Sempre com uma promoção. Várias cores de fundo sólidas disponíveis. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
       <c r="K329" s="2" t="n"/>
@@ -14860,7 +14864,7 @@
       <c r="I330" s="2" t="n"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>Banner estático em supermercados ou na parede do Glovo Market ("store wall"), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Fundo sólido. Deixar 30px de margem no topo e na base, para os produtos ficarem todos visíveis na zona central; atenção à seta de CTA no canto inferior direito. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
       <c r="K330" s="2" t="n"/>
@@ -14901,7 +14905,7 @@
       <c r="I331" s="2" t="n"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>Banner localizado dentro de diferentes categorias das lojas (fora da categoria principal da marca), com os produtos a aparecer por baixo do banner — o utilizador pode adicioná-los diretamente ao cesto ou clicar no banner para ir à loja completa. Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Fundo sólido. Deixar 90px de espaço a partir da margem inferior, onde entram a palavra "Sponsored" e o botão, assim que o banner estiver na app. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
       <c r="K331" s="2" t="n"/>
@@ -14925,7 +14929,7 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>512x348px</t>
+          <t>512x348px. Logo: altura até 150px, largura máx. 500px.</t>
         </is>
       </c>
       <c r="F332" s="2" t="n"/>
@@ -14939,10 +14943,14 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="I332" s="2" t="n"/>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>Título: obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha). Tagline: opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha). Texto "Ad": obrigatório, máx. 13 carateres.</t>
+        </is>
+      </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>Banner estático nas paredes das lojas de Groceries e Shops (Q-commerce), a mostrar a marca de forma visual e a encaminhar para compra direta dos produtos. Logo: altura até 150px, largura máx. 500px. Várias cores de fundo sólidas disponíveis. Texto: Título obrigatório, máx. 40 carateres (se ocupar 2 linhas, a tagline fica limitada a 1 linha); Tagline opcional, máx. 52 carateres (se ocupar 2 linhas, o título fica limitado a 1 linha); texto "Ad" obrigatório, máx. 13 carateres. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Várias cores de fundo sólidas disponíveis. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
       <c r="K332" s="2" t="n"/>
@@ -14980,10 +14988,14 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="I333" s="2" t="n"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 20 carateres. CTA: máx. 10 carateres.</t>
+        </is>
+      </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>Banner "skippable" (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, no fundo do ecrã, com uma secção de texto personalizável. O utilizador pode saltar o anúncio quando quiser. Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 20 carateres; CTA máx. 10 carateres. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Logo tem de estar incluído na própria imagem do banner. Evitar colocar informação importante no canto superior direito — fica sobreposta pelo botão de fechar. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
       <c r="K333" s="2" t="n"/>
@@ -15021,10 +15033,14 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="I334" s="2" t="n"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 30 carateres. Sem tagline.</t>
+        </is>
+      </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>Banner (não endémico) que aparece depois de uma compra concluída, assim que o mapa de entrega é mostrado, e depois de um OTP Premium ter sido saltado ("skipped"). Logo tem de estar incluído na própria imagem do banner. Texto: Título máx. 30 carateres; sem tagline. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
+          <t>Logo tem de estar incluído na própria imagem do banner. Várias cores de fundo sólidas disponíveis. Não colocar informação importante nas zonas coloridas do banner — o que lá estiver é cortado ou sobreposto pela seta. Todos os designs têm de ser revistos pela equipa de design da Glovo antes de entrarem em produção — enviar os ficheiros editáveis em .psd, com as camadas separadas e as fontes incluídas, ao ponto de contacto habitual.</t>
         </is>
       </c>
       <c r="K334" s="2" t="n"/>
@@ -15514,10 +15530,14 @@
       <c r="F347" s="2" t="n"/>
       <c r="G347" s="2" t="n"/>
       <c r="H347" s="2" t="n"/>
-      <c r="I347" s="2" t="n"/>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres).</t>
+        </is>
+      </c>
       <c r="J347" s="2" t="inlineStr">
         <is>
-          <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe usado pela ClickProfit — bit.ly/ChB_); sobram 142 carateres para o anunciante, podendo incluir um link (que a ClickProfit converte depois em bit.ly — esse link também conta para os 142 carateres). Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
+          <t>Enviar números de telemóvel para envio de SMS de teste. Prazo de entrega dos materiais: 72h úteis.</t>
         </is>
       </c>
       <c r="K347" s="2" t="n"/>
@@ -15559,12 +15579,12 @@
           <t>JPEG (preferencial), BMP, PNG, WBMP ou GIF</t>
         </is>
       </c>
-      <c r="I348" s="2" t="n"/>
-      <c r="J348" s="2" t="inlineStr">
+      <c r="I348" s="2" t="inlineStr">
         <is>
           <t>Título: 34-45 carateres (ideal), máx. 60. Descrição: 180 (ideal), máx. 250. Texto de marca: máx. 30 carateres.</t>
         </is>
       </c>
+      <c r="J348" s="2" t="n"/>
       <c r="K348" s="2" t="n"/>
     </row>
     <row r="349">
@@ -15596,7 +15616,7 @@
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>Máx. 50 MB (GIF: máx. 5 MB)</t>
+          <t>Máx. 50 MB (GIF: máx. 5 MB) Duração máx. 15″.</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -15604,12 +15624,12 @@
           <t>MP4, MOV ou GIF</t>
         </is>
       </c>
-      <c r="I349" s="2" t="n"/>
-      <c r="J349" s="2" t="inlineStr">
-        <is>
-          <t>Duração máx. 15″. Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
-        </is>
-      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>Título: 34-45 carateres (ideal), máx. 60. Texto de marca: máx. 30 carateres.</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="n"/>
       <c r="K349" s="2" t="n"/>
     </row>
     <row r="350">
@@ -15783,18 +15803,22 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>1200x627</t>
+          <t>1200x627 (por cartão). Mín. 3 e máx. 5 cartões.</t>
         </is>
       </c>
       <c r="F354" s="2" t="n"/>
       <c r="G354" s="2" t="n"/>
-      <c r="H354" s="2" t="n"/>
-      <c r="I354" s="2" t="n"/>
-      <c r="J354" s="2" t="inlineStr">
-        <is>
-          <t>Mín. 3 e máx. 5 cartões. Por cartão: imagem, título (máx. 50 carateres), descrição (máx. 150 carateres), CTA e URL de destino (pode variar por cartão). Suporta GIF/vídeo nos cartões.</t>
-        </is>
-      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>Imagem (também aceita GIF/vídeo) por cartão.</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>Por cartão — Título: máx. 50 carateres; Descrição: máx. 150 carateres; CTA: incluído; URL de destino: pode variar por cartão.</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="n"/>
       <c r="K354" s="2" t="n"/>
     </row>
     <row r="355">
@@ -15888,12 +15912,12 @@
       <c r="F357" s="2" t="n"/>
       <c r="G357" s="2" t="n"/>
       <c r="H357" s="2" t="n"/>
-      <c r="I357" s="2" t="n"/>
-      <c r="J357" s="2" t="inlineStr">
+      <c r="I357" s="2" t="inlineStr">
         <is>
           <t>Sender: máx. 11 carateres. Copy: máx. 160 carateres (inclui espaços, pontuação e o link de unsubscribe — Stop SMS: 91xxxxxxx); no total ~135 carateres disponíveis. Não usar o símbolo € (spam trigger), usar "EUR". Símbolos especiais (%, ?, pontuação) contam como 2 espaços.</t>
         </is>
       </c>
+      <c r="J357" s="2" t="n"/>
       <c r="K357" s="2" t="n"/>
     </row>
     <row r="358">
@@ -15925,10 +15949,14 @@
         </is>
       </c>
       <c r="H358" s="2" t="n"/>
-      <c r="I358" s="2" t="n"/>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>Proposta de valor + CTA, ambos visíveis sem necessidade de scroll.</t>
+        </is>
+      </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>Usar logo da marca. Banner = imagem + proposta de valor + CTA, visíveis sem necessidade de scroll. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
+          <t>Usar logo da marca. Newsletter não deve ser muito extensa; preferir mais texto do que imagens. A Suebi pode desenvolver o HTML sem custo para o cliente, se necessário.</t>
         </is>
       </c>
       <c r="K358" s="2" t="n"/>
@@ -15958,10 +15986,14 @@
       <c r="F359" s="2" t="n"/>
       <c r="G359" s="2" t="n"/>
       <c r="H359" s="2" t="n"/>
-      <c r="I359" s="2" t="n"/>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>Sender: 30-45 carateres. Subject: 40-50 carateres.</t>
+        </is>
+      </c>
       <c r="J359" s="2" t="inlineStr">
         <is>
-          <t>Sender: 30-45 carateres. Subject: 40-50 carateres. Awareness puro, com clicktracker.</t>
+          <t>Awareness puro, com clicktracker.</t>
         </is>
       </c>
       <c r="K359" s="2" t="n"/>
@@ -16028,10 +16060,14 @@
       <c r="F361" s="2" t="n"/>
       <c r="G361" s="2" t="n"/>
       <c r="H361" s="2" t="n"/>
-      <c r="I361" s="2" t="n"/>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>Título e texto no corpo do email: curtos, diretos ao tema. CTA (opções): Comprar ou Saiba mais.</t>
+        </is>
+      </c>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>Canal: Newsletter. Indicar título e texto no corpo do email — curtos, diretos ao tema, a captar a curiosidade do leitor. CTA: Comprar ou Saiba mais. Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
+          <t>Colocar selo de desconto na imagem, se aplicável. Indicar SKUs a linkar e respetiva categoria.</t>
         </is>
       </c>
       <c r="K361" s="3" t="inlineStr">
@@ -17004,11 +17040,7 @@
         </is>
       </c>
       <c r="I384" s="2" t="n"/>
-      <c r="J384" s="2" t="inlineStr">
-        <is>
-          <t>Conjunto genérico de banners + conjunto específico, consoante a campanha.</t>
-        </is>
-      </c>
+      <c r="J384" s="2" t="n"/>
       <c r="K384" s="2" t="n"/>
     </row>
     <row r="385">
@@ -17339,10 +17371,14 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="I392" s="2" t="n"/>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 30 carateres. Subtítulo: máx. 35 carateres. Sem emojis no texto.</t>
+        </is>
+      </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPC (mín. 150 cliques/dia). Título: máx. 30 carateres. Subtítulo: máx. 35 carateres. Sem emojis no texto. Máx. 10 criatividades por campanha.</t>
+          <t>Compra: CPC (mín. 150 cliques/dia). Máx. 10 criatividades por campanha.</t>
         </is>
       </c>
       <c r="K392" s="2" t="n"/>
@@ -17425,12 +17461,12 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I394" s="2" t="n"/>
-      <c r="J394" s="2" t="inlineStr">
+      <c r="I394" s="2" t="inlineStr">
         <is>
           <t>Short Headline (x2): máx. 30 carateres. Long Headline: máx. 90 carateres. Descrição: máx. 90 carateres. Business/Brand Name: máx. 25 carateres.</t>
         </is>
       </c>
+      <c r="J394" s="2" t="n"/>
       <c r="K394" s="2" t="n"/>
     </row>
     <row r="395">
@@ -17462,12 +17498,12 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="I395" s="2" t="n"/>
-      <c r="J395" s="2" t="inlineStr">
+      <c r="I395" s="2" t="inlineStr">
         <is>
           <t>Título: máx. 50 carateres (recomendado 16-24). Descrição: máx. 100 carateres (recomendado 32-48).</t>
         </is>
       </c>
+      <c r="J395" s="2" t="n"/>
       <c r="K395" s="2" t="n"/>
     </row>
     <row r="396">
@@ -17503,10 +17539,14 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I396" s="2" t="n"/>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>Texto/Copy: máx. 30 carateres.</t>
+        </is>
+      </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). Texto/Copy: máx. 30 carateres.</t>
+          <t>Posição: Homepage (Desktop).</t>
         </is>
       </c>
       <c r="K396" s="3" t="inlineStr">
@@ -17638,10 +17678,14 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I399" s="2" t="n"/>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+        </is>
+      </c>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+          <t>Posição: Homepage (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K399" s="3" t="inlineStr">
@@ -17683,10 +17727,14 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I400" s="2" t="n"/>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres.</t>
+        </is>
+      </c>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Título Principal: máx. 20 carateres. Título: máx. 18 carateres. Descrição: máx. 25 carateres. Existe template para download no site de specs.</t>
+          <t>Posição: Listing Page (Desktop). São necessárias duas versões para o Screening (Takeover). Ter atenção às áreas visíveis (Safe Zones). Existe template para download no site de specs.</t>
         </is>
       </c>
       <c r="K400" s="3" t="inlineStr">
@@ -17953,10 +18001,14 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I406" s="2" t="n"/>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
+        </is>
+      </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. CTA: máx. 10 carateres.</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="K406" s="3" t="inlineStr">
@@ -17998,10 +18050,14 @@
           <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
-      <c r="I407" s="2" t="n"/>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>Texto/Copy: máx. 40 carateres.</t>
+        </is>
+      </c>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+          <t>Posição: Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="K407" s="3" t="inlineStr">
@@ -18137,10 +18193,14 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I410" s="2" t="n"/>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>Texto/Copy: máx. 10 carateres.</t>
+        </is>
+      </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>Posição: Homepage (Mobile). Texto/Copy: máx. 10 carateres.</t>
+          <t>Posição: Homepage (Mobile).</t>
         </is>
       </c>
       <c r="K410" s="3" t="inlineStr">
@@ -18317,10 +18377,14 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I414" s="2" t="n"/>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
+        </is>
+      </c>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Mobile). Título: máx. 25 carateres. Descrição: máx. 35 carateres.</t>
+          <t>Posição: Listing Page (Mobile).</t>
         </is>
       </c>
       <c r="K414" s="3" t="inlineStr">
@@ -18362,10 +18426,14 @@
           <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
-      <c r="I415" s="2" t="n"/>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>Texto/Copy: máx. 20 carateres.</t>
+        </is>
+      </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+          <t>Posição: Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="K415" s="3" t="inlineStr">
@@ -18677,10 +18745,14 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="I422" s="2" t="n"/>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
+        </is>
+      </c>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>Posição: Listing Page (Desktop). Título: máx. 45 carateres. Descrição: máx. 65 carateres. CTA: máx. 10 carateres.</t>
+          <t>Posição: Listing Page (Desktop).</t>
         </is>
       </c>
       <c r="K422" s="3" t="inlineStr">
@@ -19311,10 +19383,14 @@
           <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
-      <c r="I436" s="2" t="n"/>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>Texto/Copy: máx. 40 carateres.</t>
+        </is>
+      </c>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Desktop). Texto/Copy: máx. 40 carateres.</t>
+          <t>Posição: Ad Page (Desktop).</t>
         </is>
       </c>
       <c r="K436" s="3" t="inlineStr">
@@ -19401,10 +19477,14 @@
           <t>JPG, PNG ou GIF (apenas se incluir logo)</t>
         </is>
       </c>
-      <c r="I438" s="2" t="n"/>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>Texto/Copy: máx. 20 carateres.</t>
+        </is>
+      </c>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>Posição: Ad Page (Mobile). Texto/Copy: máx. 20 carateres.</t>
+          <t>Posição: Ad Page (Mobile).</t>
         </is>
       </c>
       <c r="K438" s="3" t="inlineStr">
@@ -19446,10 +19526,14 @@
           <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
-      <c r="I439" s="2" t="n"/>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
+        </is>
+      </c>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos. CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
+          <t>Não colocar elementos importantes nas danger zones (laterais) — usar essa área só para elementos gráficos decorativos.</t>
         </is>
       </c>
       <c r="K439" s="3" t="inlineStr">
@@ -19491,10 +19575,14 @@
           <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
-      <c r="I440" s="2" t="n"/>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
+        </is>
+      </c>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
+          <t>Só elementos necessários (logo, headline, CTA); texto legível e conciso. Não colocar elementos importantes nas danger zones.</t>
         </is>
       </c>
       <c r="K440" s="3" t="inlineStr">
@@ -19536,10 +19624,14 @@
           <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
-      <c r="I441" s="2" t="n"/>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
+        </is>
+      </c>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
+          <t>Não colocar elementos importantes nas danger zones.</t>
         </is>
       </c>
       <c r="K441" s="3" t="inlineStr">
@@ -19581,10 +19673,14 @@
           <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
-      <c r="I442" s="2" t="n"/>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
+        </is>
+      </c>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
+          <t>Não colocar elementos importantes nas danger zones.</t>
         </is>
       </c>
       <c r="K442" s="3" t="inlineStr">
@@ -19626,10 +19722,14 @@
           <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
-      <c r="I443" s="2" t="n"/>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
+        </is>
+      </c>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>Unidade criativa dinâmica in-article, pensada para visibilidade máxima durante o scroll em conteúdo mobile web. Não colocar elementos importantes nas danger zones. CTA: máx. 2-3 palavras com verbo de ação.</t>
+          <t>Não colocar elementos importantes nas danger zones.</t>
         </is>
       </c>
       <c r="K443" s="3" t="inlineStr">
@@ -19671,12 +19771,12 @@
           <t>PNG, JPEG, GIF ou HTML5 (managed only)</t>
         </is>
       </c>
-      <c r="I444" s="2" t="n"/>
-      <c r="J444" s="2" t="inlineStr">
-        <is>
-          <t>Unidade in-article, pensada para consideração e tráfego qualificado. Incluído só nalguns pacotes — confirmar na recomendação de media. CTA: máx. 2-3 palavras com verbo de ação.</t>
-        </is>
-      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>CTA: máx. 2-3 palavras com verbo de ação (ex.: "Compre agora", "Descubra").</t>
+        </is>
+      </c>
+      <c r="J444" s="2" t="n"/>
       <c r="K444" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/image-design-specifications#in-article-mpu</t>
@@ -19720,10 +19820,14 @@
           <t>MP4, VAST tag ou VPAID (legacy)</t>
         </is>
       </c>
-      <c r="I445" s="2" t="n"/>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>CTA: máx. 30 carateres ("Visit website" por defeito).</t>
+        </is>
+      </c>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>Safe area: margem de 10% em cima/baixo (para overlays de UI). Som opcional — tem de ser compreensível sem áudio (autoplay mudo). Branding/mensagem clara nos primeiros 5 segundos. Tracking de terceiros (ex.: IAS, DoubleVerify) só embrulhado em VAST tags. CTA personalizável: máx. 30 carateres ("Visit website" por defeito). Opcional: skins e end card disponíveis — confirmar specs com a equipa Ogury.</t>
+          <t>Safe area: margem de 10% em cima/baixo (para overlays de UI). Som opcional — tem de ser compreensível sem áudio (autoplay mudo). Branding/mensagem clara nos primeiros 5 segundos. Tracking de terceiros (ex.: IAS, DoubleVerify) só embrulhado em VAST tags. Opcional: skins e end card disponíveis — confirmar specs com a equipa Ogury.</t>
         </is>
       </c>
       <c r="K445" s="3" t="inlineStr">
@@ -19817,7 +19921,7 @@
       </c>
       <c r="J447" s="2" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo para mostrar vários produtos, features ou mensagens de marca numa experiência deslizável (swipe). Disponível para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K447" s="3" t="inlineStr">
@@ -19862,7 +19966,7 @@
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo com navegação em camadas: o utilizador interage com elementos no ecrã de entrada para aceder a vistas de detalhe dedicadas. Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K448" s="3" t="inlineStr">
@@ -19907,7 +20011,7 @@
       </c>
       <c r="J449" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo que permite ao utilizador explorar produtos, variantes, features ou configurações diferentes dentro de uma única criatividade: ao tocar numa opção seletora, o visual principal e o conteúdo associado atualizam-se instantaneamente. Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K449" s="3" t="inlineStr">
@@ -19952,7 +20056,7 @@
       </c>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo em que o utilizador arrasta um ou mais elementos para áreas-alvo predefinidas para completar uma ação; ao concluir, revela conteúdo/novo ecrã. Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K450" s="3" t="inlineStr">
@@ -19997,7 +20101,7 @@
       </c>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo com hotspots clicáveis sobre elementos-chave de um visual; ao tocar, revela conteúdo adicional (informação de produto, features, preço, imagem, vídeo ou CTA). Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K451" s="3" t="inlineStr">
@@ -20042,7 +20146,7 @@
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo que permite comparar dois visuais arrastando um slider pelo ecrã — revela progressivamente uma imagem enquanto esconde a outra, criando uma experiência "antes e depois". Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K452" s="3" t="inlineStr">
@@ -20083,7 +20187,7 @@
       <c r="I453" s="2" t="n"/>
       <c r="J453" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo em que o utilizador reconstrói uma imagem para desbloquear conteúdo adicional; ao completar o puzzle, mostra um ecrã de revelação final. Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K453" s="3" t="inlineStr">
@@ -20128,7 +20232,7 @@
       </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>Formato interativo com uma interação simples de toque que desbloqueia conteúdo adicional: começa com um visual teaser e revela uma segunda camada de conteúdo (imagem, vídeo, slideshow, animação ou mensagem promocional). Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K454" s="3" t="inlineStr">
@@ -20173,7 +20277,7 @@
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>Combina uma criatividade de marca com um localizador de lojas integrado: o utilizador interage com um visual promocional e depois toca num CTA para aceder a um mapa interativo dentro do próprio anúncio, mostrando lojas, pontos de venda, postos de carregamento, concessionários ou outras localizações físicas próximas. Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento.</t>
+          <t>Mapa: é obrigatório um ficheiro .CSV de localizações preenchido, usando o template fornecido pela Ogury, sem alterar os nomes das colunas (caso contrário a integração do mapa falha). Campos obrigatórios: nome da localização, morada, cidade, código postal, estado/região (se aplicável), país, latitude, longitude, report label. Campos opcionais: telefone, email, URL, horário de funcionamento.</t>
         </is>
       </c>
       <c r="K455" s="3" t="inlineStr">
@@ -20216,11 +20320,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J456" s="2" t="inlineStr">
-        <is>
-          <t>Experiência imersiva multi-página que permite navegação vertical por conteúdo de marca através de swipe (cima/baixo), replicando a navegação num site/landing page, com produtos, features, storytelling ou conteúdo promocional distribuídos por várias páginas dentro do mesmo anúncio.</t>
-        </is>
-      </c>
+      <c r="J456" s="2" t="n"/>
       <c r="K456" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/site-scroller-design-specifications</t>
@@ -20267,7 +20367,7 @@
       </c>
       <c r="J457" s="2" t="inlineStr">
         <is>
-          <t>Mostra o produto a partir de todos os ângulos. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
+          <t>Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="K457" s="3" t="inlineStr">
@@ -20312,7 +20412,7 @@
       </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>Carrossel rich media interativo com navegação em camadas (entrada + vista de detalhe), orientado a pergunta/resposta. Para campanhas CPE e CPM.</t>
+          <t>Para campanhas CPE e CPM.</t>
         </is>
       </c>
       <c r="K458" s="3" t="inlineStr">
@@ -20414,7 +20514,7 @@
       </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>Reaproveita os assets da marca para emular a experiência de carrossel social (Facebook ou Instagram — escolher um layout) dentro de apps não-sociais, gerando alcance incremental. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
+          <t>Escolher um layout: Facebook ou Instagram. Unidade construída à medida pela equipa de Design da Ogury (não é self-service).</t>
         </is>
       </c>
       <c r="K460" s="3" t="inlineStr">
@@ -20457,11 +20557,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J461" s="2" t="inlineStr">
-        <is>
-          <t>Anima o storytelling: liga narrativa com transições suaves e mensagens sequenciais, ideal para destacar várias features de produto ou mensagens-chave numa única criatividade.</t>
-        </is>
-      </c>
+      <c r="J461" s="2" t="n"/>
       <c r="K461" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/slideshow-design-specifications</t>
@@ -20502,11 +20598,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J462" s="2" t="inlineStr">
-        <is>
-          <t>Efeito de expansão rápido e chamativo, que dá impacto visual instantâneo e atrai naturalmente a atenção para elementos-chave, mantendo a experiência fluida e não intrusiva.</t>
-        </is>
-      </c>
+      <c r="J462" s="2" t="n"/>
       <c r="K462" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/pop-design-specifications</t>
@@ -20547,11 +20639,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J463" s="2" t="inlineStr">
-        <is>
-          <t>Efeito de revelação horizontal: um segundo visual desliza suavemente sobre o primeiro, criando uma transição clara e envolvente — ideal para mostrar contrastes, detalhes de produto ou mensagens-chave de forma dinâmica mas controlada.</t>
-        </is>
-      </c>
+      <c r="J463" s="2" t="n"/>
       <c r="K463" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/glide-design-specifications</t>
@@ -20592,11 +20680,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J464" s="2" t="inlineStr">
-        <is>
-          <t>Transição vertical suave entre dois visuais, trazendo o conteúdo para o ecrã de forma natural e guiando a atenção do utilizador — ideal para mostrar duas mensagens/visuais complementares, com uma experiência limpa e premium.</t>
-        </is>
-      </c>
+      <c r="J464" s="2" t="n"/>
       <c r="K464" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/shift-design-specifications</t>
@@ -20637,11 +20721,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J465" s="2" t="inlineStr">
-        <is>
-          <t>Combina uma transição vertical com um efeito de revelação limpo, introduzindo visuais ou mensagens com clareza e impacto, numa experiência fluida e fácil de seguir.</t>
-        </is>
-      </c>
+      <c r="J465" s="2" t="n"/>
       <c r="K465" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/rise-design-specifications</t>
@@ -20682,11 +20762,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J466" s="2" t="inlineStr">
-        <is>
-          <t>Efeito de revelação a partir do centro: os visuais dividem-se e desdobram-se para introduzir novo conteúdo, criando uma transição dinâmica que mantém o utilizador envolvido — ideal para revelar progressivamente vários visuais de forma fluida e estruturada.</t>
-        </is>
-      </c>
+      <c r="J466" s="2" t="n"/>
       <c r="K466" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/display-creatives/unfold-design-specifications</t>
@@ -20729,7 +20805,7 @@
       <c r="I467" s="2" t="n"/>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>Add-on interativo: ícones em forma de coração (ou personalizados) flutuam pelo ecrã quando a audiência dá like ou toca duas vezes no anúncio. Pode incluir-se opcionalmente um cartão pop-up personalizado, que aparece depois da animação — ao clicar, leva à landing page do anúncio. Imagem do ícone: fornecer uma única imagem estática (é redimensionada automaticamente); design rico e preenchido com cor de fundo, evitando formas ocas, sombra, dispersão de elementos, formas finas ou efeito 3D; se retangular, cantos arredondados a 24px; deixar 2px de margem à volta da área válida; evitar que o elemento principal fique demasiado pequeno em relação à área efetiva (vermelha). Cartão pop-up: evitar design totalmente branco ou transparente.</t>
+          <t>Imagem do ícone: fornecer uma única imagem estática (é redimensionada automaticamente); design rico e preenchido com cor de fundo, evitando formas ocas, sombra, dispersão de elementos, formas finas ou efeito 3D; se retangular, cantos arredondados a 24px; deixar 2px de margem à volta da área válida; evitar que o elemento principal fique demasiado pequeno em relação à área efetiva (vermelha). Cartão pop-up: evitar design totalmente branco ou transparente.</t>
         </is>
       </c>
       <c r="K467" s="3" t="inlineStr">
@@ -20778,7 +20854,7 @@
       </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>Vídeo do anúncio: segue as specs gerais do In-Feed. O vídeo do anúncio toca normalmente e o botão CTA aparece; depois, um elemento pop-out salta para o centro do ecrã, minimiza-se e desloca-se para o canto esquerdo. O vídeo do anúncio tem de ter mín. 8 segundos (recomendado 15s+). O elemento pop-out tem de ser o mesmo produto/SKU/cor do anúncio, e só pode aparecer enquanto o produto está visível no ecrã; só pode ser definido a partir dos 3 segundos de anúncio e até, no mínimo, 5 segundos antes do fim. Sem limitação de ângulo de entrada (o elemento gira até 0° no sentido que corresponde ao ângulo de entrada). Posição do elemento: entre X 125-515, Y 200-710 (ver ferramenta de pré-visualização da TikTok). O elemento ajusta automaticamente o tamanho para não sobrepor a legenda do anúncio.</t>
+          <t>Vídeo do anúncio: segue as specs gerais do In-Feed. O vídeo do anúncio tem de ter mín. 8 segundos (recomendado 15s+). O elemento pop-out tem de ser o mesmo produto/SKU/cor do anúncio, e só pode aparecer enquanto o produto está visível no ecrã; só pode ser definido a partir dos 3 segundos de anúncio e até, no mínimo, 5 segundos antes do fim. Sem limitação de ângulo de entrada (o elemento gira até 0° no sentido que corresponde ao ângulo de entrada). Posição do elemento: entre X 125-515, Y 200-710 (ver ferramenta de pré-visualização da TikTok). O elemento ajusta automaticamente o tamanho para não sobrepor a legenda do anúncio.</t>
         </is>
       </c>
       <c r="K468" s="3" t="inlineStr">
@@ -20820,10 +20896,14 @@
           <t>JPG, JPEG ou PNG.</t>
         </is>
       </c>
-      <c r="I469" s="2" t="n"/>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>CTA: obrigatório, botão claramente visível (sem limite de carateres definido).</t>
+        </is>
+      </c>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>Card interativo que aparece dentro do anúncio in-feed, para destacar mensagens importantes, ofertas exclusivas ou direcionar para o site/app. O popup do card aparece automaticamente ao fim de alguns segundos — o momento é calculado pela plataforma consoante o objetivo, indústria e comportamento da audiência, não é configurável. Forma do card: sempre retangular. Evitar design transparente no meio do card (a margem pode ser transparente). Incluir um botão CTA claramente visível. A cor deve destacar-se do vídeo. Evitar material com pixels baixos, mosaico ou serrilhado nos contornos. As safe zones variam consoante o formato do anúncio (vertical/quadrado/horizontal) e o comprimento da legenda (legendas mais longas reduzem a safe zone) — descarregar os ficheiros de safe zone correspondentes e usar a ferramenta de pré-visualização para confirmar. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda).</t>
+          <t>O popup do card aparece automaticamente ao fim de alguns segundos — o momento é calculado pela plataforma consoante o objetivo, indústria e comportamento da audiência, não é configurável. Forma do card: sempre retangular. Evitar design transparente no meio do card (a margem pode ser transparente). A cor deve destacar-se do vídeo. Evitar material com pixels baixos, mosaico ou serrilhado nos contornos. As safe zones variam consoante o formato do anúncio (vertical/quadrado/horizontal) e o comprimento da legenda (legendas mais longas reduzem a safe zone) — descarregar os ficheiros de safe zone correspondentes e usar a ferramenta de pré-visualização para confirmar. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda).</t>
         </is>
       </c>
       <c r="K469" s="3" t="inlineStr">
@@ -20872,7 +20952,7 @@
       </c>
       <c r="J470" s="2" t="inlineStr">
         <is>
-          <t>Convida a audiência a tocar ou deslizar no anúncio para desbloquear recompensas ou mais informação. Música de fundo do pop-up obrigatória: 6 segundos, idealmente consistente com a música do próprio vídeo do anúncio. Momento do pop-up: em Reach &amp; Frequency, a partir dos 3 segundos de anúncio e até 5 segundos antes do fim; em Auction Reach, a partir dos 6 segundos e até 5 segundos antes do fim. Posição, comprimento e ângulo do gesto configuram-se na ferramenta de pré-visualização (o ângulo tem de respeitar a zona marcada a vermelho). Vídeo do anúncio: mín. 8 segundos (recomendado 15s+). Gestos suportados: clique, deslize reto ou deslize curvo. O URL do cartão usa sempre o mesmo URL do botão CTA do anúncio (não se insere em separado).</t>
+          <t>Música de fundo do pop-up obrigatória: 6 segundos, idealmente consistente com a música do próprio vídeo do anúncio. Momento do pop-up: em Reach &amp; Frequency, a partir dos 3 segundos de anúncio e até 5 segundos antes do fim; em Auction Reach, a partir dos 6 segundos e até 5 segundos antes do fim. Posição, comprimento e ângulo do gesto configuram-se na ferramenta de pré-visualização (o ângulo tem de respeitar a zona marcada a vermelho). Vídeo do anúncio: mín. 8 segundos (recomendado 15s+). Gestos suportados: clique, deslize reto ou deslize curvo. O URL do cartão usa sempre o mesmo URL do botão CTA do anúncio (não se insere em separado).</t>
         </is>
       </c>
       <c r="K470" s="3" t="inlineStr">
@@ -20909,7 +20989,7 @@
       </c>
       <c r="J471" s="2" t="inlineStr">
         <is>
-          <t>Adiciona um código promocional exclusivo ao vídeo do anúncio. Elementos do sticker: título, código, botão de copiar e botão CTA. Cor do sticker: cinzento ou azul (sem personalização de cor). Os anúncios com Gift Code Sticker têm de incluir URL (pode ser o mesmo da página de destino do anúncio). Garantir que o sticker fica dentro da safe zone.</t>
+          <t>Elementos do sticker: título, código, botão de copiar e botão CTA. Cor do sticker: cinzento ou azul (sem personalização de cor). Os anúncios com Gift Code Sticker têm de incluir URL (pode ser o mesmo da página de destino do anúncio). Garantir que o sticker fica dentro da safe zone.</t>
         </is>
       </c>
       <c r="K471" s="3" t="inlineStr">
@@ -20941,12 +21021,12 @@
       <c r="H472" s="2" t="n"/>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>Título: até 54 carateres EN ou até 27 carateres CN/JP/KR. Não suporta hashtag (#).</t>
+          <t>Título: até 54 carateres EN ou até 27 carateres CN/JP/KR. Não suporta hashtag (#). Sugestões: "termina em" / "começa em" (o texto não é traduzido automaticamente).</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr">
         <is>
-          <t>Adiciona um temporizador de contagem decrescente ao vídeo do anúncio. Tamanho, ângulo e posição ajustam-se no TikTok Ads Manager. Cor do sticker: laranja, preto, azul ou rosa (sem personalização de cor). O título mostra-se na língua em que foi escrito (não é traduzido automaticamente) — sugerir frases como "termina em"/"começa em". O CTA é o mesmo escolhido no Ads Manager, traduzido automaticamente para a língua do utilizador (suporta Dynamic CTA). Os anúncios com Countdown Sticker têm de incluir URL (pode ser o mesmo da página de destino). O tempo é traduzido e calculado automaticamente consoante o fuso horário do utilizador. Garantir que o sticker fica dentro da safe zone (azul).</t>
+          <t>Tamanho, ângulo e posição ajustam-se no TikTok Ads Manager. Cor do sticker: laranja, preto, azul ou rosa (sem personalização de cor). O CTA é o mesmo escolhido no Ads Manager, traduzido automaticamente para a língua do utilizador (suporta Dynamic CTA). Os anúncios com Countdown Sticker têm de incluir URL (pode ser o mesmo da página de destino). O tempo é traduzido e calculado automaticamente consoante o fuso horário do utilizador. Garantir que o sticker fica dentro da safe zone (azul).</t>
         </is>
       </c>
       <c r="K472" s="3" t="inlineStr">
@@ -20983,7 +21063,7 @@
       </c>
       <c r="J473" s="2" t="inlineStr">
         <is>
-          <t>Adiciona um tópico de votação com duas opções ao vídeo do anúncio, para aumentar o engagement e recolher informação relevante. Elementos: título, texto da opção A e texto da opção B. Cor do texto: título sempre a branco (sem personalização); opções A/B disponíveis em vermelho, azul claro ou azul escuro. Garantir que o sticker fica dentro da safe zone.</t>
+          <t>Cor do texto: título sempre a branco (sem personalização); opções A/B disponíveis em vermelho, azul claro ou azul escuro. Garantir que o sticker fica dentro da safe zone.</t>
         </is>
       </c>
       <c r="K473" s="3" t="inlineStr">
@@ -21016,7 +21096,7 @@
       <c r="I474" s="2" t="n"/>
       <c r="J474" s="2" t="inlineStr">
         <is>
-          <t>Mostra elementos da app promovida (avaliação, nº de reviews, indústria) dentro do anúncio in-feed — é um elemento clicável que leva à loja de download da app. Cada elemento-chave (texto, logos) tem de ficar dentro da safe zone, sob pena de ser cortado/tapado. O tamanho da safe zone depende do formato do anúncio (vertical/quadrado/horizontal) e do comprimento da legenda — legendas mais longas reduzem a safe zone; descarregar os ficheiros de safe zone correspondentes ao formato usado. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda). Confirmar sempre na ferramenta de pré-visualização.</t>
+          <t>Cada elemento-chave (texto, logos) tem de ficar dentro da safe zone, sob pena de ser cortado/tapado. O tamanho da safe zone depende do formato do anúncio (vertical/quadrado/horizontal) e do comprimento da legenda — legendas mais longas reduzem a safe zone; descarregar os ficheiros de safe zone correspondentes ao formato usado. Existe versão Standard LTR (esquerda para a direita, todas as regiões exceto árabe) e versão árabe RTL (direita para a esquerda). Confirmar sempre na ferramenta de pré-visualização.</t>
         </is>
       </c>
       <c r="K474" s="3" t="inlineStr">
@@ -21065,7 +21145,7 @@
       </c>
       <c r="J475" s="2" t="inlineStr">
         <is>
-          <t>Função de seleção de história para anúncios in-feed: a audiência escolhe o próximo vídeo que quer ver. Criativos: vídeo principal (obrigatório), tópico de seleção em texto (obrigatório), sub-vídeo A (obrigatório) + imagem de capa (opcional — se não for fornecida, a plataforma usa a imagem do primeiro segundo do sub-vídeo, mas fornecer uma melhora a experiência), sub-vídeo B (obrigatório) + imagem de capa (opcional, mesma regra). Deixar o texto afastado das margens e evitar cobrir elementos-chave com o botão Play.</t>
+          <t>Criativos: vídeo principal (obrigatório), tópico de seleção em texto (obrigatório), sub-vídeo A (obrigatório) + imagem de capa (opcional — se não for fornecida, a plataforma usa a imagem do primeiro segundo do sub-vídeo, mas fornecer uma melhora a experiência), sub-vídeo B (obrigatório) + imagem de capa (opcional, mesma regra). Deixar o texto afastado das margens e evitar cobrir elementos-chave com o botão Play.</t>
         </is>
       </c>
       <c r="K475" s="3" t="inlineStr">
@@ -21113,14 +21193,10 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>Tagline: máx. 40 carateres.</t>
-        </is>
-      </c>
-      <c r="J476" s="2" t="inlineStr">
-        <is>
-          <t>Anúncio de áudio que toca durante os intervalos entre músicas/podcasts, com uma imagem de companhia visível no ecrã enquanto o áudio toca. Nome do anunciante + logo: 1:1, 640x640px, JPEG ou PNG. Inclui botão CTA. Alcança ouvintes em qualquer momento, com ou sem o ecrã visível.</t>
-        </is>
-      </c>
+          <t>Tagline: máx. 40 carateres. CTA: incluído (obrigatório).</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="n"/>
       <c r="K476" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/audio-ad-specs/</t>
@@ -21154,7 +21230,11 @@
           <t>9:16 (imagem/vídeo em loop) — logo a 1:1</t>
         </is>
       </c>
-      <c r="G477" s="2" t="n"/>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo em loop: 3 a 8 segundos.</t>
+        </is>
+      </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
           <t>Imagem: JPG ou PNG. Vídeo em loop: MP4 ou MOV.</t>
@@ -21162,12 +21242,12 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>Tagline: máx. 40 carateres.</t>
+          <t>Tagline: máx. 40 carateres. CTA: incluído (obrigatório).</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
         <is>
-          <t>Unidade visual de companhia do Audio Ad — imagem ou vídeo curto em loop (3 a 8 segundos), reproduzido sempre sem som (para o voiceover do áudio se ouvir). Nome do anunciante + logo: 1:1, 640x640px, JPEG ou PNG. Inclui botão CTA.</t>
+          <t>Vídeo reproduzido sempre sem som (para o voiceover do áudio se ouvir).</t>
         </is>
       </c>
       <c r="K477" s="3" t="inlineStr">
@@ -21193,10 +21273,14 @@
           <t>In-Stream Video Takeover</t>
         </is>
       </c>
-      <c r="E478" s="2" t="n"/>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>Banner de companhia/logo: 640x640px.</t>
+        </is>
+      </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>9:16 (retrato) ou 16:9 (paisagem)</t>
+          <t>9:16 (retrato) ou 16:9 (paisagem); 1:1 (banner/logo).</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
@@ -21206,19 +21290,15 @@
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>MOV ou MP4</t>
+          <t>MOV ou MP4. Banner de companhia/logo: JPEG ou PNG.</t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>Tagline: máx. 40 carateres.</t>
-        </is>
-      </c>
-      <c r="J478" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo entregue com o ecrã visível, enquanto o ouvinte navega na app (descobre música, lê letras, vê podcasts, etc.). Inclui banner de companhia/CTA card personalizável. Nome do anunciante + logo: 1:1, 640x640px, JPEG ou PNG.</t>
-        </is>
-      </c>
+          <t>Tagline: máx. 40 carateres. CTA: banner/card personalizável.</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="n"/>
       <c r="K478" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/in-stream-video-ad-specs/</t>
@@ -21265,7 +21345,7 @@
       </c>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>Disponível só em mobile. Entregue na vista 'Now Playing' enquanto o ecrã está visível — o ouvinte opta por ver (toca para reproduzir), ligando a marca à música que já escolheu ouvir. Conecta com audiência qualificada que 'opta por' ouvir mais.</t>
+          <t>Disponível só em mobile.</t>
         </is>
       </c>
       <c r="K479" s="3" t="inlineStr">
@@ -21316,11 +21396,7 @@
           <t>CTA (lista fixa): Apply now, Book now, Buy now, Buy tickets, Click now, Download, Find stores, Get coupon, Get info, Learn more, Listen now, More info, Pre-save, Save now, Share, Shop now, Sign up, Visit profile, Visit site, Watch now.</t>
         </is>
       </c>
-      <c r="J480" s="2" t="inlineStr">
-        <is>
-          <t>Criativos de display integrados na experiência Spotify, em momentos de grande envolvimento dentro do Browse e do Spotify Player — presença não intrusiva, de alto impacto.</t>
-        </is>
-      </c>
+      <c r="J480" s="2" t="n"/>
       <c r="K480" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-formats/display-ads/</t>
@@ -21365,11 +21441,7 @@
         </is>
       </c>
       <c r="I481" s="2" t="n"/>
-      <c r="J481" s="2" t="inlineStr">
-        <is>
-          <t>'Compra' a homepage da Spotify durante 24 horas — solução clicável de alto impacto, com suporte a rich media e elementos interativos para captar a atenção.</t>
-        </is>
-      </c>
+      <c r="J481" s="2" t="n"/>
       <c r="K481" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/homepage-takeover-ad-specs/</t>
@@ -21393,14 +21465,22 @@
           <t>Carousel Ads</t>
         </is>
       </c>
-      <c r="E482" s="2" t="n"/>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F482" s="2" t="n"/>
       <c r="G482" s="2" t="n"/>
       <c r="H482" s="2" t="n"/>
-      <c r="I482" s="2" t="n"/>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>CTA (exemplo): Shop now.</t>
+        </is>
+      </c>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>Carrossel de vários cartões deslizáveis (swipe), cada um com imagem de produto, preço, texto e botão CTA próprio (ex.: "Shop now"), mostrado sobre o anúncio de áudio/vídeo a decorrer. Permite mostrar vários produtos, ofertas ou partes de uma história numa só criatividade. Dimensões exatas de cada cartão não vêm especificadas no documento enviado pela Cláudia — confirmar na página oficial antes de produzir.</t>
+          <t>Dimensões exatas de cada cartão não especificadas pela Spotify — confirmar na página oficial antes de produzir.</t>
         </is>
       </c>
       <c r="K482" s="3" t="inlineStr">
@@ -21446,12 +21526,12 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="I483" s="2" t="n"/>
-      <c r="J483" s="2" t="inlineStr">
-        <is>
-          <t>Unidade de display mostrada diretamente no feed de navegação da app (Browse/Search), com logo do anunciante, imagem e botão CTA.</t>
-        </is>
-      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>CTA: incluído (obrigatório).</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="n"/>
       <c r="K483" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/display-ad-specs/</t>
@@ -21486,7 +21566,7 @@
       <c r="I484" s="2" t="n"/>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>Campanha de email marketing. Split imagem/texto de 60%/40%. Código HTML limpo, sem erros e sem quebras.</t>
+          <t>Split imagem/texto de 60%/40%. Código HTML limpo, sem erros e sem quebras.</t>
         </is>
       </c>
       <c r="K484" s="2" t="n"/>
@@ -21517,11 +21597,7 @@
           <t>Texto: até 159 carateres (incluindo tudo — texto, espaços e link).</t>
         </is>
       </c>
-      <c r="J485" s="2" t="inlineStr">
-        <is>
-          <t>Campanha de SMS marketing.</t>
-        </is>
-      </c>
+      <c r="J485" s="2" t="n"/>
       <c r="K485" s="2" t="n"/>
     </row>
     <row r="486">
@@ -21560,7 +21636,7 @@
       <c r="I486" s="2" t="n"/>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
         </is>
       </c>
       <c r="K486" s="2" t="n"/>
@@ -21601,7 +21677,7 @@
       <c r="I487" s="2" t="n"/>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
         </is>
       </c>
       <c r="K487" s="2" t="n"/>
@@ -21642,7 +21718,7 @@
       <c r="I488" s="2" t="n"/>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
         </is>
       </c>
       <c r="K488" s="2" t="n"/>
@@ -21683,7 +21759,7 @@
       <c r="I489" s="2" t="n"/>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>Formato TOP 4 (foco da Kwanko, para máxima cobertura na rede). Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
+          <t>Ficheiro HTML5: entregar sempre em .ZIP (com o ficheiro index e os respetivos assets). As hiperligações devem ser inseridas como variáveis genéricas (clickTags), preparadas para receber os links de tracking dinâmico da plataforma.</t>
         </is>
       </c>
       <c r="K489" s="2" t="n"/>
@@ -21981,11 +22057,7 @@
       <c r="G497" s="2" t="n"/>
       <c r="H497" s="2" t="n"/>
       <c r="I497" s="2" t="n"/>
-      <c r="J497" s="2" t="inlineStr">
-        <is>
-          <t>Formato nativo — display e artigos relacionados/publishers.</t>
-        </is>
-      </c>
+      <c r="J497" s="2" t="n"/>
       <c r="K497" s="3" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/15zwoMEHIslyJjJK4_esTSS9uDYSXLp_W/view</t>
@@ -22028,7 +22100,7 @@
       <c r="I498" s="2" t="n"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K498" s="3" t="inlineStr">
@@ -22073,7 +22145,7 @@
       <c r="I499" s="2" t="n"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K499" s="3" t="inlineStr">
@@ -22118,7 +22190,7 @@
       <c r="I500" s="2" t="n"/>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K500" s="3" t="inlineStr">
@@ -22163,7 +22235,7 @@
       <c r="I501" s="2" t="n"/>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K501" s="3" t="inlineStr">
@@ -22245,7 +22317,7 @@
       <c r="I503" s="2" t="n"/>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K503" s="3" t="inlineStr">
@@ -22290,7 +22362,7 @@
       <c r="I504" s="2" t="n"/>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K504" s="3" t="inlineStr">
@@ -22335,7 +22407,7 @@
       <c r="I505" s="2" t="n"/>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K505" s="3" t="inlineStr">
@@ -22380,7 +22452,7 @@
       <c r="I506" s="2" t="n"/>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K506" s="3" t="inlineStr">
@@ -22425,7 +22497,7 @@
       <c r="I507" s="2" t="n"/>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K507" s="3" t="inlineStr">
@@ -22470,7 +22542,7 @@
       <c r="I508" s="2" t="n"/>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K508" s="3" t="inlineStr">
@@ -22515,7 +22587,7 @@
       <c r="I509" s="2" t="n"/>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K509" s="3" t="inlineStr">
@@ -22560,7 +22632,7 @@
       <c r="I510" s="2" t="n"/>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: JPEG, GIF.</t>
+          <t>Formato da família Display da Azerion (não vinha nomeado no ratecard, só na página de specs). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K510" s="3" t="inlineStr">
@@ -22605,7 +22677,7 @@
       <c r="I511" s="2" t="n"/>
       <c r="J511" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K511" s="3" t="inlineStr">
@@ -22650,7 +22722,7 @@
       <c r="I512" s="2" t="n"/>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 4 imagens de produto.</t>
         </is>
       </c>
       <c r="K512" s="3" t="inlineStr">
@@ -22695,7 +22767,7 @@
       <c r="I513" s="2" t="n"/>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K513" s="3" t="inlineStr">
@@ -22740,7 +22812,7 @@
       <c r="I514" s="2" t="n"/>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K514" s="3" t="inlineStr">
@@ -22785,7 +22857,7 @@
       <c r="I515" s="2" t="n"/>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K515" s="3" t="inlineStr">
@@ -22830,7 +22902,7 @@
       <c r="I516" s="2" t="n"/>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K516" s="3" t="inlineStr">
@@ -22875,7 +22947,7 @@
       <c r="I517" s="2" t="n"/>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K517" s="3" t="inlineStr">
@@ -22920,7 +22992,7 @@
       <c r="I518" s="2" t="n"/>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K518" s="3" t="inlineStr">
@@ -22965,7 +23037,7 @@
       <c r="I519" s="2" t="n"/>
       <c r="J519" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K519" s="3" t="inlineStr">
@@ -23010,7 +23082,7 @@
       <c r="I520" s="2" t="n"/>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K520" s="3" t="inlineStr">
@@ -23055,7 +23127,7 @@
       <c r="I521" s="2" t="n"/>
       <c r="J521" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K521" s="3" t="inlineStr">
@@ -23100,7 +23172,7 @@
       <c r="I522" s="2" t="n"/>
       <c r="J522" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K522" s="3" t="inlineStr">
@@ -23145,7 +23217,7 @@
       <c r="I523" s="2" t="n"/>
       <c r="J523" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto em diferentes cores.</t>
         </is>
       </c>
       <c r="K523" s="3" t="inlineStr">
@@ -23190,7 +23262,7 @@
       <c r="I524" s="2" t="n"/>
       <c r="J524" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens 360°.</t>
         </is>
       </c>
       <c r="K524" s="3" t="inlineStr">
@@ -23235,7 +23307,7 @@
       <c r="I525" s="2" t="n"/>
       <c r="J525" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K525" s="3" t="inlineStr">
@@ -23280,7 +23352,7 @@
       <c r="I526" s="2" t="n"/>
       <c r="J526" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K526" s="3" t="inlineStr">
@@ -23325,7 +23397,7 @@
       <c r="I527" s="2" t="n"/>
       <c r="J527" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo — pode conter vídeo.</t>
         </is>
       </c>
       <c r="K527" s="3" t="inlineStr">
@@ -23370,7 +23442,7 @@
       <c r="I528" s="2" t="n"/>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K528" s="3" t="inlineStr">
@@ -23415,7 +23487,7 @@
       <c r="I529" s="2" t="n"/>
       <c r="J529" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
         </is>
       </c>
       <c r="K529" s="3" t="inlineStr">
@@ -23460,7 +23532,7 @@
       <c r="I530" s="2" t="n"/>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, 2 imagens no mínimo.</t>
         </is>
       </c>
       <c r="K530" s="3" t="inlineStr">
@@ -23505,7 +23577,7 @@
       <c r="I531" s="2" t="n"/>
       <c r="J531" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K531" s="3" t="inlineStr">
@@ -23550,7 +23622,7 @@
       <c r="I532" s="2" t="n"/>
       <c r="J532" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K532" s="3" t="inlineStr">
@@ -23595,7 +23667,7 @@
       <c r="I533" s="2" t="n"/>
       <c r="J533" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
         </is>
       </c>
       <c r="K533" s="3" t="inlineStr">
@@ -23640,7 +23712,7 @@
       <c r="I534" s="2" t="n"/>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas). Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, perguntas e respostas (máx. 3 perguntas).</t>
         </is>
       </c>
       <c r="K534" s="3" t="inlineStr">
@@ -23685,7 +23757,7 @@
       <c r="I535" s="2" t="n"/>
       <c r="J535" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, pode conter vídeo.</t>
         </is>
       </c>
       <c r="K535" s="3" t="inlineStr">
@@ -23730,7 +23802,7 @@
       <c r="I536" s="2" t="n"/>
       <c r="J536" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, playlist, música ou episódio do Spotify.</t>
         </is>
       </c>
       <c r="K536" s="3" t="inlineStr">
@@ -23775,7 +23847,7 @@
       <c r="I537" s="2" t="n"/>
       <c r="J537" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K537" s="3" t="inlineStr">
@@ -23820,7 +23892,7 @@
       <c r="I538" s="2" t="n"/>
       <c r="J538" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K538" s="3" t="inlineStr">
@@ -23865,7 +23937,7 @@
       <c r="I539" s="2" t="n"/>
       <c r="J539" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K539" s="3" t="inlineStr">
@@ -23910,7 +23982,7 @@
       <c r="I540" s="2" t="n"/>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
         </is>
       </c>
       <c r="K540" s="3" t="inlineStr">
@@ -23955,7 +24027,7 @@
       <c r="I541" s="2" t="n"/>
       <c r="J541" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, áudios em formato MP3.</t>
         </is>
       </c>
       <c r="K541" s="3" t="inlineStr">
@@ -24000,7 +24072,7 @@
       <c r="I542" s="2" t="n"/>
       <c r="J542" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K542" s="3" t="inlineStr">
@@ -24045,7 +24117,7 @@
       <c r="I543" s="2" t="n"/>
       <c r="J543" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K543" s="3" t="inlineStr">
@@ -24090,7 +24162,7 @@
       <c r="I544" s="2" t="n"/>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K544" s="3" t="inlineStr">
@@ -24135,7 +24207,7 @@
       <c r="I545" s="2" t="n"/>
       <c r="J545" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localização.</t>
         </is>
       </c>
       <c r="K545" s="3" t="inlineStr">
@@ -24180,7 +24252,7 @@
       <c r="I546" s="2" t="n"/>
       <c r="J546" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K546" s="3" t="inlineStr">
@@ -24225,7 +24297,7 @@
       <c r="I547" s="2" t="n"/>
       <c r="J547" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K547" s="3" t="inlineStr">
@@ -24270,7 +24342,7 @@
       <c r="I548" s="2" t="n"/>
       <c r="J548" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, localizações.</t>
         </is>
       </c>
       <c r="K548" s="3" t="inlineStr">
@@ -24315,7 +24387,7 @@
       <c r="I549" s="2" t="n"/>
       <c r="J549" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, data.</t>
         </is>
       </c>
       <c r="K549" s="3" t="inlineStr">
@@ -24360,7 +24432,7 @@
       <c r="I550" s="2" t="n"/>
       <c r="J550" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
         </is>
       </c>
       <c r="K550" s="3" t="inlineStr">
@@ -24405,7 +24477,7 @@
       <c r="I551" s="2" t="n"/>
       <c r="J551" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, nº de telefone.</t>
         </is>
       </c>
       <c r="K551" s="3" t="inlineStr">
@@ -24450,7 +24522,7 @@
       <c r="I552" s="2" t="n"/>
       <c r="J552" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K552" s="3" t="inlineStr">
@@ -24495,7 +24567,7 @@
       <c r="I553" s="2" t="n"/>
       <c r="J553" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms). Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, formulário (por omissão: Google Forms).</t>
         </is>
       </c>
       <c r="K553" s="3" t="inlineStr">
@@ -24540,7 +24612,7 @@
       <c r="I554" s="2" t="n"/>
       <c r="J554" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K554" s="3" t="inlineStr">
@@ -24585,7 +24657,7 @@
       <c r="I555" s="2" t="n"/>
       <c r="J555" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção e produtos associados.</t>
         </is>
       </c>
       <c r="K555" s="3" t="inlineStr">
@@ -24630,7 +24702,7 @@
       <c r="I556" s="2" t="n"/>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
         </is>
       </c>
       <c r="K556" s="3" t="inlineStr">
@@ -24675,7 +24747,7 @@
       <c r="I557" s="2" t="n"/>
       <c r="J557" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim, detalhes da promoção, produtos associados e localização.</t>
         </is>
       </c>
       <c r="K557" s="3" t="inlineStr">
@@ -24720,7 +24792,7 @@
       <c r="I558" s="2" t="n"/>
       <c r="J558" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas dos diferentes produtos da campanha, logótipo, copy, data de início/fim e localização.</t>
         </is>
       </c>
       <c r="K558" s="3" t="inlineStr">
@@ -24765,7 +24837,7 @@
       <c r="I559" s="2" t="n"/>
       <c r="J559" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K559" s="3" t="inlineStr">
@@ -24806,7 +24878,7 @@
       <c r="I560" s="2" t="n"/>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>Peso máximo não indicado na página de specs (só nos outros formatos da galeria). Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL). Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Jogo com 3 ecrãs obrigatórios: ecrã de jogar (com URL), ecrã do jogo em si (sem URL), e ecrã de fim de jogo (com URL).</t>
         </is>
       </c>
       <c r="K560" s="3" t="inlineStr">
@@ -24851,7 +24923,7 @@
       <c r="I561" s="2" t="n"/>
       <c r="J561" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K561" s="3" t="inlineStr">
@@ -24896,7 +24968,7 @@
       <c r="I562" s="2" t="n"/>
       <c r="J562" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K562" s="3" t="inlineStr">
@@ -24941,7 +25013,7 @@
       <c r="I563" s="2" t="n"/>
       <c r="J563" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K563" s="3" t="inlineStr">
@@ -24986,7 +25058,7 @@
       <c r="I564" s="2" t="n"/>
       <c r="J564" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K564" s="3" t="inlineStr">
@@ -25031,7 +25103,7 @@
       <c r="I565" s="2" t="n"/>
       <c r="J565" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K565" s="3" t="inlineStr">
@@ -25076,7 +25148,7 @@
       <c r="I566" s="2" t="n"/>
       <c r="J566" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto. Formato final do anúncio: HTML5.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy, imagens de produto.</t>
         </is>
       </c>
       <c r="K566" s="3" t="inlineStr">
@@ -25121,7 +25193,7 @@
       </c>
       <c r="J567" s="2" t="inlineStr">
         <is>
-          <t>Sem redirecionamento (redirect) disponível. Material necessário: ficheiro PSD em camadas, logótipo, texto e copy. Formato final do anúncio: JPEG, PNG (estático).</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, texto e copy.</t>
         </is>
       </c>
       <c r="K567" s="3" t="inlineStr">
@@ -25155,7 +25227,7 @@
       <c r="F568" s="2" t="n"/>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -25166,7 +25238,7 @@
       <c r="I568" s="2" t="n"/>
       <c r="J568" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K568" s="3" t="inlineStr">
@@ -25200,7 +25272,7 @@
       <c r="F569" s="2" t="n"/>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -25211,7 +25283,7 @@
       <c r="I569" s="2" t="n"/>
       <c r="J569" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K569" s="3" t="inlineStr">
@@ -25245,7 +25317,7 @@
       <c r="F570" s="2" t="n"/>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H570" s="2" t="inlineStr">
@@ -25256,7 +25328,7 @@
       <c r="I570" s="2" t="n"/>
       <c r="J570" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K570" s="3" t="inlineStr">
@@ -25290,7 +25362,7 @@
       <c r="F571" s="2" t="n"/>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H571" s="2" t="inlineStr">
@@ -25301,7 +25373,7 @@
       <c r="I571" s="2" t="n"/>
       <c r="J571" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy.</t>
         </is>
       </c>
       <c r="K571" s="3" t="inlineStr">
@@ -25335,7 +25407,7 @@
       <c r="F572" s="2" t="n"/>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H572" s="2" t="inlineStr">
@@ -25346,7 +25418,7 @@
       <c r="I572" s="2" t="n"/>
       <c r="J572" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy.</t>
         </is>
       </c>
       <c r="K572" s="3" t="inlineStr">
@@ -25380,7 +25452,7 @@
       <c r="F573" s="2" t="n"/>
       <c r="G573" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H573" s="2" t="inlineStr">
@@ -25391,7 +25463,7 @@
       <c r="I573" s="2" t="n"/>
       <c r="J573" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K573" s="3" t="inlineStr">
@@ -25425,7 +25497,7 @@
       <c r="F574" s="2" t="n"/>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H574" s="2" t="inlineStr">
@@ -25436,7 +25508,7 @@
       <c r="I574" s="2" t="n"/>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K574" s="3" t="inlineStr">
@@ -25470,7 +25542,7 @@
       <c r="F575" s="2" t="n"/>
       <c r="G575" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H575" s="2" t="inlineStr">
@@ -25481,7 +25553,7 @@
       <c r="I575" s="2" t="n"/>
       <c r="J575" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy.</t>
         </is>
       </c>
       <c r="K575" s="3" t="inlineStr">
@@ -25515,7 +25587,7 @@
       <c r="F576" s="2" t="n"/>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H576" s="2" t="inlineStr">
@@ -25526,7 +25598,7 @@
       <c r="I576" s="2" t="n"/>
       <c r="J576" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K576" s="3" t="inlineStr">
@@ -25560,7 +25632,7 @@
       <c r="F577" s="2" t="n"/>
       <c r="G577" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H577" s="2" t="inlineStr">
@@ -25571,7 +25643,7 @@
       <c r="I577" s="2" t="n"/>
       <c r="J577" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy.</t>
         </is>
       </c>
       <c r="K577" s="3" t="inlineStr">
@@ -25605,7 +25677,7 @@
       <c r="F578" s="2" t="n"/>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H578" s="2" t="inlineStr">
@@ -25616,7 +25688,7 @@
       <c r="I578" s="2" t="n"/>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo, lista de músicas.</t>
         </is>
       </c>
       <c r="K578" s="3" t="inlineStr">
@@ -25650,7 +25722,7 @@
       <c r="F579" s="2" t="n"/>
       <c r="G579" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H579" s="2" t="inlineStr">
@@ -25661,7 +25733,7 @@
       <c r="I579" s="2" t="n"/>
       <c r="J579" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K579" s="3" t="inlineStr">
@@ -25695,7 +25767,7 @@
       <c r="F580" s="2" t="n"/>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H580" s="2" t="inlineStr">
@@ -25706,7 +25778,7 @@
       <c r="I580" s="2" t="n"/>
       <c r="J580" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K580" s="3" t="inlineStr">
@@ -25740,7 +25812,7 @@
       <c r="F581" s="2" t="n"/>
       <c r="G581" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H581" s="2" t="inlineStr">
@@ -25751,7 +25823,7 @@
       <c r="I581" s="2" t="n"/>
       <c r="J581" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K581" s="3" t="inlineStr">
@@ -25785,7 +25857,7 @@
       <c r="F582" s="2" t="n"/>
       <c r="G582" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H582" s="2" t="inlineStr">
@@ -25796,7 +25868,7 @@
       <c r="I582" s="2" t="n"/>
       <c r="J582" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K582" s="3" t="inlineStr">
@@ -25830,7 +25902,7 @@
       <c r="F583" s="2" t="n"/>
       <c r="G583" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H583" s="2" t="inlineStr">
@@ -25841,7 +25913,7 @@
       <c r="I583" s="2" t="n"/>
       <c r="J583" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K583" s="3" t="inlineStr">
@@ -25875,7 +25947,7 @@
       <c r="F584" s="2" t="n"/>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H584" s="2" t="inlineStr">
@@ -25886,7 +25958,7 @@
       <c r="I584" s="2" t="n"/>
       <c r="J584" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K584" s="3" t="inlineStr">
@@ -25920,7 +25992,7 @@
       <c r="F585" s="2" t="n"/>
       <c r="G585" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H585" s="2" t="inlineStr">
@@ -25931,7 +26003,7 @@
       <c r="I585" s="2" t="n"/>
       <c r="J585" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K585" s="3" t="inlineStr">
@@ -25965,7 +26037,7 @@
       <c r="F586" s="2" t="n"/>
       <c r="G586" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H586" s="2" t="inlineStr">
@@ -25976,7 +26048,7 @@
       <c r="I586" s="2" t="n"/>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de exibição (dwell time): máx. 30 seg. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo.</t>
         </is>
       </c>
       <c r="K586" s="3" t="inlineStr">
@@ -26010,7 +26082,7 @@
       <c r="F587" s="2" t="n"/>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 30 MB.</t>
+          <t>Recomendado: máx. 30 MB. Tempo de exibição (dwell time): máx. 30 seg.</t>
         </is>
       </c>
       <c r="H587" s="2" t="inlineStr">
@@ -26021,7 +26093,7 @@
       <c r="I587" s="2" t="n"/>
       <c r="J587" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável). Tempo de exibição (dwell time): máx. 30 seg. Formato de wallpaper de alto impacto, com ação especial totalmente à medida da marca — disponibilidade a confirmar com a equipa comercial da Azerion. Formato final do anúncio: JPEG, PNG; vídeo MP4, H.264.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo (se aplicável).</t>
         </is>
       </c>
       <c r="K587" s="3" t="inlineStr">
@@ -26127,7 +26199,11 @@
         </is>
       </c>
       <c r="F590" s="2" t="n"/>
-      <c r="G590" s="2" t="n"/>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H590" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26136,7 +26212,7 @@
       <c r="I590" s="2" t="n"/>
       <c r="J590" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com elementos gráficos estáticos e/ou copy, desenhado para captar a atenção do utilizador, reforçar a mensagem de marca e motivar ações que impulsionem a conversão. Disponível em diferentes opções consoante objetivos e orçamento. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K590" s="3" t="inlineStr">
@@ -26168,7 +26244,11 @@
         </is>
       </c>
       <c r="F591" s="2" t="n"/>
-      <c r="G591" s="2" t="n"/>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H591" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26177,7 +26257,7 @@
       <c r="I591" s="2" t="n"/>
       <c r="J591" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy, vídeo. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K591" s="3" t="inlineStr">
@@ -26209,7 +26289,11 @@
         </is>
       </c>
       <c r="F592" s="2" t="n"/>
-      <c r="G592" s="2" t="n"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H592" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26218,7 +26302,7 @@
       <c r="I592" s="2" t="n"/>
       <c r="J592" s="2" t="inlineStr">
         <is>
-          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K592" s="3" t="inlineStr">
@@ -26250,7 +26334,11 @@
         </is>
       </c>
       <c r="F593" s="2" t="n"/>
-      <c r="G593" s="2" t="n"/>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo em loop: 1 a 4 segundos. Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H593" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26259,7 +26347,7 @@
       <c r="I593" s="2" t="n"/>
       <c r="J593" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com vídeo de uma só cena (1 a 4 segundos) com movimento em loop contínuo. Permite incluir um botão de play que ativa o vídeo completo em ecrã inteiro, captando a atenção do utilizador e potenciando o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Opcional: botão de play que ativa o vídeo completo em ecrã inteiro. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K593" s="3" t="inlineStr">
@@ -26291,7 +26379,11 @@
         </is>
       </c>
       <c r="F594" s="2" t="n"/>
-      <c r="G594" s="2" t="n"/>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H594" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26300,7 +26392,7 @@
       <c r="I594" s="2" t="n"/>
       <c r="J594" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer interativo que, através de um slider, revela uma imagem. O logótipo e o CTA mantêm-se fixos por cima das imagens, assegurando a visibilidade da marca e potenciando a interação do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Formato com 2 imagens, reveladas através de um slider — o logótipo e o CTA mantêm-se fixos por cima das imagens. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K594" s="3" t="inlineStr">
@@ -26332,7 +26424,11 @@
         </is>
       </c>
       <c r="F595" s="2" t="n"/>
-      <c r="G595" s="2" t="n"/>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H595" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26341,7 +26437,7 @@
       <c r="I595" s="2" t="n"/>
       <c r="J595" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer em que o cursor se transforma num elemento gráfico ou num call to action sobre um fundo estático. Pode ainda incluir um botão de play que, ao clicar, reproduz um vídeo em modo CTP, captando a atenção do utilizador e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>O cursor transforma-se num elemento gráfico/call-to-action sobre o fundo estático — este elemento tem de ser fornecido à parte. Opcional: botão de play que reproduz um vídeo em modo CTP (click to play). Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K595" s="3" t="inlineStr">
@@ -26373,7 +26469,11 @@
         </is>
       </c>
       <c r="F596" s="2" t="n"/>
-      <c r="G596" s="2" t="n"/>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H596" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26382,7 +26482,7 @@
       <c r="I596" s="2" t="n"/>
       <c r="J596" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer animado, com imagens em forma de acordeão. O utilizador pode interagir com elas para as visualizar todas, aumentando a participação e o engagement com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Formato com várias imagens dispostas em acordeão — o utilizador interage para as revelar todas. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K596" s="3" t="inlineStr">
@@ -26414,7 +26514,11 @@
         </is>
       </c>
       <c r="F597" s="2" t="n"/>
-      <c r="G597" s="2" t="n"/>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H597" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26423,7 +26527,7 @@
       <c r="I597" s="2" t="n"/>
       <c r="J597" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer interativo, com um jogo de raspadinha com duas imagens a ecrã inteiro. Permite ao utilizador descobrir conteúdo ou prémios, captando atenção e potenciando a interação com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Jogo de raspadinha com 2 imagens a ecrã inteiro (a 2ª é revelada ao raspar). Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K597" s="3" t="inlineStr">
@@ -26455,7 +26559,11 @@
         </is>
       </c>
       <c r="F598" s="2" t="n"/>
-      <c r="G598" s="2" t="n"/>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H598" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26464,7 +26572,7 @@
       <c r="I598" s="2" t="n"/>
       <c r="J598" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com vídeo ou animação exclusiva que reflete a identidade da marca. Gera alto impacto visual e reforça o reconhecimento de marca, aumentando o engagement do utilizador. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K598" s="3" t="inlineStr">
@@ -26496,7 +26604,11 @@
         </is>
       </c>
       <c r="F599" s="2" t="n"/>
-      <c r="G599" s="2" t="n"/>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H599" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26505,7 +26617,7 @@
       <c r="I599" s="2" t="n"/>
       <c r="J599" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer em que o rato se transforma numa luz que ilumina a imagem de fundo. Fomenta a interação ativa do utilizador e destaca produtos ou mensagens-chave de forma apelativa. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>O cursor transforma-se numa luz que ilumina a imagem de fundo — este elemento de luz tem de ser fornecido/desenhado. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K599" s="3" t="inlineStr">
@@ -26537,7 +26649,11 @@
         </is>
       </c>
       <c r="F600" s="2" t="n"/>
-      <c r="G600" s="2" t="n"/>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H600" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26546,7 +26662,7 @@
       <c r="I600" s="2" t="n"/>
       <c r="J600" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer que permite explorar várias imagens deslizando-as horizontalmente. Aumenta a participação do utilizador e oferece múltiplas oportunidades de conversão dentro do mesmo anúncio. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Formato com várias imagens, exploradas deslizando horizontalmente (carrossel). Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K600" s="3" t="inlineStr">
@@ -26578,7 +26694,11 @@
         </is>
       </c>
       <c r="F601" s="2" t="n"/>
-      <c r="G601" s="2" t="n"/>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H601" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26587,7 +26707,7 @@
       <c r="I601" s="2" t="n"/>
       <c r="J601" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com temporizador que mostra o tempo restante para um evento ou oferta. Gera urgência e motiva o utilizador a interagir ou realizar uma ação imediata. Material necessário: ficheiro PSD em camadas, logótipo, tipografia, copy e data. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia, copy e data. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K601" s="3" t="inlineStr">
@@ -26619,7 +26739,11 @@
         </is>
       </c>
       <c r="F602" s="2" t="n"/>
-      <c r="G602" s="2" t="n"/>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H602" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26628,7 +26752,7 @@
       <c r="I602" s="2" t="n"/>
       <c r="J602" s="2" t="inlineStr">
         <is>
-          <t>Wallpaper de WeTransfer com imagem interativa que inclui pontos clicáveis (hotspots) para revelar informação, produtos ou links. Melhora a exploração do conteúdo e aumenta a interação direta com a marca. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF.</t>
+          <t>Imagem com pontos clicáveis (hotspots) — definir, para cada hotspot, a informação/produto/link que revela. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K602" s="3" t="inlineStr">
@@ -26660,7 +26784,11 @@
         </is>
       </c>
       <c r="F603" s="2" t="n"/>
-      <c r="G603" s="2" t="n"/>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H603" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26669,7 +26797,7 @@
       <c r="I603" s="2" t="n"/>
       <c r="J603" s="2" t="inlineStr">
         <is>
-          <t>24h de WeTransfer em exclusividade para a marca — campanha de um dia de duração, com inventário destinado a publicidade exclusiva para o anunciante, por país. Composto por 3 wallpapers; a campanha tem de conter uma destas opções: 2 criatividades Static + 1 criatividade Click to Play, ou 3 criatividades Static. As imagens iniciais de cada formato têm de ser bem diferentes entre si — se forem parecidas, a WeTransfer pode pedir uma criatividade adicional para otimizar melhor a campanha. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>24h de WeTransfer em exclusividade para a marca — campanha de um dia de duração, com inventário destinado a publicidade exclusiva para o anunciante, por país. Composto por 3 wallpapers; a campanha tem de conter uma destas opções: 2 criatividades Static + 1 criatividade Click to Play, ou 3 criatividades Static. As imagens iniciais de cada formato têm de ser bem diferentes entre si — se forem parecidas, a WeTransfer pode pedir uma criatividade adicional para otimizar melhor a campanha. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K603" s="3" t="inlineStr">
@@ -26701,7 +26829,11 @@
         </is>
       </c>
       <c r="F604" s="2" t="n"/>
-      <c r="G604" s="2" t="n"/>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>Tempo de permanência: 15-30 seg.</t>
+        </is>
+      </c>
       <c r="H604" s="2" t="inlineStr">
         <is>
           <t>PSD em camadas.</t>
@@ -26710,7 +26842,7 @@
       <c r="I604" s="2" t="n"/>
       <c r="J604" s="2" t="inlineStr">
         <is>
-          <t>Formato publicitário wallpaper da WeTransfer com ação personalizada e exclusiva, onde a marca pode dar largas à imaginação — disponibilidade a confirmar com a equipa comercial. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Tempo de permanência: 15-30 seg. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view Formato final do anúncio: JPEG, TIFF; vídeo MP4, MOV (H.264 ou ProRes).</t>
+          <t>Disponibilidade a confirmar com a equipa comercial. Material necessário: ficheiro PSD em camadas, logótipo, vídeo (se houver) e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K604" s="3" t="inlineStr">
@@ -26742,12 +26874,16 @@
         </is>
       </c>
       <c r="F605" s="2" t="n"/>
-      <c r="G605" s="2" t="n"/>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>Duração do vídeo: até 30".</t>
+        </is>
+      </c>
       <c r="H605" s="2" t="n"/>
       <c r="I605" s="2" t="n"/>
       <c r="J605" s="2" t="inlineStr">
         <is>
-          <t>Duração do vídeo: até 30". Compra mínima: 300 000 impressões.</t>
+          <t>Compra mínima: 300 000 impressões.</t>
         </is>
       </c>
       <c r="K605" s="3" t="inlineStr">
@@ -27052,7 +27188,7 @@
       <c r="F613" s="2" t="n"/>
       <c r="G613" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: máx. 1,4 MB.</t>
+          <t>Recomendado: máx. 1,4 MB. Duração do vídeo: 30seg (recomendado: &lt;20seg).</t>
         </is>
       </c>
       <c r="H613" s="2" t="inlineStr">
@@ -27063,7 +27199,7 @@
       <c r="I613" s="2" t="n"/>
       <c r="J613" s="2" t="inlineStr">
         <is>
-          <t>Redirect: sim. Duração do vídeo: 30seg (recomendado: &lt;20seg). Ficha técnica: https://drive.google.com/file/d/1zJfF-_mATmPi8gTtEzQBYZxHhdnrKRUm/view</t>
+          <t>Redirect: sim. Ficha técnica: https://drive.google.com/file/d/1zJfF-_mATmPi8gTtEzQBYZxHhdnrKRUm/view</t>
         </is>
       </c>
       <c r="K613" s="3" t="inlineStr">
@@ -27095,18 +27231,18 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="G614" s="2" t="n"/>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>Duração: até 30".</t>
+        </is>
+      </c>
       <c r="H614" s="2" t="inlineStr">
         <is>
           <t>MP4, 720p, 16:9.</t>
         </is>
       </c>
       <c r="I614" s="2" t="n"/>
-      <c r="J614" s="2" t="inlineStr">
-        <is>
-          <t>Duração: até 30".</t>
-        </is>
-      </c>
+      <c r="J614" s="2" t="n"/>
       <c r="K614" s="3" t="inlineStr">
         <is>
           <t>https://hubspot.azerion.com/en/formats/video</t>
@@ -27136,18 +27272,18 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="G615" s="2" t="n"/>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>Duração: até 30".</t>
+        </is>
+      </c>
       <c r="H615" s="2" t="inlineStr">
         <is>
           <t>MP4, 720p, 16:9.</t>
         </is>
       </c>
       <c r="I615" s="2" t="n"/>
-      <c r="J615" s="2" t="inlineStr">
-        <is>
-          <t>Duração: até 30".</t>
-        </is>
-      </c>
+      <c r="J615" s="2" t="n"/>
       <c r="K615" s="3" t="inlineStr">
         <is>
           <t>https://hubspot.azerion.com/en/formats/video</t>
@@ -27177,7 +27313,11 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="G616" s="2" t="n"/>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>Duração: até 30".</t>
+        </is>
+      </c>
       <c r="H616" s="2" t="inlineStr">
         <is>
           <t>MP4, 720p, 16:9.</t>
@@ -27186,7 +27326,7 @@
       <c r="I616" s="2" t="n"/>
       <c r="J616" s="2" t="inlineStr">
         <is>
-          <t>Duração: até 30". Apenas via VAST.</t>
+          <t>Apenas via VAST.</t>
         </is>
       </c>
       <c r="K616" s="2" t="n"/>
@@ -27214,7 +27354,11 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="G617" s="2" t="n"/>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>Duração: até 30".</t>
+        </is>
+      </c>
       <c r="H617" s="2" t="inlineStr">
         <is>
           <t>MP4, 720p, 16:9.</t>
@@ -27223,7 +27367,7 @@
       <c r="I617" s="2" t="n"/>
       <c r="J617" s="2" t="inlineStr">
         <is>
-          <t>Duração: até 30". Compra mínima: 100 000 impressões.</t>
+          <t>Compra mínima: 100 000 impressões.</t>
         </is>
       </c>
       <c r="K617" s="3" t="inlineStr">
@@ -27255,7 +27399,11 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="G618" s="2" t="n"/>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>Duração: até 30".</t>
+        </is>
+      </c>
       <c r="H618" s="2" t="inlineStr">
         <is>
           <t>MP4, 720p, 16:9.</t>
@@ -27264,7 +27412,7 @@
       <c r="I618" s="2" t="n"/>
       <c r="J618" s="2" t="inlineStr">
         <is>
-          <t>Duração: até 30". Conforme COPPA.</t>
+          <t>Conforme COPPA.</t>
         </is>
       </c>
       <c r="K618" s="3" t="inlineStr">
@@ -27302,7 +27450,7 @@
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB.</t>
+          <t>Máx. 25 MB. Duração máxima: 30 seg.</t>
         </is>
       </c>
       <c r="H619" s="2" t="inlineStr">
@@ -27313,7 +27461,7 @@
       <c r="I619" s="2" t="n"/>
       <c r="J619" s="2" t="inlineStr">
         <is>
-          <t>Áudio: só 2 canais. Frame rate: 30-60 FPS. Bitrate: 8000 kbps. Sem animação. Não saltável (skippable: não). Duração máxima: 30 seg. Tags aceites: VAST 2.0 ou 3.</t>
+          <t>Áudio: só 2 canais. Frame rate: 30-60 FPS. Bitrate: 8000 kbps. Sem animação. Não saltável (skippable: não). Tags aceites: VAST 2.0 ou 3.</t>
         </is>
       </c>
       <c r="K619" s="3" t="inlineStr">
@@ -27341,18 +27489,18 @@
       </c>
       <c r="E620" s="2" t="n"/>
       <c r="F620" s="2" t="n"/>
-      <c r="G620" s="2" t="n"/>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>Duração: até 30".</t>
+        </is>
+      </c>
       <c r="H620" s="2" t="inlineStr">
         <is>
           <t>MP3/WAV, 320 kbps.</t>
         </is>
       </c>
       <c r="I620" s="2" t="n"/>
-      <c r="J620" s="2" t="inlineStr">
-        <is>
-          <t>Duração: até 30".</t>
-        </is>
-      </c>
+      <c r="J620" s="2" t="n"/>
       <c r="K620" s="3" t="inlineStr">
         <is>
           <t>https://hubspot.azerion.com/en/formats/audio</t>
@@ -27378,18 +27526,18 @@
       </c>
       <c r="E621" s="2" t="n"/>
       <c r="F621" s="2" t="n"/>
-      <c r="G621" s="2" t="n"/>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>Duração recomendada: 15".</t>
+        </is>
+      </c>
       <c r="H621" s="2" t="inlineStr">
         <is>
           <t>MP3/WAV, 320 kbps.</t>
         </is>
       </c>
       <c r="I621" s="2" t="n"/>
-      <c r="J621" s="2" t="inlineStr">
-        <is>
-          <t>Duração recomendada: 15".</t>
-        </is>
-      </c>
+      <c r="J621" s="2" t="n"/>
       <c r="K621" s="3" t="inlineStr">
         <is>
           <t>https://hubspot.azerion.com/en/formats/audio</t>
@@ -27415,18 +27563,18 @@
       </c>
       <c r="E622" s="2" t="n"/>
       <c r="F622" s="2" t="n"/>
-      <c r="G622" s="2" t="n"/>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>Duração recomendada: 15".</t>
+        </is>
+      </c>
       <c r="H622" s="2" t="inlineStr">
         <is>
           <t>MP3/WAV, 320 kbps.</t>
         </is>
       </c>
       <c r="I622" s="2" t="n"/>
-      <c r="J622" s="2" t="inlineStr">
-        <is>
-          <t>Duração recomendada: 15".</t>
-        </is>
-      </c>
+      <c r="J622" s="2" t="n"/>
       <c r="K622" s="3" t="inlineStr">
         <is>
           <t>https://hubspot.azerion.com/en/formats/audio</t>
@@ -27450,22 +27598,30 @@
           <t>Audio Ads</t>
         </is>
       </c>
-      <c r="E623" s="2" t="n"/>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>Companion banner (opcional): 300x250px.</t>
+        </is>
+      </c>
       <c r="F623" s="2" t="n"/>
       <c r="G623" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 2 MB. Duração máxima: 30 seg. Companion banner (opcional): máx. 100 KB.</t>
         </is>
       </c>
       <c r="H623" s="2" t="inlineStr">
         <is>
-          <t>MP3, WAV.</t>
-        </is>
-      </c>
-      <c r="I623" s="2" t="n"/>
+          <t>MP3, WAV. Companion banner (opcional): JPEG.</t>
+        </is>
+      </c>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>Cunha personalizável com IA — 15 seg ≈ 33 palavras; 20 seg ≈ 45 palavras; 30 seg ≈ 65 palavras (nota: a página da Azerion mostra "15 seg" duas vezes para estas três linhas — reportado tal como consta, parece gralha da própria página).</t>
+        </is>
+      </c>
       <c r="J623" s="2" t="inlineStr">
         <is>
-          <t>Cunha de áudio reproduzida durante a audição de música em plataformas de streaming — impacta o utilizador num ambiente imersivo e pessoal, reforçando a mensagem de marca e potenciando a conversão. Duração máxima: 30 seg. Impression tracker: sim. Companion banner (opcional): 300x250px, JPEG, máx. 100 KB, com impression tracker e click tracker. Também personalizável com IA: cunha de 15 seg ≈ 33 palavras; cunha de 20 seg ≈ 45 palavras; cunha de 30 seg ≈ 65 palavras (nota: a página original da Azerion mostra "15 seg" duas vezes para estas três linhas — reportado tal como consta, parece gralha da própria página). Pode incluir: efeitos sonoros (MP3), música corporativa (MP3), companion banner (JPEG), voz feminina ou masculina, expressões, ênfase em palavras, sotaques, cunhas dinâmicas. Mais informação: confirmar com a equipa comercial da Azerion.</t>
+          <t>Pode incluir: efeitos sonoros, música corporativa, voz feminina ou masculina, diferentes sotaques e ênfases, cunhas dinâmicas. Confirmar mais informação com a equipa comercial da Azerion.</t>
         </is>
       </c>
       <c r="K623" s="3" t="inlineStr">
@@ -27498,7 +27654,7 @@
       <c r="I624" s="2" t="n"/>
       <c r="J624" s="2" t="inlineStr">
         <is>
-          <t>Patrocínios de marca personalizados e à medida, lidos diretamente pelos apresentadores de podcasts às suas audiências. Briefing simples; até 3 mensagens-chave de marca por leitura; ativação criativa conduzida pelo talento (apresentador); honorários e produção incluídos; atualização das leituras a cada 4 semanas; processo de aprovação transparente; entrega em 4 semanas úteis.</t>
+          <t>Até 3 mensagens-chave de marca por leitura. Ativação conduzida pelo talento (apresentador) do podcast — honorários e produção incluídos. Atualização das leituras a cada 4 semanas. Entrega em 4 semanas úteis.</t>
         </is>
       </c>
       <c r="K624" s="3" t="inlineStr">
@@ -27531,7 +27687,7 @@
       <c r="I625" s="2" t="n"/>
       <c r="J625" s="2" t="inlineStr">
         <is>
-          <t>Mais flexibilidade do que uma leitura patrocinada clássica, mais tempo com o ouvinte e SOV exclusivo na pausa do patrocinador. Pode incluir: integração do produto no conteúdo do podcast a partir do estúdio; convidar amigos/familiares/especialistas a participar na leitura; desafiar o público ou pedir-lhe ideias e gravações; gravar em locais pouco convencionais; incorporar sons representativos do produto; incluir atividades relacionadas com o produto durante a gravação.</t>
+          <t>Pode incluir: integração do produto a partir do estúdio; convidar amigos/familiares/especialistas; desafios ou pedidos de ideias ao público; gravação em locais pouco convencionais; sons representativos do produto; atividades relacionadas com o produto durante a gravação.</t>
         </is>
       </c>
       <c r="K625" s="3" t="inlineStr">
@@ -27564,7 +27720,7 @@
       <c r="I626" s="2" t="n"/>
       <c r="J626" s="2" t="inlineStr">
         <is>
-          <t>Associa a marca a um podcast, integrando-a de forma fluida no conteúdo editorial dos programas selecionados. Alinhamento editorial: abordagem colaborativa entre o cliente e o podcaster; tratamentos criativos, maquetes e exemplos de trabalhos anteriores disponíveis mediante pedido. Pode assumir a forma de entrevista, debate com um especialista, ou outra execução mais criativa para maior compromisso.</t>
+          <t>Tratamentos criativos, maquetes e exemplos de trabalhos anteriores disponíveis mediante pedido. Pode assumir a forma de entrevista, debate com especialista, ou outra execução criativa.</t>
         </is>
       </c>
       <c r="K626" s="3" t="inlineStr">
@@ -27592,12 +27748,16 @@
       </c>
       <c r="E627" s="2" t="n"/>
       <c r="F627" s="2" t="n"/>
-      <c r="G627" s="2" t="n"/>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>Episódio bónus: 30-35 minutos.</t>
+        </is>
+      </c>
       <c r="H627" s="2" t="n"/>
       <c r="I627" s="2" t="n"/>
       <c r="J627" s="2" t="inlineStr">
         <is>
-          <t>Controlo total sobre os podcasts selecionados: episódios exclusivos, sem publicidade e com a marca do cliente, publicados no mesmo RSS Feed do programa principal, com 100% de Share of Voice (SOV) — todos os restantes anúncios/espaços de patrocínio desativados nesse episódio. Episódio bónus de longa duração: 30-35 minutos.</t>
+          <t>Episódios exclusivos, sem publicidade, publicados no mesmo RSS Feed do programa principal, com 100% de Share of Voice (SOV) — todos os restantes anúncios/espaços de patrocínio desativados nesse episódio.</t>
         </is>
       </c>
       <c r="K627" s="3" t="inlineStr">
@@ -27630,7 +27790,7 @@
       <c r="I628" s="2" t="n"/>
       <c r="J628" s="2" t="inlineStr">
         <is>
-          <t>Estratégia em que os produtos/marcas são introduzidos de forma natural e orgânica no conteúdo de um podcast — desde a presença física do produto no ambiente do apresentador (em cima da mesa, no fundo do estúdio, etc.) até menções durante a gravação. Integração natural: o produto entra organicamente na narrativa do podcast, sem interromper a experiência do ouvinte, criando uma associação positiva e natural com o conteúdo.</t>
+          <t>Pode variar entre presença física do produto no ambiente do apresentador (mesa, fundo do estúdio) e menções durante a gravação.</t>
         </is>
       </c>
       <c r="K628" s="3" t="inlineStr">
@@ -27660,7 +27820,7 @@
       <c r="F629" s="2" t="n"/>
       <c r="G629" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 2 MB. Duração máxima: 30 seg.</t>
         </is>
       </c>
       <c r="H629" s="2" t="inlineStr">
@@ -27671,7 +27831,7 @@
       <c r="I629" s="2" t="n"/>
       <c r="J629" s="2" t="inlineStr">
         <is>
-          <t>Converte a leitura em audição, inserindo a mensagem publicitária no áudio gerado por tecnologia de texto-para-voz, disponível como plug-in em meios digitais (sujeito à disponibilidade do publisher) — o utilizador ouve o conteúdo do artigo enquanto a marca se integra de forma fluida e não intrusiva no início da reprodução. Duração máxima: 30 seg. Impression tracker: sim.</t>
+          <t>Reproduzido no início do áudio gerado por texto-para-voz do artigo — sujeito à disponibilidade do publisher.</t>
         </is>
       </c>
       <c r="K629" s="3" t="inlineStr">
@@ -27697,22 +27857,26 @@
           <t>Audio In-Game</t>
         </is>
       </c>
-      <c r="E630" s="2" t="n"/>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>Companion banner (opcional): logótipo 600x600px; criatividade adicional 320x50px ou 300x250px.</t>
+        </is>
+      </c>
       <c r="F630" s="2" t="n"/>
       <c r="G630" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 2 MB. Duração máxima: 30 seg.</t>
         </is>
       </c>
       <c r="H630" s="2" t="inlineStr">
         <is>
-          <t>MP3, WAV.</t>
+          <t>Companion banner: JPEG.</t>
         </is>
       </c>
       <c r="I630" s="2" t="n"/>
       <c r="J630" s="2" t="inlineStr">
         <is>
-          <t>As marcas inserem-se de forma natural na experiência de jogo, sem interromper a ação — formato não intrusivo que impacta o utilizador enquanto está totalmente imerso no seu momento de lazer digital. Duração máxima: 30 seg. Impression tracker: sim. Companion banner (opcional): logótipo em JPEG (600x600px) + criatividade adicional em JPEG (320x50px ou 300x250px). Sujeito à disponibilidade do publisher.</t>
+          <t>Companion banner sujeito à disponibilidade do publisher.</t>
         </is>
       </c>
       <c r="K630" s="3" t="inlineStr">
@@ -27742,7 +27906,7 @@
       <c r="F631" s="2" t="n"/>
       <c r="G631" s="2" t="inlineStr">
         <is>
-          <t>Máx. 2 MB.</t>
+          <t>Máx. 2 MB. Duração máxima: 30 seg.</t>
         </is>
       </c>
       <c r="H631" s="2" t="inlineStr">
@@ -27753,7 +27917,7 @@
       <c r="I631" s="2" t="n"/>
       <c r="J631" s="2" t="inlineStr">
         <is>
-          <t>Permite às marcas conectar com os utilizadores enquanto conduzem, num ambiente sem distrações visuais e com atenção elevada. Duas soluções: Pure Audio In-Car (veículos com Android Auto ou Apple CarPlay) e Connected Cars (utilizadores que ouvem rádio online ou podcasts no telemóvel ligado por Bluetooth). Duração máxima: 30 seg. Impression tracker: sim.</t>
+          <t>Duas soluções: Pure Audio In-Car (veículos com Android Auto ou Apple CarPlay) e Connected Cars (utilizadores que ouvem rádio online ou podcasts no telemóvel ligado por Bluetooth).</t>
         </is>
       </c>
       <c r="K631" s="3" t="inlineStr">
@@ -33494,7 +33658,7 @@
       <c r="E143" s="2" t="n"/>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10 MB.</t>
+          <t>Máx. 10 MB. Duração máxima: 10 seg.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -33504,7 +33668,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Sem som. Duração máxima: 10 seg.</t>
+          <t>Sem som.</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -1607,7 +1607,7 @@
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50 KB, 200 KB (800x600)</t>
+          <t>Geral: 50 KB. Formato maior: 200 KB.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       <c r="F227" s="2" t="n"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>200 KB. Animação: máx. 30 segundos.</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       <c r="I227" s="2" t="n"/>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK). Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK). Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>16:9 (alternativa a 300x250px)</t>
+          <t>16:9.</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>9:16 (alternativa a 300x600px)</t>
+          <t>9:16.</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
@@ -14610,10 +14610,14 @@
           <t>In-Article Video</t>
         </is>
       </c>
-      <c r="E325" s="2" t="n"/>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Horizontal: mín. 1280x720 ou 1280x960. Vertical: mín. 720x1280.</t>
+        </is>
+      </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+          <t>16:9 ou 4:3 (horizontal); 9:16 (vertical).</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
@@ -14626,10 +14630,14 @@
           <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
-      <c r="I325" s="2" t="n"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>CTA: "Learn More" (único elemento clicável, no fundo do anúncio).</t>
+        </is>
+      </c>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>Anúncio de vídeo autónomo entre parágrafos de conteúdo editorial (mobile, tablet e desktop). Reproduz automaticamente quando 50% do anúncio está visível; som desligado por defeito; botão "Learn More" no fundo do anúncio (único elemento clicável).</t>
+          <t>Reproduz automaticamente quando 50% do anúncio está visível; som desligado por defeito. Recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
         </is>
       </c>
       <c r="K325" s="2" t="n"/>
@@ -14651,10 +14659,14 @@
           <t>Radio Player Pre-Roll</t>
         </is>
       </c>
-      <c r="E326" s="2" t="n"/>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Horizontal: mín. 1280x720 ou 1280x960. Vertical: mín. 720x1280.</t>
+        </is>
+      </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+          <t>16:9 ou 4:3 (horizontal); 9:16 (vertical).</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
@@ -14670,7 +14682,7 @@
       <c r="I326" s="2" t="n"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer. Sem autoplay de áudio (som off por defeito).</t>
+          <t>Reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer. Sem autoplay de áudio (som off por defeito). Recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
         </is>
       </c>
       <c r="K326" s="2" t="n"/>
@@ -15099,7 +15111,11 @@
           <t>Criteo - Vídeo</t>
         </is>
       </c>
-      <c r="E336" s="2" t="n"/>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
+        </is>
+      </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
           <t>16:9, 9:16 ou 1:1</t>
@@ -15107,7 +15123,7 @@
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB. Duração máx. 30″.</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
@@ -15116,11 +15132,7 @@
         </is>
       </c>
       <c r="I336" s="2" t="n"/>
-      <c r="J336" s="2" t="inlineStr">
-        <is>
-          <t>Duração máx. 30″. Resolução até 720p (ou inferior, se o vídeo original for de qualidade inferior).</t>
-        </is>
-      </c>
+      <c r="J336" s="2" t="n"/>
       <c r="K336" s="2" t="n"/>
     </row>
     <row r="337">
@@ -15145,21 +15157,25 @@
           <t>1200x628px, 1200x1200px ou 800x1200px</t>
         </is>
       </c>
-      <c r="F337" s="2" t="n"/>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo (opcional): 1:1, 16:9 ou 9:16.</t>
+        </is>
+      </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB. Vídeo (opcional): máx. 25 MB, máx. 30″.</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>PNG ou JPG</t>
+          <t>PNG ou JPG. Vídeo (opcional): MP4.</t>
         </is>
       </c>
       <c r="I337" s="2" t="n"/>
       <c r="J337" s="2" t="inlineStr">
         <is>
-          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video). Pode incluir vídeo em vez de, ou além da, imagem: MP4, 1:1/16:9/9:16, máx. 25 MB, máx. 30″.</t>
+          <t>Engloba os formatos Adaptive, Showcase, Carousel, Cube, Slider, Scroll, Search, Story, Lead Form e Interactive Ads, e os formatos com vídeo elaborados pela equipa de criativo da Criteo a partir das mesmas imagens (Motion Video, Video with Skin, QR Video).</t>
         </is>
       </c>
       <c r="K337" s="2" t="n"/>
@@ -15193,7 +15209,7 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB</t>
+          <t>Imagem máx. 1 MB; logo da app máx. 50 KB; vídeo máx. 25 MB, máx. 30″.</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -15202,11 +15218,7 @@
         </is>
       </c>
       <c r="I338" s="2" t="n"/>
-      <c r="J338" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo opcional, máx. 30″.</t>
-        </is>
-      </c>
+      <c r="J338" s="2" t="n"/>
       <c r="K338" s="2" t="n"/>
     </row>
     <row r="339">
@@ -15694,7 +15706,7 @@
       <c r="F351" s="2" t="n"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>Máx. 200 MB</t>
+          <t>Máx. 200 MB. Duração: 5 a 30″.</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -15705,7 +15717,7 @@
       <c r="I351" s="2" t="n"/>
       <c r="J351" s="2" t="inlineStr">
         <is>
-          <t>Duração: 5 a 30″. Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
+          <t>Pode incluir áudio (vídeo arranca sem som; o utilizador pode ativar).</t>
         </is>
       </c>
       <c r="K351" s="2" t="n"/>
@@ -17120,7 +17132,7 @@
       <c r="I386" s="2" t="n"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPC. Recomendado um mínimo de 3 tamanhos por campanha (320x50, 320x480 e 300x600).</t>
+          <t>Compra: CPM ou CPC. Recomendado um mínimo de 3 tamanhos por campanha.</t>
         </is>
       </c>
       <c r="K386" s="2" t="n"/>
@@ -17185,7 +17197,7 @@
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>Recomendado: 320x480. Outros: 300x250 ou 300x600.</t>
+          <t>Recomendado: 320x480. Outros: 300x250 ou 300x600. RM Expandable Banner: 320x50 (recolhido) → 320x480 (expandido).</t>
         </is>
       </c>
       <c r="F388" s="2" t="n"/>
@@ -17202,7 +17214,7 @@
       <c r="I388" s="2" t="n"/>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPC. Inclui RM Interstitial (320x480) e RM Expandable Banner (320x50 recolhido → 320x480 expandido).</t>
+          <t>Compra: CPM ou CPC. Inclui RM Interstitial e RM Expandable Banner.</t>
         </is>
       </c>
       <c r="K388" s="2" t="n"/>
@@ -17236,7 +17248,7 @@
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 10 MB. Duração máx. 30″ (recomendado 15-30″).</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
@@ -17247,7 +17259,7 @@
       <c r="I389" s="2" t="n"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPCV. Duração máx. 30″ (recomendado 15-30″). Vídeos do YouTube não são aceites.</t>
+          <t>Compra: CPM ou CPCV. Vídeos do YouTube não são aceites.</t>
         </is>
       </c>
       <c r="K389" s="2" t="n"/>
@@ -17281,7 +17293,7 @@
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10 MB</t>
+          <t>Máx. 10 MB. Duração: 15 ou 30″, não passível de ser saltado.</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
@@ -17292,7 +17304,7 @@
       <c r="I390" s="2" t="n"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPCV. Duração: 15 ou 30″, não passível de ser saltado. Vídeos do YouTube não são aceites.</t>
+          <t>Compra: CPM ou CPCV. Vídeos do YouTube não são aceites.</t>
         </is>
       </c>
       <c r="K390" s="2" t="n"/>
@@ -17322,18 +17334,18 @@
       <c r="F391" s="2" t="n"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>Máx. 3 MB. Imagem de companhia: máx. 50 KB.</t>
+          <t>Máx. 3 MB. Imagem de companhia: máx. 50 KB. Duração: 15″, 30″ ou 60″.</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>VAST 2.0, MP3, WAV, WMA ou OGG; companion asset: JPG, JPEG, PNG ou GIF.</t>
+          <t>VAST 2.0, MP3, WAV, WMA ou OGG; companion asset: JPG, JPEG, PNG ou GIF. Qualidade mínima: 128 kbps / 44100 Hz.</t>
         </is>
       </c>
       <c r="I391" s="2" t="n"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPE. Duração: 15″, 30″ ou 60″. Qualidade mínima: 128 kbps / 44100 Hz.</t>
+          <t>Compra: CPE.</t>
         </is>
       </c>
       <c r="K391" s="2" t="n"/>
@@ -17412,7 +17424,7 @@
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>Máx. 5 MB</t>
+          <t>Máx. 5 MB. Duração: 15 ou 30″, não passível de ser saltado.</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -17423,7 +17435,7 @@
       <c r="I393" s="2" t="n"/>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM. Duração: 15 ou 30″, não passível de ser saltado. Vídeos do YouTube não são suportados; dispositivos CTV não suportam VPAID.</t>
+          <t>Compra: CPM. Vídeos do YouTube não são suportados; dispositivos CTV não suportam VPAID.</t>
         </is>
       </c>
       <c r="K393" s="2" t="n"/>
@@ -22100,7 +22112,7 @@
       <c r="I498" s="2" t="n"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K498" s="3" t="inlineStr">
@@ -22145,7 +22157,7 @@
       <c r="I499" s="2" t="n"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K499" s="3" t="inlineStr">
@@ -22190,7 +22202,7 @@
       <c r="I500" s="2" t="n"/>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K500" s="3" t="inlineStr">
@@ -22235,7 +22247,7 @@
       <c r="I501" s="2" t="n"/>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>Segmentação para qualificação dos clicks incluída. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K501" s="3" t="inlineStr">
@@ -22317,7 +22329,7 @@
       <c r="I503" s="2" t="n"/>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K503" s="3" t="inlineStr">
@@ -22362,7 +22374,7 @@
       <c r="I504" s="2" t="n"/>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K504" s="3" t="inlineStr">
@@ -22407,7 +22419,7 @@
       <c r="I505" s="2" t="n"/>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K505" s="3" t="inlineStr">
@@ -22452,7 +22464,7 @@
       <c r="I506" s="2" t="n"/>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K506" s="3" t="inlineStr">
@@ -22497,7 +22509,7 @@
       <c r="I507" s="2" t="n"/>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K507" s="3" t="inlineStr">
@@ -22542,7 +22554,7 @@
       <c r="I508" s="2" t="n"/>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>Inclui segmentações (socio-demo/geo/verticais); Azerion DMP/custom: sob consulta. Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
+          <t>Material necessário: ficheiro PSD em camadas, tipografia, logótipo e copy.</t>
         </is>
       </c>
       <c r="K508" s="3" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Imprensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$631</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Digital'!$A$1:$K$632</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OOH'!$A$1:$I$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TV'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rádio'!$A$1:$I$4</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K631"/>
+  <dimension ref="A1:K632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12795,11 +12795,7 @@
         </is>
       </c>
       <c r="I281" s="2" t="n"/>
-      <c r="J281" s="2" t="inlineStr">
-        <is>
-          <t>Pode incluir vídeo — contactar a Notícias Ilimitadas para mais informação.</t>
-        </is>
-      </c>
+      <c r="J281" s="2" t="n"/>
       <c r="K281" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/takeover/</t>
@@ -13560,11 +13556,7 @@
         </is>
       </c>
       <c r="I298" s="2" t="n"/>
-      <c r="J298" s="2" t="inlineStr">
-        <is>
-          <t>CPV contabilizado aos 20s em campanhas por visualizações.</t>
-        </is>
-      </c>
+      <c r="J298" s="2" t="n"/>
       <c r="K298" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/audio-ad/</t>
@@ -13609,11 +13601,7 @@
         </is>
       </c>
       <c r="I299" s="2" t="n"/>
-      <c r="J299" s="2" t="inlineStr">
-        <is>
-          <t>CPV contabilizado aos 20s em campanhas por visualizações.</t>
-        </is>
-      </c>
+      <c r="J299" s="2" t="n"/>
       <c r="K299" s="3" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/pre-roll/</t>
@@ -14446,11 +14434,7 @@
       <c r="G320" s="2" t="n"/>
       <c r="H320" s="2" t="n"/>
       <c r="I320" s="2" t="n"/>
-      <c r="J320" s="2" t="inlineStr">
-        <is>
-          <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio.</t>
-        </is>
-      </c>
+      <c r="J320" s="2" t="n"/>
       <c r="K320" s="2" t="n"/>
     </row>
     <row r="321">
@@ -14479,11 +14463,7 @@
       <c r="G321" s="2" t="n"/>
       <c r="H321" s="2" t="n"/>
       <c r="I321" s="2" t="n"/>
-      <c r="J321" s="2" t="inlineStr">
-        <is>
-          <t>Servido via tag de terceiros (Mobkoi).</t>
-        </is>
-      </c>
+      <c r="J321" s="2" t="n"/>
       <c r="K321" s="2" t="n"/>
     </row>
     <row r="322">
@@ -14682,7 +14662,7 @@
       <c r="I326" s="2" t="n"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>Reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer. Sem autoplay de áudio (som off por defeito). Recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+          <t>Sem autoplay de áudio (som off por defeito). Recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
         </is>
       </c>
       <c r="K326" s="2" t="n"/>
@@ -17132,7 +17112,7 @@
       <c r="I386" s="2" t="n"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPC. Recomendado um mínimo de 3 tamanhos por campanha.</t>
+          <t>Recomendado um mínimo de 3 tamanhos por campanha.</t>
         </is>
       </c>
       <c r="K386" s="2" t="n"/>
@@ -17173,7 +17153,7 @@
       <c r="I387" s="2" t="n"/>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM. Recomendado usar os 3 tamanhos por campanha.</t>
+          <t>Recomendado usar os 3 tamanhos por campanha.</t>
         </is>
       </c>
       <c r="K387" s="2" t="n"/>
@@ -17214,7 +17194,7 @@
       <c r="I388" s="2" t="n"/>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPC. Inclui RM Interstitial e RM Expandable Banner.</t>
+          <t>Inclui RM Interstitial e RM Expandable Banner.</t>
         </is>
       </c>
       <c r="K388" s="2" t="n"/>
@@ -17259,7 +17239,7 @@
       <c r="I389" s="2" t="n"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPCV. Vídeos do YouTube não são aceites.</t>
+          <t>Vídeos do YouTube não são aceites.</t>
         </is>
       </c>
       <c r="K389" s="2" t="n"/>
@@ -17304,7 +17284,7 @@
       <c r="I390" s="2" t="n"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM ou CPCV. Vídeos do YouTube não são aceites.</t>
+          <t>Vídeos do YouTube não são aceites.</t>
         </is>
       </c>
       <c r="K390" s="2" t="n"/>
@@ -17343,11 +17323,7 @@
         </is>
       </c>
       <c r="I391" s="2" t="n"/>
-      <c r="J391" s="2" t="inlineStr">
-        <is>
-          <t>Compra: CPE.</t>
-        </is>
-      </c>
+      <c r="J391" s="2" t="n"/>
       <c r="K391" s="2" t="n"/>
     </row>
     <row r="392">
@@ -17390,7 +17366,7 @@
       </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPC (mín. 150 cliques/dia). Máx. 10 criatividades por campanha.</t>
+          <t>Máx. 10 criatividades por campanha.</t>
         </is>
       </c>
       <c r="K392" s="2" t="n"/>
@@ -17435,7 +17411,7 @@
       <c r="I393" s="2" t="n"/>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>Compra: CPM. Vídeos do YouTube não são suportados; dispositivos CTV não suportam VPAID.</t>
+          <t>Vídeos do YouTube não são suportados; dispositivos CTV não suportam VPAID.</t>
         </is>
       </c>
       <c r="K393" s="2" t="n"/>
@@ -19573,10 +19549,14 @@
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>720x540 (ratio 1,3, mobile portrait). Safe zone: 648x540. Danger zone: 36x540 (cada lado).</t>
-        </is>
-      </c>
-      <c r="F440" s="2" t="n"/>
+          <t>720x540 (mobile portrait). Safe zone: 648x540. Danger zone: 36x540 (cada lado).</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>1,3:1 (mobile portrait).</t>
+        </is>
+      </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
           <t>Ideal: 50 KB. Máx.: 2 MB.</t>
@@ -19769,10 +19749,14 @@
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>300x250 (ratio 1:2)</t>
-        </is>
-      </c>
-      <c r="F444" s="2" t="n"/>
+          <t>300x250.</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>1:2.</t>
+        </is>
+      </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
           <t>Ideal: 100 KB. Máx.: 2 MB.</t>
@@ -19931,11 +19915,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J447" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J447" s="2" t="n"/>
       <c r="K447" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/brand-spotlight-design-specifications</t>
@@ -19976,11 +19956,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J448" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J448" s="2" t="n"/>
       <c r="K448" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/product-galore-design-specification</t>
@@ -20021,11 +19997,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J449" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J449" s="2" t="n"/>
       <c r="K449" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/pick-and-choose-design-specification</t>
@@ -20066,11 +20038,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J450" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J450" s="2" t="n"/>
       <c r="K450" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/drag-and-drop-design-specifications</t>
@@ -20111,11 +20079,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J451" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J451" s="2" t="n"/>
       <c r="K451" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/hotspots-design-specification</t>
@@ -20156,11 +20120,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J452" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J452" s="2" t="n"/>
       <c r="K452" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/comparison-slider-design-specification</t>
@@ -20197,11 +20157,7 @@
         </is>
       </c>
       <c r="I453" s="2" t="n"/>
-      <c r="J453" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J453" s="2" t="n"/>
       <c r="K453" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/puzzle-design-specification</t>
@@ -20242,11 +20198,7 @@
           <t>Máximo 2–4 palavras (10 a 20 carateres incl. espaços). Evitar pontuação e quebras de linha.</t>
         </is>
       </c>
-      <c r="J454" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J454" s="2" t="n"/>
       <c r="K454" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/tap-to-reveal-design-specification</t>
@@ -20422,11 +20374,7 @@
           <t>Pergunta/afirmação inicial; opções de resposta (recomendado 1-2 palavras cada); ecrã(s) de resultado (um ecrã partilhado ou dois ecrãs dedicados, um por resposta); texto de CTA para o(s) ecrã(s) final/finais.</t>
         </is>
       </c>
-      <c r="J458" s="2" t="inlineStr">
-        <is>
-          <t>Para campanhas CPE e CPM.</t>
-        </is>
-      </c>
+      <c r="J458" s="2" t="n"/>
       <c r="K458" s="3" t="inlineStr">
         <is>
           <t>https://support.ogury.com/ogury-one/creative-specifications/ogury-creative-studio/rich-media-and-engagement-studio/quiz-design-specification</t>
@@ -26629,7 +26577,7 @@
       <c r="I599" s="2" t="n"/>
       <c r="J599" s="2" t="inlineStr">
         <is>
-          <t>O cursor transforma-se numa luz que ilumina a imagem de fundo — este elemento de luz tem de ser fornecido/desenhado. Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
+          <t>Material necessário: ficheiro PSD em camadas, logótipo, tipografia e copy. Redirect: sim. Ficha técnica (PDF): https://drive.google.com/file/d/1TNvVF7bRqs-vXwVlTloNrOA_YWd6Hi2a/view</t>
         </is>
       </c>
       <c r="K599" s="3" t="inlineStr">
@@ -26893,11 +26841,7 @@
       </c>
       <c r="H605" s="2" t="n"/>
       <c r="I605" s="2" t="n"/>
-      <c r="J605" s="2" t="inlineStr">
-        <is>
-          <t>Compra mínima: 300 000 impressões.</t>
-        </is>
-      </c>
+      <c r="J605" s="2" t="n"/>
       <c r="K605" s="3" t="inlineStr">
         <is>
           <t>https://hubspot.azerion.com/en/formats/skin</t>
@@ -26930,11 +26874,7 @@
       <c r="G606" s="2" t="n"/>
       <c r="H606" s="2" t="n"/>
       <c r="I606" s="2" t="n"/>
-      <c r="J606" s="2" t="inlineStr">
-        <is>
-          <t>Compra mínima: 300 000 impressões.</t>
-        </is>
-      </c>
+      <c r="J606" s="2" t="n"/>
       <c r="K606" s="3" t="inlineStr">
         <is>
           <t>https://hubspot.azerion.com/en/formats/skin</t>
@@ -26967,11 +26907,7 @@
       <c r="G607" s="2" t="n"/>
       <c r="H607" s="2" t="n"/>
       <c r="I607" s="2" t="n"/>
-      <c r="J607" s="2" t="inlineStr">
-        <is>
-          <t>Compra mínima: 250 000 impressões. Specs: sob consulta.</t>
-        </is>
-      </c>
+      <c r="J607" s="2" t="n"/>
       <c r="K607" s="2" t="n"/>
     </row>
     <row r="608">
@@ -27000,11 +26936,7 @@
       <c r="G608" s="2" t="n"/>
       <c r="H608" s="2" t="n"/>
       <c r="I608" s="2" t="n"/>
-      <c r="J608" s="2" t="inlineStr">
-        <is>
-          <t>Compra mínima: 250 000 impressões. Specs: sob consulta.</t>
-        </is>
-      </c>
+      <c r="J608" s="2" t="n"/>
       <c r="K608" s="2" t="n"/>
     </row>
     <row r="609">
@@ -27938,8 +27870,53 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="n"/>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>Journey Ad</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO: altura mín 486px, largura mín 864px.</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
+        </is>
+      </c>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>Display: máx 1 MB (todas as fases). Vídeo: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem). Duração do vídeo — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>Display: imagens. Vídeo: MP4.</t>
+        </is>
+      </c>
+      <c r="I632" s="2" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+        </is>
+      </c>
+      <c r="J632" s="2" t="n"/>
+      <c r="K632" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K631"/>
+  <autoFilter ref="A1:K632"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15983,11 +15983,7 @@
           <t>Sender: 30-45 carateres. Subject: 40-50 carateres.</t>
         </is>
       </c>
-      <c r="J359" s="2" t="inlineStr">
-        <is>
-          <t>Awareness puro, com clicktracker.</t>
-        </is>
-      </c>
+      <c r="J359" s="2" t="n"/>
       <c r="K359" s="2" t="n"/>
     </row>
     <row r="360">
@@ -20543,7 +20539,7 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
         </is>
       </c>
       <c r="F462" s="2" t="n"/>
@@ -20584,7 +20580,7 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
         </is>
       </c>
       <c r="F463" s="2" t="n"/>
@@ -20625,7 +20621,7 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
         </is>
       </c>
       <c r="F464" s="2" t="n"/>
@@ -20666,7 +20662,7 @@
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
         </is>
       </c>
       <c r="F465" s="2" t="n"/>
@@ -20707,7 +20703,7 @@
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>Formatos próprios Ogury: Full Screen, Thumbnail, Header, Footer, In-article Reveal. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
         </is>
       </c>
       <c r="F466" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -20539,7 +20539,7 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250, 120x600, 728x90, 320x100, 300x100, 320x50, 300x50.</t>
         </is>
       </c>
       <c r="F462" s="2" t="n"/>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250, 120x600, 728x90, 320x100, 300x100, 320x50, 300x50.</t>
         </is>
       </c>
       <c r="F463" s="2" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250, 120x600, 728x90, 320x100, 300x100, 320x50, 300x50.</t>
         </is>
       </c>
       <c r="F464" s="2" t="n"/>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250, 120x600, 728x90, 320x100, 300x100, 320x50, 300x50.</t>
         </is>
       </c>
       <c r="F465" s="2" t="n"/>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: tamanhos a confirmar na página de formatos e tamanhos suportados.</t>
+          <t>Full Screen: 1388x1734px. Thumbnail: 720x540px. Header: 2640x600px. Footer: 1760x400px. In-article Reveal: 1388x1734px. Formatos IAB standard: 970x250, 300x600, 320x480, 160x600, 336x280, 300x250, 120x600, 728x90, 320x100, 300x100, 320x50, 300x50.</t>
         </is>
       </c>
       <c r="F466" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -19491,7 +19491,7 @@
       <c r="C439" s="2" t="n"/>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Image - Full Screen</t>
+          <t>Full Screen</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
@@ -19540,7 +19540,7 @@
       <c r="C440" s="2" t="n"/>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Image - Thumbnail</t>
+          <t>Thumbnail</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -19593,7 +19593,7 @@
       <c r="C441" s="2" t="n"/>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Image - Header</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
@@ -19642,7 +19642,7 @@
       <c r="C442" s="2" t="n"/>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Image - Footer</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -19691,7 +19691,7 @@
       <c r="C443" s="2" t="n"/>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Image - Reveal</t>
+          <t>Reveal</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
@@ -19740,7 +19740,7 @@
       <c r="C444" s="2" t="n"/>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Image - In-Article MPU</t>
+          <t>In-Article MPU</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
@@ -19789,7 +19789,7 @@
       <c r="C445" s="2" t="n"/>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Video Creatives - Horizontal Video</t>
+          <t>Horizontal Video</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -19842,7 +19842,7 @@
       <c r="C446" s="2" t="n"/>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Video Creatives - Vertical Video</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -19891,7 +19891,7 @@
       <c r="C447" s="2" t="n"/>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Brand Spotlight</t>
+          <t>Brand Spotlight</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       <c r="C448" s="2" t="n"/>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Product Galore</t>
+          <t>Product Galore</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
@@ -19973,7 +19973,7 @@
       <c r="C449" s="2" t="n"/>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Pick &amp; Choose</t>
+          <t>Pick &amp; Choose</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
@@ -20014,7 +20014,7 @@
       <c r="C450" s="2" t="n"/>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Drag &amp; Drop</t>
+          <t>Drag &amp; Drop</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
@@ -20055,7 +20055,7 @@
       <c r="C451" s="2" t="n"/>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Hotspots</t>
+          <t>Hotspots</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
@@ -20096,7 +20096,7 @@
       <c r="C452" s="2" t="n"/>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Comparison Slider</t>
+          <t>Comparison Slider</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
@@ -20137,7 +20137,7 @@
       <c r="C453" s="2" t="n"/>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Puzzle</t>
+          <t>Puzzle</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
@@ -20174,7 +20174,7 @@
       <c r="C454" s="2" t="n"/>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Tap to Reveal</t>
+          <t>Tap to Reveal</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -20215,7 +20215,7 @@
       <c r="C455" s="2" t="n"/>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Tap to Map</t>
+          <t>Tap to Map</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -20260,7 +20260,7 @@
       <c r="C456" s="2" t="n"/>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Site Scroller</t>
+          <t>Site Scroller</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -20301,7 +20301,7 @@
       <c r="C457" s="2" t="n"/>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - 360°</t>
+          <t>360°</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
@@ -20350,7 +20350,7 @@
       <c r="C458" s="2" t="n"/>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Quiz</t>
+          <t>Quiz</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -20391,7 +20391,7 @@
       <c r="C459" s="2" t="n"/>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Social Display</t>
+          <t>Social Display</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
@@ -20440,7 +20440,7 @@
       <c r="C460" s="2" t="n"/>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>Rich Media &amp; Engagement Studio - Social Carousel</t>
+          <t>Social Carousel</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -15051,7 +15051,7 @@
       <c r="C335" s="2" t="n"/>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Criteo - Standard (Imagem)</t>
+          <t>Standard (Imagem)</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -15088,7 +15088,7 @@
       <c r="C336" s="2" t="n"/>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Criteo - Vídeo</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -15129,7 +15129,7 @@
       <c r="C337" s="2" t="n"/>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Criteo - Rich Media / Responsivo</t>
+          <t>Rich Media / Responsivo</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -15174,7 +15174,7 @@
       <c r="C338" s="2" t="n"/>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Criteo - App Install</t>
+          <t>App Install</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -15215,7 +15215,7 @@
       <c r="C339" s="2" t="n"/>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Criteo - Hero SKU</t>
+          <t>Hero SKU</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -15252,7 +15252,7 @@
       <c r="C340" s="2" t="n"/>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Criteo - 3.60</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -15548,7 +15548,7 @@
       <c r="C348" s="2" t="n"/>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Native Ads (Imagem)</t>
+          <t>Native Ads (Imagem)</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -15593,7 +15593,7 @@
       <c r="C349" s="2" t="n"/>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Motion Ads (Vídeo)</t>
+          <t>Motion Ads (Vídeo)</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -15638,7 +15638,7 @@
       <c r="C350" s="2" t="n"/>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Imagem)</t>
+          <t>Display Hosted (Imagem)</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -15675,7 +15675,7 @@
       <c r="C351" s="2" t="n"/>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (Vídeo)</t>
+          <t>Display Hosted (Vídeo)</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -15716,7 +15716,7 @@
       <c r="C352" s="2" t="n"/>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display Hosted (HTML5)</t>
+          <t>Display Hosted (HTML5)</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -15757,7 +15757,7 @@
       <c r="C353" s="2" t="n"/>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Display (Tag de 3ºs)</t>
+          <t>Display (Tag de 3ºs)</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -15790,7 +15790,7 @@
       <c r="C354" s="2" t="n"/>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Carousel</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -15827,7 +15827,7 @@
       <c r="C355" s="2" t="n"/>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Social Importer (Facebook/Instagram)</t>
+          <t>Social Importer (Facebook/Instagram)</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -15860,7 +15860,7 @@
       <c r="C356" s="2" t="n"/>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Taboola - Vertical</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="E356" s="2" t="n"/>
@@ -20493,7 +20493,7 @@
       <c r="C461" s="2" t="n"/>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Slideshow</t>
+          <t>Slideshow</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -20534,7 +20534,7 @@
       <c r="C462" s="2" t="n"/>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Pop</t>
+          <t>Pop</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -20575,7 +20575,7 @@
       <c r="C463" s="2" t="n"/>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Glide</t>
+          <t>Glide</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -20616,7 +20616,7 @@
       <c r="C464" s="2" t="n"/>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Shift</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -20657,7 +20657,7 @@
       <c r="C465" s="2" t="n"/>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Rise</t>
+          <t>Rise</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -20698,7 +20698,7 @@
       <c r="C466" s="2" t="n"/>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>Display Creatives - Unfold</t>
+          <t>Unfold</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -28620,23 +28620,23 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3 tamanhos disponíveis (obrigatórios os três): 640x417px, 800x522px ou 1024x668px. 3 momentos distintos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 imagens diferentes, ou combinar com vídeo nos vários momentos).</t>
+          <t>3 tamanhos disponíveis (obrigatórios os três): 640x417px, 800x522px ou 1024x668px.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB. Tamanho até 1000kB/s (125KB/s). 3 momentos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 imagens diferentes, ou combinar com vídeo nos vários momentos).</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>JPG ou PNG, resolução entre 72 e 100 DPI</t>
+          <t>JPG ou PNG, resolução entre 72 e 100 DPI. Profundidade de cor: 24 bits/pixel.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tamanho até 1000kB/s (125KB/s). Profundidade de cor: 24 bits/pixel. Não é possível apresentar conteúdos que mostrem, de forma explícita e não contextualizada, partes do corpo habitualmente resguardadas; mencionem instituições financeiras monetárias e de pagamento, partidos/associações políticas ou sindicais, organizações religiosas; usem símbolos/linguagem que se possam confundir com o funcionamento do caixa automático; ou que, no primeiro momento publicitário, mostrem qualquer preço sem identificação clara de que é um preço do anunciante, produto ou serviço. Para todos os outros princípios aplica-se o código da publicidade.</t>
+          <t>Não é possível apresentar conteúdos que mostrem, de forma explícita e não contextualizada, partes do corpo habitualmente resguardadas; mencionem instituições financeiras monetárias e de pagamento, partidos/associações políticas ou sindicais, organizações religiosas; usem símbolos/linguagem que se possam confundir com o funcionamento do caixa automático; ou que, no primeiro momento publicitário, mostrem qualquer preço sem identificação clara de que é um preço do anunciante, produto ou serviço. Para todos os outros princípios aplica-se o código da publicidade.</t>
         </is>
       </c>
       <c r="I4" s="2" t="n"/>
@@ -28659,23 +28659,23 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3 tamanhos disponíveis (obrigatórios os três): 640x417px, 800x522px ou 1024x668px. 3 momentos distintos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 vídeos diferentes, ou combinar com imagens nos vários momentos; sugestão: terminar com a imagem estática do último frame).</t>
+          <t>3 tamanhos disponíveis (obrigatórios os três): 640x417px, 800x522px ou 1024x668px.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Máx. 1 MB</t>
+          <t>Máx. 1 MB. Tamanho até 1000kB/s (125KB/s). Bitrate médio 1 Mb/s, máximo 8 Mb/s. 3 momentos: 1º momento 10s, 2º momento 3s, 3º momento 10s (pode usar 1, 2 ou 3 vídeos diferentes, ou combinar com imagens nos vários momentos; sugestão: terminar com a imagem estática do último frame).</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MP4, resolução entre 72 e 100 DPI</t>
+          <t>MP4, resolução entre 72 e 100 DPI. Frame rate: 24 ou 30 frames/s. Profundidade de cor: 24 bits/pixel.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Bitrate médio 1 Mb/s, máximo 8 Mb/s. Tamanho até 1000kB/s (125KB/s). Frame rate: 24 ou 30 frames/s. Profundidade de cor: 24 bits/pixel. Mesmos princípios de conteúdo do formato "Multibanco - Imagem".</t>
+          <t>Sem canal áudio. Mesmos princípios de conteúdo do formato "Multibanco - Imagem".</t>
         </is>
       </c>
       <c r="I5" s="2" t="n"/>
@@ -28733,7 +28733,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1920x1080px. Pode ser utilizado em suporte LED 16x9, ecrã triplo (3 ecrãs) ou Tomi Spot TV.</t>
+          <t>1920x1080px.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -28743,17 +28743,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB</t>
+          <t>Máx. 100 MB. Duração: múltiplos de 10 segundos, máx. 1 minuto. Bitrate máx. 6 Mbps.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264. Framerate 30 frames/s.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Duração: múltiplos de 10 segundos, com um máximo de 1 minuto. Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. No suporte de 3 ecrãs existe uma separação real de 2,5cm entre ecrãs, que divide/corta a imagem — deve ser tido em conta para não deformar frases ou elementos relevantes (zonas de quebra). Este ficheiro pode também ser utilizado no suporte LED 16x9, ecrã triplo (3 ecrãs) ou Tomi Spot TV.</t>
+          <t>Pode também ser utilizado no suporte LED 16x9, ecrã triplo (3 ecrãs) ou Tomi Spot TV. No suporte de 3 ecrãs existe uma separação real de 2,5cm entre ecrãs, que divide/corta a imagem — deve ser tido em conta para não deformar frases ou elementos relevantes (zonas de quebra).</t>
         </is>
       </c>
       <c r="I7" s="2" t="n"/>
@@ -28786,17 +28786,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Máx. 100 MB</t>
+          <t>Máx. 100 MB. Duração: múltiplos de 10 segundos, máx. 1 minuto. Bitrate máx. 6 Mbps.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264. Framerate 30 frames/s.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Duração: múltiplos de 10 segundos, com um máximo de 1 minuto. Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Este ficheiro pode ser utilizado no suporte dos formatos digitais verticais: Mupi Digital ou Tomi OOH.</t>
+          <t>Este ficheiro pode ser utilizado no suporte dos formatos digitais verticais: Mupi Digital ou Tomi OOH.</t>
         </is>
       </c>
       <c r="I8" s="2" t="n"/>
@@ -28994,7 +28994,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1080x1920px (Full HD).</t>
+          <t>1080x1920px (Full HD). Margem de segurança: 30px.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -29002,7 +29002,11 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10″.</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Vídeo pronto: .MOV ou .MP4 (MP4 preferencial), RGB, 30fps ou 60fps. Materiais abertos para produção também aceites: Adobe Photoshop (1080x1920px, layers abertos, RGB, 72dpi, fontes em curvas) ou Adobe Illustrator/After Effects (1080x1920px, fontes em curvas, imagens rasterizadas no ficheiro).</t>
@@ -29010,7 +29014,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Duração: 10″. Em anúncios/vídeos com textos sobrepostos, enviar também as imagens/vídeos limpos, para a inclusão dos textos ser aplicada e editada à parte. Margem de segurança: 30px. Prazo de entrega: 72 horas antes do início da campanha. Enviar para digital@dreammedia.pt (via WeTransfer/Dropbox/Google Drive se superior a 15Mb).</t>
+          <t>Em anúncios/vídeos com textos sobrepostos, enviar também as imagens/vídeos limpos, para a inclusão dos textos ser aplicada e editada à parte. Prazo de entrega: 72 horas antes do início da campanha. Enviar para digital@dreammedia.pt (via WeTransfer/Dropbox/Google Drive se superior a 15Mb).</t>
         </is>
       </c>
       <c r="I14" s="2" t="n"/>
@@ -29216,15 +29220,19 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Após envio, a JCDecaux declina responsabilidade por falhas no vídeo apresentado. Alterações ao vídeo carecem de aprovação final do cliente; a JCDecaux não se responsabiliza por atraso na entrega (sem compensação de airing).</t>
         </is>
       </c>
       <c r="I20" s="2" t="n"/>
@@ -29255,7 +29263,11 @@
           <t>16:9 (ficheiro) / 9:16 (exibição)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes.</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Ficheiro nativo (compressão nativa), bitrate máx. 20.000.</t>
@@ -29263,7 +29275,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Duração do spot: 10 segundos, dentro de um loop de 60 segundos com outros anunciantes. Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
+          <t>Enviar o vídeo 2 dias antes do início da campanha, por e-mail para o contacto JCDecaux. Alterações carecem de aprovação final do cliente; a JCDecaux declina responsabilidade por falhas no vídeo após o envio, e não se responsabiliza por atraso na entrega.</t>
         </is>
       </c>
       <c r="I21" s="2" t="n"/>
@@ -29364,15 +29376,19 @@
           <t>2:3</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -29403,15 +29419,19 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I25" s="2" t="n"/>
@@ -29442,15 +29462,19 @@
           <t>1.91:1</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I26" s="2" t="n"/>
@@ -29481,15 +29505,19 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
@@ -29520,15 +29548,19 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I28" s="2" t="n"/>
@@ -29555,15 +29587,19 @@
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I29" s="2" t="n"/>
@@ -29590,15 +29626,19 @@
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I30" s="2" t="n"/>
@@ -29625,15 +29665,19 @@
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000.</t>
+          <t>Quicktime (.MOV) ou .MP4, codec H264, compressão nativa, bitrate entre 6.000 e 20.000. Framerate 25fps.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Framerate 25fps; duração 10 seg.; sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I31" s="2" t="n"/>
@@ -30049,15 +30093,19 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB. Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps.</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264. Framerate 30 frames/s.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máx. 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
+          <t>Existe uma separação real de 2,5cm (medida real) na junção entre os três ecrãs, que divide e corta a imagem total — deve ser tido em conta para evitar que frases ou elementos relevantes fiquem deformados (zonas de quebra).</t>
         </is>
       </c>
       <c r="I43" s="2" t="n"/>
@@ -30088,17 +30136,17 @@
           <t>4:3</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB. Duração: 10 segundos. Bitrate máximo 6 Mbps.</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Duração: 10 segundos. Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB. Compressão nativa.</t>
-        </is>
-      </c>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264. Framerate 30 frames/s. Compressão nativa.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
     </row>
     <row r="45">
@@ -30119,7 +30167,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1080x810px.</t>
+          <t>1080x810px. Espaço reservado para o logótipo TOMI: 125x125px (canto da moldura).</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -30130,12 +30178,12 @@
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>PNG. Profundidade de cor: 8 bits ou superior.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Profundidade de cor: 8 bits ou superior. Deve ter sempre um espaço vazio de conteúdo de 125x125px para o logótipo TOMI no canto da moldura. Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
+          <t>Por ser impossível tirar uma fotografia sem o efeito de espelho com uma câmara frontal, é sempre necessário o envio da moldura espelhada.</t>
         </is>
       </c>
       <c r="I45" s="2" t="n"/>
@@ -30166,17 +30214,17 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB. Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps.</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>MP4 (sem fundo), codec H264</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Duração: múltiplos de 5 segundos. Bitrate máximo 6 Mbps. Tamanho máximo: 100MB.</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
     </row>
     <row r="47">
@@ -30201,17 +30249,17 @@
         </is>
       </c>
       <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB. Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps.</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Duração: 10 segundos (obrigatório). Bitrate máximo 6 Mbps. Framerate 30 frames/s. Tamanho máximo: 100MB.</t>
-        </is>
-      </c>
+          <t>Vídeo: MP4/MOV; Imagem: qualquer formato; Web: HTML/URL — codec H264. Framerate 30 frames/s.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
     </row>
     <row r="48">
@@ -30347,7 +30395,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Máx. 10MB (vídeo produzido pelo cliente).</t>
+          <t>Máx. 10MB (vídeo produzido pelo cliente). Duração máxima: 10 segundos.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -30357,7 +30405,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Duração máxima: 10 segundos. Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
+          <t>Criatividade tem de estar em português. A emissão do material só se inicia após validação da criatividade pela Unimidia. Data de entrega: 15 dias antes do início da campanha se produzido pela Unimidia (sujeito a orçamento), ou 2 dias úteis antes se produzido pelo cliente. Ficheiros enviados por email para universidades@unimidia.pt.</t>
         </is>
       </c>
       <c r="I51" s="2" t="n"/>
@@ -30598,15 +30646,19 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 segundos.</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>MP4.</t>
+          <t>MP4. Frame rate: 30 frames por segundo.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Duração: 10 segundos. Frame rate: 30 frames por segundo. Rede de mupis digitais em hospitais e clínicas.</t>
+          <t>Rede de mupis digitais em hospitais e clínicas.</t>
         </is>
       </c>
       <c r="I58" s="2" t="n"/>
@@ -30637,7 +30689,11 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Duração do vídeo: 10 segundos.</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
@@ -30645,7 +30701,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+          <t>Aceite tanto criativo em vídeo como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
         </is>
       </c>
       <c r="I59" s="2" t="n"/>
@@ -30676,7 +30732,11 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Duração do vídeo: 10 segundos.</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Vídeo: MP4, codec H.264, frame rate constante até 30fps, bitrate até 3000 Kbps (recomendado 1500-2500 Kbps para vídeo com imagem real; cerca de 600 Kbps para animações ou imagens estáticas), encoder profile Baseline ou Main, encoder level entre 3.0 e 4.2 (recomendado 3.2). Estático: JPEG (preferencial) ou PNG.</t>
@@ -30684,7 +30744,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Duração do vídeo: 10 segundos. Aceite tanto criativo em vídeo (10 segundos) como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+          <t>Aceite tanto criativo em vídeo como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
         </is>
       </c>
       <c r="I60" s="2" t="n"/>
@@ -30999,17 +31059,17 @@
         </is>
       </c>
       <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Duração do spot: 10 segundos.</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>MOV/MP4, codec H264</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Duração do spot: 10 segundos.</t>
-        </is>
-      </c>
+      <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
     </row>
     <row r="70">
@@ -31034,7 +31094,11 @@
         </is>
       </c>
       <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Duração do spot: 10 segundos.</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>MOV/MP4</t>
@@ -31042,7 +31106,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Duração do spot: 10 segundos. Entrada de material: quarta-feira às 06h00. Exibição 7 dias por semana.</t>
+          <t>Entrada de material: quarta-feira às 06h00. Exibição 7 dias por semana.</t>
         </is>
       </c>
       <c r="I70" s="2" t="n"/>
@@ -31362,7 +31426,7 @@
       <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg. Bitrate recomendado: 10 Mbps.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -31372,7 +31436,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM; entrega da AF segundo indicações ISM.</t>
+          <t>Emissão só após validação ISM; entrega da AF segundo indicações ISM.</t>
         </is>
       </c>
       <c r="I80" s="2" t="n"/>
@@ -31401,7 +31465,7 @@
       <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg. Bitrate recomendado: 10 Mbps.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -31411,7 +31475,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Emissão só após validação ISM.</t>
+          <t>Emissão só após validação ISM.</t>
         </is>
       </c>
       <c r="I81" s="2" t="n"/>
@@ -31866,7 +31930,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Mesmo material/impressão das restantes. Tem uma variante de tamanho extra (180x100) face a Auchan/Continente.</t>
+          <t>O tamanho 180x100 é uma variante extra específica do Pingo Doce (face a Auchan/Continente).</t>
         </is>
       </c>
       <c r="I94" s="2" t="n"/>
@@ -32175,7 +32239,7 @@
       <c r="E103" s="2" t="n"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -32185,7 +32249,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Emissão só após validação ISM; entrega até 5 dias antes do início da campanha.</t>
+          <t>Emissão só após validação ISM; entrega até 5 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I103" s="2" t="n"/>
@@ -32214,7 +32278,7 @@
       <c r="E104" s="2" t="n"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -32224,7 +32288,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I104" s="2" t="n"/>
@@ -32253,7 +32317,7 @@
       <c r="E105" s="2" t="n"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB; vídeo &lt; 4000 kbps</t>
+          <t>Máx. 25 MB; vídeo &lt; 4000 kbps Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -32263,7 +32327,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Resolução/ecrã diferentes das restantes Live Markets (720x1280 vs. 1080x1920). Entrega: 15 dias antes do início da campanha.</t>
+          <t>Resolução diferente das restantes Live Markets. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I105" s="2" t="n"/>
@@ -32292,7 +32356,7 @@
       <c r="E106" s="2" t="n"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -32302,7 +32366,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Conteúdo deve ser animado (não estático). LCDs Samsung. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Conteúdo deve ser animado (não estático). LCDs Samsung. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I106" s="2" t="n"/>
@@ -32331,7 +32395,7 @@
       <c r="E107" s="2" t="n"/>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -32341,7 +32405,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Écran exterior/totem de grande formato em localização específica (Matosinhos). Entrega: 15 dias antes do início da campanha.</t>
+          <t>Écran exterior/totem de grande formato em localização específica (Matosinhos). Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I107" s="2" t="n"/>
@@ -32370,7 +32434,7 @@
       <c r="E108" s="2" t="n"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -32380,7 +32444,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I108" s="2" t="n"/>
@@ -32442,7 +32506,11 @@
         </is>
       </c>
       <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Duração: 10 seg.</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>WMV ou MP4</t>
@@ -32450,7 +32518,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Filme em português ou legendado/traduzido. Entrega 5 dias antes; emissão só após validação ISM.</t>
+          <t>Filme em português ou legendado/traduzido. Entrega 5 dias antes; emissão só após validação ISM.</t>
         </is>
       </c>
       <c r="I110" s="2" t="n"/>
@@ -32514,7 +32582,7 @@
       <c r="E112" s="2" t="n"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -32524,7 +32592,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I112" s="2" t="n"/>
@@ -32658,7 +32726,7 @@
       <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg. Bitrate recomendado: 10 Mbps.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -32668,7 +32736,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Entrega 5 dias antes; emissão só após validação ISM. Formato genérico, sem retalhista específico.</t>
+          <t>Entrega 5 dias antes; emissão só após validação ISM. Formato genérico, sem retalhista específico.</t>
         </is>
       </c>
       <c r="I116" s="2" t="n"/>
@@ -32763,7 +32831,7 @@
       <c r="E119" s="2" t="n"/>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -32773,7 +32841,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha. Nota: um dos documentos de origem indicava a nomenclatura de ficheiro "1060X3840", que não bate com a resolução declarada (1080x1920) — reportado tal como consta, sem correção.</t>
+          <t>Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha. Nota: um dos documentos de origem indicava a nomenclatura de ficheiro "1060X3840", que não bate com a resolução declarada (1080x1920) — reportado tal como consta, sem correção.</t>
         </is>
       </c>
       <c r="I119" s="2" t="n"/>
@@ -32802,7 +32870,7 @@
       <c r="E120" s="2" t="n"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg. Bitrate recomendado: 10 Mbps.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -32812,7 +32880,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-HALL-666X1920.mp4. Criatividade em português, sem áudio. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Nomenclatura: "Anunciante"-HALL-666X1920.mp4. Criatividade em português, sem áudio. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I120" s="2" t="n"/>
@@ -32841,7 +32909,7 @@
       <c r="E121" s="2" t="n"/>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB (produzido pelo cliente)</t>
+          <t>Máx. 25 MB (produzido pelo cliente) Duração: 8 a 10 seg (produzido pelo cliente).</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -32851,7 +32919,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
+          <t>Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
         </is>
       </c>
       <c r="I121" s="2" t="n"/>
@@ -32880,7 +32948,7 @@
       <c r="E122" s="2" t="n"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB (produzido pelo cliente)</t>
+          <t>Máx. 25 MB (produzido pelo cliente) Duração: 8 a 10 seg (produzido pelo cliente).</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -32890,7 +32958,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Duração 8 a 10 seg (produzido pelo cliente). Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
+          <t>Emissão só após validação da criatividade pela ISM. Produção ISM: entrega 13 dias antes. Produzido pelo cliente: entrega 5 dias antes. Criatividade em português.</t>
         </is>
       </c>
       <c r="I122" s="2" t="n"/>
@@ -32989,7 +33057,7 @@
       <c r="E125" s="2" t="n"/>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg. Bitrate recomendado: 10 Mbps.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -32999,7 +33067,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.GAIA-1248X2212.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Nomenclatura: "Anunciante"-MONTRA.GAIA-1248X2212.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I125" s="2" t="n"/>
@@ -33028,7 +33096,7 @@
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -33038,7 +33106,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Material: ecrã LED de 198m². Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Material: ecrã LED de 198m². Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I126" s="2" t="n"/>
@@ -33102,7 +33170,7 @@
       <c r="E128" s="2" t="n"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Máx. 25 MB</t>
+          <t>Máx. 25 MB Duração: 10 seg. Bitrate recomendado: 10 Mbps.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -33112,7 +33180,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Duração 10 seg. Bitrate recomendado 10 Mbps. Nomenclatura: "Anunciante"-MONTRA.LISBOA-1600X1800.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
+          <t>Nomenclatura: "Anunciante"-MONTRA.LISBOA-1600X1800.mp4. Sem áudio, criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I128" s="2" t="n"/>
@@ -33320,17 +33388,17 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Máx.: 3 MB.</t>
+          <t>Máx.: 3 MB. Duração recomendada: 10 segundos.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>MP4, WMV ou AVI</t>
+          <t>MP4, WMV ou AVI Taxa de frames: 30 FPS.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Duração recomendada: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Sem áudio.</t>
         </is>
       </c>
       <c r="I134" s="2" t="n"/>
@@ -33363,17 +33431,17 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Máx.: 3 MB.</t>
+          <t>Máx.: 3 MB. Duração recomendada: 10 segundos.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>MP4, WMV ou AVI</t>
+          <t>MP4, WMV ou AVI Taxa de frames: 30 FPS.</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Duração recomendada: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Sem áudio.</t>
         </is>
       </c>
       <c r="I135" s="2" t="n"/>
@@ -33406,17 +33474,17 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Máx.: 400 KB.</t>
+          <t>Máx.: 400 KB. Duração: 10 segundos.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>MP4 ou JPG</t>
+          <t>MP4 ou JPG Taxa de frames: 30 FPS.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Ecrã digital instalado no interior de elevadores de edifícios residenciais (Canal Residencial), rede com 868 ecrãs em 578 edifícios em Portugal. Duração: 10 segundos. Sem áudio. Taxa de frames: 30 FPS.</t>
+          <t>Ecrã digital instalado no interior de elevadores de edifícios residenciais (Canal Residencial), rede com 868 ecrãs em 578 edifícios em Portugal. Sem áudio.</t>
         </is>
       </c>
       <c r="I136" s="2" t="n"/>
@@ -33447,7 +33515,11 @@
           <t>9:16</t>
         </is>
       </c>
-      <c r="F137" s="2" t="n"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Duração do anúncio: 10 segundos, em loop a cada 1 minuto.</t>
+        </is>
+      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>MP4, orientação vertical.</t>
@@ -33455,7 +33527,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Duração do anúncio: 10 segundos, em loop a cada 1 minuto. Prazo de envio dos ficheiros: 7 dias antes do início da campanha. Formato Retail Media.</t>
+          <t>Prazo de envio dos ficheiros: 7 dias antes do início da campanha. Formato Retail Media.</t>
         </is>
       </c>
       <c r="I137" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -21434,11 +21434,7 @@
           <t>CTA (exemplo): Shop now.</t>
         </is>
       </c>
-      <c r="J482" s="2" t="inlineStr">
-        <is>
-          <t>Dimensões exatas de cada cartão não especificadas pela Spotify — confirmar na página oficial antes de produzir.</t>
-        </is>
-      </c>
+      <c r="J482" s="2" t="n"/>
       <c r="K482" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-formats/carousel-ads/</t>
@@ -22346,7 +22342,7 @@
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>970x250px (Desktop) no ratecard — nota: a página de specs técnicas da Azerion mostra 920x250px para este formato; confirmar com a Azerion qual a medida correta antes de produzir.</t>
+          <t>970x250px (Desktop).</t>
         </is>
       </c>
       <c r="F505" s="2" t="n"/>
@@ -27556,7 +27552,7 @@
       </c>
       <c r="I623" s="2" t="inlineStr">
         <is>
-          <t>Cunha personalizável com IA — 15 seg ≈ 33 palavras; 20 seg ≈ 45 palavras; 30 seg ≈ 65 palavras (nota: a página da Azerion mostra "15 seg" duas vezes para estas três linhas — reportado tal como consta, parece gralha da própria página).</t>
+          <t>Cunha personalizável com IA — 15 seg ≈ 33 palavras; 20 seg ≈ 45 palavras; 30 seg ≈ 65 palavras.</t>
         </is>
       </c>
       <c r="J623" s="2" t="inlineStr">
@@ -31288,7 +31284,7 @@
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Nome do ficheiro indica "140x255cm", mas os valores no PDF (em cm) não batem certo — possível troca de unidade (cm/mm) no documento de origem. Reportado literalmente, sem correção. Molde técnico, sem retalhista nem specs de produção.</t>
+          <t>Molde técnico, sem retalhista nem specs de produção.</t>
         </is>
       </c>
       <c r="I76" s="2" t="n"/>
@@ -31790,7 +31786,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha. Nota: o nome do ficheiro de origem referia "Supercor Restelo", mas o conteúdo do documento identifica claramente este suporte como El Corte Inglês Gaia.</t>
+          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I90" s="2" t="n"/>
@@ -32841,7 +32837,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha. Nota: um dos documentos de origem indicava a nomenclatura de ficheiro "1060X3840", que não bate com a resolução declarada (1080x1920) — reportado tal como consta, sem correção.</t>
+          <t>Material: ecrã LED; criatividade em português. Entrega: 15 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I119" s="2" t="n"/>
@@ -33558,7 +33554,7 @@
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Mupi de 2 faces com vidro temperado "securit" de 8mm; estrutura em aço galvanizado com tratamento anticorrosivo; quadro em alumínio com tratamento polyester; iluminado. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>Mupi de 2 faces com vidro temperado "securit" de 8mm; estrutura em aço galvanizado com tratamento anticorrosivo; quadro em alumínio com tratamento polyester; iluminado.</t>
         </is>
       </c>
       <c r="I138" s="2" t="n"/>
@@ -33589,7 +33585,7 @@
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Módulos fixos a 2 vigas de ferro I 120-IPN, distanciadas 2,60m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>Módulos fixos a 2 vigas de ferro I 120-IPN, distanciadas 2,60m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca.</t>
         </is>
       </c>
       <c r="I139" s="2" t="n"/>
@@ -33620,7 +33616,7 @@
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Módulos fixos a 4 vigas de ferro I 120-IPN, distanciadas 2,40m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca. Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>Módulos fixos a 4 vigas de ferro I 120-IPN, distanciadas 2,40m entre si, chumbadas ao solo; moldura de alumínio de 10cm, branca.</t>
         </is>
       </c>
       <c r="I140" s="2" t="n"/>
@@ -33651,7 +33647,7 @@
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Iluminação por 8 projetores LED de 100W (4 por face). Nota: a GirodMedias não indicou especificações de ficheiro (tipo, resolução, bleed) para este formato — confirmar diretamente com o fornecedor antes de produzir a arte final.</t>
+          <t>Iluminação por 8 projetores LED de 100W (4 por face).</t>
         </is>
       </c>
       <c r="I141" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -29384,7 +29384,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 4 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I25" s="2" t="n"/>
@@ -29470,7 +29470,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I26" s="2" t="n"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I28" s="2" t="n"/>
@@ -29595,7 +29595,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Vídeo em estilo "Subtle Motion" recomendado: movimento lento e gradual dos elementos criativos (slow motion sem cortes bruscos; fundos deslocados/ampliados lentamente em vez de intermitentes; texto a desvanecer gradualmente em vez de deslizar/pulsar; luzes a brilhar em vez de piscar); marca visível em pelo menos 80% da criatividade. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I29" s="2" t="n"/>
@@ -29634,7 +29634,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 12,5%. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I30" s="2" t="n"/>
@@ -29673,7 +29673,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Share of time: 16,7%. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
+          <t>Sem canal áudio. Envio do vídeo 2 dias úteis antes do início da campanha, por e-mail para o contacto JCDecaux. Vídeo em estilo "Subtle Motion" recomendado (ver formato "Premium LED 22m²" para guidelines completas). A JCDecaux declina responsabilidade por falhas no vídeo após o envio; não se responsabiliza por atraso na entrega (sem compensação de airing); alterações carecem de aprovação final do cliente.</t>
         </is>
       </c>
       <c r="I31" s="2" t="n"/>
@@ -30652,11 +30652,7 @@
           <t>MP4. Frame rate: 30 frames por segundo.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Rede de mupis digitais em hospitais e clínicas.</t>
-        </is>
-      </c>
+      <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
     </row>
     <row r="59">
@@ -30697,7 +30693,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Aceite tanto criativo em vídeo como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+          <t>Aceite tanto criativo em vídeo como criativo estático, consoante os materiais disponíveis do anunciante.</t>
         </is>
       </c>
       <c r="I59" s="2" t="n"/>
@@ -30740,7 +30736,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Aceite tanto criativo em vídeo como criativo estático, consoante os materiais disponíveis do anunciante. Rede de publicidade digital em farmácias.</t>
+          <t>Aceite tanto criativo em vídeo como criativo estático, consoante os materiais disponíveis do anunciante.</t>
         </is>
       </c>
       <c r="I60" s="2" t="n"/>
@@ -30839,11 +30835,7 @@
           <t>Conteúdo: 1920x1080px, MP4.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Estes ecrãs passam trailers de filmes; entre os trailers, passam spots de TV dos parceiros, incluindo a Tequilha.</t>
-        </is>
-      </c>
+      <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
     </row>
     <row r="64">
@@ -30948,11 +30940,7 @@
           <t>MP4, codec H264 (livraria x264), bitrate &lt; 3000</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
-        </is>
-      </c>
+      <c r="H66" s="2" t="n"/>
       <c r="I66" s="3" t="inlineStr">
         <is>
           <t>https://thankful-dinner-552.notion.site/Ledwall-Video-123e4d8f0b188253b2e481717ab1e89d</t>
@@ -30991,11 +30979,7 @@
           <t>JPG e/ou PNG, modo de cor RGB, resolução 72dpi</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Ecospots — rede de 28 lojas Continente. Objetivo: Awareness.</t>
-        </is>
-      </c>
+      <c r="H67" s="2" t="n"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
           <t>https://thankful-dinner-552.notion.site/Ledwall-179e4d8f0b18839bbee701966fbfe361</t>
@@ -31028,7 +31012,7 @@
       <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Publicidade em fachadas/empenas de grande dimensão — medida específica por local; consultar a Clearspot para o site em concreto.</t>
+          <t>Medida específica por local — consultar a Clearspot para o site em concreto.</t>
         </is>
       </c>
       <c r="I68" s="2" t="n"/>
@@ -31127,11 +31111,7 @@
       <c r="E71" s="2" t="n"/>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Rede de 50 faces instalada nas principais entradas das praias. Especificações técnicas (dimensão/peso/tipo de ficheiro) não indicadas no media kit — confirmar com a Clearspot.</t>
-        </is>
-      </c>
+      <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
     </row>
     <row r="72">
@@ -31160,7 +31140,7 @@
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Molde técnico (die-line) para a categoria Higiene — sem retalhista nem especificações de produção/impressão indicadas no documento.</t>
+          <t>Molde técnico (die-line) para a categoria Higiene, sem retalhista específico.</t>
         </is>
       </c>
       <c r="I72" s="2" t="n"/>
@@ -31191,7 +31171,7 @@
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+          <t>Molde técnico (die-line), sem retalhista específico.</t>
         </is>
       </c>
       <c r="I73" s="2" t="n"/>
@@ -31222,7 +31202,7 @@
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+          <t>Molde técnico (die-line), sem retalhista específico.</t>
         </is>
       </c>
       <c r="I74" s="2" t="n"/>
@@ -31253,7 +31233,7 @@
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Molde técnico (die-line) — sem retalhista nem especificações de material/impressão.</t>
+          <t>Molde técnico (die-line), sem retalhista específico.</t>
         </is>
       </c>
       <c r="I75" s="2" t="n"/>
@@ -31284,7 +31264,7 @@
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Molde técnico, sem retalhista nem specs de produção.</t>
+          <t>Molde técnico (die-line), sem retalhista específico.</t>
         </is>
       </c>
       <c r="I76" s="2" t="n"/>
@@ -31323,7 +31303,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0. Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Contratação mínima de 2 meses. Entrega 1,5 meses antes do início da campanha. Documento da In-Store Media España.</t>
+          <t>Suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0. Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Entrega 1,5 meses antes do início da campanha.</t>
         </is>
       </c>
       <c r="I77" s="2" t="n"/>
@@ -31716,7 +31696,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Não colocar informação entre 31,5 e 47,5 cm da base (zona de defesa variável por loja). Documento da In-Store Media España.</t>
+          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Não colocar informação entre 31,5 e 47,5 cm da base (zona de defesa variável por loja).</t>
         </is>
       </c>
       <c r="I88" s="2" t="n"/>
@@ -32798,7 +32778,7 @@
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Documento disponível é só de logística de instalação, não uma ficha técnica de produção completa — sem resolução, DPI, formato de ficheiro, peso máximo ou prazo de entrega indicados. Opções de corte do vinil: (1) criatividade única cortada em 2 partes; (2) duas criatividades separadas, uma por porta; (3) criatividade com friso central incluído. Confirmar specs de produção com a In-Store Media antes de fechar o pedido.</t>
+          <t>Opções de corte do vinil: (1) criatividade única cortada em 2 partes; (2) duas criatividades separadas, uma por porta; (3) criatividade com friso central incluído.</t>
         </is>
       </c>
       <c r="I118" s="2" t="n"/>
@@ -32989,7 +32969,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Material: white back paper 150 grs, corte simples; offset 4/0. Criatividade em português. Entrega: 10 dias antes do início da campanha. Atenção: o documento identifica o mercado como "In-Store Media España" — confirmar se este formato se aplica às lojas portuguesas (Gaia/Lisboa) ou se é exclusivo de Espanha antes de o usar num pedido.</t>
+          <t>Material: white back paper 150 grs, corte simples; offset 4/0. Criatividade em português. Entrega: 10 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I123" s="2" t="n"/>
@@ -33199,19 +33179,23 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Área de impressão: 21x5m (escala 1:10, 210x50cm). Área de conteúdo relevante: 20,60x4,70m.</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="n"/>
+          <t>Área de impressão: 21x5m (210x50cm à escala). Área de conteúdo relevante: 20,60x4,70m.</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>1:10 (escala de produção do ficheiro).</t>
+        </is>
+      </c>
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>PDF, JPG, TIF, CDR ou AI</t>
+          <t>PDF, JPG, TIF, CDR ou AI. Resolução recomendada: 300dpi. CMYK.</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+          <t>Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
         </is>
       </c>
       <c r="I129" s="2" t="n"/>
@@ -33234,19 +33218,23 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Área de impressão: 32,12x5,04m (escala 1:10, 321,2x50,4cm). Área de conteúdo relevante: 31,8x4,8m.</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="n"/>
+          <t>Área de impressão: 32,12x5,04m (321,2x50,4cm à escala). Área de conteúdo relevante: 31,8x4,8m.</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>1:10 (escala de produção do ficheiro).</t>
+        </is>
+      </c>
       <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>PDF, JPG, TIF, CDR ou AI</t>
+          <t>PDF, JPG, TIF, CDR ou AI. Resolução recomendada: 300dpi. CMYK.</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+          <t>Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
         </is>
       </c>
       <c r="I130" s="2" t="n"/>
@@ -33269,19 +33257,23 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Área de impressão: 8,35x3m (escala 1:10, 83,5x30cm). Área de conteúdo relevante: 8,15x2,80m.</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="n"/>
+          <t>Área de impressão: 8,35x3m (83,5x30cm à escala). Área de conteúdo relevante: 8,15x2,80m.</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>1:10 (escala de produção do ficheiro).</t>
+        </is>
+      </c>
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>PDF, JPG, TIF, CDR ou AI</t>
+          <t>PDF, JPG, TIF, CDR ou AI. Resolução recomendada: 300dpi. CMYK.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+          <t>Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
         </is>
       </c>
       <c r="I131" s="2" t="n"/>
@@ -33304,19 +33296,23 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Área de impressão: 10x5m (escala 1:10, 100x50cm). Área de conteúdo relevante: 9,80x4,80m.</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="n"/>
+          <t>Área de impressão: 10x5m (100x50cm à escala). Área de conteúdo relevante: 9,80x4,80m.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1:10 (escala de produção do ficheiro).</t>
+        </is>
+      </c>
       <c r="F132" s="2" t="n"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>PDF, JPG, TIF, CDR ou AI</t>
+          <t>PDF, JPG, TIF, CDR ou AI. Resolução recomendada: 300dpi. CMYK.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+          <t>Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
         </is>
       </c>
       <c r="I132" s="2" t="n"/>
@@ -33339,19 +33335,23 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Área de impressão: 4x3m (escala 1:10, 40x30cm). Área de conteúdo relevante: 3,80x2,80m.</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="n"/>
+          <t>Área de impressão: 4x3m (40x30cm à escala). Área de conteúdo relevante: 3,80x2,80m.</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>1:10 (escala de produção do ficheiro).</t>
+        </is>
+      </c>
       <c r="F133" s="2" t="n"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>PDF, JPG, TIF, CDR ou AI</t>
+          <t>PDF, JPG, TIF, CDR ou AI. Resolução recomendada: 300dpi. CMYK.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Imagem à escala 1:10. Resolução recomendada: 300dpi. Ficheiro em CMYK. Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
+          <t>Enviar fontes ou converter textos em curvas. Incluir um JPG para visualização. Enviar por email, pen ou CD.</t>
         </is>
       </c>
       <c r="I133" s="2" t="n"/>
@@ -33394,7 +33394,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Sem áudio.</t>
+          <t>Sem áudio.</t>
         </is>
       </c>
       <c r="I134" s="2" t="n"/>
@@ -33437,7 +33437,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Ecrã digital instalado no interior de elevadores de edifícios de escritórios (Canal Executivo). Sem áudio.</t>
+          <t>Sem áudio.</t>
         </is>
       </c>
       <c r="I135" s="2" t="n"/>
@@ -33480,7 +33480,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Ecrã digital instalado no interior de elevadores de edifícios residenciais (Canal Residencial), rede com 868 ecrãs em 578 edifícios em Portugal. Sem áudio.</t>
+          <t>Sem áudio.</t>
         </is>
       </c>
       <c r="I136" s="2" t="n"/>

--- a/data/CSBuilder_Base_Formatos.xlsx
+++ b/data/CSBuilder_Base_Formatos.xlsx
@@ -10895,11 +10895,7 @@
           <t>1:1</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>não especificado</t>
-        </is>
-      </c>
+      <c r="G240" s="2" t="n"/>
       <c r="H240" s="2" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
@@ -10940,11 +10936,7 @@
           <t>1:1 ou 1.91:1</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
-          <t>não especificado</t>
-        </is>
-      </c>
+      <c r="G241" s="2" t="n"/>
       <c r="H241" s="2" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
@@ -31298,12 +31290,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>PDF qualidade de imprensa (PDF 1.4, CMYK, 300 dpi, tipografia incrustada, transparências conservadas)</t>
+          <t>PDF qualidade de imprensa (PDF 1.4, CMYK, 300 dpi, tipografia incrustada, transparências conservadas). Material: suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Suporte metálico em meia-lua com iluminação LED interior; vinil Easy Dot; impressão digital 4/0. Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Entrega 1,5 meses antes do início da campanha.</t>
+          <t>Só pode exibir 1 produto por suporte; marcas com mínimo de 2 linhas de facing. Entrega 1,5 meses antes do início da campanha.</t>
         </is>
       </c>
       <c r="I77" s="2" t="n"/>
@@ -31326,19 +31318,19 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48 cm)</t>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48 cm). Zona de exclusão: 40-56cm da base (alturas de defesas de alarme variam por loja).</t>
         </is>
       </c>
       <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1. Material: cartão micro canelado, corte simples; impressão digital 4/0.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Criatividade em português. Não colocar informação importante entre 40 e 56 cm da base (alturas de defesas de alarme variam por loja). Entrega: 1 mês antes para validação, 2 semanas antes para Arte Final.</t>
+          <t>Criatividade em português. Entrega: 1 mês antes para validação, 2 semanas antes para Arte Final.</t>
         </is>
       </c>
       <c r="I78" s="2" t="n"/>
@@ -31368,12 +31360,12 @@
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1. Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Material: vinil monomérico com brilho, adesivo removível; impressão tintas low solvent 720 DPI + laminação brilho. Criatividade em português. Não colocar texto/imagem no centro onde abrem as portas.</t>
+          <t>Criatividade em português. Não colocar texto/imagem no centro onde abrem as portas.</t>
         </is>
       </c>
       <c r="I79" s="2" t="n"/>
@@ -31474,21 +31466,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>120x52x4 cms, 105x52x4 cms ou 90x52x4 cms (segmentos 4/52/4/52cm)</t>
+          <t>120x52x4 cms, 105x52x4 cms ou 90x52x4 cms (segmentos 4/52/4/52cm). Zona de exclusão: 40-56cm da base.</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
-        </is>
-      </c>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1. Material: cartão micro canelado, corte simples; impressão digital 4/0.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
     </row>
     <row r="83">
@@ -31509,19 +31497,19 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm). Zona de exclusão: 40-56cm da base (defesas variam por loja).</t>
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1. Material: cartão micro canelado, corte simples; impressão digital 4/0.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Recomenda-se logo da marca nas laterais. Não colocar informação entre 40 e 56 cm da base (defesas variam por loja).</t>
+          <t>Recomenda-se logo da marca nas laterais.</t>
         </is>
       </c>
       <c r="I83" s="2" t="n"/>
@@ -31544,19 +31532,19 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm). Zona de exclusão: 40-56cm da base.</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1. Material: cartão micro canelado, corte simples; impressão digital 4/0.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+          <t>Sugere-se logo nas laterais.</t>
         </is>
       </c>
       <c r="I84" s="2" t="n"/>
@@ -31579,21 +31567,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>140x48x14 cms</t>
+          <t>140x48x14 cms. Zona de exclusão: 40-56cm da base.</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base.</t>
-        </is>
-      </c>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1. Material: cartão micro canelado, corte simples; impressão digital 4/0.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
     </row>
     <row r="86">
@@ -31621,12 +31605,12 @@
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1. Material: white back paper 200 grs, corte simples; impressão offset 4/0, quadricromia.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0, quadricromia. Pode colocar logo/nome da marca na faixa lateral.</t>
+          <t>Pode colocar logo/nome da marca na faixa lateral.</t>
         </is>
       </c>
       <c r="I86" s="2" t="n"/>
@@ -31656,12 +31640,12 @@
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1. Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
+          <t>Entrega: 1 mês antes para validação, 2 semanas antes para AF.</t>
         </is>
       </c>
       <c r="I87" s="2" t="n"/>
@@ -31684,21 +31668,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>49x121,5 cms</t>
+          <t>49x121,5 cms. Zona de exclusão: 31,5-47,5cm da base (variável por loja).</t>
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia. Não colocar informação entre 31,5 e 47,5 cm da base (zona de defesa variável por loja).</t>
-        </is>
-      </c>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1. Material: white back paper 150 grs, corte simples; impressão offset 4/0, quadricromia.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
     </row>
     <row r="89">
@@ -31719,19 +31699,19 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm)</t>
+          <t>140x48x14 cms e 140x40x11 cms (segmentos 14/48/14/48cm). Zona de exclusão: 40-56cm da base.</t>
         </is>
       </c>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1</t>
+          <t>Adobe Illustrator (aberto, sem bleed); CMYK; resolução mín. 150 DPI à escala 1:1. Material: cartão micro canelado, corte simples; impressão digital 4/0.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Material: cartão micro canelado, corte simples; impressão digital 4/0. Não colocar informação entre 40 e 56 cm da base; sugere-se logo nas laterais.</t>
+          <t>Sugere-se logo nas laterais.</t>
         </is>
       </c>
       <c r="I89" s="2" t="n"/>
@@ -31761,12 +31741,12 @@
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1. Material: white back paper 200 grs, corte simples; impressão offset 4/0.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha.</t>
+          <t>Nas tiras laterais colocar nome, logo ou slogan. Entrega: 10 dias antes do início da campanha.</t>
         </is>
       </c>
       <c r="I90" s="2" t="n"/>
@@ -31796,12 +31776,12 @@
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1. Material: white back paper 200 grs, corte simples; impressão offset 4/0.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Material: white back paper 200 grs, corte simples; impressão offset 4/0. Entrega: 10 dias úteis antes do início da campanha.</t>
+          <t>Entrega: 10 dias úteis antes do início da campanha.</t>
         </is>
       </c>
       <c r="I91" s="2" t="n"/>
@@ -31831,12 +31811,12 @@
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Qualquer formato suportado pelo Adobe; CMYK; resolução mín. 300 DPI à escala 1:1</t>
+          <t>Qualqu